--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -226,7 +226,7 @@
     <t>tool</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>,,</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -226,7 +226,7 @@
     <t>tool</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
   </si>
   <si>
     <t>,,</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="375">
   <si>
     <t>ID</t>
   </si>
@@ -226,10 +226,13 @@
     <t>tool</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>,,</t>
+  </si>
+  <si>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -1796,7 +1799,7 @@
         <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1898,34 +1901,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -1939,19 +1942,19 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -1963,13 +1966,13 @@
         <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
@@ -1980,19 +1983,19 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2004,13 +2007,13 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L3" t="s">
         <v>57</v>
@@ -2021,19 +2024,19 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -2045,13 +2048,13 @@
         <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -2062,19 +2065,19 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -2086,13 +2089,13 @@
         <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -2103,19 +2106,19 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -2127,13 +2130,13 @@
         <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -2144,19 +2147,19 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -2168,13 +2171,13 @@
         <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
@@ -2185,19 +2188,19 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -2209,13 +2212,13 @@
         <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -2226,19 +2229,19 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -2250,13 +2253,13 @@
         <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -2277,34 +2280,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -2318,19 +2321,19 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -2342,13 +2345,13 @@
         <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
@@ -2359,19 +2362,19 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -2383,13 +2386,13 @@
         <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L3" t="s">
         <v>57</v>
@@ -2400,19 +2403,19 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -2424,13 +2427,13 @@
         <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -2441,19 +2444,19 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -2465,13 +2468,13 @@
         <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -2482,19 +2485,19 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -2506,13 +2509,13 @@
         <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -2523,19 +2526,19 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
@@ -2547,13 +2550,13 @@
         <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
@@ -2564,19 +2567,19 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -2588,13 +2591,13 @@
         <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -2605,19 +2608,19 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2629,13 +2632,13 @@
         <v>27</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -2646,19 +2649,19 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -2670,13 +2673,13 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L10" t="s">
         <v>57</v>
@@ -2687,19 +2690,19 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -2711,13 +2714,13 @@
         <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L11" t="s">
         <v>57</v>
@@ -2728,19 +2731,19 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -2752,13 +2755,13 @@
         <v>27</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L12" t="s">
         <v>57</v>
@@ -2769,19 +2772,19 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
         <v>20</v>
@@ -2793,13 +2796,13 @@
         <v>29</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
@@ -2810,19 +2813,19 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -2834,13 +2837,13 @@
         <v>27</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
@@ -2851,19 +2854,19 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -2875,13 +2878,13 @@
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L15" t="s">
         <v>57</v>
@@ -2892,19 +2895,19 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -2916,13 +2919,13 @@
         <v>27</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s">
         <v>57</v>
@@ -2933,19 +2936,19 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -2957,13 +2960,13 @@
         <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s">
         <v>57</v>
@@ -2974,19 +2977,19 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -2998,13 +3001,13 @@
         <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s">
         <v>57</v>
@@ -3015,19 +3018,19 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -3039,13 +3042,13 @@
         <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L19" t="s">
         <v>57</v>
@@ -3056,19 +3059,19 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -3080,13 +3083,13 @@
         <v>27</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
@@ -3097,19 +3100,19 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -3121,13 +3124,13 @@
         <v>27</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
@@ -3138,19 +3141,19 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -3162,13 +3165,13 @@
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s">
         <v>57</v>
@@ -3179,19 +3182,19 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -3203,13 +3206,13 @@
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s">
         <v>57</v>
@@ -3230,34 +3233,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3280,28 +3283,28 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
@@ -3321,28 +3324,28 @@
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L3" t="s">
         <v>57</v>
@@ -3362,28 +3365,28 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -3403,28 +3406,28 @@
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -3444,28 +3447,28 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -3485,28 +3488,28 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
@@ -3526,28 +3529,28 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -3567,28 +3570,28 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -3608,28 +3611,28 @@
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L10" t="s">
         <v>57</v>
@@ -3649,28 +3652,28 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L11" t="s">
         <v>57</v>
@@ -3690,28 +3693,28 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L12" t="s">
         <v>57</v>
@@ -3731,28 +3734,28 @@
         <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
@@ -3772,28 +3775,28 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
@@ -3813,28 +3816,28 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L15" t="s">
         <v>57</v>
@@ -3854,28 +3857,28 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L16" t="s">
         <v>57</v>
@@ -3895,28 +3898,28 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L17" t="s">
         <v>57</v>
@@ -3936,28 +3939,28 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L18" t="s">
         <v>57</v>
@@ -3977,28 +3980,28 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L19" t="s">
         <v>57</v>
@@ -4018,28 +4021,28 @@
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
@@ -4059,28 +4062,28 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I21" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
@@ -4100,28 +4103,28 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L22" t="s">
         <v>57</v>
@@ -4141,28 +4144,28 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J23" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L23" t="s">
         <v>57</v>
@@ -4182,28 +4185,28 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L24" t="s">
         <v>57</v>
@@ -4223,28 +4226,28 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L25" t="s">
         <v>57</v>
@@ -4264,28 +4267,28 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L26" t="s">
         <v>57</v>
@@ -4305,28 +4308,28 @@
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L27" t="s">
         <v>57</v>
@@ -4346,28 +4349,28 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L28" t="s">
         <v>57</v>
@@ -4387,28 +4390,28 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L29" t="s">
         <v>57</v>
@@ -4428,28 +4431,28 @@
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L30" t="s">
         <v>57</v>
@@ -4469,28 +4472,28 @@
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J31" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L31" t="s">
         <v>57</v>
@@ -4510,28 +4513,28 @@
         <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K32" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L32" t="s">
         <v>57</v>
@@ -4551,28 +4554,28 @@
         <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L33" t="s">
         <v>57</v>
@@ -4592,28 +4595,28 @@
         <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K34" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L34" t="s">
         <v>57</v>
@@ -4633,28 +4636,28 @@
         <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K35" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L35" t="s">
         <v>57</v>
@@ -4674,28 +4677,28 @@
         <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G36" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L36" t="s">
         <v>57</v>
@@ -4715,28 +4718,28 @@
         <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H37" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K37" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L37" t="s">
         <v>57</v>
@@ -4756,28 +4759,28 @@
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K38" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L38" t="s">
         <v>57</v>
@@ -4797,28 +4800,28 @@
         <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K39" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L39" t="s">
         <v>57</v>
@@ -4838,28 +4841,28 @@
         <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G40" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J40" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K40" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L40" t="s">
         <v>57</v>
@@ -4879,28 +4882,28 @@
         <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F41" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H41" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K41" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s">
         <v>57</v>
@@ -4920,28 +4923,28 @@
         <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G42" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H42" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J42" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K42" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L42" t="s">
         <v>57</v>
@@ -4962,10 +4965,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -4973,24 +4976,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="374">
   <si>
     <t>ID</t>
   </si>
@@ -226,13 +226,10 @@
     <t>tool</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>,,</t>
-  </si>
-  <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -1799,7 +1796,7 @@
         <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1901,34 +1898,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>72</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>74</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>75</v>
-      </c>
-      <c r="J1" t="s">
-        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -1942,19 +1939,19 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -1966,13 +1963,13 @@
         <v>24</v>
       </c>
       <c r="I2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" t="s">
         <v>88</v>
       </c>
-      <c r="J2" t="s">
-        <v>89</v>
-      </c>
       <c r="K2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
@@ -1983,19 +1980,19 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -2007,13 +2004,13 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
         <v>57</v>
@@ -2024,19 +2021,19 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -2048,13 +2045,13 @@
         <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -2065,19 +2062,19 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -2089,13 +2086,13 @@
         <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -2106,19 +2103,19 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -2130,13 +2127,13 @@
         <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -2147,19 +2144,19 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
         <v>85</v>
       </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -2171,13 +2168,13 @@
         <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
@@ -2188,19 +2185,19 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
         <v>85</v>
       </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -2212,13 +2209,13 @@
         <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -2229,19 +2226,19 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
         <v>85</v>
       </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -2253,13 +2250,13 @@
         <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -2280,34 +2277,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>72</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>74</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>75</v>
-      </c>
-      <c r="J1" t="s">
-        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -2321,19 +2318,19 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -2345,13 +2342,13 @@
         <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
@@ -2362,19 +2359,19 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -2386,13 +2383,13 @@
         <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L3" t="s">
         <v>57</v>
@@ -2403,19 +2400,19 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -2427,13 +2424,13 @@
         <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -2444,19 +2441,19 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -2468,13 +2465,13 @@
         <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -2485,19 +2482,19 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -2509,13 +2506,13 @@
         <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -2526,19 +2523,19 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
@@ -2550,13 +2547,13 @@
         <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
@@ -2567,19 +2564,19 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -2591,13 +2588,13 @@
         <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -2608,19 +2605,19 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2632,13 +2629,13 @@
         <v>27</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -2649,19 +2646,19 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -2673,13 +2670,13 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L10" t="s">
         <v>57</v>
@@ -2690,19 +2687,19 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -2714,13 +2711,13 @@
         <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L11" t="s">
         <v>57</v>
@@ -2731,19 +2728,19 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -2755,13 +2752,13 @@
         <v>27</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L12" t="s">
         <v>57</v>
@@ -2772,19 +2769,19 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
         <v>20</v>
@@ -2796,13 +2793,13 @@
         <v>29</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
@@ -2813,19 +2810,19 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -2837,13 +2834,13 @@
         <v>27</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
@@ -2854,19 +2851,19 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -2878,13 +2875,13 @@
         <v>24</v>
       </c>
       <c r="I15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" t="s">
         <v>88</v>
       </c>
-      <c r="J15" t="s">
-        <v>89</v>
-      </c>
       <c r="K15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s">
         <v>57</v>
@@ -2895,19 +2892,19 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -2919,13 +2916,13 @@
         <v>27</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s">
         <v>57</v>
@@ -2936,19 +2933,19 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -2960,13 +2957,13 @@
         <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s">
         <v>57</v>
@@ -2977,19 +2974,19 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -3001,13 +2998,13 @@
         <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s">
         <v>57</v>
@@ -3018,19 +3015,19 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -3042,13 +3039,13 @@
         <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L19" t="s">
         <v>57</v>
@@ -3059,19 +3056,19 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -3083,13 +3080,13 @@
         <v>27</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
@@ -3100,19 +3097,19 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -3124,13 +3121,13 @@
         <v>27</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
@@ -3141,19 +3138,19 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -3165,13 +3162,13 @@
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s">
         <v>57</v>
@@ -3182,19 +3179,19 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" t="s">
         <v>155</v>
       </c>
-      <c r="D23" t="s">
-        <v>156</v>
-      </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -3206,13 +3203,13 @@
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s">
         <v>57</v>
@@ -3233,34 +3230,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>72</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>74</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>75</v>
-      </c>
-      <c r="J1" t="s">
-        <v>76</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3283,28 +3280,28 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J2" t="s">
         <v>301</v>
       </c>
-      <c r="J2" t="s">
-        <v>302</v>
-      </c>
       <c r="K2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L2" t="s">
         <v>57</v>
@@ -3324,28 +3321,28 @@
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L3" t="s">
         <v>57</v>
@@ -3365,28 +3362,28 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -3406,28 +3403,28 @@
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -3447,28 +3444,28 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -3488,28 +3485,28 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
@@ -3529,28 +3526,28 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -3570,28 +3567,28 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -3611,28 +3608,28 @@
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L10" t="s">
         <v>57</v>
@@ -3652,28 +3649,28 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" t="s">
+        <v>201</v>
+      </c>
+      <c r="G11" t="s">
+        <v>237</v>
+      </c>
+      <c r="H11" t="s">
+        <v>273</v>
+      </c>
+      <c r="I11" t="s">
+        <v>300</v>
+      </c>
+      <c r="J11" t="s">
         <v>88</v>
       </c>
-      <c r="E11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" t="s">
-        <v>238</v>
-      </c>
-      <c r="H11" t="s">
-        <v>274</v>
-      </c>
-      <c r="I11" t="s">
-        <v>301</v>
-      </c>
-      <c r="J11" t="s">
-        <v>89</v>
-      </c>
       <c r="K11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L11" t="s">
         <v>57</v>
@@ -3693,28 +3690,28 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L12" t="s">
         <v>57</v>
@@ -3734,28 +3731,28 @@
         <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
@@ -3775,28 +3772,28 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
@@ -3816,28 +3813,28 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L15" t="s">
         <v>57</v>
@@ -3857,28 +3854,28 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L16" t="s">
         <v>57</v>
@@ -3898,28 +3895,28 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L17" t="s">
         <v>57</v>
@@ -3939,28 +3936,28 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L18" t="s">
         <v>57</v>
@@ -3980,28 +3977,28 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L19" t="s">
         <v>57</v>
@@ -4021,28 +4018,28 @@
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
@@ -4062,28 +4059,28 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
@@ -4103,28 +4100,28 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L22" t="s">
         <v>57</v>
@@ -4144,28 +4141,28 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L23" t="s">
         <v>57</v>
@@ -4185,28 +4182,28 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L24" t="s">
         <v>57</v>
@@ -4226,28 +4223,28 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I25" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L25" t="s">
         <v>57</v>
@@ -4267,28 +4264,28 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L26" t="s">
         <v>57</v>
@@ -4308,28 +4305,28 @@
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L27" t="s">
         <v>57</v>
@@ -4349,28 +4346,28 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L28" t="s">
         <v>57</v>
@@ -4390,28 +4387,28 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L29" t="s">
         <v>57</v>
@@ -4431,28 +4428,28 @@
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L30" t="s">
         <v>57</v>
@@ -4472,28 +4469,28 @@
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L31" t="s">
         <v>57</v>
@@ -4513,28 +4510,28 @@
         <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L32" t="s">
         <v>57</v>
@@ -4554,28 +4551,28 @@
         <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J33" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K33" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L33" t="s">
         <v>57</v>
@@ -4595,28 +4592,28 @@
         <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J34" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L34" t="s">
         <v>57</v>
@@ -4636,28 +4633,28 @@
         <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K35" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L35" t="s">
         <v>57</v>
@@ -4677,28 +4674,28 @@
         <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L36" t="s">
         <v>57</v>
@@ -4718,28 +4715,28 @@
         <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K37" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L37" t="s">
         <v>57</v>
@@ -4759,28 +4756,28 @@
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G38" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L38" t="s">
         <v>57</v>
@@ -4800,28 +4797,28 @@
         <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L39" t="s">
         <v>57</v>
@@ -4841,28 +4838,28 @@
         <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J40" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K40" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L40" t="s">
         <v>57</v>
@@ -4882,28 +4879,28 @@
         <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s">
         <v>57</v>
@@ -4923,28 +4920,28 @@
         <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G42" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H42" t="s">
+        <v>299</v>
+      </c>
+      <c r="I42" t="s">
         <v>300</v>
       </c>
-      <c r="I42" t="s">
-        <v>301</v>
-      </c>
       <c r="J42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L42" t="s">
         <v>57</v>
@@ -4965,10 +4962,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1" t="s">
         <v>367</v>
-      </c>
-      <c r="B1" t="s">
-        <v>368</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -4976,24 +4973,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5090" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5154" uniqueCount="1424">
   <si>
     <t>ID</t>
   </si>
@@ -98,46 +98,46 @@
     <t>S0013</t>
   </si>
   <si>
-    <t>tool--5394d58d-07e5-4728-8984-3cfebe978683</t>
-  </si>
-  <si>
-    <t>tool--07ed755a-398c-4330-8349-2f5ed4ca4c1c</t>
-  </si>
-  <si>
-    <t>tool--63c492b1-88b1-4df6-8737-003e09b95b91</t>
-  </si>
-  <si>
-    <t>tool--2be11800-685c-4062-97e0-08a0312813c2</t>
-  </si>
-  <si>
-    <t>tool--093e831e-738d-4d35-a139-a2c858be92a3</t>
-  </si>
-  <si>
-    <t>tool--be70b110-ba24-40a9-a494-db8bbac83de8</t>
-  </si>
-  <si>
-    <t>tool--13c02cc3-f597-4c27-b187-bb691a376e8d</t>
-  </si>
-  <si>
-    <t>tool--8584cec6-6377-4946-ac42-132e7d9dfc47</t>
-  </si>
-  <si>
-    <t>tool--508817a5-f547-4738-b33f-2073c7e7bb46</t>
-  </si>
-  <si>
-    <t>tool--a284d8f6-38fa-45a8-b856-19580195c4b5</t>
-  </si>
-  <si>
-    <t>tool--8dee1f22-2f1a-49e4-9cd7-3ad55f270afa</t>
-  </si>
-  <si>
-    <t>tool--c318b583-5c74-4d4c-af96-44d2a38cc28b</t>
-  </si>
-  <si>
-    <t>tool--49b4cf66-92e2-4bfe-9ee7-c7836c48f1bd</t>
-  </si>
-  <si>
-    <t>tool--0cab0eb6-aab8-491e-87e0-90065cad619f</t>
+    <t>tool--2f1392d9-db88-4ab3-af47-b48f5be5e4d1</t>
+  </si>
+  <si>
+    <t>tool--f772df95-d66e-4e57-8645-b8020a451f65</t>
+  </si>
+  <si>
+    <t>tool--f92083ef-3b0a-455a-a6ca-fc137cb4a6c0</t>
+  </si>
+  <si>
+    <t>tool--229ccd55-af8b-4954-9d37-c01c7b007daf</t>
+  </si>
+  <si>
+    <t>tool--f69553b2-8023-4d84-b754-92e67a665955</t>
+  </si>
+  <si>
+    <t>tool--4556118e-edf6-43e4-9cee-24e270ae451e</t>
+  </si>
+  <si>
+    <t>tool--72e7409f-63c7-43bd-9414-02a61e50b0b2</t>
+  </si>
+  <si>
+    <t>tool--29369b13-242b-4f23-92f0-f8c810bc8cd4</t>
+  </si>
+  <si>
+    <t>tool--ea14cd7b-585a-494b-88e8-d9f8da2455eb</t>
+  </si>
+  <si>
+    <t>tool--60e274fe-60d9-44b4-b2e2-19ab1948bd5e</t>
+  </si>
+  <si>
+    <t>tool--f74fade6-c2ba-4cbc-8833-3daf6cc482ae</t>
+  </si>
+  <si>
+    <t>tool--88321b03-b598-459c-b69c-53b4cb0ebb20</t>
+  </si>
+  <si>
+    <t>tool--f889d8a2-0000-47c9-b8b3-1a12089eec06</t>
+  </si>
+  <si>
+    <t>tool--cdc507d7-2b86-4fd9-9a01-b0172cfc5205</t>
   </si>
   <si>
     <t>Верховный тайный совет</t>
@@ -298,43 +298,43 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Російсько-українська війна (з 2014),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Рашизм: Звір з безодні 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Серпневий путч — Вікіпедія 2026)</t>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026),(Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026),(Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026)</t>
+    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
   </si>
   <si>
     <t>,(Citation: Друга Малоросійська колегія — Вікіпедія 2026),</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: «Рашизм: Звір з безодні» 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: «Рашизм: Звір з безодні» 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Московсько-українська війна (1658—1659),(Citation: Польское восстание (1863—1864),(Citation: Московські статті (1665),(Citation: Мазепа 2007),(Citation: Переяславські статті (1659),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Крымская война — Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Русско-турецкая война (1877—1878),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Повстання бузьких козаків (1817),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Північна війна (1700—1721),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Московсько-українська війна (1658—1659),(Citation: Переяславські статті (1659),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Руїна — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Історія України — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Московські статті (1665),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Азовські походи (1695—1696),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026)</t>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Російсько-українська війна (з 2014),(Citation: Повстання бузьких козаків (1817),(Citation: Російсько-турецька війна (1806—1812),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславські статті (1659),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Польское восстание (1863—1864),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Русско-турецкая война (1877—1878),(Citation: Листопадове повстання (1830—1831),(Citation: Русско-турецкая война (1768—1774),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Московські статті (1665),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Переяславські статті (1659)</t>
+  </si>
+  <si>
+    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Ліквідація Запорозької Січі (1775),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Мазепа 2007),(Citation: Московські статті (1665),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Азовські походи (1695—1696),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -403,22 +403,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--f2ca30a8-03bd-4610-b8a2-0148c877e608</t>
-  </si>
-  <si>
-    <t>intrusion-set--17a091f6-8db4-4483-acf7-a69fd4cc7457</t>
-  </si>
-  <si>
-    <t>intrusion-set--6981af28-a9ac-4529-a24e-b9b57a3b8686</t>
-  </si>
-  <si>
-    <t>intrusion-set--ac141584-6691-4008-b480-83deaf636398</t>
-  </si>
-  <si>
-    <t>intrusion-set--468d1617-0966-4f71-bc4e-0a45dacd6316</t>
-  </si>
-  <si>
-    <t>intrusion-set--27b388cb-7c36-4aca-b91e-792abce31837</t>
+    <t>intrusion-set--764cac65-3338-4105-9501-152d67a8fc5b</t>
+  </si>
+  <si>
+    <t>intrusion-set--d02a2528-4983-49ba-9958-e3dca5f57c1a</t>
+  </si>
+  <si>
+    <t>intrusion-set--7077cfc8-f533-42d0-bc5a-a2bbebf847e1</t>
+  </si>
+  <si>
+    <t>intrusion-set--8837e6ef-c6bb-4b41-b8c6-c0588be2db1c</t>
+  </si>
+  <si>
+    <t>intrusion-set--a6148444-d09e-4aa5-8c32-50da2bd25525</t>
+  </si>
+  <si>
+    <t>intrusion-set--43830a9b-2a24-4049-8b19-d210028de96e</t>
   </si>
   <si>
     <t>group</t>
@@ -502,7 +502,7 @@
     <t>Уничтожение гражданских и просветительских структур в местах компактного проживания диаспоры: «Ліквідація 'Просвіт' на Кубані, в Зеленому Клину» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026)</t>
+    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
   </si>
   <si>
     <t>Организация фейковых безальтернативных «Народных сборов» под контролем оккупационных войск для юридического оформления захвата. (Citation: Історія України — Вікіпедія 2026)</t>
@@ -532,106 +532,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--d7ea1ab8-025e-4b6e-a5c7-86a391459eed</t>
-  </si>
-  <si>
-    <t>relationship--ac2e501f-0758-4b20-a333-d02acbb950af</t>
-  </si>
-  <si>
-    <t>relationship--1a9c8662-c949-44bf-b6b1-833d11c186a5</t>
-  </si>
-  <si>
-    <t>relationship--0f53a25c-0f03-441b-ad1c-7674b783b199</t>
-  </si>
-  <si>
-    <t>relationship--2c4fa17c-2209-4a40-b22a-55bdea253cda</t>
-  </si>
-  <si>
-    <t>relationship--8c9e5558-8227-41ff-a75e-21a3f8532d7f</t>
-  </si>
-  <si>
-    <t>relationship--9d2b26ef-4e84-4be7-817c-c74a389a9f51</t>
-  </si>
-  <si>
-    <t>relationship--408d8f52-413c-42a8-919e-67f2b99109dd</t>
-  </si>
-  <si>
-    <t>relationship--e1e1633c-0999-4e95-be36-82e0dc88b110</t>
-  </si>
-  <si>
-    <t>relationship--48d38274-ef36-489f-8b60-9a3b4f553ee9</t>
-  </si>
-  <si>
-    <t>relationship--75dff56e-a641-42c1-81d7-cc01cf050ff0</t>
-  </si>
-  <si>
-    <t>relationship--fc56e0c9-99c5-49cc-9cfd-09bc149451c6</t>
-  </si>
-  <si>
-    <t>relationship--337f129e-d16f-480e-ac54-4f061e6c880b</t>
-  </si>
-  <si>
-    <t>relationship--3d784d40-619f-4ca0-af03-ba343ea69cd5</t>
-  </si>
-  <si>
-    <t>relationship--99d96b37-135f-40fd-ba36-d4d55bb9766d</t>
-  </si>
-  <si>
-    <t>relationship--601217c6-fb88-40f9-8280-68ebdd62ddba</t>
-  </si>
-  <si>
-    <t>relationship--dea8fc3f-877d-4c62-add4-e03698dacd2f</t>
-  </si>
-  <si>
-    <t>relationship--c872eab0-0498-4947-ad9c-9a2924c9306b</t>
-  </si>
-  <si>
-    <t>relationship--74a70429-5b5d-4c35-8db7-fcfd294946da</t>
-  </si>
-  <si>
-    <t>relationship--b3a02b27-cf4f-42c3-beca-1c10ede4807b</t>
-  </si>
-  <si>
-    <t>relationship--98da7cc5-b9c5-417d-b02a-0361fc935dea</t>
-  </si>
-  <si>
-    <t>relationship--202ab4bc-13d5-491d-823e-bc50f8209bec</t>
-  </si>
-  <si>
-    <t>relationship--717df117-efc9-4c77-b40d-226042f70222</t>
-  </si>
-  <si>
-    <t>relationship--bef09119-3db5-4bb1-a056-098fd03cccf4</t>
-  </si>
-  <si>
-    <t>relationship--0cc68637-28ae-4177-8901-d266c832b3a0</t>
-  </si>
-  <si>
-    <t>relationship--832b1243-e8f2-4fc4-af1c-41ab83456edd</t>
-  </si>
-  <si>
-    <t>relationship--1dbe522d-14a4-4057-90d8-990032137b34</t>
-  </si>
-  <si>
-    <t>relationship--917c2eca-6937-45e6-89b5-f496d8e114ef</t>
-  </si>
-  <si>
-    <t>relationship--65ccd26d-9548-4633-9ab2-fc8e97230822</t>
-  </si>
-  <si>
-    <t>relationship--f235ee48-a7a4-403d-9a9a-40115d544af4</t>
-  </si>
-  <si>
-    <t>relationship--75016b03-b7b1-4be5-99e1-19676222792c</t>
-  </si>
-  <si>
-    <t>relationship--81e0ad75-6b2a-4bce-b911-9cc62c51dfd5</t>
-  </si>
-  <si>
-    <t>relationship--2762d722-5e5f-4d70-a27d-6a3f4ab872df</t>
-  </si>
-  <si>
-    <t>relationship--c4e5c92d-7b95-49e1-babc-737f0151f38a</t>
+    <t>relationship--07ff3bf1-da85-48ff-a7f1-092087360a4b</t>
+  </si>
+  <si>
+    <t>relationship--a568902c-2781-4c02-9561-daa3cd389fdd</t>
+  </si>
+  <si>
+    <t>relationship--7fc72472-9b9e-4c55-b0f6-b594a238d151</t>
+  </si>
+  <si>
+    <t>relationship--6adb2573-0b76-4a78-814e-f1065642ca10</t>
+  </si>
+  <si>
+    <t>relationship--d18a5e90-6666-473b-a5d4-61e0229c1b0c</t>
+  </si>
+  <si>
+    <t>relationship--5147f80b-0d35-4fb9-b077-7e4edb6625b7</t>
+  </si>
+  <si>
+    <t>relationship--755b810b-2223-4724-8f71-7b5b131558ad</t>
+  </si>
+  <si>
+    <t>relationship--e37f82fa-879e-4232-b4e6-cbb67afc4eed</t>
+  </si>
+  <si>
+    <t>relationship--73c719f0-ddaa-4188-8ee1-0a2d1d18072c</t>
+  </si>
+  <si>
+    <t>relationship--1ff820f2-be59-4c12-bfa9-d93a821cabff</t>
+  </si>
+  <si>
+    <t>relationship--bb015f20-2518-43a7-83d6-c248c75697d9</t>
+  </si>
+  <si>
+    <t>relationship--f2117157-5739-4fb7-ba0e-b8755049c60c</t>
+  </si>
+  <si>
+    <t>relationship--3c6e4570-df11-4a98-880a-bf4b2b08c35e</t>
+  </si>
+  <si>
+    <t>relationship--9d83a076-25c0-4350-a631-2d2d8e92c550</t>
+  </si>
+  <si>
+    <t>relationship--cf5e11df-ba9e-44b4-af92-9bd3834541a3</t>
+  </si>
+  <si>
+    <t>relationship--9fbf80bb-c4c6-4ae9-8210-bac7d061d88c</t>
+  </si>
+  <si>
+    <t>relationship--f28dec40-aeef-4066-baf1-a4503f18169d</t>
+  </si>
+  <si>
+    <t>relationship--17e09586-8594-4ad7-b94d-e29a9543f19b</t>
+  </si>
+  <si>
+    <t>relationship--4d20a15e-ffdf-4500-9ab7-1f578cad1263</t>
+  </si>
+  <si>
+    <t>relationship--5a177542-b091-4817-b666-f322dcb7ed63</t>
+  </si>
+  <si>
+    <t>relationship--f7b12560-78ed-4f92-a296-151ccd80b9f0</t>
+  </si>
+  <si>
+    <t>relationship--08a05095-e51f-45a7-b895-568a10262260</t>
+  </si>
+  <si>
+    <t>relationship--cec33e7a-2cda-46f4-8a37-90a991776503</t>
+  </si>
+  <si>
+    <t>relationship--078c6efe-8978-4f8f-95ce-4d632f3c68d7</t>
+  </si>
+  <si>
+    <t>relationship--5083da2c-53cc-44ff-b31d-af6bc2ec1075</t>
+  </si>
+  <si>
+    <t>relationship--c2ba08ea-f1d1-492d-9287-fb0f293fbbbc</t>
+  </si>
+  <si>
+    <t>relationship--f6ea15aa-1bac-42ac-8f0b-abf92500a9cf</t>
+  </si>
+  <si>
+    <t>relationship--5f605d53-64c0-4be6-9bb1-aa9ecbdb4041</t>
+  </si>
+  <si>
+    <t>relationship--b27d1694-379e-4dc8-9a89-6c8f149fcb4b</t>
+  </si>
+  <si>
+    <t>relationship--154a4f4b-614f-4e7a-afc2-a72aabf44daa</t>
+  </si>
+  <si>
+    <t>relationship--4627ab63-1c88-4c31-8390-c649f58d53e4</t>
+  </si>
+  <si>
+    <t>relationship--256ea25f-fba9-4b0c-93c1-f19726910d48</t>
+  </si>
+  <si>
+    <t>relationship--6c4b53a7-4999-421a-bef6-7f49392b9aa2</t>
+  </si>
+  <si>
+    <t>relationship--4b52815f-e22e-41e1-824e-e531749f5f65</t>
   </si>
   <si>
     <t>C0009</t>
@@ -1234,304 +1234,304 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--469310ef-4094-4e7c-9c67-f45b0aaa8547</t>
-  </si>
-  <si>
-    <t>campaign--1da9ae08-d4bb-4d3f-ac74-ec943ba5eaea</t>
-  </si>
-  <si>
-    <t>campaign--06564046-4d40-460a-97a4-3ed307685e40</t>
-  </si>
-  <si>
-    <t>campaign--f35b3b1e-3566-45f5-bffd-36b87158a0a8</t>
-  </si>
-  <si>
-    <t>campaign--1ed15b75-60c6-4d37-9d70-217b0e2c459f</t>
-  </si>
-  <si>
-    <t>campaign--37f47ace-f541-4346-bc8d-914ef07293a2</t>
-  </si>
-  <si>
-    <t>campaign--a7b14767-cae0-4491-88c0-9f89c9121a90</t>
-  </si>
-  <si>
-    <t>campaign--fbc5edd1-be5a-43d9-b787-a616fa2715dc</t>
-  </si>
-  <si>
-    <t>campaign--57bc5e5f-ccdc-40e4-afad-02434f0b2fb6</t>
-  </si>
-  <si>
-    <t>campaign--96476361-e0d6-4535-b346-9c3b912bd9e3</t>
-  </si>
-  <si>
-    <t>campaign--a9efd6f6-ecda-44af-b7fc-43a9dc8ccd12</t>
-  </si>
-  <si>
-    <t>campaign--2d54bb22-7db2-4405-9c6b-03591652ceb7</t>
-  </si>
-  <si>
-    <t>campaign--babba679-aee3-44e3-b357-607640fb6ac5</t>
-  </si>
-  <si>
-    <t>campaign--a1e496e7-7199-4d75-83ef-a86810a706b0</t>
-  </si>
-  <si>
-    <t>campaign--02829ff9-ab24-4d0b-8fd1-50d95a2c675a</t>
-  </si>
-  <si>
-    <t>campaign--c075447d-3770-4539-8fa3-c78e83db5533</t>
-  </si>
-  <si>
-    <t>campaign--0b6e405c-a036-47dd-8c12-ec160b0ebf20</t>
-  </si>
-  <si>
-    <t>campaign--9ee49c05-78a5-441d-b6b6-3803e9cf6b2e</t>
-  </si>
-  <si>
-    <t>campaign--bbdb7af2-2478-4231-bf88-140096111cf0</t>
-  </si>
-  <si>
-    <t>campaign--7ed527f9-2a59-48e7-84fa-2207c3867e21</t>
-  </si>
-  <si>
-    <t>campaign--878cb2cf-11b1-450d-8240-874e6cee55db</t>
-  </si>
-  <si>
-    <t>campaign--31b050af-e3bb-418b-ba1f-3e3900d3b5c1</t>
-  </si>
-  <si>
-    <t>campaign--b58bf5e2-8288-406d-873a-d6c557000725</t>
-  </si>
-  <si>
-    <t>campaign--b47a06ee-5194-4931-ae87-651748ad7ba6</t>
-  </si>
-  <si>
-    <t>campaign--d058c586-e582-45f0-b4e2-194c6599f119</t>
-  </si>
-  <si>
-    <t>campaign--a4cd4a1b-d1c5-45c5-bb7d-3018adbdeaaa</t>
-  </si>
-  <si>
-    <t>campaign--9f1c9c14-749e-4471-96a6-36e2a8ce16f3</t>
-  </si>
-  <si>
-    <t>campaign--138818ae-7e8e-4838-858a-fc252dff9953</t>
-  </si>
-  <si>
-    <t>campaign--5eeb401c-84e2-46fd-b61f-f0f6a3b8942a</t>
-  </si>
-  <si>
-    <t>campaign--94dae670-09c9-4e10-a03e-bace8ecddebb</t>
-  </si>
-  <si>
-    <t>campaign--1bd11010-5386-41c3-aa33-79321c801f6d</t>
-  </si>
-  <si>
-    <t>campaign--351bcd52-1012-4ba8-9014-071de5495f66</t>
-  </si>
-  <si>
-    <t>campaign--e2ddf00a-7479-4e93-92ef-75f49f3e574e</t>
-  </si>
-  <si>
-    <t>campaign--979cdf7e-8431-4d0e-9edf-97c67a396fab</t>
-  </si>
-  <si>
-    <t>campaign--61eacb32-a063-44cc-acba-9691d4504970</t>
-  </si>
-  <si>
-    <t>campaign--0f123e76-dbd9-42e8-83fa-94c42ab45546</t>
-  </si>
-  <si>
-    <t>campaign--a4e9875b-4377-4409-8e0d-ba4bf6817fe1</t>
-  </si>
-  <si>
-    <t>campaign--ffcd0dcc-ce70-4d9a-b06e-ad29c6a5faa7</t>
-  </si>
-  <si>
-    <t>campaign--9d75ac21-abcf-4195-9c50-287324e7013e</t>
-  </si>
-  <si>
-    <t>campaign--1be51ecb-8994-4135-b846-3a4d2fc03bbc</t>
-  </si>
-  <si>
-    <t>campaign--0ff0500d-6a60-465d-ad50-d1f1c3b9bb2f</t>
-  </si>
-  <si>
-    <t>campaign--b7427601-e8ad-4808-86ad-e348d4d8e8e8</t>
-  </si>
-  <si>
-    <t>campaign--23562267-63c1-45f6-a2e5-2c8be7dea1ca</t>
-  </si>
-  <si>
-    <t>campaign--ccd6e591-b2f6-401c-9432-d880013c9109</t>
-  </si>
-  <si>
-    <t>campaign--4375f375-22bc-45fa-a6a1-647d169ca8d2</t>
-  </si>
-  <si>
-    <t>campaign--00e9c967-4b34-4582-addc-71e4e7138765</t>
-  </si>
-  <si>
-    <t>campaign--39681d6f-63c5-4f46-b65d-e9e278c89ffd</t>
-  </si>
-  <si>
-    <t>campaign--579698e2-118e-4ece-9ae6-68677abbfcfb</t>
-  </si>
-  <si>
-    <t>campaign--85ed260f-1c25-4943-94cb-7889f41f7e49</t>
-  </si>
-  <si>
-    <t>campaign--3120da56-f8d8-4bfe-820e-a5c81422a643</t>
-  </si>
-  <si>
-    <t>campaign--1a4c53de-829f-4e74-98d2-669ac8260fa5</t>
-  </si>
-  <si>
-    <t>campaign--d25530f7-12c2-4aa6-93dd-6eb9e3e64e45</t>
-  </si>
-  <si>
-    <t>campaign--d2388221-289a-4666-8ea7-09aa68582270</t>
-  </si>
-  <si>
-    <t>campaign--0824f4a5-da79-4989-bde2-a1cd6d32bbb0</t>
-  </si>
-  <si>
-    <t>campaign--2e6f6e3e-6481-4991-8daa-f31bbd1ddcd4</t>
-  </si>
-  <si>
-    <t>campaign--19eabd02-641a-470f-ba96-16bd2e8fbb7c</t>
-  </si>
-  <si>
-    <t>campaign--31a84130-e0f4-4b6a-b733-a13fe388aca1</t>
-  </si>
-  <si>
-    <t>campaign--7ad99995-4346-4b9f-8ee6-7456085ee8f4</t>
-  </si>
-  <si>
-    <t>campaign--6a417d5d-08fd-494a-8e38-a849469200d5</t>
-  </si>
-  <si>
-    <t>campaign--80cc78f4-303a-4e14-b362-205a0455754d</t>
-  </si>
-  <si>
-    <t>campaign--41aeb17b-6211-408d-b7d2-38119809d10e</t>
-  </si>
-  <si>
-    <t>campaign--f05ed4f4-f2e3-4913-a735-82027728ce05</t>
-  </si>
-  <si>
-    <t>campaign--d1e226e3-fc33-499c-a10e-cf0a09450014</t>
-  </si>
-  <si>
-    <t>campaign--0fe96e75-417a-47b7-892d-e68565b241b6</t>
-  </si>
-  <si>
-    <t>campaign--df7c84da-94a8-4648-9f1c-6c33cfe71f0c</t>
-  </si>
-  <si>
-    <t>campaign--a85fa0a4-c62b-4a2d-89ab-350311b71890</t>
-  </si>
-  <si>
-    <t>campaign--3fc95fda-cd5c-4e2a-8075-55803606d10e</t>
-  </si>
-  <si>
-    <t>campaign--4eacde73-d9c1-4355-afec-7d8f87610f1f</t>
-  </si>
-  <si>
-    <t>campaign--5dad886c-01bc-4d38-8168-6177fd6a7349</t>
-  </si>
-  <si>
-    <t>campaign--548b6a19-f9f3-4763-bdbc-1c12c12267ae</t>
-  </si>
-  <si>
-    <t>campaign--221ad627-69c6-436e-bd69-70f81103fcc4</t>
-  </si>
-  <si>
-    <t>campaign--b1c0f594-4c32-4525-a394-f0cfa965e9df</t>
-  </si>
-  <si>
-    <t>campaign--b64e83f5-f457-4774-9be1-66c261e50854</t>
-  </si>
-  <si>
-    <t>campaign--790d7f8e-2c25-48b5-8533-65b3f8ac2b9b</t>
-  </si>
-  <si>
-    <t>campaign--4e7c9498-5134-492c-8a41-ad881a983a77</t>
-  </si>
-  <si>
-    <t>campaign--de5f6586-4723-47b4-bea0-fc192727aebd</t>
-  </si>
-  <si>
-    <t>campaign--a21034da-0578-4297-bffe-b1f389435ff6</t>
-  </si>
-  <si>
-    <t>campaign--ccfe0a05-ff11-4dfd-8f07-e5c961c2afcd</t>
-  </si>
-  <si>
-    <t>campaign--fe66cc4f-a868-42fc-898d-619bdfe66830</t>
-  </si>
-  <si>
-    <t>campaign--ed294a47-7e87-40fa-993e-de2cb99245bb</t>
-  </si>
-  <si>
-    <t>campaign--d9465ad8-c135-4770-ab09-965c31194f8a</t>
-  </si>
-  <si>
-    <t>campaign--953fcd6f-5a7f-4ddd-9a05-c1d081d3febd</t>
-  </si>
-  <si>
-    <t>campaign--e7714c89-03d9-4e0f-8667-cb52fb36e11b</t>
-  </si>
-  <si>
-    <t>campaign--05051bcd-4e18-474e-a19a-a127de638f55</t>
-  </si>
-  <si>
-    <t>campaign--74724121-ec58-4506-a35d-f9b712da7b67</t>
-  </si>
-  <si>
-    <t>campaign--d6cabbf1-27c3-45d6-9c3c-1cec382515d8</t>
-  </si>
-  <si>
-    <t>campaign--67d98968-5982-4041-9eb1-b366e631d16f</t>
-  </si>
-  <si>
-    <t>campaign--04131151-85c0-4189-9ffd-9508eb1a253d</t>
-  </si>
-  <si>
-    <t>campaign--f4378eab-dead-40c5-a510-fca43c057d18</t>
-  </si>
-  <si>
-    <t>campaign--98342c99-3a98-4b8f-b49e-7e00b435bd99</t>
-  </si>
-  <si>
-    <t>campaign--8893f759-a738-4bd4-9a5b-12ee22480623</t>
-  </si>
-  <si>
-    <t>campaign--3a522944-77dd-4455-99bd-9bb3662762c6</t>
-  </si>
-  <si>
-    <t>campaign--f00cb9d8-2806-467d-9675-3953a6f7998c</t>
-  </si>
-  <si>
-    <t>campaign--ebbf432f-457f-4477-be87-0dd1c7ba2b06</t>
-  </si>
-  <si>
-    <t>campaign--fafde296-b6ea-4b0a-8c05-fae5907ad781</t>
-  </si>
-  <si>
-    <t>campaign--97b9ca95-4c48-46e3-9c0c-69a1c2a83695</t>
-  </si>
-  <si>
-    <t>campaign--7d79a2a7-6f18-45c3-ad5b-a726a4fb6e93</t>
-  </si>
-  <si>
-    <t>campaign--b3ebfffc-4e30-4091-83e3-6ad673c7e2d4</t>
-  </si>
-  <si>
-    <t>campaign--22c4105c-6aba-421f-933e-40a47b6a0ce0</t>
-  </si>
-  <si>
-    <t>campaign--ec0283ed-3be9-48ad-b31f-4ac278e8e07a</t>
+    <t>campaign--6cb77d0a-3451-4de8-87da-b018068dfb90</t>
+  </si>
+  <si>
+    <t>campaign--8b42609d-df97-4863-be72-6956976733bf</t>
+  </si>
+  <si>
+    <t>campaign--9a411991-5759-4401-bf8b-1d035755a82e</t>
+  </si>
+  <si>
+    <t>campaign--87f90c81-65f7-408a-869c-13c15763058d</t>
+  </si>
+  <si>
+    <t>campaign--79792109-8930-4868-a0d5-c36b7e4d35d2</t>
+  </si>
+  <si>
+    <t>campaign--a2a50721-74ad-4a1b-8f10-4729fe218d77</t>
+  </si>
+  <si>
+    <t>campaign--e0b2ee1f-02d9-420b-95ec-c5e69e7683ba</t>
+  </si>
+  <si>
+    <t>campaign--f1f99961-521b-4e4c-ad7b-41a7f7fbb47d</t>
+  </si>
+  <si>
+    <t>campaign--b00634c3-5732-436e-b8ac-a379eb11a3a5</t>
+  </si>
+  <si>
+    <t>campaign--946006e7-080a-4089-846c-570e294df9de</t>
+  </si>
+  <si>
+    <t>campaign--120e2810-9671-4bbd-89dd-fdd5e5664bd8</t>
+  </si>
+  <si>
+    <t>campaign--e31eeb50-d21f-4f54-94fc-7a1265e3f422</t>
+  </si>
+  <si>
+    <t>campaign--4b4c6c32-adfd-4839-a189-784041b133e3</t>
+  </si>
+  <si>
+    <t>campaign--bbf4f7b4-df46-40fb-9560-91bbccaa69dd</t>
+  </si>
+  <si>
+    <t>campaign--d71c0044-37aa-487b-a348-d665b548d364</t>
+  </si>
+  <si>
+    <t>campaign--db3cd6c5-fdee-4f60-a49a-78a6842a0bdd</t>
+  </si>
+  <si>
+    <t>campaign--76bb2459-6ee0-4d14-9d96-4608d7fb554f</t>
+  </si>
+  <si>
+    <t>campaign--6763e8dc-524b-4121-9c95-1badc8d4ac5e</t>
+  </si>
+  <si>
+    <t>campaign--f7092c6b-af00-4ffc-bbc9-d41fdc3d22c0</t>
+  </si>
+  <si>
+    <t>campaign--02c01b67-1582-41d8-9cb8-89286d93e772</t>
+  </si>
+  <si>
+    <t>campaign--aedfaa2b-061a-4e70-8824-e88b30dbe4c4</t>
+  </si>
+  <si>
+    <t>campaign--452ec2f1-3adb-4883-a2a6-240c40bc70bc</t>
+  </si>
+  <si>
+    <t>campaign--467c7d12-8c86-49b3-accf-f377d0d7d0cc</t>
+  </si>
+  <si>
+    <t>campaign--a124adf3-a386-46f5-ab54-3b856f8a8bad</t>
+  </si>
+  <si>
+    <t>campaign--b25b509c-ab0c-4256-8f81-968d821c5915</t>
+  </si>
+  <si>
+    <t>campaign--18b1943c-1241-40fe-aae3-033c9ffa418c</t>
+  </si>
+  <si>
+    <t>campaign--50f07b8d-3a52-4520-9e5a-1f1eb1e83dea</t>
+  </si>
+  <si>
+    <t>campaign--05ca5326-ae3e-481b-ad1b-07a246c88714</t>
+  </si>
+  <si>
+    <t>campaign--5263d574-5eed-4573-a592-aff86805b317</t>
+  </si>
+  <si>
+    <t>campaign--87b0aff4-b9bb-4edb-b847-a3eb826f374e</t>
+  </si>
+  <si>
+    <t>campaign--4b8f603c-2beb-40c6-9db9-d9823f6e0437</t>
+  </si>
+  <si>
+    <t>campaign--45fafe35-cd3c-444a-a268-46b6a7370a63</t>
+  </si>
+  <si>
+    <t>campaign--4f403031-7401-483e-8eed-57761453596d</t>
+  </si>
+  <si>
+    <t>campaign--8cae9b2b-74d5-4ad1-9fea-e453ecc7f425</t>
+  </si>
+  <si>
+    <t>campaign--040c2b9c-df77-4197-bd95-495a7034b4c1</t>
+  </si>
+  <si>
+    <t>campaign--c7253f1e-c38d-4816-aa0b-fcd9f8dbbc27</t>
+  </si>
+  <si>
+    <t>campaign--d706a65d-715e-48ed-967a-3f237212463e</t>
+  </si>
+  <si>
+    <t>campaign--c3ef8acc-0599-468f-8956-3b91f3f30511</t>
+  </si>
+  <si>
+    <t>campaign--9a4f57ab-6a5e-462f-9d19-5421174ca868</t>
+  </si>
+  <si>
+    <t>campaign--3eab6e53-2449-478f-bf55-dd8afe89a40f</t>
+  </si>
+  <si>
+    <t>campaign--66baf89b-527e-4143-b19f-5621e74abb52</t>
+  </si>
+  <si>
+    <t>campaign--d33f72f9-20ea-4c43-a97d-85d6b536eda0</t>
+  </si>
+  <si>
+    <t>campaign--bebaab35-7783-4d15-b58b-ad2b0da41e64</t>
+  </si>
+  <si>
+    <t>campaign--1d62a197-4c67-4f24-8a41-5890204c4c85</t>
+  </si>
+  <si>
+    <t>campaign--ab5f7d10-2bd1-4ecb-b899-e478c9e2bedd</t>
+  </si>
+  <si>
+    <t>campaign--f9faba2b-2963-4108-975a-2425bcf557ff</t>
+  </si>
+  <si>
+    <t>campaign--d99a23fc-75f2-454e-a013-ef34ceee1c09</t>
+  </si>
+  <si>
+    <t>campaign--f36b045a-dea2-4a27-9a7e-dd439efff501</t>
+  </si>
+  <si>
+    <t>campaign--b93d1b44-3dc6-4818-b008-6748d0af33e9</t>
+  </si>
+  <si>
+    <t>campaign--2152c27e-8fb6-4d17-9545-ece61b0abb3d</t>
+  </si>
+  <si>
+    <t>campaign--da5bc58c-582e-4e35-83a7-a7616031ccf5</t>
+  </si>
+  <si>
+    <t>campaign--25d28320-21cd-47c2-8697-a1311d1d96f7</t>
+  </si>
+  <si>
+    <t>campaign--9232f8d3-d677-410c-9237-89f745f0288d</t>
+  </si>
+  <si>
+    <t>campaign--4b2262cd-ff27-411a-979d-6212f210b82d</t>
+  </si>
+  <si>
+    <t>campaign--9b0bbb08-af99-4a34-b75d-4014845f167d</t>
+  </si>
+  <si>
+    <t>campaign--29d1bd6c-71fb-4d83-862b-cbd6746a86b0</t>
+  </si>
+  <si>
+    <t>campaign--8d7e51bc-58cf-4cf3-891f-e30a45c03432</t>
+  </si>
+  <si>
+    <t>campaign--767abf96-8a3c-4500-9ec1-0d0a1fb32a88</t>
+  </si>
+  <si>
+    <t>campaign--009b3fbb-eb3e-4dd6-a04c-a439731c1854</t>
+  </si>
+  <si>
+    <t>campaign--210bd249-aeb2-4415-8206-e60090b574d1</t>
+  </si>
+  <si>
+    <t>campaign--142059e7-8457-48d4-8716-7aa6b587ab1b</t>
+  </si>
+  <si>
+    <t>campaign--6bb7b821-0e8b-4422-ad1b-764fff0a37e9</t>
+  </si>
+  <si>
+    <t>campaign--a7570eea-ac8a-4869-a00b-367790a7b200</t>
+  </si>
+  <si>
+    <t>campaign--9d9fbae1-5595-4a19-bd8c-7ddd1e2168ec</t>
+  </si>
+  <si>
+    <t>campaign--08748419-8e5d-40dc-aaff-c88e0fff5983</t>
+  </si>
+  <si>
+    <t>campaign--bbc072e6-4905-4dc0-a250-6a9d2dc9d66b</t>
+  </si>
+  <si>
+    <t>campaign--e30cc2e9-1add-4397-876e-067e0ede49ff</t>
+  </si>
+  <si>
+    <t>campaign--d787d857-4e39-4e4a-8103-3f6a4562de40</t>
+  </si>
+  <si>
+    <t>campaign--3c84c661-3fb6-44a6-ab75-7b4399e54925</t>
+  </si>
+  <si>
+    <t>campaign--33b91be6-6f1e-4aa6-ae4b-0099423adbf4</t>
+  </si>
+  <si>
+    <t>campaign--c8a3e3e3-0e8c-491a-b935-3ee30c72989d</t>
+  </si>
+  <si>
+    <t>campaign--9ed45ec0-7d71-4336-ba95-741c9cb1c4ad</t>
+  </si>
+  <si>
+    <t>campaign--c655b524-c56f-484c-b29f-132f99d873d6</t>
+  </si>
+  <si>
+    <t>campaign--256cf231-0b45-47ef-8398-143a78d0dbbf</t>
+  </si>
+  <si>
+    <t>campaign--ee36ce57-051f-4c20-8a09-69d43a2c1de6</t>
+  </si>
+  <si>
+    <t>campaign--b7e2e05a-2a56-49bf-af17-f86e431bece0</t>
+  </si>
+  <si>
+    <t>campaign--5cb4ced0-dedd-48cf-82cb-86724811997b</t>
+  </si>
+  <si>
+    <t>campaign--22649a71-e98f-4dce-a1cc-ed19d9c75cee</t>
+  </si>
+  <si>
+    <t>campaign--b3642930-149d-4b8d-ad0d-64d9d7c22e31</t>
+  </si>
+  <si>
+    <t>campaign--41303f5c-3cb5-48f0-afe0-1b97bae4f54b</t>
+  </si>
+  <si>
+    <t>campaign--2d672617-e7ff-4186-b99a-6c0e59b2069d</t>
+  </si>
+  <si>
+    <t>campaign--065b7c0a-b8f7-4351-9b58-96cb67b5bacb</t>
+  </si>
+  <si>
+    <t>campaign--4929ab8d-cac2-4c99-a2b4-d3012a155cfd</t>
+  </si>
+  <si>
+    <t>campaign--168b36b5-425a-4f37-8a93-b1b55d5a1da7</t>
+  </si>
+  <si>
+    <t>campaign--144ec9d9-444e-43fe-9d0e-3a2394ee8b53</t>
+  </si>
+  <si>
+    <t>campaign--65523a6a-2868-4b87-be5d-4ae9b29134b1</t>
+  </si>
+  <si>
+    <t>campaign--fe715480-d6ee-406e-ac1c-97428a212e65</t>
+  </si>
+  <si>
+    <t>campaign--88abdeab-1534-4131-aa37-73e84eb546ae</t>
+  </si>
+  <si>
+    <t>campaign--1c35fcdc-a6e6-4112-aa74-de7560d1bba3</t>
+  </si>
+  <si>
+    <t>campaign--ee0f26e4-d128-460c-9682-7492020544fb</t>
+  </si>
+  <si>
+    <t>campaign--0e177b96-42bc-49d8-a7a4-87d001a7b97d</t>
+  </si>
+  <si>
+    <t>campaign--09aa5cdd-2b55-4270-9ede-505fce974966</t>
+  </si>
+  <si>
+    <t>campaign--4a354ca0-b612-41ae-a22d-d5c6fb7a028a</t>
+  </si>
+  <si>
+    <t>campaign--01263d76-7a3e-4516-b993-39c444830762</t>
+  </si>
+  <si>
+    <t>campaign--513a8978-9c37-43cb-852f-88eaf99d3f6d</t>
+  </si>
+  <si>
+    <t>campaign--e667332a-68bc-4c3b-8f13-e19634de4d9f</t>
+  </si>
+  <si>
+    <t>campaign--65767352-3a24-4af7-a88e-481714d18d9c</t>
+  </si>
+  <si>
+    <t>campaign--54b232b3-84e1-4abc-a84d-f4855390eec4</t>
+  </si>
+  <si>
+    <t>campaign--2750145d-cbe0-49fc-b789-75f9234b1e96</t>
+  </si>
+  <si>
+    <t>campaign--8f92c47c-028b-41e2-b632-00565ffce2c8</t>
   </si>
   <si>
     <t>campaign</t>
@@ -1654,7 +1654,7 @@
     <t>Публикация В. Путиным манифеста «Об историческом единстве русских и украинцев» (июль 2021), в котором конструируется псевдоисторический миф о том, что современную Украину якобы «создал Ленин», а историческая Россия была искусственно расчленена большевиками. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Тотальная индоктринация российского общества идеями философа И. Ильина (так называемый «белый фашизм») и превращение концепта «Русского мира» в государственную идеологию (рашизм), обосновывающую культурное превосходство и экзистенциальное право метрополии на насилие над соседями. (Citation: «Рашизм: Звір з безодні» 2023)</t>
+    <t>Тотальная индоктринация российского общества идеями философа И. Ильина (так называемый «белый фашизм») и превращение концепта «Русского мира» в государственную идеологию (рашизм), обосновывающую культурное превосходство и экзистенциальное право метрополии на насилие над соседями. (Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
     <t>Для идеологического обоснования захвата и расчленения территорий московские власти инициировали создание нового исторического канона, призванного легитимизировать оккупацию задним числом: «Синопсис, или Краткое собрание от различных летописцев о начале славяно-росийского народа и первоначальных князьях богоспасаемого града Киева» (Citation: Киевский синопсис — Википедия 2026).</t>
@@ -1777,7 +1777,7 @@
     <t>Ликвидация казацких административных единиц и внедрение имперского деления: «Маніфестом 1765 р. Катерина II скасувала козацький устрій... утворила Слобідсько-Українську губернію» (Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Целенаправленные аресты новой украинской интеллигенции, диссидентов и участников протестов (в т.ч. после премьеры «Теней забытых предков») для подавления зарождающегося сопротивления. (Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) - ХПГ 2026)</t>
+    <t>Целенаправленные аресты новой украинской интеллигенции, диссидентов и участников протестов (в т.ч. после премьеры «Теней забытых предков») для подавления зарождающегося сопротивления. (Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026)</t>
   </si>
   <si>
     <t>Принудительный призыв миллионов украинцев в российскую императорскую армию для участия в Первой мировой войне за чужие геополитические интересы империй (Citation: Україна в Першій світовій війні — Вікіпедія 2026).</t>
@@ -1807,7 +1807,7 @@
     <t>Использование регулярной армии для силового подавления [Январского восстания](https://ru.wikipedia.org/wiki/Польское_восстание_(1863—1864)). Российское правительство решает силой «искоренить любые предпосылки к самостоятельности» (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Польское восстание (1863—1864) — Википедия 2026).</t>
   </si>
   <si>
-    <t>Зачистка гражданских сообществ: запрет деятельности украинских просветительских громад на Правобережье после подавления восстания (Citation: Історія України — Вікіпедія 2026).</t>
+    <t>Зачистка гражданских сообществ: запрет деятельности украинских просветительских громад на Правобережье после подавления восстания (Citation: Історія України — Вікіпедія 2026).</t>
   </si>
   <si>
     <t>Применение регулярных войск и танков для подавления масштабных бунтов украинских политзаключенных в системе концлагерей (в частности, в Кенгире). (Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
@@ -1978,538 +1978,538 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--1cdfd3f0-541c-46ef-bbb7-57a694bb8048</t>
-  </si>
-  <si>
-    <t>relationship--d495d79d-34f6-49d9-9a53-82b1b44b932e</t>
-  </si>
-  <si>
-    <t>relationship--c3a1ebf2-6376-41a0-8da9-9559ab938f54</t>
-  </si>
-  <si>
-    <t>relationship--4275b59a-eb45-4ef4-8326-636a04a0ac05</t>
-  </si>
-  <si>
-    <t>relationship--17d269a7-f021-4844-ba97-285385aa5a05</t>
-  </si>
-  <si>
-    <t>relationship--8ff83813-6c82-4ab8-9564-9a97297a517b</t>
-  </si>
-  <si>
-    <t>relationship--e86385b6-78ef-4f5b-b86a-3451ef4fb67a</t>
-  </si>
-  <si>
-    <t>relationship--e7e68ba5-bf1c-4e7b-b4b9-fce42d55812e</t>
-  </si>
-  <si>
-    <t>relationship--4f3a2482-9355-4569-b86a-336d346b028f</t>
-  </si>
-  <si>
-    <t>relationship--d7f85bae-60a9-4a89-962e-bdca90445fd7</t>
-  </si>
-  <si>
-    <t>relationship--f5887284-ec26-4787-96de-d48cb0bdfc1f</t>
-  </si>
-  <si>
-    <t>relationship--11fe4de9-dec3-4e00-b181-ead6b952fe0c</t>
-  </si>
-  <si>
-    <t>relationship--ecf760dd-1173-412c-ad70-81d9e69c6948</t>
-  </si>
-  <si>
-    <t>relationship--1aaa7ddc-9a79-4ed7-85c2-be1a33b6a156</t>
-  </si>
-  <si>
-    <t>relationship--c85a9687-a983-4bbf-ad54-1d226493a38f</t>
-  </si>
-  <si>
-    <t>relationship--fe47f8f9-3736-4608-b9d0-5893ad2c1a20</t>
-  </si>
-  <si>
-    <t>relationship--d5ac8e63-17dd-47cd-81f7-ed9630d5c3ac</t>
-  </si>
-  <si>
-    <t>relationship--3abd1255-9cd6-478b-8fcd-86fa79d7a7d7</t>
-  </si>
-  <si>
-    <t>relationship--b62ca932-d26f-4ee7-ac33-a5a511103bcb</t>
-  </si>
-  <si>
-    <t>relationship--b5699099-cc20-45f1-b5ce-c03e07c2717a</t>
-  </si>
-  <si>
-    <t>relationship--6e2f5430-1f89-48c3-a07b-4a3bf4a5c063</t>
-  </si>
-  <si>
-    <t>relationship--2a69c0df-229f-4cb1-ac1f-3238e18c9baf</t>
-  </si>
-  <si>
-    <t>relationship--a82b5c09-7ce9-44fc-8754-1f4b7c6d6b33</t>
-  </si>
-  <si>
-    <t>relationship--69431d70-4fef-408c-a215-aacb1d4d004d</t>
-  </si>
-  <si>
-    <t>relationship--038a681e-750f-4a0a-b5cb-f0dcef35c08f</t>
-  </si>
-  <si>
-    <t>relationship--1ba8353d-9752-48c5-bf67-b4d140483403</t>
-  </si>
-  <si>
-    <t>relationship--2bc1ff86-36cf-42b9-844b-05f25c23c468</t>
-  </si>
-  <si>
-    <t>relationship--ecc7b820-6f33-43ab-ab90-c682a1be8336</t>
-  </si>
-  <si>
-    <t>relationship--93d90a0a-63ee-4661-8f45-7edc33476ee4</t>
-  </si>
-  <si>
-    <t>relationship--32d85f0d-22c0-41aa-9a04-009cbec9908d</t>
-  </si>
-  <si>
-    <t>relationship--eeaaf694-091d-4a77-a389-8ce77831e4a2</t>
-  </si>
-  <si>
-    <t>relationship--8dbe975d-70a2-4dbf-bc37-047267e4cd6f</t>
-  </si>
-  <si>
-    <t>relationship--b9cae21b-21a4-442b-a5e0-a4177c3e1890</t>
-  </si>
-  <si>
-    <t>relationship--91a138d5-48e6-4841-81f9-f0cfe4e51eb1</t>
-  </si>
-  <si>
-    <t>relationship--5003f1ac-cf34-41b5-b829-f13c40a2e702</t>
-  </si>
-  <si>
-    <t>relationship--88e13235-bafa-4ec6-91bc-c39b564b85da</t>
-  </si>
-  <si>
-    <t>relationship--a0860cd0-758f-4062-be11-c20b22d79471</t>
-  </si>
-  <si>
-    <t>relationship--7ebf24ab-cbe1-436a-afe9-5c16fb858ecf</t>
-  </si>
-  <si>
-    <t>relationship--ea64dad1-2022-47bd-b2a8-b9d96756e301</t>
-  </si>
-  <si>
-    <t>relationship--bb8e0007-4bcb-430c-8611-f195c41eb35a</t>
-  </si>
-  <si>
-    <t>relationship--3e18b328-12eb-4972-9cfe-bd5b4518bba0</t>
-  </si>
-  <si>
-    <t>relationship--46fd9d5f-a9ec-45a6-b954-0759b6c20a85</t>
-  </si>
-  <si>
-    <t>relationship--c24ba103-dbdf-4f6c-9ac9-82676d6029d4</t>
-  </si>
-  <si>
-    <t>relationship--902c7b16-7751-4272-802f-b60a53d1527f</t>
-  </si>
-  <si>
-    <t>relationship--967afc2b-34b6-42e4-b19f-ff55d27f154f</t>
-  </si>
-  <si>
-    <t>relationship--f440f70b-b325-40f3-a514-7388745133c9</t>
-  </si>
-  <si>
-    <t>relationship--633ca8be-925a-4e14-97f8-4994f1ee83e6</t>
-  </si>
-  <si>
-    <t>relationship--780d743b-1356-4890-b4d5-f4b8d0834b72</t>
-  </si>
-  <si>
-    <t>relationship--60f31cc5-629b-4d37-9a05-00641db8c720</t>
-  </si>
-  <si>
-    <t>relationship--cdc12329-4f34-4ad3-8299-fa8f7ce39bc4</t>
-  </si>
-  <si>
-    <t>relationship--d70cd8dc-7476-4c3e-8cfa-ac68ca5d402e</t>
-  </si>
-  <si>
-    <t>relationship--fdc13399-0dc4-42c2-a70c-764aa1293fc0</t>
-  </si>
-  <si>
-    <t>relationship--47e10c42-9a84-45f5-b104-fb5324ebf8c7</t>
-  </si>
-  <si>
-    <t>relationship--a1220d18-cbde-4f2e-9889-a8a2e18f394b</t>
-  </si>
-  <si>
-    <t>relationship--34433281-ac06-431b-bd5f-2213d1e4da91</t>
-  </si>
-  <si>
-    <t>relationship--c5abc27a-dc5a-405b-ae79-769efb4e10e9</t>
-  </si>
-  <si>
-    <t>relationship--0e6f0900-a388-4c25-a11d-378f3cae1130</t>
-  </si>
-  <si>
-    <t>relationship--b5cd62b4-dea8-4068-a0fa-e55b018ea237</t>
-  </si>
-  <si>
-    <t>relationship--9404262b-dc1c-4696-be6c-fad1aa7554c7</t>
-  </si>
-  <si>
-    <t>relationship--276a166b-5637-43b3-aeb9-77c877438848</t>
-  </si>
-  <si>
-    <t>relationship--f2c4cec2-d81e-4dca-a191-e35842b29fd2</t>
-  </si>
-  <si>
-    <t>relationship--87a894f3-208c-452c-862e-a9d9b4c102b2</t>
-  </si>
-  <si>
-    <t>relationship--66bbd274-033a-4f63-a101-1a6ab18b7bd2</t>
-  </si>
-  <si>
-    <t>relationship--c80e0195-3fbb-45e9-b72d-74a151137581</t>
-  </si>
-  <si>
-    <t>relationship--60f800c4-5d5d-4d39-bfb8-ca8aa4638e4b</t>
-  </si>
-  <si>
-    <t>relationship--c0644e3b-a1a9-485d-ad11-82c755d2687b</t>
-  </si>
-  <si>
-    <t>relationship--b58d72ea-68d4-4083-9fa3-a22add914005</t>
-  </si>
-  <si>
-    <t>relationship--eebe6013-7f34-4d64-9822-b18a454d0d10</t>
-  </si>
-  <si>
-    <t>relationship--c0baffae-39e5-4ca8-85e9-bc702c8dcfba</t>
-  </si>
-  <si>
-    <t>relationship--695a9636-88ca-4dd3-b589-942963e4156f</t>
-  </si>
-  <si>
-    <t>relationship--e88bdaef-60f1-4119-964e-01f69f60bb51</t>
-  </si>
-  <si>
-    <t>relationship--b1c69f86-8c7c-4af6-88d3-b19e3c5e2fba</t>
-  </si>
-  <si>
-    <t>relationship--dffb6d3f-25b1-4514-83ae-cc167e523d72</t>
-  </si>
-  <si>
-    <t>relationship--11029e5c-57ac-46ae-8f08-6bca2acbc93e</t>
-  </si>
-  <si>
-    <t>relationship--7ce5ed6e-610b-4ae3-b4be-bbf7dfc9e166</t>
-  </si>
-  <si>
-    <t>relationship--61ae46e5-0b72-42ac-be14-0b1ea28d9423</t>
-  </si>
-  <si>
-    <t>relationship--434436ae-32d9-47bc-b0dd-22bec94579cc</t>
-  </si>
-  <si>
-    <t>relationship--f0488f83-03a7-4d16-9837-511b214e8ec9</t>
-  </si>
-  <si>
-    <t>relationship--50900495-ce2f-4374-8aac-dc046af7894d</t>
-  </si>
-  <si>
-    <t>relationship--56c2e33c-ff02-45cf-997e-e185fb8284d5</t>
-  </si>
-  <si>
-    <t>relationship--cd07c225-e684-4721-87a0-cca930a0df0b</t>
-  </si>
-  <si>
-    <t>relationship--625be509-1c87-4659-96ea-444501a59ebc</t>
-  </si>
-  <si>
-    <t>relationship--f8dcd5fe-c1b4-44ca-b402-373dfc5417ae</t>
-  </si>
-  <si>
-    <t>relationship--4e783095-de36-446d-831c-48bb2b0b1b02</t>
-  </si>
-  <si>
-    <t>relationship--0b74edca-140c-4e19-b47d-aa12c64ed50b</t>
-  </si>
-  <si>
-    <t>relationship--130424c7-894e-4b77-a1b6-7d68a7fbb786</t>
-  </si>
-  <si>
-    <t>relationship--914ac410-74b1-4d63-95d9-6dd9b8c71eca</t>
-  </si>
-  <si>
-    <t>relationship--79050ddd-6640-4e75-b080-e475b0d8975b</t>
-  </si>
-  <si>
-    <t>relationship--ce1bf1e0-dc9f-40bb-a42c-30efd808e3b1</t>
-  </si>
-  <si>
-    <t>relationship--e74de5ee-3f90-4b88-8422-e3ba16f5bdf6</t>
-  </si>
-  <si>
-    <t>relationship--506a1a08-e298-4edf-b8c0-5657fc9e45a7</t>
-  </si>
-  <si>
-    <t>relationship--c07440af-65cd-4234-a5e8-d42c0529a636</t>
-  </si>
-  <si>
-    <t>relationship--210deede-586f-494b-a4f2-7a313d2e5469</t>
-  </si>
-  <si>
-    <t>relationship--aa93a03f-3dd5-4f2e-b15e-db1651483c9b</t>
-  </si>
-  <si>
-    <t>relationship--2051de94-1c9d-4463-98aa-438798808410</t>
-  </si>
-  <si>
-    <t>relationship--51f7a69a-2e4a-4d10-a03d-11900999275c</t>
-  </si>
-  <si>
-    <t>relationship--46546620-8293-410c-ad64-a773cab1f209</t>
-  </si>
-  <si>
-    <t>relationship--ad420e9a-6920-4f5f-925d-523ea56a45e9</t>
-  </si>
-  <si>
-    <t>relationship--7acc1852-4ef0-40ef-b37c-c8f2f9fac56e</t>
-  </si>
-  <si>
-    <t>relationship--758e247d-f39c-46ac-8cef-bdddf76bc9d9</t>
-  </si>
-  <si>
-    <t>relationship--bd03b7b2-94b0-4219-9416-bf901b225690</t>
-  </si>
-  <si>
-    <t>relationship--42fb59ab-4d4c-41bf-926d-4a4bc95bf45c</t>
-  </si>
-  <si>
-    <t>relationship--cacfc402-9f00-4407-a735-ab09e75094a4</t>
-  </si>
-  <si>
-    <t>relationship--87d649c2-7d7e-4f10-b90b-ed6475279488</t>
-  </si>
-  <si>
-    <t>relationship--6f1756f2-1539-43cb-9996-33580fb9e881</t>
-  </si>
-  <si>
-    <t>relationship--153a2818-cc0b-4f35-9cc4-0a2e217995e6</t>
-  </si>
-  <si>
-    <t>relationship--6d8a5ae3-cc8f-40c3-8811-6a3bf10f557e</t>
-  </si>
-  <si>
-    <t>relationship--60a19e2e-729e-4de3-a802-826a2782bb59</t>
-  </si>
-  <si>
-    <t>relationship--ee60bad0-c865-4880-b61d-cd448625421c</t>
-  </si>
-  <si>
-    <t>relationship--c3785308-59c1-4f4e-ba70-1882ca413e0f</t>
-  </si>
-  <si>
-    <t>relationship--475be7dc-0bc6-4a77-a1d9-a878992a9f19</t>
-  </si>
-  <si>
-    <t>relationship--e2206cb5-af2c-49e8-ba91-2f4054442efc</t>
-  </si>
-  <si>
-    <t>relationship--3ef2fca5-cdc7-468a-8d50-f31920d1fee4</t>
-  </si>
-  <si>
-    <t>relationship--646d6b42-11a6-45fd-8542-6d2b46c09280</t>
-  </si>
-  <si>
-    <t>relationship--d4e46347-6d3c-4959-8927-94fd180da28d</t>
-  </si>
-  <si>
-    <t>relationship--32e0e1bf-6626-47ca-a8d0-c2372e080abe</t>
-  </si>
-  <si>
-    <t>relationship--e9e83d95-bffe-40a5-b5ba-aa0ec6dca05f</t>
-  </si>
-  <si>
-    <t>relationship--2951b2fa-de71-492a-9d6f-80e5a9f1d972</t>
-  </si>
-  <si>
-    <t>relationship--2e4721a4-2bde-486a-858e-0db6024a79b1</t>
-  </si>
-  <si>
-    <t>relationship--8b7392e1-b6ba-4cd8-8ca3-e7682da3c3d2</t>
-  </si>
-  <si>
-    <t>relationship--07e1f68a-0a5c-48b2-86a9-e2c9da36c3f6</t>
-  </si>
-  <si>
-    <t>relationship--7a9605db-5367-4646-bddc-3c9c4a4845e3</t>
-  </si>
-  <si>
-    <t>relationship--ad4315eb-e04b-4f42-b869-d0b9c5583b24</t>
-  </si>
-  <si>
-    <t>relationship--f0715d2a-127e-4a91-8afa-eb98e9855e0d</t>
-  </si>
-  <si>
-    <t>relationship--e1ca466a-14e1-4bdc-a9b4-3a82d16573b2</t>
-  </si>
-  <si>
-    <t>relationship--c5b841c9-1fbc-47f5-ac79-d1ee7a652b27</t>
-  </si>
-  <si>
-    <t>relationship--bc9989b6-c70a-4741-aee6-eadad2f7f632</t>
-  </si>
-  <si>
-    <t>relationship--21e5d65f-f85b-4717-b1d3-ba74ff6f0752</t>
-  </si>
-  <si>
-    <t>relationship--b90729d8-7dd4-4708-8496-8418c70e4971</t>
-  </si>
-  <si>
-    <t>relationship--40de2cbe-a25c-482e-9c27-44904b5ecb02</t>
-  </si>
-  <si>
-    <t>relationship--0b2249dd-99ec-4fc6-85bc-fbc274f259e5</t>
-  </si>
-  <si>
-    <t>relationship--6798be57-0f6e-47c8-b8d2-f58d9d149764</t>
-  </si>
-  <si>
-    <t>relationship--ba31761f-897b-4f8f-968a-e59925f8d6fa</t>
-  </si>
-  <si>
-    <t>relationship--91aa061c-0ed0-46c3-abc1-441bcb58d942</t>
-  </si>
-  <si>
-    <t>relationship--9bb17497-5ced-46d4-8e49-19478609770e</t>
-  </si>
-  <si>
-    <t>relationship--f32b2650-c2d7-4d69-8d67-18d8b776f9e8</t>
-  </si>
-  <si>
-    <t>relationship--a7cc2842-95fa-49f7-afc5-e5fba2503da4</t>
-  </si>
-  <si>
-    <t>relationship--f9481fe5-2017-4a84-9bc1-d2e3d995b101</t>
-  </si>
-  <si>
-    <t>relationship--26b8177c-dc31-4935-b650-c23f16e1961a</t>
-  </si>
-  <si>
-    <t>relationship--6844cf1e-add2-4a34-bfe0-3347bafc0a9f</t>
-  </si>
-  <si>
-    <t>relationship--e5b5c765-82fe-4964-aead-5414f522b718</t>
-  </si>
-  <si>
-    <t>relationship--c5af5ee1-c2d4-40cc-b7b6-ae4abaff53b6</t>
-  </si>
-  <si>
-    <t>relationship--a7e785d3-d07b-4e9a-bb4d-ef89ea1a9f5f</t>
-  </si>
-  <si>
-    <t>relationship--ee6d5d17-128a-440b-af31-6ae771a8292d</t>
-  </si>
-  <si>
-    <t>relationship--e9778606-9150-4f14-b119-01e6b1e85502</t>
-  </si>
-  <si>
-    <t>relationship--14a32943-f91e-48c3-8ee9-8ad808687bc1</t>
-  </si>
-  <si>
-    <t>relationship--12cd06be-5eff-42d6-acbb-a89a987992dc</t>
-  </si>
-  <si>
-    <t>relationship--d0ebd6a9-9219-480c-beac-b1fe4801880b</t>
-  </si>
-  <si>
-    <t>relationship--194539c1-2cf8-4240-bcbf-24a8064f6b8b</t>
-  </si>
-  <si>
-    <t>relationship--84f966a1-0e37-4246-ab85-33e30d8439bf</t>
-  </si>
-  <si>
-    <t>relationship--af457245-7456-45e2-b0f5-ffb032c38189</t>
-  </si>
-  <si>
-    <t>relationship--74e76fa7-fa51-41c4-9307-dfcd67a3fff5</t>
-  </si>
-  <si>
-    <t>relationship--b4b9ece4-7fca-4d13-b796-f780283e170c</t>
-  </si>
-  <si>
-    <t>relationship--cb18f39c-b72f-434d-b0ba-2f9469c2e3a9</t>
-  </si>
-  <si>
-    <t>relationship--f1ce89a9-70cd-4b29-945c-3f0e75e93323</t>
-  </si>
-  <si>
-    <t>relationship--94c1394f-ff7d-4eec-b6be-47b1198c0831</t>
-  </si>
-  <si>
-    <t>relationship--4dafb5e2-1c32-48fd-a176-ff2384d8ad4c</t>
-  </si>
-  <si>
-    <t>relationship--75dfd531-7cf6-4fcd-a4a5-bc9b434c5929</t>
-  </si>
-  <si>
-    <t>relationship--005eea82-2f46-4916-8974-19efe9a0a2db</t>
-  </si>
-  <si>
-    <t>relationship--84ad2176-58e3-46ac-b6b8-c13c7003204c</t>
-  </si>
-  <si>
-    <t>relationship--062e6e55-26ed-441a-9fb9-12a14eee63a8</t>
-  </si>
-  <si>
-    <t>relationship--510d4bcb-7a47-493f-ba01-cb1758383dc6</t>
-  </si>
-  <si>
-    <t>relationship--847ad2f4-da00-4510-a9c3-2c433ac3c7af</t>
-  </si>
-  <si>
-    <t>relationship--9b53807b-e85c-4c3e-b896-741f3120f8f8</t>
-  </si>
-  <si>
-    <t>relationship--159acf55-c89e-4b96-ac79-c109e70b6d50</t>
-  </si>
-  <si>
-    <t>relationship--085707c3-a1f3-49ed-96a6-925b6a1df8a3</t>
-  </si>
-  <si>
-    <t>relationship--3a3ad8b1-a0c1-4f39-a1f6-6e363ff281ad</t>
-  </si>
-  <si>
-    <t>relationship--c75a8d56-a880-48b5-b10b-3cca05274dae</t>
-  </si>
-  <si>
-    <t>relationship--10f99ae2-c75c-47da-893b-cfd21283673b</t>
-  </si>
-  <si>
-    <t>relationship--c0ee9936-c01c-454c-b1d4-ea76e1334b76</t>
-  </si>
-  <si>
-    <t>relationship--c51902d5-3216-4c0a-92d4-755ba6e18971</t>
-  </si>
-  <si>
-    <t>relationship--74e4be03-35a9-4b2b-bb31-5ee352fbfe4b</t>
-  </si>
-  <si>
-    <t>relationship--e14de57d-3551-48b7-b7fa-4f0c4f9c8ad6</t>
-  </si>
-  <si>
-    <t>relationship--026a5211-c9ca-427e-b85b-31369a0515b5</t>
-  </si>
-  <si>
-    <t>relationship--0fa3717a-abec-48e7-bf72-de0846014da8</t>
-  </si>
-  <si>
-    <t>relationship--787e5842-1c07-4a27-a240-39e502105e39</t>
-  </si>
-  <si>
-    <t>relationship--9e8b6ddb-22d8-48dd-a284-a1fc3fb4f706</t>
-  </si>
-  <si>
-    <t>relationship--6c36f8a8-3b33-43c5-bce4-9e382648a9fa</t>
+    <t>relationship--441881a9-009f-4fee-a84f-69e4dab72d5c</t>
+  </si>
+  <si>
+    <t>relationship--407bea55-52b8-4513-b233-41b08397fbe1</t>
+  </si>
+  <si>
+    <t>relationship--fc7d4fd2-bc39-4034-9208-2c0620054b59</t>
+  </si>
+  <si>
+    <t>relationship--c558e80f-a8c2-437d-9ade-a0f376fe7e79</t>
+  </si>
+  <si>
+    <t>relationship--9b0fbe4c-0035-4a4b-a8d7-10f2cce3df63</t>
+  </si>
+  <si>
+    <t>relationship--b0694f7a-56c9-4c82-a43a-81af0a4f3bb9</t>
+  </si>
+  <si>
+    <t>relationship--d6d8e6e8-b3e8-46ca-b8ac-642e0a298f3a</t>
+  </si>
+  <si>
+    <t>relationship--4b7a94b8-42f2-49cd-a391-8e8f4e99c93b</t>
+  </si>
+  <si>
+    <t>relationship--961f8807-6832-4dc3-a94c-cb50484d6d4f</t>
+  </si>
+  <si>
+    <t>relationship--57e2158b-8a11-4f88-b7be-e2145f4a8414</t>
+  </si>
+  <si>
+    <t>relationship--7612f698-4e79-4079-bb58-7f9dd7632c89</t>
+  </si>
+  <si>
+    <t>relationship--e50a2e6b-8ff6-45d0-a644-acbe67737007</t>
+  </si>
+  <si>
+    <t>relationship--7e1ed3b9-48bc-440f-9642-35a01ae689d0</t>
+  </si>
+  <si>
+    <t>relationship--b644ebfa-43b6-4469-accc-7b28e9870fdd</t>
+  </si>
+  <si>
+    <t>relationship--a2676ea5-5fb6-4831-bed3-0c639585820a</t>
+  </si>
+  <si>
+    <t>relationship--5b45a746-3a8b-4c4e-a51c-dce4b3364093</t>
+  </si>
+  <si>
+    <t>relationship--7273265b-2eeb-42fc-a808-8abcf8b2b615</t>
+  </si>
+  <si>
+    <t>relationship--3838bffd-1e3e-4887-aa0b-14734c4ec124</t>
+  </si>
+  <si>
+    <t>relationship--e60441a0-fec1-41d5-a7d7-2c45407cac67</t>
+  </si>
+  <si>
+    <t>relationship--5b876a2f-7dd3-4088-bf8f-bd2b1edf7028</t>
+  </si>
+  <si>
+    <t>relationship--3011500f-0a55-413c-8d8c-9d7caf1bfc3b</t>
+  </si>
+  <si>
+    <t>relationship--a138e90f-cfd8-4675-933a-666be4ce0dfd</t>
+  </si>
+  <si>
+    <t>relationship--6321420c-7f8a-4134-ac3a-24cd8e083e27</t>
+  </si>
+  <si>
+    <t>relationship--57fb9d6f-4241-4202-9128-7d51c0385fbc</t>
+  </si>
+  <si>
+    <t>relationship--d9487cc0-d30b-42b0-933f-7daa67a4d305</t>
+  </si>
+  <si>
+    <t>relationship--781440d6-1c17-413a-b7dc-ca8a39850699</t>
+  </si>
+  <si>
+    <t>relationship--4bef0001-77f5-465c-abf3-0d402b77ace8</t>
+  </si>
+  <si>
+    <t>relationship--c7486468-93f2-4754-a50c-16283298d211</t>
+  </si>
+  <si>
+    <t>relationship--f9dd9271-ea96-4ff7-b724-681af78a04e7</t>
+  </si>
+  <si>
+    <t>relationship--dbd9631b-2f68-4370-9b80-c1089da85d5d</t>
+  </si>
+  <si>
+    <t>relationship--a7bdb3f3-64fc-45f0-b3a9-1ba82698426d</t>
+  </si>
+  <si>
+    <t>relationship--00bb7bc3-1a65-49d9-91b3-2450fc194238</t>
+  </si>
+  <si>
+    <t>relationship--2fad882f-decd-4932-a722-ef77eb92437c</t>
+  </si>
+  <si>
+    <t>relationship--b6eb1c53-17ef-4a3b-a873-cf14b724f163</t>
+  </si>
+  <si>
+    <t>relationship--6175913f-69fb-4a98-b3b8-bbaa760f13be</t>
+  </si>
+  <si>
+    <t>relationship--a6368f7a-9b39-4475-84d7-276b0d039abe</t>
+  </si>
+  <si>
+    <t>relationship--60bebbf9-8e9f-4a42-9491-0bc43bbf4d17</t>
+  </si>
+  <si>
+    <t>relationship--f4604e84-a2b2-4f14-91ff-195750ee404e</t>
+  </si>
+  <si>
+    <t>relationship--74e179a8-6abe-4ea7-af21-b6592b6b8890</t>
+  </si>
+  <si>
+    <t>relationship--f5f2de92-6fc7-42bd-b3a8-217af9374e86</t>
+  </si>
+  <si>
+    <t>relationship--83cdbbf8-7a00-4751-9447-3833cb0cacfc</t>
+  </si>
+  <si>
+    <t>relationship--8b91af60-3fee-4992-9550-3e9e979cf5b2</t>
+  </si>
+  <si>
+    <t>relationship--813b29fc-9542-49f0-b7d6-d85caac81af1</t>
+  </si>
+  <si>
+    <t>relationship--b3283625-fa86-4cf5-aa10-0ded7dbcb529</t>
+  </si>
+  <si>
+    <t>relationship--0811f3c0-1321-4781-802f-97b87c5afaa3</t>
+  </si>
+  <si>
+    <t>relationship--1d8d1b56-f5f2-4999-920a-cfb7f9f56594</t>
+  </si>
+  <si>
+    <t>relationship--751638bf-cebc-4abf-860a-a7c1c08da3c0</t>
+  </si>
+  <si>
+    <t>relationship--0f0c0423-83ee-4518-9de1-30d4302248d4</t>
+  </si>
+  <si>
+    <t>relationship--b7b482f4-4d21-44c5-9ce6-c605f47bdde4</t>
+  </si>
+  <si>
+    <t>relationship--917b2898-4587-4f51-a21f-6ff22db57b1e</t>
+  </si>
+  <si>
+    <t>relationship--2825feda-f6cd-42e9-b930-ee0e52daf77a</t>
+  </si>
+  <si>
+    <t>relationship--1ac52934-fe96-4ed7-86fe-e3ee711af5e9</t>
+  </si>
+  <si>
+    <t>relationship--c8737263-bf11-425d-91dd-55d0f549bfcb</t>
+  </si>
+  <si>
+    <t>relationship--07b70a83-2609-4c90-8909-9baa1f31f740</t>
+  </si>
+  <si>
+    <t>relationship--cbbd604a-0e5d-42e5-98c5-d38f4719f206</t>
+  </si>
+  <si>
+    <t>relationship--9136c6c2-0744-4a54-8d09-5f4caecb5cde</t>
+  </si>
+  <si>
+    <t>relationship--2868298e-2343-4014-a92f-2d33a27f0baa</t>
+  </si>
+  <si>
+    <t>relationship--b612f9af-4857-41e8-a956-2eca718f33df</t>
+  </si>
+  <si>
+    <t>relationship--8af6a667-ed82-4d95-9a4d-1607edd3f8a1</t>
+  </si>
+  <si>
+    <t>relationship--f5d1dea0-93dc-4ac9-b4ce-accf7602a45f</t>
+  </si>
+  <si>
+    <t>relationship--3ad90ba9-4488-46e0-a3ec-17bd34367b66</t>
+  </si>
+  <si>
+    <t>relationship--0daf0622-2f9b-4ac7-9aef-053994bded64</t>
+  </si>
+  <si>
+    <t>relationship--9f2d31c8-f2d9-4759-b736-d11d86178f4f</t>
+  </si>
+  <si>
+    <t>relationship--890d8899-b99a-479e-be08-dfb3daca60da</t>
+  </si>
+  <si>
+    <t>relationship--d404fecc-e9e3-404b-b30d-f00b42103b51</t>
+  </si>
+  <si>
+    <t>relationship--07f4735b-2a05-4307-97ad-0ff4415765a0</t>
+  </si>
+  <si>
+    <t>relationship--f1f57dce-f052-4f8e-a2f5-03d7751c58fa</t>
+  </si>
+  <si>
+    <t>relationship--93f11158-e77e-4fa4-bd95-5728ab2a8113</t>
+  </si>
+  <si>
+    <t>relationship--5df2074b-c8a0-4157-b089-75337e602753</t>
+  </si>
+  <si>
+    <t>relationship--f447b07a-9053-4453-aaf8-9c9ea45c45c5</t>
+  </si>
+  <si>
+    <t>relationship--be1b4978-dc1b-4f3c-8662-47ff662c36d6</t>
+  </si>
+  <si>
+    <t>relationship--b5841b12-d9f7-403a-8a50-78a27bfb9637</t>
+  </si>
+  <si>
+    <t>relationship--9afdae70-50ff-49fb-8225-e5b90c0b7a58</t>
+  </si>
+  <si>
+    <t>relationship--9b2ebf13-bbfd-4b19-a9e7-af835e586c97</t>
+  </si>
+  <si>
+    <t>relationship--9780392f-c787-47d4-9a1e-e1c1cf64ac87</t>
+  </si>
+  <si>
+    <t>relationship--e322cdd6-030e-4540-a15c-8d503576b6b9</t>
+  </si>
+  <si>
+    <t>relationship--4c6f4f3e-53d8-4424-af5c-ccd1a3a988b3</t>
+  </si>
+  <si>
+    <t>relationship--5e4dae36-7bf6-4af9-9c2e-d5352b1d6114</t>
+  </si>
+  <si>
+    <t>relationship--8697ca8e-9f1f-4407-925d-a68046c1c2c8</t>
+  </si>
+  <si>
+    <t>relationship--718f9d9c-6317-4a19-b6bd-8d258d006860</t>
+  </si>
+  <si>
+    <t>relationship--da549cde-da67-4e1f-915f-09b238dc04ec</t>
+  </si>
+  <si>
+    <t>relationship--bb8a48ae-aa01-4454-a12e-ed18437b96a8</t>
+  </si>
+  <si>
+    <t>relationship--3dcb809b-592f-4127-ac8c-8de9bc67cec6</t>
+  </si>
+  <si>
+    <t>relationship--4c540dc0-b860-4ac0-b792-993e3cd0aab8</t>
+  </si>
+  <si>
+    <t>relationship--a0826615-5551-4d3d-9f6b-e703807aae14</t>
+  </si>
+  <si>
+    <t>relationship--132041e5-ed6d-4e6c-aade-210229974629</t>
+  </si>
+  <si>
+    <t>relationship--67096cdb-92e3-4272-b1e8-546a902485c0</t>
+  </si>
+  <si>
+    <t>relationship--9e8f67e4-47db-449a-b6f7-a63170c53dc7</t>
+  </si>
+  <si>
+    <t>relationship--46b68874-1f2f-43a7-863c-90e55d9734bd</t>
+  </si>
+  <si>
+    <t>relationship--abb7e5c8-7b40-42fb-90e2-9bc557f5f67f</t>
+  </si>
+  <si>
+    <t>relationship--5c36eb4a-457e-4a46-ab2d-4cc902dda01e</t>
+  </si>
+  <si>
+    <t>relationship--762b0536-840f-46d5-86c2-97e1f4487006</t>
+  </si>
+  <si>
+    <t>relationship--2e12471b-3432-438d-adf1-9e2ab4053a60</t>
+  </si>
+  <si>
+    <t>relationship--2ac7264f-d24c-4c49-9ce7-c27d0b872ab6</t>
+  </si>
+  <si>
+    <t>relationship--5638a773-0cb3-4bbb-b24c-273c8817a364</t>
+  </si>
+  <si>
+    <t>relationship--12960d4d-8926-4ac5-af99-14db2dd9cee8</t>
+  </si>
+  <si>
+    <t>relationship--78e20bd1-2285-4dae-b5b2-a7983a786965</t>
+  </si>
+  <si>
+    <t>relationship--d3e23368-e5d8-4f94-aa52-413d60355cc5</t>
+  </si>
+  <si>
+    <t>relationship--dd230c6e-165b-4696-bdf3-782fd5285305</t>
+  </si>
+  <si>
+    <t>relationship--6d29f5ca-d360-43b4-a3ed-250c47e735ef</t>
+  </si>
+  <si>
+    <t>relationship--b09e905f-2b9c-4372-8c3e-fb2b49a913f5</t>
+  </si>
+  <si>
+    <t>relationship--90c464bb-bc62-4073-85ba-a201cb8b595e</t>
+  </si>
+  <si>
+    <t>relationship--4925bc85-a414-4035-832d-1d33ac5fa39e</t>
+  </si>
+  <si>
+    <t>relationship--4a65083f-36e3-4f13-a4d8-be9b52bf5fc0</t>
+  </si>
+  <si>
+    <t>relationship--304e95a0-6dd4-47ff-934b-4f0d7348b944</t>
+  </si>
+  <si>
+    <t>relationship--d2bdc03f-4476-4881-a541-1588fba0f385</t>
+  </si>
+  <si>
+    <t>relationship--805cc33d-f3ec-4c22-a0c5-5df17b7cbfb9</t>
+  </si>
+  <si>
+    <t>relationship--2abda4bd-6317-4cb6-924f-4e224e08ac1e</t>
+  </si>
+  <si>
+    <t>relationship--b43f380a-aa32-481a-9b24-037eb5b38f99</t>
+  </si>
+  <si>
+    <t>relationship--52675a0d-26a3-4b64-aa61-52a2056ae15c</t>
+  </si>
+  <si>
+    <t>relationship--e510f063-e11d-4317-ba14-1f87a6460b67</t>
+  </si>
+  <si>
+    <t>relationship--55591725-3491-422a-af15-c02e3bc5fb94</t>
+  </si>
+  <si>
+    <t>relationship--2dd7c50e-1819-46ca-9396-51cdb484f7aa</t>
+  </si>
+  <si>
+    <t>relationship--caf85b66-0b95-4d45-8ac1-84b6e4ebf785</t>
+  </si>
+  <si>
+    <t>relationship--288214cb-c73d-4f1e-927b-05a37e2453b0</t>
+  </si>
+  <si>
+    <t>relationship--6aa37a01-a801-45f0-a20a-7751db643b6d</t>
+  </si>
+  <si>
+    <t>relationship--0d1fc3e4-d8b3-4e98-a93d-fd3f90915d36</t>
+  </si>
+  <si>
+    <t>relationship--22623415-7c83-4632-bc56-9caeb313f36c</t>
+  </si>
+  <si>
+    <t>relationship--a9e00f4b-a679-4509-a041-87a902b91e02</t>
+  </si>
+  <si>
+    <t>relationship--3409df06-8599-4282-8ed0-e820a152383b</t>
+  </si>
+  <si>
+    <t>relationship--86bf5a2e-684d-4fd7-9477-de3c9a619a4a</t>
+  </si>
+  <si>
+    <t>relationship--d576c757-7f1f-43e8-bc1b-f8cb73428c43</t>
+  </si>
+  <si>
+    <t>relationship--04e7c1ff-1012-404b-b3ad-e98d8843ffa2</t>
+  </si>
+  <si>
+    <t>relationship--36b34d55-9914-4c75-b7fc-565891a12cc2</t>
+  </si>
+  <si>
+    <t>relationship--cf73e4cc-b8ff-44d1-9c57-3e82caeef378</t>
+  </si>
+  <si>
+    <t>relationship--f585c65b-6983-48f9-a53b-2f7fb7d68f36</t>
+  </si>
+  <si>
+    <t>relationship--5e4f1d76-4a8e-44d9-a9d7-48b44bfc73cb</t>
+  </si>
+  <si>
+    <t>relationship--d14dbb7c-7a09-4a21-8b8d-98a33df3e20d</t>
+  </si>
+  <si>
+    <t>relationship--3210750f-ed45-4edc-ac7e-cc55c042046b</t>
+  </si>
+  <si>
+    <t>relationship--cb4ddc60-71cd-4eac-8132-94f3468d8fe6</t>
+  </si>
+  <si>
+    <t>relationship--8d4cdc65-64eb-4e30-b6e4-a0ec6a72f846</t>
+  </si>
+  <si>
+    <t>relationship--c98e2e93-8511-4dc3-ac72-4b0903d5ccc1</t>
+  </si>
+  <si>
+    <t>relationship--da032b93-902c-49d4-b8cb-9d1553699b74</t>
+  </si>
+  <si>
+    <t>relationship--25889eda-19fb-4ed7-803c-763e1a7a7b26</t>
+  </si>
+  <si>
+    <t>relationship--e84bf0ea-af23-4787-a5a6-a72d0d16f927</t>
+  </si>
+  <si>
+    <t>relationship--7bd172c9-3e04-42c6-9602-d5f2158880c7</t>
+  </si>
+  <si>
+    <t>relationship--3a61fd94-bc71-47e3-a578-ff29a1decaef</t>
+  </si>
+  <si>
+    <t>relationship--0391717a-029b-486d-80c8-08787e305aef</t>
+  </si>
+  <si>
+    <t>relationship--79180226-0bf3-49ee-8c4d-cba479e72236</t>
+  </si>
+  <si>
+    <t>relationship--cdaaeb34-75ee-42a4-9666-f14f74502646</t>
+  </si>
+  <si>
+    <t>relationship--a737ce26-ab27-43ee-9cb0-431b3cdffaf4</t>
+  </si>
+  <si>
+    <t>relationship--21301ffa-1e23-47af-aa68-a3450f199bfa</t>
+  </si>
+  <si>
+    <t>relationship--37682e0d-76fa-487b-8bc0-ae6238b763ee</t>
+  </si>
+  <si>
+    <t>relationship--dfaa1d89-6e3b-4130-b1f8-11cbb0027e79</t>
+  </si>
+  <si>
+    <t>relationship--92c9ff8e-3781-4d02-9662-d6991e6e9d37</t>
+  </si>
+  <si>
+    <t>relationship--be07c2e6-6261-44d2-bc83-e6e04630c204</t>
+  </si>
+  <si>
+    <t>relationship--da8dd423-80b8-41fc-9a3b-89b56d0c70f7</t>
+  </si>
+  <si>
+    <t>relationship--3a5d0d2f-eae1-4c3d-9e82-831b8e45fe96</t>
+  </si>
+  <si>
+    <t>relationship--58da3d5c-9f22-4eb1-8fa0-9e3839a8c93d</t>
+  </si>
+  <si>
+    <t>relationship--57091e5d-9bba-4e83-bbcb-cf292c2ff158</t>
+  </si>
+  <si>
+    <t>relationship--7c88bce6-dd2e-4328-889a-991ca4996a38</t>
+  </si>
+  <si>
+    <t>relationship--aad938fe-6411-4b9c-bea1-46f98ee0686e</t>
+  </si>
+  <si>
+    <t>relationship--48e1bb2c-4c2b-43f9-9f02-6fbe777e68b7</t>
+  </si>
+  <si>
+    <t>relationship--7059bef7-58be-4188-96b9-50a70f8cb9e2</t>
+  </si>
+  <si>
+    <t>relationship--3398d3d3-0037-4f35-bb48-2088250200e2</t>
+  </si>
+  <si>
+    <t>relationship--bc841a9c-6502-4865-91c5-00ba71e7da19</t>
+  </si>
+  <si>
+    <t>relationship--4d058eb2-0689-44d7-9be7-4d3a0bae4ef1</t>
+  </si>
+  <si>
+    <t>relationship--28a8b3b6-c862-456c-b28a-d5333961be22</t>
+  </si>
+  <si>
+    <t>relationship--e8fe1d3d-d0d9-4f86-9c5d-6284b4ec4182</t>
+  </si>
+  <si>
+    <t>relationship--0039a511-54e6-4a57-8a3b-05ab6a13e667</t>
+  </si>
+  <si>
+    <t>relationship--6ec2c473-2c58-49c4-b086-380209da8aef</t>
+  </si>
+  <si>
+    <t>relationship--767b6cc7-96f4-4fbe-aec0-eaf007da9ff5</t>
+  </si>
+  <si>
+    <t>relationship--50bda0bd-4368-43b2-ac17-04d8f46d2a05</t>
+  </si>
+  <si>
+    <t>relationship--22540bd2-e90f-4607-b488-32eb394d3a2d</t>
+  </si>
+  <si>
+    <t>relationship--315f5761-3336-4dbd-9ad9-8445740126ee</t>
+  </si>
+  <si>
+    <t>relationship--6a92abcc-0bfb-407e-b7d1-e532b4036cb3</t>
+  </si>
+  <si>
+    <t>relationship--2caf81eb-8f2e-451c-a2bb-1c894ae2afa9</t>
+  </si>
+  <si>
+    <t>relationship--3fb41385-b9bf-4494-b268-fc212e3f9685</t>
+  </si>
+  <si>
+    <t>relationship--4b5e9197-0b24-4317-9dbb-5d23d1614316</t>
+  </si>
+  <si>
+    <t>relationship--33ca54ea-b2f3-4ffd-a547-e2f67737c98a</t>
+  </si>
+  <si>
+    <t>relationship--7bb0e65b-ac66-4bb1-be32-6b6967e8695e</t>
+  </si>
+  <si>
+    <t>relationship--ce68e232-5128-4316-8b29-26a268892c48</t>
+  </si>
+  <si>
+    <t>relationship--06badfd9-eea9-40b1-98a5-0a5e6d8a1751</t>
+  </si>
+  <si>
+    <t>relationship--76498daa-ef4a-4043-9dd9-2b4b26e1d087</t>
+  </si>
+  <si>
+    <t>relationship--012253ee-0b1b-4c2f-a160-3bf410c37184</t>
+  </si>
+  <si>
+    <t>relationship--ad3bfa98-f3de-4c9e-98dd-e49f5db0d59f</t>
+  </si>
+  <si>
+    <t>relationship--a622899b-6756-442b-80ef-e57635e6056f</t>
+  </si>
+  <si>
+    <t>relationship--13b95caf-63ea-4fc2-abc9-e3569fbb4ae1</t>
   </si>
   <si>
     <t>T0030</t>
@@ -2731,27 +2731,24 @@
     <t>T0077</t>
   </si>
   <si>
-    <t>T0123</t>
+    <t>T0104</t>
+  </si>
+  <si>
+    <t>T0041</t>
+  </si>
+  <si>
+    <t>T0049</t>
+  </si>
+  <si>
+    <t>T0105</t>
+  </si>
+  <si>
+    <t>T0136</t>
   </si>
   <si>
     <t>T0124</t>
   </si>
   <si>
-    <t>T0104</t>
-  </si>
-  <si>
-    <t>T0041</t>
-  </si>
-  <si>
-    <t>T0049</t>
-  </si>
-  <si>
-    <t>T0105</t>
-  </si>
-  <si>
-    <t>T0136</t>
-  </si>
-  <si>
     <t>T0015</t>
   </si>
   <si>
@@ -2983,27 +2980,24 @@
     <t>Карательные экспедиции</t>
   </si>
   <si>
-    <t>Лишение питьевой воды</t>
+    <t>Массовые убийства гражданских</t>
+  </si>
+  <si>
+    <t>Подселение чиновников и военных</t>
+  </si>
+  <si>
+    <t>Принудительная мобилизация</t>
+  </si>
+  <si>
+    <t>Тотальное уничтожение инфраструктуры</t>
+  </si>
+  <si>
+    <t>Кибероперации</t>
   </si>
   <si>
     <t>Лишение электричества и отопления</t>
   </si>
   <si>
-    <t>Массовые убийства гражданских</t>
-  </si>
-  <si>
-    <t>Подселение чиновников и военных</t>
-  </si>
-  <si>
-    <t>Принудительная мобилизация</t>
-  </si>
-  <si>
-    <t>Тотальное уничтожение инфраструктуры</t>
-  </si>
-  <si>
-    <t>Кибероперации</t>
-  </si>
-  <si>
     <t>Подкуп элит</t>
   </si>
   <si>
@@ -3016,256 +3010,253 @@
     <t>Спонсирование внутреннего экстремизма и радикалов</t>
   </si>
   <si>
-    <t>attack-pattern--6e7e75e1-0db0-4d82-b49a-0d53a8377673</t>
-  </si>
-  <si>
-    <t>attack-pattern--d353ed6f-c3e5-4632-9f6d-9fd389c16231</t>
-  </si>
-  <si>
-    <t>attack-pattern--ee5bb8e1-fee2-4e46-a264-77b6fca28401</t>
-  </si>
-  <si>
-    <t>attack-pattern--4026908a-0f17-4fb5-a50a-e8c8a747c58e</t>
-  </si>
-  <si>
-    <t>attack-pattern--fdf6886c-4a4e-4067-9cac-a018da349cc1</t>
-  </si>
-  <si>
-    <t>attack-pattern--7a4074d0-24b3-4fd5-b768-e156c78db7db</t>
-  </si>
-  <si>
-    <t>attack-pattern--65fb49b6-79ef-40ce-89c4-ff952b19011b</t>
-  </si>
-  <si>
-    <t>attack-pattern--23b6daf2-9f20-46eb-8671-920d60e4176b</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae6f538f-2867-497c-b74a-c0bb0726a49f</t>
-  </si>
-  <si>
-    <t>attack-pattern--4202af9f-2d34-4e0c-a33f-e3bab246965b</t>
-  </si>
-  <si>
-    <t>attack-pattern--0baf716e-a678-48a1-a89f-01fae4b785c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--bd51216b-c2ed-44fe-947f-259544f66886</t>
-  </si>
-  <si>
-    <t>attack-pattern--317902b3-2928-42ce-aab1-77bf6464d029</t>
-  </si>
-  <si>
-    <t>attack-pattern--14882788-8da6-4e89-8b0a-369f6b46aac1</t>
-  </si>
-  <si>
-    <t>attack-pattern--da34d411-6ba3-4e4d-a8c3-a9fd1ff0adcd</t>
-  </si>
-  <si>
-    <t>attack-pattern--5dcc3a96-1d9f-421c-ac46-9c396f68ea34</t>
-  </si>
-  <si>
-    <t>attack-pattern--e2637ab4-aa90-4f26-9f0c-643026911644</t>
-  </si>
-  <si>
-    <t>attack-pattern--42950ff4-99e9-43e0-9c84-fca26222c4c1</t>
-  </si>
-  <si>
-    <t>attack-pattern--99acd4f0-c847-453e-96c6-f1024d62f2e9</t>
-  </si>
-  <si>
-    <t>attack-pattern--be992ef6-3881-4236-9c72-93ad885fecf9</t>
-  </si>
-  <si>
-    <t>attack-pattern--9452fecd-32ce-4960-851a-e7805c6edbc3</t>
-  </si>
-  <si>
-    <t>attack-pattern--c5770ebc-aaeb-40b0-af29-fd3d63ca97a2</t>
-  </si>
-  <si>
-    <t>attack-pattern--5eee076f-a070-4da8-b6e4-9a8f68bb602e</t>
-  </si>
-  <si>
-    <t>attack-pattern--a15399bd-925c-44e3-a75c-cb1b53d8c074</t>
-  </si>
-  <si>
-    <t>attack-pattern--44ad371d-f921-4b4d-9334-2dce2da4aaaf</t>
-  </si>
-  <si>
-    <t>attack-pattern--f73d8a36-0521-4724-927a-92af6f36e696</t>
-  </si>
-  <si>
-    <t>attack-pattern--bfef93ab-ace2-46de-ba41-96702238ef93</t>
-  </si>
-  <si>
-    <t>attack-pattern--9fbabf63-9dce-4492-b220-0d1e461df010</t>
-  </si>
-  <si>
-    <t>attack-pattern--e28fa69e-65b0-418e-a24e-461b222259e6</t>
-  </si>
-  <si>
-    <t>attack-pattern--e9e41389-66eb-43b4-9cdf-f5b0ac2dc057</t>
-  </si>
-  <si>
-    <t>attack-pattern--17d9ac61-a2aa-417e-b5ea-4de8b5986439</t>
-  </si>
-  <si>
-    <t>attack-pattern--d2d6833f-93e2-47c4-9ed5-6cc66a10e99c</t>
-  </si>
-  <si>
-    <t>attack-pattern--6a1c7124-cdb4-497c-9174-c8b73fd00307</t>
-  </si>
-  <si>
-    <t>attack-pattern--07476ac0-71a4-44ac-8a17-b01278057e19</t>
-  </si>
-  <si>
-    <t>attack-pattern--22fb0501-e69d-4266-9e11-6d271bcd7c5d</t>
-  </si>
-  <si>
-    <t>attack-pattern--57c19e77-979f-4af9-8f76-b8842e0eccc9</t>
-  </si>
-  <si>
-    <t>attack-pattern--d175845f-f2f1-4e62-b02f-758d61f90f48</t>
-  </si>
-  <si>
-    <t>attack-pattern--cb4b534f-b8a9-4926-baa3-b078694b8519</t>
-  </si>
-  <si>
-    <t>attack-pattern--e56f5dcd-3983-435f-93da-a93a60ca1e47</t>
-  </si>
-  <si>
-    <t>attack-pattern--ccb1c983-8262-4840-a946-316971a55893</t>
-  </si>
-  <si>
-    <t>attack-pattern--074400fc-9c8c-409c-96e6-91b0f42eb110</t>
-  </si>
-  <si>
-    <t>attack-pattern--f220f5b7-f3f0-4fef-86af-ade60ec7305a</t>
-  </si>
-  <si>
-    <t>attack-pattern--c1901e96-2107-4e8d-a22a-2f0abf79e67c</t>
-  </si>
-  <si>
-    <t>attack-pattern--3886a528-955b-4e5e-a31a-a297076adfd2</t>
-  </si>
-  <si>
-    <t>attack-pattern--792c75be-6b88-40e7-8dbb-df0dd4841993</t>
-  </si>
-  <si>
-    <t>attack-pattern--147076ae-f3b0-4e8d-a3f2-6018cfab8120</t>
-  </si>
-  <si>
-    <t>attack-pattern--07b87f7d-539f-40f7-be97-6078fae34324</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2e968ce-b955-4609-885e-9a94a97d9bc9</t>
-  </si>
-  <si>
-    <t>attack-pattern--dff3ad94-5c20-4925-a7b9-a62b37efeb45</t>
-  </si>
-  <si>
-    <t>attack-pattern--1c8963ba-44f5-4619-bfbe-d74b9db41464</t>
-  </si>
-  <si>
-    <t>attack-pattern--103f63dc-a6d5-4ba1-abc7-0184491b5271</t>
-  </si>
-  <si>
-    <t>attack-pattern--dbed37eb-3e38-48b6-98f6-1a9aac1076d5</t>
-  </si>
-  <si>
-    <t>attack-pattern--170785ac-cac2-48cd-8acf-e8c5bc941503</t>
-  </si>
-  <si>
-    <t>attack-pattern--a211ed94-8a7b-4e48-b03d-c43ec7c2c14b</t>
-  </si>
-  <si>
-    <t>attack-pattern--aac436e7-dadf-43f1-8cda-44882c19612a</t>
-  </si>
-  <si>
-    <t>attack-pattern--b3baffe4-a060-4523-b819-913ba26178c2</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2671755-9e9d-4f4b-a531-cb8e290024f8</t>
-  </si>
-  <si>
-    <t>attack-pattern--3e70f8b3-4681-42f1-8a6b-a1baece08ac6</t>
-  </si>
-  <si>
-    <t>attack-pattern--e2267790-f642-490c-9da2-d96e13dff98b</t>
-  </si>
-  <si>
-    <t>attack-pattern--6ad16641-500b-4819-acbe-66e0bbd9553e</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1eb4ee9-8cf3-491b-bf9e-62b29e6ee4bf</t>
-  </si>
-  <si>
-    <t>attack-pattern--919d30d7-6892-423a-a8bb-8fbe7d66e8ff</t>
-  </si>
-  <si>
-    <t>attack-pattern--9de68747-f426-4db4-b51f-b53282321fe1</t>
-  </si>
-  <si>
-    <t>attack-pattern--f3d8f555-581e-4ed0-add2-4dddb1b28f8a</t>
-  </si>
-  <si>
-    <t>attack-pattern--d21a2253-ea3b-42b9-9bd2-5d602c76bed0</t>
-  </si>
-  <si>
-    <t>attack-pattern--6b474b4b-ff3a-40f7-8aa2-f96235b52ef8</t>
-  </si>
-  <si>
-    <t>attack-pattern--70479515-9b93-4ec1-ba31-632cd23e4574</t>
-  </si>
-  <si>
-    <t>attack-pattern--86ca32e1-923d-4a0c-8dab-76cc249df7bb</t>
-  </si>
-  <si>
-    <t>attack-pattern--c75bc202-aba2-48a6-add2-b139f4c14017</t>
-  </si>
-  <si>
-    <t>attack-pattern--69f3396d-7553-450c-9443-80126d293837</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d6a8a93-d876-4698-a4cd-c7cfcc14197c</t>
-  </si>
-  <si>
-    <t>attack-pattern--2534c0c4-3a14-4ef3-9ec3-e1ce52e4c596</t>
-  </si>
-  <si>
-    <t>attack-pattern--9164d0d6-f747-40be-b2ab-c64baa5cd6e8</t>
-  </si>
-  <si>
-    <t>attack-pattern--3a06b121-ff1a-4e8d-b37a-ef2084f74cd7</t>
-  </si>
-  <si>
-    <t>attack-pattern--ffd8d85d-efff-4145-a4f3-d46d5c558bb8</t>
-  </si>
-  <si>
-    <t>attack-pattern--ad1006c7-69a5-4235-9644-77a665afffaf</t>
-  </si>
-  <si>
-    <t>attack-pattern--e3fb11b9-94a3-4399-b897-c0f602fcd3d7</t>
-  </si>
-  <si>
-    <t>attack-pattern--e5f42ecf-13cd-4984-af2e-f1a5fbd73b22</t>
-  </si>
-  <si>
-    <t>attack-pattern--63ec97cd-e76f-4242-855c-65e2ce960aff</t>
-  </si>
-  <si>
-    <t>attack-pattern--5bd16692-e9de-4fb0-aaf2-203c5654c3be</t>
-  </si>
-  <si>
-    <t>attack-pattern--90055235-0572-4542-b108-29375451d387</t>
-  </si>
-  <si>
-    <t>attack-pattern--ffef9fde-b807-4346-848c-fd66677fc503</t>
-  </si>
-  <si>
-    <t>attack-pattern--2595f410-b103-4103-99dc-7cc1b896315b</t>
-  </si>
-  <si>
-    <t>attack-pattern--08d8cad1-e1cc-4796-a3a1-6d4762590e75</t>
+    <t>attack-pattern--9f3fdc90-cca7-485e-b78b-eefe2753dc95</t>
+  </si>
+  <si>
+    <t>attack-pattern--e236beed-9135-4388-92da-004919b6e1c8</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7c2ef21-3827-4a2e-91f2-e658ba4e6fa5</t>
+  </si>
+  <si>
+    <t>attack-pattern--7b14e908-93a7-43b6-a8d4-ef9881f7b070</t>
+  </si>
+  <si>
+    <t>attack-pattern--cc247977-b994-472a-a92f-a82cf26cbbe2</t>
+  </si>
+  <si>
+    <t>attack-pattern--ff63c265-0310-4574-82ad-3dc8a99c3488</t>
+  </si>
+  <si>
+    <t>attack-pattern--eb3aa6f0-74f5-4e0a-861e-a2c82ffc0798</t>
+  </si>
+  <si>
+    <t>attack-pattern--5a357495-f376-4a5e-a3f7-0066f362328b</t>
+  </si>
+  <si>
+    <t>attack-pattern--af2dabb3-15cb-4c7a-87ae-6953c2686480</t>
+  </si>
+  <si>
+    <t>attack-pattern--c0383ad6-d98f-4336-963f-37398fe3c9a3</t>
+  </si>
+  <si>
+    <t>attack-pattern--e27e053b-85f7-4f3b-9caa-70ba91cc3a44</t>
+  </si>
+  <si>
+    <t>attack-pattern--57e6c6c4-a591-4903-9985-4d284b4eaf64</t>
+  </si>
+  <si>
+    <t>attack-pattern--d5f1412a-2885-40f5-a71f-f39ad84178c0</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7e4beb6-0682-47aa-acf9-03c1ca5d415a</t>
+  </si>
+  <si>
+    <t>attack-pattern--a0d79fcb-de29-4b04-ab91-078640aa7942</t>
+  </si>
+  <si>
+    <t>attack-pattern--9336c78d-5a9f-4d5b-b674-0e344c73b809</t>
+  </si>
+  <si>
+    <t>attack-pattern--48d4b99e-6c35-41df-9bca-54744d0eb5bd</t>
+  </si>
+  <si>
+    <t>attack-pattern--9dfb75d7-34d0-4b59-a463-4300cf5493a6</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea0a04c0-9769-475c-8c33-4f5c369808b9</t>
+  </si>
+  <si>
+    <t>attack-pattern--ae2812e0-2ac6-48c0-aaf1-8a649e218bd7</t>
+  </si>
+  <si>
+    <t>attack-pattern--c9e6ccf7-a8ae-4556-bede-76dbb5670f16</t>
+  </si>
+  <si>
+    <t>attack-pattern--952c089f-d14e-4e35-a31d-95ebc0496362</t>
+  </si>
+  <si>
+    <t>attack-pattern--49a44b3e-87a2-4cf6-a4f0-fd58d82d63ea</t>
+  </si>
+  <si>
+    <t>attack-pattern--f09d31c3-1ef9-4f13-9587-c5645517cfe0</t>
+  </si>
+  <si>
+    <t>attack-pattern--55fed0eb-37e3-4ce6-b9a3-a924f2578368</t>
+  </si>
+  <si>
+    <t>attack-pattern--61b8a224-eb09-443f-822a-8009280fcdc5</t>
+  </si>
+  <si>
+    <t>attack-pattern--a45e2a90-8a79-47a9-ad3e-2c1f33b089f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--53cb5b45-acd8-45ad-8e44-a1db86632a2d</t>
+  </si>
+  <si>
+    <t>attack-pattern--ba2aee33-7edc-416e-921b-2aece2032428</t>
+  </si>
+  <si>
+    <t>attack-pattern--91f8404d-6987-41b7-b7a9-df79fe77afe5</t>
+  </si>
+  <si>
+    <t>attack-pattern--3fb03caa-0900-45aa-b166-8e7282b52a60</t>
+  </si>
+  <si>
+    <t>attack-pattern--e5c43fec-3847-47e6-aad1-56f38d6c0723</t>
+  </si>
+  <si>
+    <t>attack-pattern--e99f7a3a-594c-4175-9d82-5b5c75db890d</t>
+  </si>
+  <si>
+    <t>attack-pattern--46228d06-6a20-4748-9cdb-8155982fdceb</t>
+  </si>
+  <si>
+    <t>attack-pattern--a46ec1d7-5bdd-4e55-a04f-a6f259b5e12e</t>
+  </si>
+  <si>
+    <t>attack-pattern--5111de41-6dbf-4ce2-ab89-beaa810e1cf7</t>
+  </si>
+  <si>
+    <t>attack-pattern--bf051bf8-cc3b-4bed-921d-d093e17d11b6</t>
+  </si>
+  <si>
+    <t>attack-pattern--c3384966-9c95-434d-bcf2-3be46383e578</t>
+  </si>
+  <si>
+    <t>attack-pattern--262ba99b-f4f8-41cb-b5cd-5b08f6bb8bd3</t>
+  </si>
+  <si>
+    <t>attack-pattern--896791e3-5b2d-426b-a067-e6e79c492c4a</t>
+  </si>
+  <si>
+    <t>attack-pattern--8209784f-cde9-413a-bc2b-2ad5da2f0bba</t>
+  </si>
+  <si>
+    <t>attack-pattern--e0246bcc-9820-45fa-bfea-862bed9dd573</t>
+  </si>
+  <si>
+    <t>attack-pattern--069c328b-ad93-472b-bf2f-08db21002615</t>
+  </si>
+  <si>
+    <t>attack-pattern--8056b7be-c173-4a65-8710-6ea8194a3741</t>
+  </si>
+  <si>
+    <t>attack-pattern--a4deb5e5-f8da-46dc-91ed-17f22df9d9f1</t>
+  </si>
+  <si>
+    <t>attack-pattern--024d1d49-921a-479d-b8c4-90d4f7f94d35</t>
+  </si>
+  <si>
+    <t>attack-pattern--cd8bb5ae-5aff-4b70-8d6f-31ac36eadbde</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d84c262-0100-44cc-9fd7-a698ee3776dc</t>
+  </si>
+  <si>
+    <t>attack-pattern--22a5b731-e091-4444-bc84-5e60eba2a2bb</t>
+  </si>
+  <si>
+    <t>attack-pattern--7aa1b36a-86ff-4f8b-b158-ee648a9ef31a</t>
+  </si>
+  <si>
+    <t>attack-pattern--f98477fa-369f-4d0d-8064-a2180d75714c</t>
+  </si>
+  <si>
+    <t>attack-pattern--0ef67418-f9c5-4e0f-9e36-0747bc8f210c</t>
+  </si>
+  <si>
+    <t>attack-pattern--cffadcf5-6a6b-4e1f-8b87-85adf27c9f9c</t>
+  </si>
+  <si>
+    <t>attack-pattern--3cb79497-d461-4586-860f-71737528f775</t>
+  </si>
+  <si>
+    <t>attack-pattern--50d263b4-e04e-4942-a7d4-026ee3dd7f03</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a9a83e5-2d69-4928-8efc-9a84de5d0373</t>
+  </si>
+  <si>
+    <t>attack-pattern--a903cd8c-c914-4408-ae0a-c915df961d3b</t>
+  </si>
+  <si>
+    <t>attack-pattern--09a18447-c729-43f1-8ceb-2d48687eac97</t>
+  </si>
+  <si>
+    <t>attack-pattern--f3ce3c11-3e28-4d6e-b4f2-426f987041f8</t>
+  </si>
+  <si>
+    <t>attack-pattern--ecc01b5f-5093-4549-972c-ff73588df011</t>
+  </si>
+  <si>
+    <t>attack-pattern--a83e27a1-55ce-4327-8003-590d22630ae9</t>
+  </si>
+  <si>
+    <t>attack-pattern--ecf3feb7-137c-4f53-9e1c-2e1181947f3c</t>
+  </si>
+  <si>
+    <t>attack-pattern--65b7c386-1376-4ee1-a83e-d9a77c643142</t>
+  </si>
+  <si>
+    <t>attack-pattern--816d2931-33e2-4dde-a98f-1bdcd38931b3</t>
+  </si>
+  <si>
+    <t>attack-pattern--4de692cb-753a-45d3-ac80-34255162bcaf</t>
+  </si>
+  <si>
+    <t>attack-pattern--25092de4-9a0b-4dbc-8b23-6d1a000a5f42</t>
+  </si>
+  <si>
+    <t>attack-pattern--972bf47e-c0f5-4dae-97cd-9451c7bc4603</t>
+  </si>
+  <si>
+    <t>attack-pattern--1d927ea8-3d2b-413f-8459-9786ccf5b725</t>
+  </si>
+  <si>
+    <t>attack-pattern--404cbad7-d4cf-4dfa-a2d5-f7e771b4c804</t>
+  </si>
+  <si>
+    <t>attack-pattern--7d791de3-2e04-431d-ba88-dbdde6add3f4</t>
+  </si>
+  <si>
+    <t>attack-pattern--b66ac526-6f64-4e32-9922-2d68e51631b1</t>
+  </si>
+  <si>
+    <t>attack-pattern--20693395-073f-458c-b2a1-7be782d97354</t>
+  </si>
+  <si>
+    <t>attack-pattern--281579e8-e28f-4e62-9971-a18fab84e0af</t>
+  </si>
+  <si>
+    <t>attack-pattern--4a7ebe15-e0c5-424d-8581-ba13a207baf0</t>
+  </si>
+  <si>
+    <t>attack-pattern--69a3d9fe-d220-4cc1-ac9e-0eb3c8da7a10</t>
+  </si>
+  <si>
+    <t>attack-pattern--d7da24f0-8fe5-4136-85ff-12c3f911587f</t>
+  </si>
+  <si>
+    <t>attack-pattern--154481f0-8068-45c2-9e46-31ae7dc6853a</t>
+  </si>
+  <si>
+    <t>attack-pattern--dba55821-e44f-42a3-b519-056650fee6a3</t>
+  </si>
+  <si>
+    <t>attack-pattern--85ac27b3-8e0a-481a-8960-03146d6387b9</t>
+  </si>
+  <si>
+    <t>attack-pattern--d080b90a-f3a6-4503-8b13-e422b7a47265</t>
+  </si>
+  <si>
+    <t>attack-pattern--e64e3ca3-6b6e-482c-bdb2-3d3a64794457</t>
+  </si>
+  <si>
+    <t>attack-pattern--953bf0ac-d5ae-4b33-a124-4c223463b0fa</t>
+  </si>
+  <si>
+    <t>attack-pattern--f4ee8a5d-0fb9-42f8-8046-04b5e02d18be</t>
   </si>
   <si>
     <t>technique</t>
@@ -3328,10 +3319,10 @@
     <t>Использование дешевой рабочей силы местного населения на шахтах и металлургических заводах в условиях тяжелейшей эксплуатации (Citation: Історія Донецької області — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Открытый ядерный шантаж со стороны руководства РФ и силовой захват войсками Чернобыльской и Запорожской АЭС для создания глобальной угрозы радиационной катастрофы. (Citation: Рашизм: Звір з безодні 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026)</t>
+    <t>Открытый ядерный шантаж со стороны руководства РФ и силовой захват войсками Чернобыльской и Запорожской АЭС для создания глобальной угрозы радиационной катастрофы. (Citation: Рашизм: Звір з безодні 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
   </si>
   <si>
     <t>Вслед за установлением контроля над митрополией последовал постепенный запрет на использование киевского извода церковнославянского языка и украинского произношения в богослужениях и книгах, что заложило фундамент для полных языковых запретов XVIII века (Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026).</t>
@@ -3355,10 +3346,10 @@
     <t>Запрет белогвардейским командованием печати и распространения украинских книг на захваченных территориях. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
   </si>
   <si>
-    <t>Масштабное разграбление экономических ресурсов: вывоз дорогостоящего промышленного оборудования (в т.ч. стали с завода «Азовсталь»), незаконная добыча полезных ископаемых и кража более 15 млн тонн украинского зерна. (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>Систематическое разграбление историко-культурного наследия, археологические кражи и массовый вывоз фондов украинских музеев с оккупированных территорий в РФ. (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
+    <t>Масштабное разграбление экономических ресурсов: вывоз дорогостоящего промышленного оборудования (в т.ч. стали с завода «Азовсталь»), незаконная добыча полезных ископаемых и кража более 15 млн тонн украинского зерна. (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>Систематическое разграбление историко-культурного наследия, археологические кражи и массовый вывоз фондов украинских музеев с оккупированных территорий в РФ. (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>Искусственное изменение демографического состава населения на оккупированных территориях (например, в разрушенном Мариуполе) путем стимулирования переезда граждан РФ и массовой скупки ими жилья на фоне выдавливания коренных жителей.</t>
@@ -3436,15 +3427,9 @@
     <t>Целенаправленный вывоз интеллектуального и исторического наследия. Имперские войска не просто мародерствовали, они изымали уникальные документы: «Меншиков успел вывезти... гетманский архив, библиотеку Мазепы» (Citation: Мазепа 2007)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>Спровоцированные каскадные отключения водоснабжения из-за обесточивания насосных станций, а также прямые ракетные удары по гидротехническим сооружениям (например, удар по дамбе Карачуновского водохранилища в Кривом Роге в сентябре 2022 года). (Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026)</t>
-  </si>
-  <si>
     <t>Передача казацких полков под прямое командование имперских офицеров и чиновников вне казацкой иерархии (Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>Систематическое нанесение массированных ударов крылатыми ракетами и дронами-камикадзе (Shahed) по объектам генерации (Змиевская ТЭЦ, Харьковская ТЭЦ-5, Трипольская ТЭС, ДнепроГЭС) и трансформаторным подстанциям для создания блэкаутов. (Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026)</t>
-  </si>
-  <si>
     <t>Установление полностью подконтрольного Москве правительства после уничтожения столицы. Навязывание лояльного гетмана Ивана Скоропадского для обеспечения бесперебойной эксплуатации Гетманщины (Citation: Война и наказание: Как Россия уничтожала Украину 2023)(Citation: Мазепа 2007).</t>
   </si>
   <si>
@@ -3463,7 +3448,7 @@
     <t>Использование подконтрольной спецслужбам хакерской группировки Fancy Bear для взлома программного обеспечения украинских артиллеристов (через заражение приложения Ярослава Шерстюка) с целью получения геолокационных данных и уничтожения артиллерии ВСУ. (Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>Целенаправленные кибератаки российских спецслужб на распределительные подстанции украинской энергосети зимой 2015 и 2016 годов с целью массового отключения электроэнергии для гражданского населения. (Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®) (Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®)</t>
+    <t>Целенаправленные кибератаки российских спецслужб на распределительные подстанции украинской энергосети зимой 2015 и 2016 годов с целью массового отключения электроэнергии для гражданского населения. (Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023) (Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023)</t>
   </si>
   <si>
     <t>Использование черносотенцев для организации массовых и кровавых еврейских погромов и расправ над оппозицией при попустительстве или прямой поддержке полиции (Citation: Чорносотенці — Вікіпедія 2026).</t>
@@ -3508,487 +3493,481 @@
     <t>Введение обязанности предоставлять полные финансовые отчеты о доходах региона под надзор центра (Citation: Решетилівські статті — Вікіпедія 2026)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>relationship--63088be3-9992-4339-b356-74d379e0480b</t>
-  </si>
-  <si>
-    <t>relationship--c96d45d4-6ee4-4bd2-9fa7-bae64cff0d60</t>
-  </si>
-  <si>
-    <t>relationship--e7871979-1acd-4938-8ac8-6441b97719ac</t>
-  </si>
-  <si>
-    <t>relationship--ef999523-9ce8-43d6-b7db-cb570443b3e6</t>
-  </si>
-  <si>
-    <t>relationship--b341f4db-a2f3-4382-9649-12fcf589b6ce</t>
-  </si>
-  <si>
-    <t>relationship--f43a9216-e1c8-4a79-9cc7-89e4d2786b30</t>
-  </si>
-  <si>
-    <t>relationship--11d2f274-ec09-457c-994c-2d9b54736451</t>
-  </si>
-  <si>
-    <t>relationship--995a8bbd-693e-4d85-a943-12c1ee1f344f</t>
-  </si>
-  <si>
-    <t>relationship--0e430b62-9cbb-445b-a9b5-345cd51c4435</t>
-  </si>
-  <si>
-    <t>relationship--388fd3c2-c9e1-4eae-8e3a-7144ee1315f5</t>
-  </si>
-  <si>
-    <t>relationship--bd4255a4-6d37-4bce-870f-254b6a9c6a38</t>
-  </si>
-  <si>
-    <t>relationship--237188bc-0d7b-4916-848c-eedd15d0d13f</t>
-  </si>
-  <si>
-    <t>relationship--4b693b15-3411-45f6-8b2d-1acf496ed365</t>
-  </si>
-  <si>
-    <t>relationship--1c65b0f8-bd38-4521-b905-db68c454ea05</t>
-  </si>
-  <si>
-    <t>relationship--5b890b35-9574-4db1-8214-71791d6cbe82</t>
-  </si>
-  <si>
-    <t>relationship--b8029f34-a789-44ad-b6df-701e9584fffe</t>
-  </si>
-  <si>
-    <t>relationship--45e43ce6-7a07-4593-aac7-27eac5eb7a7b</t>
-  </si>
-  <si>
-    <t>relationship--f08bdd1a-161d-457e-9a10-89a125247b13</t>
-  </si>
-  <si>
-    <t>relationship--8da366a5-d4ca-4da8-8bbf-9ba46340bd3a</t>
-  </si>
-  <si>
-    <t>relationship--de1ec585-2dca-4edf-bfff-ee2443da7ac5</t>
-  </si>
-  <si>
-    <t>relationship--95488b89-3b4d-4362-9303-b1d86329c67f</t>
-  </si>
-  <si>
-    <t>relationship--2162ac28-bba2-4247-841e-404c1eb41b0d</t>
-  </si>
-  <si>
-    <t>relationship--d0346190-f43d-4e5a-aabb-b8c721cb1338</t>
-  </si>
-  <si>
-    <t>relationship--ae135b47-6460-4193-bbf8-c17b5c2a8a4a</t>
-  </si>
-  <si>
-    <t>relationship--7361f1f2-9c2c-45a4-bc66-c3b5bb904ae9</t>
-  </si>
-  <si>
-    <t>relationship--9ca8773a-be9c-414e-83cc-cb20c85bcc83</t>
-  </si>
-  <si>
-    <t>relationship--dd6d270b-9719-4d07-b6f3-6af0c72d091f</t>
-  </si>
-  <si>
-    <t>relationship--aa27928a-b789-4113-b052-ddca4bc4ea57</t>
-  </si>
-  <si>
-    <t>relationship--192e97c6-7eea-4a12-84e1-d42b65015cfc</t>
-  </si>
-  <si>
-    <t>relationship--a83c1c5f-5a4c-4c43-b64e-addb69958502</t>
-  </si>
-  <si>
-    <t>relationship--3360270d-f359-46b3-8b59-643070412efe</t>
-  </si>
-  <si>
-    <t>relationship--d5d8a37a-6489-46ab-ba82-24e8e4ea1448</t>
-  </si>
-  <si>
-    <t>relationship--5ce76ba7-3a48-4b10-90e5-198ffa362920</t>
-  </si>
-  <si>
-    <t>relationship--3c705994-dbef-46e5-bbc9-2727f089591d</t>
-  </si>
-  <si>
-    <t>relationship--b6238b0b-1c5a-42ab-98be-88421a823c3b</t>
-  </si>
-  <si>
-    <t>relationship--ac27774c-564e-4b3e-a657-5b6b9fef44cb</t>
-  </si>
-  <si>
-    <t>relationship--823d0a75-d450-41bb-821c-e9eb0dc6fc18</t>
-  </si>
-  <si>
-    <t>relationship--18ba73b7-6eae-45da-b3c2-852661ae764c</t>
-  </si>
-  <si>
-    <t>relationship--1eb7a894-9326-4a81-bd95-765d8663e6bd</t>
-  </si>
-  <si>
-    <t>relationship--6422b08d-658e-4158-9fad-7a8c96c95605</t>
-  </si>
-  <si>
-    <t>relationship--9a58d79c-8c2d-4bba-b648-4043bc36ffc1</t>
-  </si>
-  <si>
-    <t>relationship--2aa29e63-8a59-4504-b4ea-b643cb750905</t>
-  </si>
-  <si>
-    <t>relationship--4f9065f0-7c0c-4736-a6ca-7827a90d9d19</t>
-  </si>
-  <si>
-    <t>relationship--e52375de-90ff-45a7-92be-7a182eda695c</t>
-  </si>
-  <si>
-    <t>relationship--179f57b1-c910-4149-81f7-eb3d85a9a034</t>
-  </si>
-  <si>
-    <t>relationship--28b73c47-f92d-4012-8d2d-0a54354ff998</t>
-  </si>
-  <si>
-    <t>relationship--0846c941-f535-42f4-bbed-93bd88de61a3</t>
-  </si>
-  <si>
-    <t>relationship--4bfe08b0-dae8-48bd-8d97-e38392618d7e</t>
-  </si>
-  <si>
-    <t>relationship--abc2475e-7cb3-48de-8fe3-77dcc3c6b7c5</t>
-  </si>
-  <si>
-    <t>relationship--66814061-23fb-43a0-9fda-98d06aeff256</t>
-  </si>
-  <si>
-    <t>relationship--b20498b6-be7d-4519-9812-2f99445c1b08</t>
-  </si>
-  <si>
-    <t>relationship--7ccd088f-274f-4e1c-91dd-b56434c8d45d</t>
-  </si>
-  <si>
-    <t>relationship--bd4963e2-3a2c-4aa2-9166-e49f8888524e</t>
-  </si>
-  <si>
-    <t>relationship--520a65a1-3657-4044-818e-128044be1988</t>
-  </si>
-  <si>
-    <t>relationship--09695269-0bb0-49a6-ad92-2fbd5fa043bb</t>
-  </si>
-  <si>
-    <t>relationship--c50465fe-3661-4cb1-a570-4c18647b0b40</t>
-  </si>
-  <si>
-    <t>relationship--d62e5a82-0915-4c6f-8e5c-631e8f428bc0</t>
-  </si>
-  <si>
-    <t>relationship--bf8391b0-8a09-4a5a-8aca-b569340bea96</t>
-  </si>
-  <si>
-    <t>relationship--2be0a756-128d-4e0b-8f96-00e9c6708140</t>
-  </si>
-  <si>
-    <t>relationship--de1ffdc8-d778-4bb3-beb7-97b48322d544</t>
-  </si>
-  <si>
-    <t>relationship--6bac4f94-1f0f-4724-bf80-f3461aefa513</t>
-  </si>
-  <si>
-    <t>relationship--5aeecf78-6afc-4ebe-931d-05e0e0a37b08</t>
-  </si>
-  <si>
-    <t>relationship--5f80c5d9-3615-47a5-8fa8-9b56c5fbfec3</t>
-  </si>
-  <si>
-    <t>relationship--d59eba6f-c6c9-4cbd-b1ad-20327d38bc37</t>
-  </si>
-  <si>
-    <t>relationship--6a8da905-9a1c-43f7-8689-191052c5c472</t>
-  </si>
-  <si>
-    <t>relationship--08889113-b3b5-4868-827d-686d6905c6b1</t>
-  </si>
-  <si>
-    <t>relationship--02546a04-7379-4592-b214-848d09556f5f</t>
-  </si>
-  <si>
-    <t>relationship--ec9c992c-a1a3-4c5f-929e-66080ca44d3d</t>
-  </si>
-  <si>
-    <t>relationship--92dcc0ba-b934-4df1-9aa2-92bd4abfcc87</t>
-  </si>
-  <si>
-    <t>relationship--51b325e0-6cbc-4191-80d5-7852e52ece70</t>
-  </si>
-  <si>
-    <t>relationship--94b99374-34a2-4052-88cd-f4aa19d7c2b9</t>
-  </si>
-  <si>
-    <t>relationship--56ffd478-8f6e-4efc-a060-52e9c1c86496</t>
-  </si>
-  <si>
-    <t>relationship--83c12395-10c6-485b-a723-c9b13cc07157</t>
-  </si>
-  <si>
-    <t>relationship--f729692a-134c-405e-bbfb-fb6eb6fd7220</t>
-  </si>
-  <si>
-    <t>relationship--5c6a47f0-242d-41f8-9a5d-adffd9e19239</t>
-  </si>
-  <si>
-    <t>relationship--e699e3ac-0f36-452e-b698-ca148a267344</t>
-  </si>
-  <si>
-    <t>relationship--ddcfba4e-b61a-4606-8af9-b3359874b18f</t>
-  </si>
-  <si>
-    <t>relationship--b969943c-54d3-4ecb-89db-475f1f2ffc08</t>
-  </si>
-  <si>
-    <t>relationship--f84a1f0c-15da-4c21-ab34-95a67f789ed9</t>
-  </si>
-  <si>
-    <t>relationship--27c7f321-20ad-4af2-a87c-d9bed18a362c</t>
-  </si>
-  <si>
-    <t>relationship--dc952b82-96a7-4233-b7c5-eea1c319b585</t>
-  </si>
-  <si>
-    <t>relationship--d35523c7-ed4b-4c41-8024-4509d119a946</t>
-  </si>
-  <si>
-    <t>relationship--aae7b6b8-8e93-4cf0-b262-5c0a953c66ed</t>
-  </si>
-  <si>
-    <t>relationship--f9c3422f-a851-44aa-8ed8-30ee0162c2a1</t>
-  </si>
-  <si>
-    <t>relationship--21d4f69f-3447-4b17-849d-ef9dd2cb92f5</t>
-  </si>
-  <si>
-    <t>relationship--66808b80-9e25-427f-9399-da99fae04d40</t>
-  </si>
-  <si>
-    <t>relationship--b8f58495-0454-48b9-829e-2accc143b26b</t>
-  </si>
-  <si>
-    <t>relationship--75142ef9-8611-46e4-a099-085e6762d9e6</t>
-  </si>
-  <si>
-    <t>relationship--351d6979-9871-477c-a000-e47683c74f07</t>
-  </si>
-  <si>
-    <t>relationship--efe188ee-08a9-4499-b7bc-31feb4b4ca8a</t>
-  </si>
-  <si>
-    <t>relationship--56a697fe-9957-49f9-bb54-7985d87026cf</t>
-  </si>
-  <si>
-    <t>relationship--e2366f75-d746-4d9b-bc9d-6a8cdb13d659</t>
-  </si>
-  <si>
-    <t>relationship--70a9efb0-f8ef-4594-9052-52e2b8e541d8</t>
-  </si>
-  <si>
-    <t>relationship--f6726f3c-140c-4e3f-9948-01cb1fdff12b</t>
-  </si>
-  <si>
-    <t>relationship--964c2333-f5ac-4470-8481-c2c37c0b1d86</t>
-  </si>
-  <si>
-    <t>relationship--67dcd8fb-abb1-40a8-8b94-c0b471d70dc0</t>
-  </si>
-  <si>
-    <t>relationship--35ac0f5f-4c08-4165-bb55-e2caf958fa4b</t>
-  </si>
-  <si>
-    <t>relationship--acc7f7f8-1940-4dac-a5e8-a61e6aaeb704</t>
-  </si>
-  <si>
-    <t>relationship--c8bae29d-6b3b-44e2-9837-9c88d45813d1</t>
-  </si>
-  <si>
-    <t>relationship--b334682c-0130-4caf-8f75-1fc44dcb69ba</t>
-  </si>
-  <si>
-    <t>relationship--79262f14-5a84-4da5-83db-3a778c7412fb</t>
-  </si>
-  <si>
-    <t>relationship--949ff990-9719-454c-a38b-a17c82d1327b</t>
-  </si>
-  <si>
-    <t>relationship--c3cecb1c-770e-47b5-96ae-67be5fdc204e</t>
-  </si>
-  <si>
-    <t>relationship--435769c0-f5c3-4fd7-b9b5-f3dfbdf106f9</t>
-  </si>
-  <si>
-    <t>relationship--8a9d808e-af8d-4294-bd77-502699ec0370</t>
-  </si>
-  <si>
-    <t>relationship--356a3acc-0038-4b84-b190-afab93380c5e</t>
-  </si>
-  <si>
-    <t>relationship--0165c119-2717-4fb7-b872-160280520a8e</t>
-  </si>
-  <si>
-    <t>relationship--2b2dfcda-c520-4d73-8caf-ecf825fb847e</t>
-  </si>
-  <si>
-    <t>relationship--7d879ede-4938-49df-8c54-a43b4a9f54e7</t>
-  </si>
-  <si>
-    <t>relationship--66b3b581-d829-415d-91d9-5fa9f788f904</t>
-  </si>
-  <si>
-    <t>relationship--e331eef5-8644-4e70-83f3-95eac37c4f51</t>
-  </si>
-  <si>
-    <t>relationship--a6dca3bd-25a8-4192-b4ff-e83c12641909</t>
-  </si>
-  <si>
-    <t>relationship--9f971b79-26aa-453a-85b4-c8a2ac04c2d6</t>
-  </si>
-  <si>
-    <t>relationship--4da3ce3c-6f59-45f7-87c0-f1a8de267d05</t>
-  </si>
-  <si>
-    <t>relationship--e9ab29a8-a673-4043-a950-e97581d517ea</t>
-  </si>
-  <si>
-    <t>relationship--b1406741-6561-496d-b3ae-0a1fa17cc0b3</t>
-  </si>
-  <si>
-    <t>relationship--dcb7030a-3233-4831-9619-766ffc985f9c</t>
-  </si>
-  <si>
-    <t>relationship--11ce048c-09a0-4511-937d-90b9abda16d5</t>
-  </si>
-  <si>
-    <t>relationship--71714f1b-c50e-4805-b3fb-f2aa3a1145db</t>
-  </si>
-  <si>
-    <t>relationship--02f1ea05-77d5-492f-a60c-4e77c1dd0d56</t>
-  </si>
-  <si>
-    <t>relationship--321a084e-2aa3-4b4e-ba25-21a40548e555</t>
-  </si>
-  <si>
-    <t>relationship--534fa98c-37ae-4ae8-b50a-2d372a9a524b</t>
-  </si>
-  <si>
-    <t>relationship--1e660181-af7b-4201-8217-696472e8f658</t>
-  </si>
-  <si>
-    <t>relationship--daa0419c-a9f4-4d46-935b-b55382061697</t>
-  </si>
-  <si>
-    <t>relationship--92d00a4f-6936-4650-8b40-82620ca2d6f5</t>
-  </si>
-  <si>
-    <t>relationship--3f5f0ff1-0a2f-4f2a-87ad-84afee8cce02</t>
-  </si>
-  <si>
-    <t>relationship--4b4473a5-7650-48a0-b527-d314921cec84</t>
-  </si>
-  <si>
-    <t>relationship--b81d57bc-d772-4301-902d-24bd076054a2</t>
-  </si>
-  <si>
-    <t>relationship--5a0e7a8f-7d47-467d-8647-6c960ddb9d17</t>
-  </si>
-  <si>
-    <t>relationship--95ab8c24-c9e4-4eac-b65f-b7a6da3d6ce3</t>
-  </si>
-  <si>
-    <t>relationship--058d1028-80d0-480f-a9a1-d8cfe688cedd</t>
-  </si>
-  <si>
-    <t>relationship--716f8f04-2cb8-4fe3-8161-20f874014261</t>
-  </si>
-  <si>
-    <t>relationship--55131080-1b36-4e4c-a590-948bf51af3ed</t>
-  </si>
-  <si>
-    <t>relationship--6428b6a8-88bb-4e7d-8699-eecbb3fa320c</t>
-  </si>
-  <si>
-    <t>relationship--c55feac6-6eb0-4e01-9916-e259f2cda102</t>
-  </si>
-  <si>
-    <t>relationship--bc6fa3cf-3387-4b92-b81d-45dded61f26a</t>
-  </si>
-  <si>
-    <t>relationship--d4708896-df5c-46e7-8f1b-48c56c0791e7</t>
-  </si>
-  <si>
-    <t>relationship--eea10264-3b7d-4fa6-833c-1b295dc16f3d</t>
-  </si>
-  <si>
-    <t>relationship--98c9eae8-320a-442c-a16e-86f161449b7f</t>
-  </si>
-  <si>
-    <t>relationship--be48ee88-830f-46a1-9d84-e049128513d4</t>
-  </si>
-  <si>
-    <t>relationship--0d05109f-48d6-46e1-8d6b-efcad30695fe</t>
-  </si>
-  <si>
-    <t>relationship--3d9d94c6-cf39-44ed-a142-200cf583aab7</t>
-  </si>
-  <si>
-    <t>relationship--2960e500-191a-4f87-83b3-992973b0742b</t>
-  </si>
-  <si>
-    <t>relationship--c14c18f9-6d4f-4b32-8ac3-2b1b046fbe67</t>
-  </si>
-  <si>
-    <t>relationship--3a0434d7-e031-4fac-936d-09bbb03f4588</t>
-  </si>
-  <si>
-    <t>relationship--643acbd6-2bbb-4c33-b4be-5f6c3be2fdaf</t>
-  </si>
-  <si>
-    <t>relationship--aa2c18e9-324e-4ba1-8ee3-38823c02e603</t>
-  </si>
-  <si>
-    <t>relationship--9253edf4-2c7a-4255-b31b-fc2a4c5f9b07</t>
-  </si>
-  <si>
-    <t>relationship--2f24f0b5-e448-4cd9-88ee-62991b928968</t>
-  </si>
-  <si>
-    <t>relationship--69eff671-b723-4395-9563-310d3b3f7e06</t>
-  </si>
-  <si>
-    <t>relationship--4403dc32-835f-492f-ac71-9aacd28248ff</t>
-  </si>
-  <si>
-    <t>relationship--fa88cc75-341c-49bd-8754-f3f3e09035ca</t>
-  </si>
-  <si>
-    <t>relationship--f15900bc-ab11-4ec0-992c-dd2570d62b3e</t>
-  </si>
-  <si>
-    <t>relationship--e7516d9e-6763-49d7-a224-7f2289320e56</t>
-  </si>
-  <si>
-    <t>relationship--61ac1bfb-73d3-4dc5-b356-327526001323</t>
-  </si>
-  <si>
-    <t>relationship--7a8c7555-7987-496e-9818-200c20dc85cb</t>
-  </si>
-  <si>
-    <t>relationship--36e7582d-956f-4a2a-ae32-4cf2a1a936c7</t>
-  </si>
-  <si>
-    <t>relationship--4b513dcc-b59b-4133-87e5-c77381e8fa4c</t>
-  </si>
-  <si>
-    <t>relationship--ae0c3c71-639a-4c4f-82bb-e32ad916f84c</t>
-  </si>
-  <si>
-    <t>relationship--e83bcf7e-551c-4b08-be46-530290bcabbd</t>
-  </si>
-  <si>
-    <t>relationship--248a433d-9ac1-4c3a-886c-e08fb21868ec</t>
+    <t>relationship--73f20dcc-3287-4113-82e8-763e48894190</t>
+  </si>
+  <si>
+    <t>relationship--825c1637-5f28-4639-a0bd-24c0faa81abc</t>
+  </si>
+  <si>
+    <t>relationship--9b84a32e-e650-4926-a17a-fd035bb4ce0d</t>
+  </si>
+  <si>
+    <t>relationship--ea769fbd-117e-430b-92ed-25ff35585e3d</t>
+  </si>
+  <si>
+    <t>relationship--87b0f876-75be-44ff-8099-a8e5ae593e79</t>
+  </si>
+  <si>
+    <t>relationship--4861abcc-0e82-446a-99c2-80cda33c4127</t>
+  </si>
+  <si>
+    <t>relationship--89b7d64b-f141-4f96-a8e0-930817df0320</t>
+  </si>
+  <si>
+    <t>relationship--b054503e-b646-483d-a551-828dbf7a8151</t>
+  </si>
+  <si>
+    <t>relationship--e8d9b939-0a6d-4ad9-af33-f11e2607ac62</t>
+  </si>
+  <si>
+    <t>relationship--27ac00bd-526e-496f-8ab9-e266cd5de598</t>
+  </si>
+  <si>
+    <t>relationship--b0fb517a-0586-42ea-9436-6d3952feeb23</t>
+  </si>
+  <si>
+    <t>relationship--738cca6f-b075-4217-8ad7-ecc7fb91a62c</t>
+  </si>
+  <si>
+    <t>relationship--ce5a8fb7-7e19-4a86-a3c3-b761c23b12ca</t>
+  </si>
+  <si>
+    <t>relationship--a1e0b883-9981-4990-9400-f37eded667b0</t>
+  </si>
+  <si>
+    <t>relationship--3409c684-c51c-4372-804f-eeee9a54f23d</t>
+  </si>
+  <si>
+    <t>relationship--71c46d3c-5f6c-41c3-a7ae-c1b4bdeb7e2a</t>
+  </si>
+  <si>
+    <t>relationship--e44a4bc8-64db-4832-8cf0-562a90e0fc53</t>
+  </si>
+  <si>
+    <t>relationship--3e192972-8162-4a25-a8ab-f45d3f33235c</t>
+  </si>
+  <si>
+    <t>relationship--d230d59f-6f0c-403c-94b5-6aa1a2a34ec9</t>
+  </si>
+  <si>
+    <t>relationship--afe384cd-f757-437c-97ee-e0c1d4184e67</t>
+  </si>
+  <si>
+    <t>relationship--dc444d1b-1eb7-45e7-9790-f510c4c6c253</t>
+  </si>
+  <si>
+    <t>relationship--6ddf4f24-f1cf-40d6-89ad-de97601a08df</t>
+  </si>
+  <si>
+    <t>relationship--39ff2ea9-2ff9-4ff8-8717-f7350079b10a</t>
+  </si>
+  <si>
+    <t>relationship--15f43936-3510-4a13-9f21-0dda01b64009</t>
+  </si>
+  <si>
+    <t>relationship--5b636ded-6985-4994-a104-b8582384181a</t>
+  </si>
+  <si>
+    <t>relationship--5f037cbf-b46a-4887-bca9-72daf25ed1d7</t>
+  </si>
+  <si>
+    <t>relationship--89bad90d-4410-4b38-88cd-a16cfa325e29</t>
+  </si>
+  <si>
+    <t>relationship--c0468dfe-b7ac-4779-8c8a-3f6b3e43d235</t>
+  </si>
+  <si>
+    <t>relationship--a2adbbdf-93be-4b60-86a4-51a2164b7167</t>
+  </si>
+  <si>
+    <t>relationship--290f2398-ec7e-4be1-8ede-fed7a71dd7a1</t>
+  </si>
+  <si>
+    <t>relationship--ac2a2a4b-309e-413b-8758-57f4f1ac1eaf</t>
+  </si>
+  <si>
+    <t>relationship--cbd15ce4-2b9f-4ea2-89f0-ee36d9995f87</t>
+  </si>
+  <si>
+    <t>relationship--f7bc6506-b418-4004-9784-ca575e0b60d1</t>
+  </si>
+  <si>
+    <t>relationship--aa4b1dd5-1001-41f5-a9b0-61247e6f7e13</t>
+  </si>
+  <si>
+    <t>relationship--8a147269-87e1-4deb-87be-de18401cfab0</t>
+  </si>
+  <si>
+    <t>relationship--1d05e6d5-773f-4a8c-bfed-544a29cd7109</t>
+  </si>
+  <si>
+    <t>relationship--f4b5ba92-b9a6-4410-8e2a-98ef7262205d</t>
+  </si>
+  <si>
+    <t>relationship--14a7d33f-5779-4f29-abea-c3d49fdbb8b4</t>
+  </si>
+  <si>
+    <t>relationship--0c46f147-c31e-491f-9379-3e7ee25bd9ee</t>
+  </si>
+  <si>
+    <t>relationship--91773f08-387e-4984-836d-7d67371dfd6d</t>
+  </si>
+  <si>
+    <t>relationship--858793e2-3f3e-4bcc-bca7-59c7beb80add</t>
+  </si>
+  <si>
+    <t>relationship--14614238-5879-4612-a1ec-3e4d0f352d81</t>
+  </si>
+  <si>
+    <t>relationship--3ada6b62-8220-4fb7-8a72-3def0588a353</t>
+  </si>
+  <si>
+    <t>relationship--86eb6e33-ac73-4417-aeeb-22a6cedc080e</t>
+  </si>
+  <si>
+    <t>relationship--73f01780-806a-422f-a8f4-cabf25166c0b</t>
+  </si>
+  <si>
+    <t>relationship--40f8d8bb-2c4d-4700-a925-7784b07d244a</t>
+  </si>
+  <si>
+    <t>relationship--a6bdbc5c-d45e-4a06-9946-051b39c4560e</t>
+  </si>
+  <si>
+    <t>relationship--f6fb2529-dc26-42c8-a7ea-58c242d4f200</t>
+  </si>
+  <si>
+    <t>relationship--19a98b28-98c2-4874-8176-5e7fa0b8da0d</t>
+  </si>
+  <si>
+    <t>relationship--e1b43f7a-b513-430a-94de-3196185b004e</t>
+  </si>
+  <si>
+    <t>relationship--de0c9f07-9007-4633-9c99-7c28d4899b09</t>
+  </si>
+  <si>
+    <t>relationship--6b3798f0-f1a1-44c7-86c9-e6b8657dd3eb</t>
+  </si>
+  <si>
+    <t>relationship--ef4fb288-6d1b-4a63-b4ef-0cd172aa8b95</t>
+  </si>
+  <si>
+    <t>relationship--b6e69f84-75ee-4166-9d8f-f08ad175cc43</t>
+  </si>
+  <si>
+    <t>relationship--6d6709b6-c044-4dc6-a3d0-fa6432fc9a48</t>
+  </si>
+  <si>
+    <t>relationship--d8b223fc-c80d-481b-8bde-eef09983f126</t>
+  </si>
+  <si>
+    <t>relationship--193685e2-986a-4c5a-99e4-e78d66db9dec</t>
+  </si>
+  <si>
+    <t>relationship--1b49e28e-e1d4-41d2-bacf-8b1f006cd635</t>
+  </si>
+  <si>
+    <t>relationship--f996d274-e5b4-43e9-a6b5-0e48fcea0a2c</t>
+  </si>
+  <si>
+    <t>relationship--dca500fa-289c-4ee1-ae79-07927e05747d</t>
+  </si>
+  <si>
+    <t>relationship--ec157337-eb2b-4268-8f45-d20014653430</t>
+  </si>
+  <si>
+    <t>relationship--628d5a81-67d8-46c6-820e-e862013770a7</t>
+  </si>
+  <si>
+    <t>relationship--9e8855aa-f40e-4b22-a4bd-48d84689c5a1</t>
+  </si>
+  <si>
+    <t>relationship--c28d6011-02ea-422b-aefd-f702730a4b4c</t>
+  </si>
+  <si>
+    <t>relationship--0becd2d6-b2cf-4b70-968c-e2aa3b9520f3</t>
+  </si>
+  <si>
+    <t>relationship--b3298cf0-1c17-46f0-8138-bed44069713b</t>
+  </si>
+  <si>
+    <t>relationship--b4c8f95c-ca7f-4887-ae6b-5bff4255013a</t>
+  </si>
+  <si>
+    <t>relationship--6fdf9afb-71f4-4178-9067-4d9907e8adcf</t>
+  </si>
+  <si>
+    <t>relationship--9f8c3d3a-f083-4ac7-a518-97d3b18e3936</t>
+  </si>
+  <si>
+    <t>relationship--465b765f-ba41-4ec4-989c-ed896c7ece17</t>
+  </si>
+  <si>
+    <t>relationship--adfe0022-a944-4a01-8c13-69e5b583d5df</t>
+  </si>
+  <si>
+    <t>relationship--768b12e1-f78b-4e30-8cb7-39676315bcd0</t>
+  </si>
+  <si>
+    <t>relationship--0b31535b-a10f-4f5c-862c-9b7d160e6205</t>
+  </si>
+  <si>
+    <t>relationship--a2265b6a-482c-480b-9ede-976de4da4ae9</t>
+  </si>
+  <si>
+    <t>relationship--216dd862-a40b-41c0-b69c-a70838cbe764</t>
+  </si>
+  <si>
+    <t>relationship--2b177521-99b8-4ea0-948b-1a735ec8dbcb</t>
+  </si>
+  <si>
+    <t>relationship--afa240ea-6764-42c0-b426-643557f02661</t>
+  </si>
+  <si>
+    <t>relationship--a2f1422a-10b4-451b-a0bc-8e8d9c35a4cd</t>
+  </si>
+  <si>
+    <t>relationship--070cf034-5fb0-4431-af8a-fa71e78c9001</t>
+  </si>
+  <si>
+    <t>relationship--2e16e028-ac5d-4d45-bac8-8c31f26a9279</t>
+  </si>
+  <si>
+    <t>relationship--e8c4c1a2-5957-4bf3-b14e-23d9fb79abd8</t>
+  </si>
+  <si>
+    <t>relationship--b38399e8-39fd-4aea-82b0-85266cbe1150</t>
+  </si>
+  <si>
+    <t>relationship--b42eb8ed-46be-4e80-8a06-7eeb1a8d3654</t>
+  </si>
+  <si>
+    <t>relationship--6a247917-bc82-4a68-b144-9ba68e457f4a</t>
+  </si>
+  <si>
+    <t>relationship--04dee79b-b91a-44f2-9fb4-868c8c64047d</t>
+  </si>
+  <si>
+    <t>relationship--2e3d8420-56eb-4bc9-8225-c57f102d466c</t>
+  </si>
+  <si>
+    <t>relationship--b21fd63c-05bb-4949-8e69-5eb9dc9e177f</t>
+  </si>
+  <si>
+    <t>relationship--27e65b1e-0a60-4a2d-ae17-4e881330c997</t>
+  </si>
+  <si>
+    <t>relationship--4c989230-7c3a-4028-a28b-a9ae49f21bc4</t>
+  </si>
+  <si>
+    <t>relationship--82faebbf-2e43-4316-b719-c426de7048a7</t>
+  </si>
+  <si>
+    <t>relationship--40d2b7ae-17ee-45a8-aae9-4d0a4d026ccc</t>
+  </si>
+  <si>
+    <t>relationship--766873b9-82d0-4763-a029-e6327abf0f14</t>
+  </si>
+  <si>
+    <t>relationship--bdbfe523-30c9-4bf3-82ff-b7f20ef66b0d</t>
+  </si>
+  <si>
+    <t>relationship--6a1b7f43-e90c-4df1-b098-96c80b843d9b</t>
+  </si>
+  <si>
+    <t>relationship--8985aa74-99fc-45b6-a040-778b3d7eab9f</t>
+  </si>
+  <si>
+    <t>relationship--c403cc2b-7a92-4e7c-82fb-c7526ff8a7cf</t>
+  </si>
+  <si>
+    <t>relationship--acb539b2-cb36-47c1-8619-c9ae617d695e</t>
+  </si>
+  <si>
+    <t>relationship--4d051db8-6747-4405-a00e-c998a45c755c</t>
+  </si>
+  <si>
+    <t>relationship--213847f6-c8a3-4a5b-8b79-11e067b8bee7</t>
+  </si>
+  <si>
+    <t>relationship--c21c9f86-0cb0-46f9-84fb-3fca41a5aa00</t>
+  </si>
+  <si>
+    <t>relationship--483e57d7-4db4-4991-b4ae-5f2d4dcaf11f</t>
+  </si>
+  <si>
+    <t>relationship--70e110c8-4865-4f59-8c79-b36006a76761</t>
+  </si>
+  <si>
+    <t>relationship--1c0fc89f-a14e-47dc-8f3f-ef2c323b26db</t>
+  </si>
+  <si>
+    <t>relationship--b5ce6355-c729-46e9-89e9-141841ea5943</t>
+  </si>
+  <si>
+    <t>relationship--e41dc4c4-c759-4221-b8fe-9803170609ed</t>
+  </si>
+  <si>
+    <t>relationship--f947ba97-7c9a-48e9-a77f-45b3ae01a69b</t>
+  </si>
+  <si>
+    <t>relationship--029160c9-4243-4475-b40a-5c21215ccd4f</t>
+  </si>
+  <si>
+    <t>relationship--3550a101-c9c1-42c9-a174-df445f533c91</t>
+  </si>
+  <si>
+    <t>relationship--49bb34d9-5d45-45f7-a371-6b9ff5c1eecb</t>
+  </si>
+  <si>
+    <t>relationship--18f7c652-f252-4994-a03b-281abf187525</t>
+  </si>
+  <si>
+    <t>relationship--19f3f9fd-dfa2-41e7-b409-c6e5e3f5f327</t>
+  </si>
+  <si>
+    <t>relationship--46e72ca2-adc4-4ffc-947b-a452fd7a020a</t>
+  </si>
+  <si>
+    <t>relationship--a71230d7-8dad-4642-bef6-3daa0c8689f4</t>
+  </si>
+  <si>
+    <t>relationship--b93831ac-46c3-456f-bd1c-77c922e7dbd2</t>
+  </si>
+  <si>
+    <t>relationship--c88d1483-158f-4262-9d3d-42408b002c5b</t>
+  </si>
+  <si>
+    <t>relationship--83c84a53-49c5-42f6-9272-19f81095abd7</t>
+  </si>
+  <si>
+    <t>relationship--8d333dd7-a4b3-47c5-b1b2-87b29a3b523b</t>
+  </si>
+  <si>
+    <t>relationship--7ef6ab36-d85e-4a57-9e93-28814c7db27e</t>
+  </si>
+  <si>
+    <t>relationship--c5de9e8b-dfea-40d8-813f-f31984b4596a</t>
+  </si>
+  <si>
+    <t>relationship--f3953353-84c1-4e19-b4fd-a5dca45229b6</t>
+  </si>
+  <si>
+    <t>relationship--ee8cf95f-33ca-4246-a6c4-f4030944bac0</t>
+  </si>
+  <si>
+    <t>relationship--106b1bb0-a0b3-4b9c-9fb7-3844da45ac9b</t>
+  </si>
+  <si>
+    <t>relationship--e55e439c-988d-4213-a908-b93b9f4994a0</t>
+  </si>
+  <si>
+    <t>relationship--8259c4e0-23ab-4ea5-a0db-cf4a7c941025</t>
+  </si>
+  <si>
+    <t>relationship--236bef8d-15ad-469c-b9a2-63a52b7a3fb9</t>
+  </si>
+  <si>
+    <t>relationship--0a04227f-5225-4f85-97b0-aea75255eaf2</t>
+  </si>
+  <si>
+    <t>relationship--c5be3c4c-aff7-455a-a539-acba0d6deb5f</t>
+  </si>
+  <si>
+    <t>relationship--e4b1bd51-89ce-402d-bd37-d4110908aa38</t>
+  </si>
+  <si>
+    <t>relationship--fac775df-582f-43ad-988c-a3a5df08244f</t>
+  </si>
+  <si>
+    <t>relationship--d2f11487-cb52-42e4-810d-e0f0734924a5</t>
+  </si>
+  <si>
+    <t>relationship--df601479-1fb0-4ba4-bf65-a4e3a1862492</t>
+  </si>
+  <si>
+    <t>relationship--cd7cf5cf-c473-4089-8114-1b0dba6344d0</t>
+  </si>
+  <si>
+    <t>relationship--7e06e945-c7f3-4b02-99e9-e896e7af97d0</t>
+  </si>
+  <si>
+    <t>relationship--c21bc1f1-dc57-401b-a994-9bbe3b723226</t>
+  </si>
+  <si>
+    <t>relationship--61e15e02-e284-4ae8-b53c-2b95cb53b410</t>
+  </si>
+  <si>
+    <t>relationship--04c28215-eeb1-4d72-b951-17c055ee786e</t>
+  </si>
+  <si>
+    <t>relationship--5dc03638-0a07-48b9-929a-0611d60f3a6d</t>
+  </si>
+  <si>
+    <t>relationship--93afc855-8d44-47b3-816b-6e2342aab400</t>
+  </si>
+  <si>
+    <t>relationship--93291f26-af2e-43fa-899a-8c254bf5158c</t>
+  </si>
+  <si>
+    <t>relationship--3e7f9ecb-ce42-48c2-b399-70f7c51d752c</t>
+  </si>
+  <si>
+    <t>relationship--c30eccbe-7487-47b4-9c12-c524ae39cf7a</t>
+  </si>
+  <si>
+    <t>relationship--45120c9c-c022-424a-b5eb-965319b86013</t>
+  </si>
+  <si>
+    <t>relationship--51017bb7-a23c-4d53-87d6-e2339dd733b2</t>
+  </si>
+  <si>
+    <t>relationship--d9c3c96d-86b3-4e20-8f9f-7d3e73dbe3b6</t>
+  </si>
+  <si>
+    <t>relationship--04774318-e7f4-43f2-87d9-d3de0d7ddaa7</t>
+  </si>
+  <si>
+    <t>relationship--25ec490c-0666-4696-bba9-782fa14ea67b</t>
+  </si>
+  <si>
+    <t>relationship--0b847cdd-aa0c-4bc7-8b99-2f0a61cffb09</t>
+  </si>
+  <si>
+    <t>relationship--5ffe9769-e4f7-4815-adaf-c0fc5a052833</t>
+  </si>
+  <si>
+    <t>relationship--dc962fb8-e350-461a-b6bf-1287c5090183</t>
+  </si>
+  <si>
+    <t>relationship--77de5738-1c23-459e-8330-743c3402f91b</t>
+  </si>
+  <si>
+    <t>relationship--f0de7c24-aedb-439c-8762-fcc3536e0f3e</t>
+  </si>
+  <si>
+    <t>relationship--73edb35e-3d6f-443d-a907-c5c2ce785365</t>
+  </si>
+  <si>
+    <t>relationship--652ef8f6-2b43-4205-b0aa-61d1c83c8f5c</t>
+  </si>
+  <si>
+    <t>relationship--08c45469-fee0-4502-8330-eb86a9ec7e7a</t>
+  </si>
+  <si>
+    <t>relationship--2c6fbbb6-34df-4592-a85a-c5b558077a71</t>
+  </si>
+  <si>
+    <t>relationship--8ec17a37-ba03-4609-aa19-1750ac0e7f45</t>
+  </si>
+  <si>
+    <t>relationship--f8a7c715-8187-4870-83a1-1d7e31f8245a</t>
+  </si>
+  <si>
+    <t>relationship--27af02db-806e-4d27-bfb5-2e246e46c450</t>
+  </si>
+  <si>
+    <t>relationship--aa45ed64-523e-4f79-b8ff-3a692f1aadca</t>
   </si>
   <si>
     <t>reference</t>
@@ -3997,64 +3976,334 @@
     <t>citation</t>
   </si>
   <si>
+    <t>2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
+  </si>
+  <si>
+    <t>2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
+  </si>
+  <si>
+    <t>Історія України — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
+    <t>Всесоюзний референдум про збереження СРСР — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Дезінформація під час російсько-української війни — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Друга Малоросійська колегія — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Задунайська Січ — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Запорозька Січ — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
+    <t>Карательная психиатрия в России: назад в СССР? 2026</t>
+  </si>
+  <si>
+    <t>Кенгирское восстание заключённых - Википедия 2026</t>
+  </si>
+  <si>
     <t>Киевский синопсис — Википедия 2026</t>
   </si>
   <si>
+    <t>Кирило-Мефодіївське товариство — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Конотопські статті — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Крымская война — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Лубенський договір — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Ліквідація автономії Гетьманщини — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Мазепа 2007</t>
   </si>
   <si>
-    <t>РАШИЗМ ЗВІР З БЕЗОДНІ 2023</t>
+    <t>Малоросійське генерал-губернаторство — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Малоросійський приказ — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Народний рух України — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Поділи Речі Посполитої — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Рашизм: Звір з безодні 2023</t>
+  </si>
+  <si>
+    <t>Решетилівські статті — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Российские удары по украинской энергосистеме — Википедия 2026</t>
   </si>
   <si>
     <t>Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010</t>
   </si>
   <si>
+    <t>Русифікація України — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Руїна — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Рішительні пункти — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Серпневий путч — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Смуга осілості — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Столипінська реформа — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Україна в Першій світовій війні — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Україна у війнах Наполеона — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Хроника первой российской войны в Чечне 2026</t>
   </si>
   <si>
+    <t>Чорносотенці — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK®. (2023). 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK®. (2023). 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Всесоюзний референдум про збереження СРСР — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Дезінформація під час російсько-української війни — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Друга Малоросійська колегія — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Задунайська Січ — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Запорозька Січ — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
+    <t>Riddle Russia. (2026). Карательная психиатрия в России: назад в СССР?.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Киевский синопсис — Википедия.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Кирило-Мефодіївське товариство — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Конотопські статті — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Крымская война — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Лубенський договір — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Ліквідація автономії Гетьманщини — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Татьяна Таирова-Яковлева. (2007). Мазепа.</t>
   </si>
   <si>
-    <t>Лариса Якубова. (2023). РАШИЗМ ЗВІР З БЕЗОДНІ.</t>
+    <t>Вікіпедія. (2026). Малоросійське генерал-губернаторство — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Малоросійський приказ — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Народний рух України — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Поділи Речі Посполитої — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Лариса Якубова. (2023). Рашизм: Звір з безодні.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Решетилівські статті — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Российские удары по украинской энергосистеме — Википедия.</t>
   </si>
   <si>
     <t>Мемориал, О.П.Орлов, А.В.Черкасов. (2010). Россия - Чечня - цепь ошибок и преступлений. 1994—1996.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Русифікація України — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Руїна — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Рішительні пункти — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Серпневий путч — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Скасування козацького устрою в Слобідській Україні — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Смуга осілості — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Столипінська реформа — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Україна в Першій світовій війні — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Україна у війнах Наполеона — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Beda Media. (2026). Хроника первой российской войны в Чечне.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Чорносотенці — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>https://attack.mitre.org/campaigns/C0028/</t>
+  </si>
+  <si>
+    <t>https://attack.mitre.org/campaigns/C0025/</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B4%25D0%25B5%25D0%25B7%25D1%2596%25D0%25BD%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2594%25D1%2580%25D1%2583%25D0%25B3%25D0%25B0_%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25B3%25D1%2596%25D1%258F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25B4%25D1%2583%25D0%25BD%25D0%25B0%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+  </si>
+  <si>
+    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B8%D0%B5%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%81%D0%B8%D0%BD%D0%BE%D0%BF%D1%81%D0%B8%D1%81</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2580%25D0%25B8%25D0%25BB%25D0%25BE-%25D0%259C%25D0%25B5%25D1%2584%25D0%25BE%25D0%25B4%25D1%2596%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D1%2582%25D0%25BE%25D0%25B2%25D0%25B0%25D1%2580%25D0%25B8%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D0%25BD%25D0%25BE%25D1%2582%25D0%25BE%25D0%25BF%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D1%2580%25D1%258B%25D0%25BC%25D1%2581%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2583%25D0%25B1%25D0%25B5%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25B4%25D0%25BE%25D0%25B3%25D0%25BE%25D0%25B2%25D1%2596%25D1%2580</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2580%25D0%25B8%25D0%25BA%25D0%25B0%25D0%25B7</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259D%25D0%25B0%25D1%2580%25D0%25BE%25D0%25B4%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B4%25D1%2596%25D0%25BB%25D0%25B8_%25D0%25A0%25D0%25B5%25D1%2587%25D1%2596_%25D0%259F%25D0%25BE%25D1%2581%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B8%25D1%2582%25D0%25BE%25D1%2597</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25B5%25D1%2588%25D0%25B5%25D1%2582%25D0%25B8%25D0%25BB%25D1%2596%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25B8%25D0%25B5_%25D1%2583%25D0%25B4%25D0%25B0%25D1%2580%25D1%258B_%25D0%25BF%25D0%25BE_%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D0%25B8%25D0%25BD%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D1%258D%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B3%25D0%25BE%25D1%2581%25D0%25B8%25D1%2581%25D1%2582%25D0%25B5%25D0%25BC%25D0%25B5</t>
+  </si>
+  <si>
     <t>https://web.archive.org/web/20160304195659/http%3A//www.memo.ru/2010/09/27/rch.pdf</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D0%25B8%25D1%2584%25D1%2596%25D0%25BA%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%97%D0%BD%D0%B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2596%25D1%2588%25D0%25B8%25D1%2582%25D0%25B5%25D0%25BB%25D1%258C%25D0%25BD%25D1%2596_%25D0%25BF%25D1%2583%25D0%25BD%25D0%25BA%25D1%2582%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25B5%25D1%2580%25D0%25BF%25D0%25BD%25D0%25B5%25D0%25B2%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2583%25D1%2582%25D1%2587</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BA%25D0%25B0%25D1%2581%25D1%2583%25D0%25B2%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2581%25D1%2582%25D1%2580%25D0%25BE%25D1%258E_%25D0%25B2_%25D0%25A1%25D0%25BB%25D0%25BE%25D0%25B1%25D1%2596%25D0%25B4%25D1%2581%25D1%258C%25D0%25BA%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BC%25D1%2583%25D0%25B3%25D0%25B0_%25D0%25BE%25D1%2581%25D1%2596%25D0%25BB%25D0%25BE%25D1%2581%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D1%2582%25D0%25BE%25D0%25BB%25D0%25B8%25D0%25BF%25D1%2596%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2580%25D0%25B5%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D0%25B2_%25D0%259F%25D0%25B5%25D1%2580%25D1%2588%25D1%2596%25D0%25B9_%25D1%2581%25D0%25B2%25D1%2596%25D1%2582%25D0%25BE%25D0%25B2%25D1%2596%25D0%25B9_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D1%2583_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0%25D1%2585_%25D0%259D%25D0%25B0%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25BE%25D0%25BD%25D0%25B0</t>
+  </si>
+  <si>
     <t>https://beda.media/ru/articles/war-in-chechnya-chronicle-part1-ru</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
   </si>
 </sst>
 </file>
@@ -13786,7 +14035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -13850,19 +14099,19 @@
         <v>826</v>
       </c>
       <c r="G2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J2" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="K2" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="L2" t="s">
         <v>81</v>
@@ -13891,19 +14140,19 @@
         <v>827</v>
       </c>
       <c r="G3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="I3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J3" t="s">
         <v>615</v>
       </c>
       <c r="K3" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="L3" t="s">
         <v>81</v>
@@ -13932,19 +14181,19 @@
         <v>828</v>
       </c>
       <c r="G4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="I4" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J4" t="s">
         <v>641</v>
       </c>
       <c r="K4" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="L4" t="s">
         <v>81</v>
@@ -13973,19 +14222,19 @@
         <v>829</v>
       </c>
       <c r="G5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H5" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="I5" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J5" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="K5" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="L5" t="s">
         <v>81</v>
@@ -14014,19 +14263,19 @@
         <v>830</v>
       </c>
       <c r="G6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H6" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="I6" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J6" t="s">
         <v>623</v>
       </c>
       <c r="K6" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="L6" t="s">
         <v>81</v>
@@ -14055,19 +14304,19 @@
         <v>831</v>
       </c>
       <c r="G7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H7" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="I7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="J7" t="s">
         <v>1078</v>
       </c>
-      <c r="J7" t="s">
-        <v>1081</v>
-      </c>
       <c r="K7" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="L7" t="s">
         <v>81</v>
@@ -14096,19 +14345,19 @@
         <v>832</v>
       </c>
       <c r="G8" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H8" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I8" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J8" t="s">
         <v>627</v>
       </c>
       <c r="K8" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="L8" t="s">
         <v>81</v>
@@ -14137,19 +14386,19 @@
         <v>833</v>
       </c>
       <c r="G9" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H9" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="I9" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J9" t="s">
         <v>567</v>
       </c>
       <c r="K9" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="L9" t="s">
         <v>81</v>
@@ -14178,19 +14427,19 @@
         <v>834</v>
       </c>
       <c r="G10" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H10" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="I10" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J10" t="s">
         <v>548</v>
       </c>
       <c r="K10" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="L10" t="s">
         <v>81</v>
@@ -14219,19 +14468,19 @@
         <v>835</v>
       </c>
       <c r="G11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H11" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="I11" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J11" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="K11" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="L11" t="s">
         <v>81</v>
@@ -14260,19 +14509,19 @@
         <v>836</v>
       </c>
       <c r="G12" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H12" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="I12" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J12" t="s">
         <v>629</v>
       </c>
       <c r="K12" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="L12" t="s">
         <v>81</v>
@@ -14301,19 +14550,19 @@
         <v>837</v>
       </c>
       <c r="G13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H13" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="I13" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J13" t="s">
         <v>533</v>
       </c>
       <c r="K13" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="L13" t="s">
         <v>81</v>
@@ -14342,19 +14591,19 @@
         <v>838</v>
       </c>
       <c r="G14" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H14" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="I14" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J14" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="K14" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="L14" t="s">
         <v>81</v>
@@ -14383,19 +14632,19 @@
         <v>839</v>
       </c>
       <c r="G15" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H15" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="I15" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J15" t="s">
         <v>636</v>
       </c>
       <c r="K15" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="L15" t="s">
         <v>81</v>
@@ -14424,19 +14673,19 @@
         <v>840</v>
       </c>
       <c r="G16" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H16" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="I16" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J16" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="K16" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="L16" t="s">
         <v>81</v>
@@ -14465,19 +14714,19 @@
         <v>841</v>
       </c>
       <c r="G17" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H17" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="I17" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J17" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="K17" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="L17" t="s">
         <v>81</v>
@@ -14506,19 +14755,19 @@
         <v>842</v>
       </c>
       <c r="G18" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H18" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I18" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J18" t="s">
         <v>514</v>
       </c>
       <c r="K18" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="L18" t="s">
         <v>81</v>
@@ -14547,19 +14796,19 @@
         <v>843</v>
       </c>
       <c r="G19" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H19" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="I19" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J19" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="K19" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="L19" t="s">
         <v>81</v>
@@ -14588,19 +14837,19 @@
         <v>844</v>
       </c>
       <c r="G20" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H20" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I20" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J20" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="K20" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="L20" t="s">
         <v>81</v>
@@ -14629,19 +14878,19 @@
         <v>845</v>
       </c>
       <c r="G21" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H21" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="I21" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J21" t="s">
         <v>511</v>
       </c>
       <c r="K21" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="L21" t="s">
         <v>81</v>
@@ -14670,19 +14919,19 @@
         <v>846</v>
       </c>
       <c r="G22" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H22" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="I22" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J22" t="s">
         <v>141</v>
       </c>
       <c r="K22" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="L22" t="s">
         <v>81</v>
@@ -14711,19 +14960,19 @@
         <v>847</v>
       </c>
       <c r="G23" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H23" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="I23" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J23" t="s">
         <v>617</v>
       </c>
       <c r="K23" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="L23" t="s">
         <v>81</v>
@@ -14752,19 +15001,19 @@
         <v>848</v>
       </c>
       <c r="G24" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H24" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="I24" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J24" t="s">
         <v>598</v>
       </c>
       <c r="K24" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="L24" t="s">
         <v>81</v>
@@ -14793,19 +15042,19 @@
         <v>849</v>
       </c>
       <c r="G25" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H25" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I25" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J25" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="K25" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="L25" t="s">
         <v>81</v>
@@ -14834,19 +15083,19 @@
         <v>850</v>
       </c>
       <c r="G26" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H26" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="I26" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J26" t="s">
         <v>510</v>
       </c>
       <c r="K26" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="L26" t="s">
         <v>81</v>
@@ -14875,19 +15124,19 @@
         <v>851</v>
       </c>
       <c r="G27" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H27" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="I27" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J27" t="s">
         <v>539</v>
       </c>
       <c r="K27" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="L27" t="s">
         <v>81</v>
@@ -14916,19 +15165,19 @@
         <v>852</v>
       </c>
       <c r="G28" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H28" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="I28" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J28" t="s">
         <v>161</v>
       </c>
       <c r="K28" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="L28" t="s">
         <v>81</v>
@@ -14957,19 +15206,19 @@
         <v>853</v>
       </c>
       <c r="G29" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H29" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="I29" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J29" t="s">
         <v>550</v>
       </c>
       <c r="K29" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="L29" t="s">
         <v>81</v>
@@ -14998,19 +15247,19 @@
         <v>854</v>
       </c>
       <c r="G30" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H30" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I30" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J30" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="K30" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="L30" t="s">
         <v>81</v>
@@ -15039,19 +15288,19 @@
         <v>855</v>
       </c>
       <c r="G31" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H31" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I31" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J31" t="s">
         <v>135</v>
       </c>
       <c r="K31" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="L31" t="s">
         <v>81</v>
@@ -15080,19 +15329,19 @@
         <v>856</v>
       </c>
       <c r="G32" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H32" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="I32" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J32" t="s">
         <v>645</v>
       </c>
       <c r="K32" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="L32" t="s">
         <v>81</v>
@@ -15121,19 +15370,19 @@
         <v>857</v>
       </c>
       <c r="G33" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H33" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I33" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J33" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="K33" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="L33" t="s">
         <v>81</v>
@@ -15162,19 +15411,19 @@
         <v>858</v>
       </c>
       <c r="G34" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H34" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="I34" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J34" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="K34" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="L34" t="s">
         <v>81</v>
@@ -15203,19 +15452,19 @@
         <v>859</v>
       </c>
       <c r="G35" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H35" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="I35" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J35" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K35" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="L35" t="s">
         <v>81</v>
@@ -15244,19 +15493,19 @@
         <v>860</v>
       </c>
       <c r="G36" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H36" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="I36" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J36" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="K36" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="L36" t="s">
         <v>81</v>
@@ -15285,19 +15534,19 @@
         <v>861</v>
       </c>
       <c r="G37" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H37" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="I37" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J37" t="s">
         <v>542</v>
       </c>
       <c r="K37" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="L37" t="s">
         <v>81</v>
@@ -15326,19 +15575,19 @@
         <v>862</v>
       </c>
       <c r="G38" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H38" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="I38" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J38" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="K38" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="L38" t="s">
         <v>81</v>
@@ -15367,19 +15616,19 @@
         <v>863</v>
       </c>
       <c r="G39" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H39" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="I39" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J39" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="K39" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="L39" t="s">
         <v>81</v>
@@ -15408,19 +15657,19 @@
         <v>864</v>
       </c>
       <c r="G40" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H40" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="I40" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J40" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="K40" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="L40" t="s">
         <v>81</v>
@@ -15449,19 +15698,19 @@
         <v>865</v>
       </c>
       <c r="G41" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H41" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="I41" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J41" t="s">
         <v>526</v>
       </c>
       <c r="K41" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="L41" t="s">
         <v>81</v>
@@ -15490,19 +15739,19 @@
         <v>866</v>
       </c>
       <c r="G42" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H42" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="I42" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J42" t="s">
         <v>571</v>
       </c>
       <c r="K42" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="L42" t="s">
         <v>81</v>
@@ -15531,19 +15780,19 @@
         <v>867</v>
       </c>
       <c r="G43" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H43" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="I43" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J43" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="K43" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="L43" t="s">
         <v>81</v>
@@ -15572,19 +15821,19 @@
         <v>868</v>
       </c>
       <c r="G44" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H44" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="I44" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J44" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="K44" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="L44" t="s">
         <v>81</v>
@@ -15613,19 +15862,19 @@
         <v>866</v>
       </c>
       <c r="G45" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H45" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="I45" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J45" t="s">
         <v>142</v>
       </c>
       <c r="K45" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="L45" t="s">
         <v>81</v>
@@ -15654,19 +15903,19 @@
         <v>869</v>
       </c>
       <c r="G46" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H46" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="I46" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J46" t="s">
         <v>156</v>
       </c>
       <c r="K46" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="L46" t="s">
         <v>81</v>
@@ -15695,19 +15944,19 @@
         <v>870</v>
       </c>
       <c r="G47" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H47" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="I47" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J47" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="K47" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="L47" t="s">
         <v>81</v>
@@ -15736,19 +15985,19 @@
         <v>871</v>
       </c>
       <c r="G48" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H48" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="I48" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J48" t="s">
         <v>143</v>
       </c>
       <c r="K48" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="L48" t="s">
         <v>81</v>
@@ -15777,19 +16026,19 @@
         <v>872</v>
       </c>
       <c r="G49" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H49" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="I49" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J49" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="K49" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="L49" t="s">
         <v>81</v>
@@ -15818,19 +16067,19 @@
         <v>873</v>
       </c>
       <c r="G50" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H50" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="I50" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J50" t="s">
         <v>506</v>
       </c>
       <c r="K50" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="L50" t="s">
         <v>81</v>
@@ -15859,19 +16108,19 @@
         <v>874</v>
       </c>
       <c r="G51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H51" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="I51" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J51" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="K51" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="L51" t="s">
         <v>81</v>
@@ -15900,19 +16149,19 @@
         <v>875</v>
       </c>
       <c r="G52" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H52" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="I52" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J52" t="s">
         <v>562</v>
       </c>
       <c r="K52" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="L52" t="s">
         <v>81</v>
@@ -15941,19 +16190,19 @@
         <v>847</v>
       </c>
       <c r="G53" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H53" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="I53" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J53" t="s">
         <v>136</v>
       </c>
       <c r="K53" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="L53" t="s">
         <v>81</v>
@@ -15982,19 +16231,19 @@
         <v>849</v>
       </c>
       <c r="G54" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H54" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I54" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J54" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="K54" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="L54" t="s">
         <v>81</v>
@@ -16023,19 +16272,19 @@
         <v>851</v>
       </c>
       <c r="G55" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H55" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="I55" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J55" t="s">
         <v>541</v>
       </c>
       <c r="K55" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="L55" t="s">
         <v>81</v>
@@ -16064,19 +16313,19 @@
         <v>876</v>
       </c>
       <c r="G56" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H56" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="I56" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J56" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="K56" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="L56" t="s">
         <v>81</v>
@@ -16105,19 +16354,19 @@
         <v>877</v>
       </c>
       <c r="G57" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H57" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="I57" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J57" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="K57" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="L57" t="s">
         <v>81</v>
@@ -16146,19 +16395,19 @@
         <v>864</v>
       </c>
       <c r="G58" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H58" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="I58" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J58" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="K58" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="L58" t="s">
         <v>81</v>
@@ -16187,19 +16436,19 @@
         <v>831</v>
       </c>
       <c r="G59" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H59" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="I59" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J59" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="K59" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="L59" t="s">
         <v>81</v>
@@ -16228,19 +16477,19 @@
         <v>832</v>
       </c>
       <c r="G60" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H60" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I60" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J60" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="K60" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="L60" t="s">
         <v>81</v>
@@ -16269,19 +16518,19 @@
         <v>833</v>
       </c>
       <c r="G61" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H61" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="I61" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J61" t="s">
         <v>157</v>
       </c>
       <c r="K61" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="L61" t="s">
         <v>81</v>
@@ -16310,19 +16559,19 @@
         <v>835</v>
       </c>
       <c r="G62" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H62" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="I62" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J62" t="s">
         <v>151</v>
       </c>
       <c r="K62" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="L62" t="s">
         <v>81</v>
@@ -16351,19 +16600,19 @@
         <v>878</v>
       </c>
       <c r="G63" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H63" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="I63" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J63" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="K63" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="L63" t="s">
         <v>81</v>
@@ -16392,19 +16641,19 @@
         <v>839</v>
       </c>
       <c r="G64" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H64" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="I64" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J64" t="s">
         <v>145</v>
       </c>
       <c r="K64" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="L64" t="s">
         <v>81</v>
@@ -16433,19 +16682,19 @@
         <v>879</v>
       </c>
       <c r="G65" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H65" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="I65" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J65" t="s">
         <v>162</v>
       </c>
       <c r="K65" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="L65" t="s">
         <v>81</v>
@@ -16474,19 +16723,19 @@
         <v>842</v>
       </c>
       <c r="G66" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H66" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I66" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J66" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="K66" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="L66" t="s">
         <v>81</v>
@@ -16515,19 +16764,19 @@
         <v>845</v>
       </c>
       <c r="G67" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H67" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="I67" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J67" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="K67" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="L67" t="s">
         <v>81</v>
@@ -16556,19 +16805,19 @@
         <v>850</v>
       </c>
       <c r="G68" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H68" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="I68" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J68" t="s">
         <v>133</v>
       </c>
       <c r="K68" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="L68" t="s">
         <v>81</v>
@@ -16597,19 +16846,19 @@
         <v>880</v>
       </c>
       <c r="G69" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H69" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="I69" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J69" t="s">
         <v>604</v>
       </c>
       <c r="K69" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="L69" t="s">
         <v>81</v>
@@ -16638,19 +16887,19 @@
         <v>881</v>
       </c>
       <c r="G70" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H70" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="I70" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J70" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="K70" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="L70" t="s">
         <v>81</v>
@@ -16679,19 +16928,19 @@
         <v>882</v>
       </c>
       <c r="G71" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H71" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="I71" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J71" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="K71" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="L71" t="s">
         <v>81</v>
@@ -16720,19 +16969,19 @@
         <v>870</v>
       </c>
       <c r="G72" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H72" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="I72" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J72" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="K72" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="L72" t="s">
         <v>81</v>
@@ -16761,19 +17010,19 @@
         <v>858</v>
       </c>
       <c r="G73" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H73" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="I73" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J73" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="K73" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="L73" t="s">
         <v>81</v>
@@ -16802,19 +17051,19 @@
         <v>883</v>
       </c>
       <c r="G74" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H74" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="I74" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J74" t="s">
         <v>631</v>
       </c>
       <c r="K74" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="L74" t="s">
         <v>81</v>
@@ -16843,19 +17092,19 @@
         <v>866</v>
       </c>
       <c r="G75" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H75" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="I75" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J75" t="s">
         <v>521</v>
       </c>
       <c r="K75" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="L75" t="s">
         <v>81</v>
@@ -16884,19 +17133,19 @@
         <v>884</v>
       </c>
       <c r="G76" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H76" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="I76" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J76" t="s">
         <v>163</v>
       </c>
       <c r="K76" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="L76" t="s">
         <v>81</v>
@@ -16925,19 +17174,19 @@
         <v>885</v>
       </c>
       <c r="G77" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H77" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="I77" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J77" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="K77" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="L77" t="s">
         <v>81</v>
@@ -16966,19 +17215,19 @@
         <v>826</v>
       </c>
       <c r="G78" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H78" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I78" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J78" t="s">
         <v>580</v>
       </c>
       <c r="K78" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="L78" t="s">
         <v>81</v>
@@ -17007,19 +17256,19 @@
         <v>832</v>
       </c>
       <c r="G79" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H79" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I79" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J79" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="K79" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="L79" t="s">
         <v>81</v>
@@ -17048,19 +17297,19 @@
         <v>837</v>
       </c>
       <c r="G80" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H80" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="I80" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J80" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="K80" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="L80" t="s">
         <v>81</v>
@@ -17089,19 +17338,19 @@
         <v>841</v>
       </c>
       <c r="G81" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H81" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="I81" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J81" t="s">
         <v>146</v>
       </c>
       <c r="K81" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="L81" t="s">
         <v>81</v>
@@ -17130,19 +17379,19 @@
         <v>886</v>
       </c>
       <c r="G82" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H82" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="I82" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J82" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="K82" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="L82" t="s">
         <v>81</v>
@@ -17171,19 +17420,19 @@
         <v>887</v>
       </c>
       <c r="G83" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H83" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="I83" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J83" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="K83" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="L83" t="s">
         <v>81</v>
@@ -17212,19 +17461,19 @@
         <v>828</v>
       </c>
       <c r="G84" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H84" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="I84" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J84" t="s">
         <v>540</v>
       </c>
       <c r="K84" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="L84" t="s">
         <v>81</v>
@@ -17253,19 +17502,19 @@
         <v>829</v>
       </c>
       <c r="G85" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H85" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="I85" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J85" t="s">
         <v>529</v>
       </c>
       <c r="K85" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="L85" t="s">
         <v>81</v>
@@ -17294,19 +17543,19 @@
         <v>888</v>
       </c>
       <c r="G86" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H86" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="I86" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J86" t="s">
         <v>532</v>
       </c>
       <c r="K86" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="L86" t="s">
         <v>81</v>
@@ -17335,19 +17584,19 @@
         <v>874</v>
       </c>
       <c r="G87" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H87" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="I87" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J87" t="s">
         <v>549</v>
       </c>
       <c r="K87" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="L87" t="s">
         <v>81</v>
@@ -17376,19 +17625,19 @@
         <v>849</v>
       </c>
       <c r="G88" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H88" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I88" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J88" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="K88" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="L88" t="s">
         <v>81</v>
@@ -17417,19 +17666,19 @@
         <v>851</v>
       </c>
       <c r="G89" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H89" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="I89" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J89" t="s">
         <v>158</v>
       </c>
       <c r="K89" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="L89" t="s">
         <v>81</v>
@@ -17458,19 +17707,19 @@
         <v>889</v>
       </c>
       <c r="G90" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H90" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="I90" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J90" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="K90" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="L90" t="s">
         <v>81</v>
@@ -17499,19 +17748,19 @@
         <v>883</v>
       </c>
       <c r="G91" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H91" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="I91" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J91" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="K91" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="L91" t="s">
         <v>81</v>
@@ -17540,19 +17789,19 @@
         <v>864</v>
       </c>
       <c r="G92" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H92" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="I92" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J92" t="s">
         <v>600</v>
       </c>
       <c r="K92" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="L92" t="s">
         <v>81</v>
@@ -17581,19 +17830,19 @@
         <v>831</v>
       </c>
       <c r="G93" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H93" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="I93" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J93" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="K93" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="L93" t="s">
         <v>81</v>
@@ -17622,19 +17871,19 @@
         <v>890</v>
       </c>
       <c r="G94" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H94" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="I94" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J94" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="K94" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="L94" t="s">
         <v>81</v>
@@ -17663,19 +17912,19 @@
         <v>873</v>
       </c>
       <c r="G95" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H95" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="I95" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J95" t="s">
         <v>563</v>
       </c>
       <c r="K95" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="L95" t="s">
         <v>81</v>
@@ -17704,19 +17953,19 @@
         <v>835</v>
       </c>
       <c r="G96" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H96" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="I96" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J96" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="K96" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="L96" t="s">
         <v>81</v>
@@ -17745,19 +17994,19 @@
         <v>839</v>
       </c>
       <c r="G97" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H97" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="I97" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J97" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="K97" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="L97" t="s">
         <v>81</v>
@@ -17786,19 +18035,19 @@
         <v>850</v>
       </c>
       <c r="G98" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H98" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="I98" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J98" t="s">
         <v>612</v>
       </c>
       <c r="K98" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="L98" t="s">
         <v>81</v>
@@ -17827,19 +18076,19 @@
         <v>891</v>
       </c>
       <c r="G99" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H99" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="I99" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J99" t="s">
         <v>147</v>
       </c>
       <c r="K99" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="L99" t="s">
         <v>81</v>
@@ -17868,19 +18117,19 @@
         <v>887</v>
       </c>
       <c r="G100" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H100" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="I100" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J100" t="s">
         <v>639</v>
       </c>
       <c r="K100" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="L100" t="s">
         <v>81</v>
@@ -17909,19 +18158,19 @@
         <v>860</v>
       </c>
       <c r="G101" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H101" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="I101" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J101" t="s">
         <v>517</v>
       </c>
       <c r="K101" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="L101" t="s">
         <v>81</v>
@@ -17950,19 +18199,19 @@
         <v>871</v>
       </c>
       <c r="G102" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H102" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="I102" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J102" t="s">
         <v>579</v>
       </c>
       <c r="K102" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="L102" t="s">
         <v>81</v>
@@ -17991,19 +18240,19 @@
         <v>864</v>
       </c>
       <c r="G103" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H103" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="I103" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J103" t="s">
         <v>137</v>
       </c>
       <c r="K103" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="L103" t="s">
         <v>81</v>
@@ -18032,19 +18281,19 @@
         <v>827</v>
       </c>
       <c r="G104" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H104" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="I104" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J104" t="s">
         <v>525</v>
       </c>
       <c r="K104" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="L104" t="s">
         <v>81</v>
@@ -18073,19 +18322,19 @@
         <v>892</v>
       </c>
       <c r="G105" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H105" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="I105" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J105" t="s">
         <v>138</v>
       </c>
       <c r="K105" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="L105" t="s">
         <v>81</v>
@@ -18114,19 +18363,19 @@
         <v>893</v>
       </c>
       <c r="G106" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H106" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="I106" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J106" t="s">
         <v>551</v>
       </c>
       <c r="K106" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="L106" t="s">
         <v>81</v>
@@ -18155,19 +18404,19 @@
         <v>832</v>
       </c>
       <c r="G107" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H107" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I107" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J107" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="K107" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="L107" t="s">
         <v>81</v>
@@ -18196,19 +18445,19 @@
         <v>833</v>
       </c>
       <c r="G108" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H108" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="I108" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J108" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="K108" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="L108" t="s">
         <v>81</v>
@@ -18237,19 +18486,19 @@
         <v>894</v>
       </c>
       <c r="G109" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H109" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="I109" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J109" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="K109" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="L109" t="s">
         <v>81</v>
@@ -18278,19 +18527,19 @@
         <v>895</v>
       </c>
       <c r="G110" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H110" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I110" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J110" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="K110" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="L110" t="s">
         <v>81</v>
@@ -18319,19 +18568,19 @@
         <v>896</v>
       </c>
       <c r="G111" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H111" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="I111" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J111" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="K111" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="L111" t="s">
         <v>81</v>
@@ -18360,19 +18609,19 @@
         <v>897</v>
       </c>
       <c r="G112" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H112" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="I112" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="K112" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="L112" t="s">
         <v>81</v>
@@ -18401,19 +18650,19 @@
         <v>898</v>
       </c>
       <c r="G113" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H113" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I113" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J113" t="s">
         <v>585</v>
       </c>
       <c r="K113" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="L113" t="s">
         <v>81</v>
@@ -18442,19 +18691,19 @@
         <v>878</v>
       </c>
       <c r="G114" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H114" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="I114" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J114" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="K114" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="L114" t="s">
         <v>81</v>
@@ -18480,22 +18729,22 @@
         <v>130</v>
       </c>
       <c r="F115" t="s">
-        <v>899</v>
+        <v>841</v>
       </c>
       <c r="G115" t="s">
-        <v>983</v>
+        <v>924</v>
       </c>
       <c r="H115" t="s">
-        <v>1067</v>
+        <v>1007</v>
       </c>
       <c r="I115" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J115" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="K115" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="L115" t="s">
         <v>81</v>
@@ -18521,22 +18770,22 @@
         <v>130</v>
       </c>
       <c r="F116" t="s">
-        <v>841</v>
+        <v>879</v>
       </c>
       <c r="G116" t="s">
-        <v>925</v>
+        <v>962</v>
       </c>
       <c r="H116" t="s">
-        <v>1009</v>
+        <v>1045</v>
       </c>
       <c r="I116" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J116" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="K116" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="L116" t="s">
         <v>81</v>
@@ -18562,22 +18811,22 @@
         <v>130</v>
       </c>
       <c r="F117" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G117" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="H117" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="I117" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J117" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K117" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="L117" t="s">
         <v>81</v>
@@ -18603,22 +18852,22 @@
         <v>130</v>
       </c>
       <c r="F118" t="s">
-        <v>879</v>
+        <v>845</v>
       </c>
       <c r="G118" t="s">
-        <v>963</v>
+        <v>928</v>
       </c>
       <c r="H118" t="s">
-        <v>1047</v>
+        <v>1011</v>
       </c>
       <c r="I118" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J118" t="s">
-        <v>1137</v>
+        <v>596</v>
       </c>
       <c r="K118" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="L118" t="s">
         <v>81</v>
@@ -18644,22 +18893,22 @@
         <v>130</v>
       </c>
       <c r="F119" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G119" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="H119" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="I119" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J119" t="s">
-        <v>1138</v>
+        <v>587</v>
       </c>
       <c r="K119" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="L119" t="s">
         <v>81</v>
@@ -18685,22 +18934,22 @@
         <v>130</v>
       </c>
       <c r="F120" t="s">
-        <v>845</v>
+        <v>901</v>
       </c>
       <c r="G120" t="s">
-        <v>929</v>
+        <v>984</v>
       </c>
       <c r="H120" t="s">
-        <v>1013</v>
+        <v>1067</v>
       </c>
       <c r="I120" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J120" t="s">
-        <v>596</v>
+        <v>546</v>
       </c>
       <c r="K120" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="L120" t="s">
         <v>81</v>
@@ -18726,22 +18975,22 @@
         <v>130</v>
       </c>
       <c r="F121" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="G121" t="s">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="H121" t="s">
-        <v>1070</v>
+        <v>1049</v>
       </c>
       <c r="I121" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J121" t="s">
-        <v>587</v>
+        <v>1134</v>
       </c>
       <c r="K121" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="L121" t="s">
         <v>81</v>
@@ -18767,22 +19016,22 @@
         <v>130</v>
       </c>
       <c r="F122" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G122" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H122" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="I122" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J122" t="s">
-        <v>546</v>
+        <v>1135</v>
       </c>
       <c r="K122" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="L122" t="s">
         <v>81</v>
@@ -18808,22 +19057,22 @@
         <v>130</v>
       </c>
       <c r="F123" t="s">
-        <v>883</v>
+        <v>860</v>
       </c>
       <c r="G123" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="H123" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="I123" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J123" t="s">
-        <v>1139</v>
+        <v>635</v>
       </c>
       <c r="K123" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="L123" t="s">
         <v>81</v>
@@ -18849,22 +19098,22 @@
         <v>130</v>
       </c>
       <c r="F124" t="s">
-        <v>904</v>
+        <v>865</v>
       </c>
       <c r="G124" t="s">
-        <v>988</v>
+        <v>948</v>
       </c>
       <c r="H124" t="s">
-        <v>1072</v>
+        <v>1031</v>
       </c>
       <c r="I124" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J124" t="s">
-        <v>1140</v>
+        <v>159</v>
       </c>
       <c r="K124" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="L124" t="s">
         <v>81</v>
@@ -18890,22 +19139,22 @@
         <v>130</v>
       </c>
       <c r="F125" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="G125" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="H125" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="I125" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J125" t="s">
-        <v>635</v>
+        <v>504</v>
       </c>
       <c r="K125" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="L125" t="s">
         <v>81</v>
@@ -18916,13 +19165,13 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B126" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C126" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D126" t="s">
         <v>131</v>
@@ -18931,22 +19180,22 @@
         <v>130</v>
       </c>
       <c r="F126" t="s">
-        <v>865</v>
+        <v>830</v>
       </c>
       <c r="G126" t="s">
-        <v>949</v>
+        <v>913</v>
       </c>
       <c r="H126" t="s">
-        <v>1033</v>
+        <v>996</v>
       </c>
       <c r="I126" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J126" t="s">
-        <v>159</v>
+        <v>583</v>
       </c>
       <c r="K126" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="L126" t="s">
         <v>81</v>
@@ -18957,13 +19206,13 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B127" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C127" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D127" t="s">
         <v>131</v>
@@ -18972,22 +19221,22 @@
         <v>130</v>
       </c>
       <c r="F127" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="G127" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="H127" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="I127" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J127" t="s">
-        <v>504</v>
+        <v>1136</v>
       </c>
       <c r="K127" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="L127" t="s">
         <v>81</v>
@@ -19013,22 +19262,22 @@
         <v>130</v>
       </c>
       <c r="F128" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G128" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H128" t="s">
         <v>998</v>
       </c>
       <c r="I128" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J128" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="K128" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="L128" t="s">
         <v>81</v>
@@ -19054,22 +19303,22 @@
         <v>130</v>
       </c>
       <c r="F129" t="s">
-        <v>873</v>
+        <v>896</v>
       </c>
       <c r="G129" t="s">
-        <v>957</v>
+        <v>979</v>
       </c>
       <c r="H129" t="s">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="I129" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J129" t="s">
-        <v>1141</v>
+        <v>160</v>
       </c>
       <c r="K129" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="L129" t="s">
         <v>81</v>
@@ -19095,22 +19344,22 @@
         <v>130</v>
       </c>
       <c r="F130" t="s">
-        <v>832</v>
+        <v>898</v>
       </c>
       <c r="G130" t="s">
-        <v>916</v>
+        <v>981</v>
       </c>
       <c r="H130" t="s">
-        <v>1000</v>
+        <v>1064</v>
       </c>
       <c r="I130" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J130" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="K130" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="L130" t="s">
         <v>81</v>
@@ -19136,22 +19385,22 @@
         <v>130</v>
       </c>
       <c r="F131" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="G131" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="H131" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="I131" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J131" t="s">
-        <v>160</v>
+        <v>1137</v>
       </c>
       <c r="K131" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="L131" t="s">
         <v>81</v>
@@ -19177,22 +19426,22 @@
         <v>130</v>
       </c>
       <c r="F132" t="s">
-        <v>898</v>
+        <v>839</v>
       </c>
       <c r="G132" t="s">
-        <v>982</v>
+        <v>922</v>
       </c>
       <c r="H132" t="s">
-        <v>1066</v>
+        <v>1005</v>
       </c>
       <c r="I132" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J132" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="K132" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="L132" t="s">
         <v>81</v>
@@ -19218,22 +19467,22 @@
         <v>130</v>
       </c>
       <c r="F133" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G133" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H133" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="I133" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J133" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="K133" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="L133" t="s">
         <v>81</v>
@@ -19259,22 +19508,22 @@
         <v>130</v>
       </c>
       <c r="F134" t="s">
-        <v>839</v>
+        <v>879</v>
       </c>
       <c r="G134" t="s">
-        <v>923</v>
+        <v>962</v>
       </c>
       <c r="H134" t="s">
-        <v>1007</v>
+        <v>1045</v>
       </c>
       <c r="I134" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J134" t="s">
-        <v>610</v>
+        <v>578</v>
       </c>
       <c r="K134" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="L134" t="s">
         <v>81</v>
@@ -19300,22 +19549,22 @@
         <v>130</v>
       </c>
       <c r="F135" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G135" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="H135" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="I135" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J135" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="K135" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="L135" t="s">
         <v>81</v>
@@ -19341,22 +19590,22 @@
         <v>130</v>
       </c>
       <c r="F136" t="s">
-        <v>879</v>
+        <v>845</v>
       </c>
       <c r="G136" t="s">
-        <v>963</v>
+        <v>928</v>
       </c>
       <c r="H136" t="s">
-        <v>1047</v>
+        <v>1011</v>
       </c>
       <c r="I136" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J136" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="K136" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="L136" t="s">
         <v>81</v>
@@ -19382,22 +19631,22 @@
         <v>130</v>
       </c>
       <c r="F137" t="s">
-        <v>901</v>
+        <v>848</v>
       </c>
       <c r="G137" t="s">
-        <v>985</v>
+        <v>931</v>
       </c>
       <c r="H137" t="s">
-        <v>1069</v>
+        <v>1014</v>
       </c>
       <c r="I137" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J137" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="K137" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="L137" t="s">
         <v>81</v>
@@ -19423,22 +19672,22 @@
         <v>130</v>
       </c>
       <c r="F138" t="s">
-        <v>845</v>
+        <v>905</v>
       </c>
       <c r="G138" t="s">
-        <v>929</v>
+        <v>988</v>
       </c>
       <c r="H138" t="s">
-        <v>1013</v>
+        <v>1071</v>
       </c>
       <c r="I138" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J138" t="s">
-        <v>558</v>
+        <v>513</v>
       </c>
       <c r="K138" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="L138" t="s">
         <v>81</v>
@@ -19464,22 +19713,22 @@
         <v>130</v>
       </c>
       <c r="F139" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="G139" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="H139" t="s">
-        <v>1016</v>
+        <v>1046</v>
       </c>
       <c r="I139" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J139" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="K139" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="L139" t="s">
         <v>81</v>
@@ -19505,22 +19754,22 @@
         <v>130</v>
       </c>
       <c r="F140" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="G140" t="s">
-        <v>990</v>
+        <v>965</v>
       </c>
       <c r="H140" t="s">
-        <v>1074</v>
+        <v>1048</v>
       </c>
       <c r="I140" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J140" t="s">
-        <v>513</v>
+        <v>139</v>
       </c>
       <c r="K140" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="L140" t="s">
         <v>81</v>
@@ -19546,22 +19795,22 @@
         <v>130</v>
       </c>
       <c r="F141" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="G141" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="H141" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="I141" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J141" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="K141" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="L141" t="s">
         <v>81</v>
@@ -19587,22 +19836,22 @@
         <v>130</v>
       </c>
       <c r="F142" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="G142" t="s">
-        <v>966</v>
+        <v>989</v>
       </c>
       <c r="H142" t="s">
-        <v>1050</v>
+        <v>1072</v>
       </c>
       <c r="I142" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J142" t="s">
-        <v>139</v>
+        <v>1143</v>
       </c>
       <c r="K142" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="L142" t="s">
         <v>81</v>
@@ -19628,22 +19877,22 @@
         <v>130</v>
       </c>
       <c r="F143" t="s">
-        <v>870</v>
+        <v>907</v>
       </c>
       <c r="G143" t="s">
-        <v>954</v>
+        <v>990</v>
       </c>
       <c r="H143" t="s">
-        <v>1038</v>
+        <v>1073</v>
       </c>
       <c r="I143" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J143" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="K143" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="L143" t="s">
         <v>81</v>
@@ -19669,22 +19918,22 @@
         <v>130</v>
       </c>
       <c r="F144" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G144" t="s">
         <v>991</v>
       </c>
       <c r="H144" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I144" t="s">
         <v>1075</v>
       </c>
-      <c r="I144" t="s">
-        <v>1078</v>
-      </c>
       <c r="J144" t="s">
-        <v>1148</v>
+        <v>643</v>
       </c>
       <c r="K144" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="L144" t="s">
         <v>81</v>
@@ -19710,22 +19959,22 @@
         <v>130</v>
       </c>
       <c r="F145" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
       <c r="G145" t="s">
-        <v>992</v>
+        <v>966</v>
       </c>
       <c r="H145" t="s">
-        <v>1076</v>
+        <v>1049</v>
       </c>
       <c r="I145" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J145" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="K145" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="L145" t="s">
         <v>81</v>
@@ -19751,22 +20000,22 @@
         <v>130</v>
       </c>
       <c r="F146" t="s">
-        <v>909</v>
+        <v>860</v>
       </c>
       <c r="G146" t="s">
-        <v>993</v>
+        <v>943</v>
       </c>
       <c r="H146" t="s">
-        <v>1077</v>
+        <v>1026</v>
       </c>
       <c r="I146" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J146" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="K146" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="L146" t="s">
         <v>81</v>
@@ -19792,22 +20041,22 @@
         <v>130</v>
       </c>
       <c r="F147" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="G147" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="H147" t="s">
-        <v>1051</v>
+        <v>1037</v>
       </c>
       <c r="I147" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J147" t="s">
-        <v>1150</v>
+        <v>544</v>
       </c>
       <c r="K147" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="L147" t="s">
         <v>81</v>
@@ -19833,22 +20082,22 @@
         <v>130</v>
       </c>
       <c r="F148" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="G148" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="H148" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="I148" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J148" t="s">
-        <v>634</v>
+        <v>599</v>
       </c>
       <c r="K148" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="L148" t="s">
         <v>81</v>
@@ -19874,22 +20123,22 @@
         <v>130</v>
       </c>
       <c r="F149" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="G149" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="H149" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="I149" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J149" t="s">
-        <v>544</v>
+        <v>1146</v>
       </c>
       <c r="K149" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="L149" t="s">
         <v>81</v>
@@ -19900,13 +20149,13 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B150" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D150" t="s">
         <v>131</v>
@@ -19915,22 +20164,22 @@
         <v>130</v>
       </c>
       <c r="F150" t="s">
-        <v>864</v>
+        <v>826</v>
       </c>
       <c r="G150" t="s">
-        <v>948</v>
+        <v>909</v>
       </c>
       <c r="H150" t="s">
-        <v>1032</v>
+        <v>992</v>
       </c>
       <c r="I150" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J150" t="s">
-        <v>599</v>
+        <v>140</v>
       </c>
       <c r="K150" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="L150" t="s">
         <v>81</v>
@@ -19941,13 +20190,13 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D151" t="s">
         <v>131</v>
@@ -19956,22 +20205,22 @@
         <v>130</v>
       </c>
       <c r="F151" t="s">
-        <v>867</v>
+        <v>837</v>
       </c>
       <c r="G151" t="s">
-        <v>951</v>
+        <v>920</v>
       </c>
       <c r="H151" t="s">
-        <v>1035</v>
+        <v>1003</v>
       </c>
       <c r="I151" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J151" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="K151" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="L151" t="s">
         <v>81</v>
@@ -19997,22 +20246,22 @@
         <v>130</v>
       </c>
       <c r="F152" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="G152" t="s">
-        <v>910</v>
+        <v>924</v>
       </c>
       <c r="H152" t="s">
-        <v>994</v>
+        <v>1007</v>
       </c>
       <c r="I152" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J152" t="s">
-        <v>140</v>
+        <v>1148</v>
       </c>
       <c r="K152" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="L152" t="s">
         <v>81</v>
@@ -20038,22 +20287,22 @@
         <v>130</v>
       </c>
       <c r="F153" t="s">
-        <v>837</v>
+        <v>886</v>
       </c>
       <c r="G153" t="s">
-        <v>921</v>
+        <v>969</v>
       </c>
       <c r="H153" t="s">
-        <v>1005</v>
+        <v>1052</v>
       </c>
       <c r="I153" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J153" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="K153" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="L153" t="s">
         <v>81</v>
@@ -20079,22 +20328,22 @@
         <v>130</v>
       </c>
       <c r="F154" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="G154" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="H154" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="I154" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J154" t="s">
-        <v>1153</v>
+        <v>553</v>
       </c>
       <c r="K154" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="L154" t="s">
         <v>81</v>
@@ -20120,22 +20369,22 @@
         <v>130</v>
       </c>
       <c r="F155" t="s">
-        <v>886</v>
+        <v>849</v>
       </c>
       <c r="G155" t="s">
-        <v>970</v>
+        <v>932</v>
       </c>
       <c r="H155" t="s">
-        <v>1054</v>
+        <v>1015</v>
       </c>
       <c r="I155" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J155" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="K155" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="L155" t="s">
         <v>81</v>
@@ -20161,22 +20410,22 @@
         <v>130</v>
       </c>
       <c r="F156" t="s">
-        <v>846</v>
+        <v>891</v>
       </c>
       <c r="G156" t="s">
-        <v>930</v>
+        <v>974</v>
       </c>
       <c r="H156" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="I156" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J156" t="s">
-        <v>553</v>
+        <v>1151</v>
       </c>
       <c r="K156" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="L156" t="s">
         <v>81</v>
@@ -20202,22 +20451,22 @@
         <v>130</v>
       </c>
       <c r="F157" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="G157" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="H157" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="I157" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J157" t="s">
-        <v>1155</v>
+        <v>626</v>
       </c>
       <c r="K157" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="L157" t="s">
         <v>81</v>
@@ -20243,22 +20492,22 @@
         <v>130</v>
       </c>
       <c r="F158" t="s">
-        <v>891</v>
+        <v>860</v>
       </c>
       <c r="G158" t="s">
-        <v>975</v>
+        <v>943</v>
       </c>
       <c r="H158" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="I158" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J158" t="s">
-        <v>1156</v>
+        <v>586</v>
       </c>
       <c r="K158" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="L158" t="s">
         <v>81</v>
@@ -20284,22 +20533,22 @@
         <v>130</v>
       </c>
       <c r="F159" t="s">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="G159" t="s">
-        <v>938</v>
+        <v>954</v>
       </c>
       <c r="H159" t="s">
-        <v>1022</v>
+        <v>1037</v>
       </c>
       <c r="I159" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J159" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="K159" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="L159" t="s">
         <v>81</v>
@@ -20325,109 +20574,27 @@
         <v>130</v>
       </c>
       <c r="F160" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="G160" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="H160" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="I160" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="J160" t="s">
-        <v>586</v>
+        <v>1152</v>
       </c>
       <c r="K160" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="L160" t="s">
         <v>81</v>
       </c>
       <c r="M160" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13">
-      <c r="A161" t="s">
-        <v>25</v>
-      </c>
-      <c r="B161" t="s">
-        <v>53</v>
-      </c>
-      <c r="C161" t="s">
-        <v>39</v>
-      </c>
-      <c r="D161" t="s">
-        <v>131</v>
-      </c>
-      <c r="E161" t="s">
-        <v>130</v>
-      </c>
-      <c r="F161" t="s">
-        <v>871</v>
-      </c>
-      <c r="G161" t="s">
-        <v>955</v>
-      </c>
-      <c r="H161" t="s">
-        <v>1039</v>
-      </c>
-      <c r="I161" t="s">
-        <v>1078</v>
-      </c>
-      <c r="J161" t="s">
-        <v>620</v>
-      </c>
-      <c r="K161" t="s">
-        <v>1317</v>
-      </c>
-      <c r="L161" t="s">
-        <v>81</v>
-      </c>
-      <c r="M161" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13">
-      <c r="A162" t="s">
-        <v>25</v>
-      </c>
-      <c r="B162" t="s">
-        <v>53</v>
-      </c>
-      <c r="C162" t="s">
-        <v>39</v>
-      </c>
-      <c r="D162" t="s">
-        <v>131</v>
-      </c>
-      <c r="E162" t="s">
-        <v>130</v>
-      </c>
-      <c r="F162" t="s">
-        <v>866</v>
-      </c>
-      <c r="G162" t="s">
-        <v>950</v>
-      </c>
-      <c r="H162" t="s">
-        <v>1034</v>
-      </c>
-      <c r="I162" t="s">
-        <v>1078</v>
-      </c>
-      <c r="J162" t="s">
-        <v>1157</v>
-      </c>
-      <c r="K162" t="s">
-        <v>1318</v>
-      </c>
-      <c r="L162" t="s">
-        <v>81</v>
-      </c>
-      <c r="M162" t="s">
         <v>81</v>
       </c>
     </row>
@@ -20438,15 +20605,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="B1" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -20454,86 +20621,446 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="B2" t="s">
-        <v>1329</v>
+        <v>1352</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1390</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
       <c r="B3" t="s">
-        <v>1330</v>
+        <v>1353</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1391</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
       <c r="B4" t="s">
-        <v>1331</v>
+        <v>1354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1337</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1324</v>
+        <v>1317</v>
       </c>
       <c r="B5" t="s">
-        <v>1332</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>1325</v>
+        <v>1318</v>
       </c>
       <c r="B6" t="s">
-        <v>1333</v>
+        <v>1356</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1393</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
       <c r="B7" t="s">
-        <v>1334</v>
+        <v>1357</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1338</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
       <c r="B8" t="s">
-        <v>1335</v>
+        <v>1358</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1339</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>1328</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B16" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>1336</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B24" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>1340</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1423</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1"/>
-    <hyperlink ref="C7" r:id="rId2"/>
-    <hyperlink ref="C8" r:id="rId3"/>
-    <hyperlink ref="C9" r:id="rId4"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C6" r:id="rId4"/>
+    <hyperlink ref="C7" r:id="rId5"/>
+    <hyperlink ref="C8" r:id="rId6"/>
+    <hyperlink ref="C9" r:id="rId7"/>
+    <hyperlink ref="C10" r:id="rId8"/>
+    <hyperlink ref="C12" r:id="rId9"/>
+    <hyperlink ref="C13" r:id="rId10"/>
+    <hyperlink ref="C14" r:id="rId11"/>
+    <hyperlink ref="C15" r:id="rId12"/>
+    <hyperlink ref="C16" r:id="rId13"/>
+    <hyperlink ref="C17" r:id="rId14"/>
+    <hyperlink ref="C18" r:id="rId15"/>
+    <hyperlink ref="C19" r:id="rId16"/>
+    <hyperlink ref="C21" r:id="rId17"/>
+    <hyperlink ref="C22" r:id="rId18"/>
+    <hyperlink ref="C23" r:id="rId19"/>
+    <hyperlink ref="C24" r:id="rId20"/>
+    <hyperlink ref="C26" r:id="rId21"/>
+    <hyperlink ref="C27" r:id="rId22"/>
+    <hyperlink ref="C28" r:id="rId23"/>
+    <hyperlink ref="C29" r:id="rId24"/>
+    <hyperlink ref="C30" r:id="rId25"/>
+    <hyperlink ref="C31" r:id="rId26"/>
+    <hyperlink ref="C32" r:id="rId27"/>
+    <hyperlink ref="C33" r:id="rId28"/>
+    <hyperlink ref="C34" r:id="rId29"/>
+    <hyperlink ref="C35" r:id="rId30"/>
+    <hyperlink ref="C36" r:id="rId31"/>
+    <hyperlink ref="C37" r:id="rId32"/>
+    <hyperlink ref="C38" r:id="rId33"/>
+    <hyperlink ref="C39" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5234" uniqueCount="1450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5251" uniqueCount="1464">
   <si>
     <t>ID</t>
   </si>
@@ -98,46 +98,46 @@
     <t>S0013</t>
   </si>
   <si>
-    <t>tool--545d5d1f-54c2-4f20-868a-7a0689b98583</t>
-  </si>
-  <si>
-    <t>tool--6fd47d4c-bac8-4dcd-b582-e6a42bb51313</t>
-  </si>
-  <si>
-    <t>tool--6faacf93-e3f5-43f6-8d94-9d2c7c6382a9</t>
-  </si>
-  <si>
-    <t>tool--43db716c-e55e-4798-8810-4606ebb81e52</t>
-  </si>
-  <si>
-    <t>tool--1652bd4f-c611-4f10-aedc-6581590e2df2</t>
-  </si>
-  <si>
-    <t>tool--4d2e439d-9619-4447-8a41-1af8960acc55</t>
-  </si>
-  <si>
-    <t>tool--4a55efd1-b775-4318-8adc-ebb029729960</t>
-  </si>
-  <si>
-    <t>tool--b591e96e-6cd5-4b20-9c6f-aa7dc5747255</t>
-  </si>
-  <si>
-    <t>tool--03b1e023-5469-49ea-9988-c7118a91b725</t>
-  </si>
-  <si>
-    <t>tool--ed0808d4-111e-4057-a345-7d951b669eb5</t>
-  </si>
-  <si>
-    <t>tool--60f65bd4-46b3-4eed-9418-254cf51965fd</t>
-  </si>
-  <si>
-    <t>tool--78806636-7cbc-4a54-9f61-2a5a98a33f13</t>
-  </si>
-  <si>
-    <t>tool--17849785-49e2-4f22-9488-618cbc11cec9</t>
-  </si>
-  <si>
-    <t>tool--b8bf442f-c688-4983-bc89-7fc0e5a2d70f</t>
+    <t>tool--7a23a962-6a24-49c1-80ad-d7ef44f2ccac</t>
+  </si>
+  <si>
+    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
+  </si>
+  <si>
+    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
+  </si>
+  <si>
+    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
+  </si>
+  <si>
+    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
+  </si>
+  <si>
+    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
+  </si>
+  <si>
+    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
+  </si>
+  <si>
+    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
+  </si>
+  <si>
+    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
+  </si>
+  <si>
+    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
+  </si>
+  <si>
+    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
+  </si>
+  <si>
+    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
+  </si>
+  <si>
+    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
+  </si>
+  <si>
+    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
   </si>
   <si>
     <t>Верховный тайный совет</t>
@@ -298,43 +298,43 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Історія Донецької області — Вікіпедія 2026)</t>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Перепис населення Російської імперії (1897),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Історія України — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026)</t>
   </si>
   <si>
     <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>,(Citation: Друга Малоросійська колегія — Вікіпедія 2026),</t>
   </si>
   <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014)</t>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Історія України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Історія України — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Московсько-українська війна (1658—1659),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Русско-турецкая война (1877—1878),(Citation: Повстання бузьких козаків (1817),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Листопадове повстання (1830—1831),(Citation: Переяславські статті (1659),(Citation: Мазепа 2007),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Російсько-українська війна (з 2014),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Московсько-українська війна (1658—1659),(Citation: Російсько-турецька війна (1806—1812),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Переяславські статті (1659),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Північна війна (1700—1721),(Citation: Запорозька Січ — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Руїна — Вікіпедія 2026),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: Руїна — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Північна війна (1700—1721),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Решетилівські статті — Вікіпедія 2026)</t>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Московсько-українська війна (1658—1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Крымская война — Википедия 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Московські статті (1665),(Citation: Русско-турецкая война (1877—1878),(Citation: Повстання бузьких козаків (1817),(Citation: Мазепа 2007),(Citation: Російсько-українська війна (з 2014),(Citation: Переяславські статті (1659),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Північна війна (1700—1721),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659)</t>
+  </si>
+  <si>
+    <t>(Citation: Руїна — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Руїна — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -403,22 +403,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--6bb397ce-d257-45ef-9a68-fd682239dc91</t>
-  </si>
-  <si>
-    <t>intrusion-set--080fc39f-be32-4bdf-aa6b-d86e3dcd4f81</t>
-  </si>
-  <si>
-    <t>intrusion-set--6fcf2657-4840-4754-a318-5cee4b91d670</t>
-  </si>
-  <si>
-    <t>intrusion-set--4f0187aa-3964-42bb-8185-827fd9232dcb</t>
-  </si>
-  <si>
-    <t>intrusion-set--1e2aa43d-a27c-407c-b94a-405123ec52f9</t>
-  </si>
-  <si>
-    <t>intrusion-set--701ece7a-3998-432c-ab53-b4496887b072</t>
+    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
+  </si>
+  <si>
+    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
+  </si>
+  <si>
+    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
+  </si>
+  <si>
+    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
+  </si>
+  <si>
+    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
+  </si>
+  <si>
+    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
   </si>
   <si>
     <t>group</t>
@@ -502,7 +502,7 @@
     <t>Уничтожение гражданских и просветительских структур в местах компактного проживания диаспоры: «Ліквідація 'Просвіт' на Кубані, в Зеленому Клину» (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Организация фейковых безальтернативных «Народных сборов» под контролем оккупационных войск для юридического оформления захвата. (Citation: Історія України — Вікіпедія 2026)</t>
@@ -532,106 +532,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--748adbe7-f59c-4bc0-97f4-de3ec43934c9</t>
-  </si>
-  <si>
-    <t>relationship--223dcaad-ae78-43af-86c8-5494371b1d37</t>
-  </si>
-  <si>
-    <t>relationship--54823f51-aa85-4d2f-ba24-5f50309914c7</t>
-  </si>
-  <si>
-    <t>relationship--ac746805-7a46-4ae9-8b34-a32e9a11c539</t>
-  </si>
-  <si>
-    <t>relationship--4964717a-b221-499a-927d-39dcb9db33a2</t>
-  </si>
-  <si>
-    <t>relationship--7c711dce-6dd9-45f8-8bc2-7343d77afe0f</t>
-  </si>
-  <si>
-    <t>relationship--6b10a528-82da-42f7-9cdc-1aa588fab481</t>
-  </si>
-  <si>
-    <t>relationship--bc8eb603-4feb-4413-bf43-80cb97d78378</t>
-  </si>
-  <si>
-    <t>relationship--6156c3c7-b5ba-49fd-b912-528c84e7a683</t>
-  </si>
-  <si>
-    <t>relationship--addd0ef0-894f-455c-8180-38cd60e04c37</t>
-  </si>
-  <si>
-    <t>relationship--ffc52e98-63f1-4ff9-9e6c-0ecf73c132a4</t>
-  </si>
-  <si>
-    <t>relationship--5e3dfb1e-eacc-43fe-ab72-12a4adcd0e10</t>
-  </si>
-  <si>
-    <t>relationship--b13a8a02-0a0e-461c-bb4b-4a4376ff35c6</t>
-  </si>
-  <si>
-    <t>relationship--6a268ffe-5e34-4dff-86c0-07aa08dcb5a2</t>
-  </si>
-  <si>
-    <t>relationship--be640a50-5ff4-4b10-ba98-384c9b0d55c8</t>
-  </si>
-  <si>
-    <t>relationship--7776534d-2830-47ec-a5f7-3cfce9bb3d44</t>
-  </si>
-  <si>
-    <t>relationship--374dc1bc-6679-4a55-9b31-fb16e91b7f00</t>
-  </si>
-  <si>
-    <t>relationship--c8637b07-3a35-46c8-aa81-13619be9953e</t>
-  </si>
-  <si>
-    <t>relationship--8dd4ccd1-6e48-4e5c-9b30-f06ab1d93521</t>
-  </si>
-  <si>
-    <t>relationship--5dcc9361-437b-4a59-a451-3d954258d94d</t>
-  </si>
-  <si>
-    <t>relationship--9d98aef8-2024-4ee4-84cc-07e3af7e47c5</t>
-  </si>
-  <si>
-    <t>relationship--856984be-eae4-4f32-b090-8ed806b87c1e</t>
-  </si>
-  <si>
-    <t>relationship--df3c4fca-1b31-4f57-a805-f4f74a87dfe7</t>
-  </si>
-  <si>
-    <t>relationship--014fda40-f5c3-47ed-a2ed-3b6b46c55878</t>
-  </si>
-  <si>
-    <t>relationship--f85f034d-6561-4988-abaa-ac7172a7bd76</t>
-  </si>
-  <si>
-    <t>relationship--55964349-3162-4e27-bb1e-abf01bb55215</t>
-  </si>
-  <si>
-    <t>relationship--4534db45-fe9b-4f0e-aedc-98ad60b13128</t>
-  </si>
-  <si>
-    <t>relationship--4330ffb9-d8ff-4288-ac43-6a065a313900</t>
-  </si>
-  <si>
-    <t>relationship--3d908446-973f-47fc-a39e-3789efe97ff3</t>
-  </si>
-  <si>
-    <t>relationship--232d9c6f-6ad7-4312-a2d8-c607f9ee0276</t>
-  </si>
-  <si>
-    <t>relationship--e642c95f-3e56-4c24-a977-d86cc4c20ba3</t>
-  </si>
-  <si>
-    <t>relationship--8227572b-82be-4c2c-861b-5113f97dfddd</t>
-  </si>
-  <si>
-    <t>relationship--f7a0de34-a733-435a-9ec1-62e98780f91a</t>
-  </si>
-  <si>
-    <t>relationship--06fe07f5-9a2f-47f1-b0a5-6e296fb85588</t>
+    <t>relationship--ee1770df-945f-4564-9553-b1d84f490dcd</t>
+  </si>
+  <si>
+    <t>relationship--8bc54604-c986-43f2-a701-b12592389a95</t>
+  </si>
+  <si>
+    <t>relationship--653bfee4-8148-4228-b9ad-a0dd9f6fb024</t>
+  </si>
+  <si>
+    <t>relationship--8c5d41d1-9fc6-4849-a964-d4d4cd88d808</t>
+  </si>
+  <si>
+    <t>relationship--5be4de54-a976-41cf-9a3e-801a66dd4ab0</t>
+  </si>
+  <si>
+    <t>relationship--f005b199-111a-4b05-aefa-24a35febc482</t>
+  </si>
+  <si>
+    <t>relationship--0dbf3ce6-19bd-478e-adf9-32c6e80ed0ea</t>
+  </si>
+  <si>
+    <t>relationship--c208739a-827c-4d0e-bf28-61b916f15cfe</t>
+  </si>
+  <si>
+    <t>relationship--614fbc69-8cba-40a0-98f9-936eaac5419e</t>
+  </si>
+  <si>
+    <t>relationship--ca9d96ad-f282-4c8a-a7f1-c49268bc3a88</t>
+  </si>
+  <si>
+    <t>relationship--086b6153-43f4-47de-80df-44693f738943</t>
+  </si>
+  <si>
+    <t>relationship--8a4808c1-777c-40fc-aa35-f6cd68dc33c2</t>
+  </si>
+  <si>
+    <t>relationship--37a411b5-a9ad-4aa3-b275-64db44664d5d</t>
+  </si>
+  <si>
+    <t>relationship--aee80eb9-ab23-4760-8add-e0216bd30a05</t>
+  </si>
+  <si>
+    <t>relationship--ca3971ca-3608-4f4b-ba38-3b8e016ebf03</t>
+  </si>
+  <si>
+    <t>relationship--80974889-50af-4c79-93b8-102362fc0530</t>
+  </si>
+  <si>
+    <t>relationship--e6ca03f6-6ec1-4870-bcb9-a3c507268afb</t>
+  </si>
+  <si>
+    <t>relationship--2a6b0d1a-4fc7-40de-9362-c8eb8abcb9fa</t>
+  </si>
+  <si>
+    <t>relationship--df0ae14a-9167-4c70-bba9-d917ecd1bcbe</t>
+  </si>
+  <si>
+    <t>relationship--38cbf6e2-05be-4c93-9361-7c3355dec29f</t>
+  </si>
+  <si>
+    <t>relationship--eb3986b1-fecd-4d37-92dd-0c8250ef0740</t>
+  </si>
+  <si>
+    <t>relationship--388cb58a-f6b1-432c-aa19-57cc86f8713f</t>
+  </si>
+  <si>
+    <t>relationship--c6850c22-f194-48a1-b786-c5cf857b99cd</t>
+  </si>
+  <si>
+    <t>relationship--917fb287-22e5-452a-9dc2-8c5c8aca7d1b</t>
+  </si>
+  <si>
+    <t>relationship--34cf12dd-b962-4ebe-830a-d8f1c7ff5c4f</t>
+  </si>
+  <si>
+    <t>relationship--94711d8b-0578-438a-9d73-eafd0c1bc983</t>
+  </si>
+  <si>
+    <t>relationship--8045380f-5282-4b2f-ab8f-cb92ffd304a3</t>
+  </si>
+  <si>
+    <t>relationship--3536b790-3098-4639-9c74-ac882b5ab83e</t>
+  </si>
+  <si>
+    <t>relationship--c09a449b-0b73-4e67-abc0-922897a14e61</t>
+  </si>
+  <si>
+    <t>relationship--079404c8-fadc-4028-b464-f31ba21f9514</t>
+  </si>
+  <si>
+    <t>relationship--51aabffe-86e6-4eaa-bf10-1d5525e930ad</t>
+  </si>
+  <si>
+    <t>relationship--49567418-6145-460a-ab69-bcb7861395ac</t>
+  </si>
+  <si>
+    <t>relationship--69dc0331-617e-4089-ac23-257dbeee91a6</t>
+  </si>
+  <si>
+    <t>relationship--57e6a8bb-5b08-4144-8f3d-8b095b08d609</t>
   </si>
   <si>
     <t>C0009</t>
@@ -1240,307 +1240,307 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--84bc21e9-f278-45cd-8acb-817742dcff21</t>
-  </si>
-  <si>
-    <t>campaign--4bf56bd2-d5ca-438b-a3aa-5cbc36381133</t>
-  </si>
-  <si>
-    <t>campaign--3bd127a5-73b3-4aac-8fd7-982a95669434</t>
-  </si>
-  <si>
-    <t>campaign--1b611c93-e848-4ee1-8527-8bbbdf2e62a5</t>
-  </si>
-  <si>
-    <t>campaign--09a157f6-2eda-4e89-85e1-0705374ca9ee</t>
-  </si>
-  <si>
-    <t>campaign--d2e92b25-7923-452d-8885-6245a64315da</t>
-  </si>
-  <si>
-    <t>campaign--20b4d9b6-86c9-414d-b7c2-ba45639bfae6</t>
-  </si>
-  <si>
-    <t>campaign--dbcf8329-be72-43a6-9503-bd3b5f80e167</t>
-  </si>
-  <si>
-    <t>campaign--06e4cf4f-1d7a-4669-bfe2-46cf114cf71f</t>
-  </si>
-  <si>
-    <t>campaign--d1a75343-e6bc-456b-af9c-67abfebd8778</t>
-  </si>
-  <si>
-    <t>campaign--a1253a3a-9d62-49e1-acc7-7430a198b8bc</t>
-  </si>
-  <si>
-    <t>campaign--7c61ae27-c860-4b7d-9dbc-12b393680025</t>
-  </si>
-  <si>
-    <t>campaign--0c5ea36b-4e12-47ff-8d99-a4a35e4327b0</t>
-  </si>
-  <si>
-    <t>campaign--8ba7050c-642b-4ab9-9ce1-6ca4a4676ab5</t>
-  </si>
-  <si>
-    <t>campaign--6232bf9b-bb63-402d-b03e-9a0515ee09d8</t>
-  </si>
-  <si>
-    <t>campaign--9f962768-2e42-4c2e-a172-9291db92461b</t>
-  </si>
-  <si>
-    <t>campaign--2e0766ba-2d5c-4bab-a68b-5fe011747831</t>
-  </si>
-  <si>
-    <t>campaign--4a0448c0-0001-4134-acd4-941aa1379172</t>
-  </si>
-  <si>
-    <t>campaign--eedf404e-3e21-4116-be4d-0d7601599b91</t>
-  </si>
-  <si>
-    <t>campaign--e62f4c80-a205-4fe1-91c4-85256ac37f31</t>
-  </si>
-  <si>
-    <t>campaign--6ceef077-03f6-482f-8e76-a98491db2913</t>
-  </si>
-  <si>
-    <t>campaign--2248df9e-ba27-43a8-98d8-9026a6b9de03</t>
-  </si>
-  <si>
-    <t>campaign--05daf063-815a-43c4-bdef-868e86a89149</t>
-  </si>
-  <si>
-    <t>campaign--584843e9-c5e0-4087-a142-c385deeb2bdf</t>
-  </si>
-  <si>
-    <t>campaign--a657f3f9-0df3-4ed7-a7a4-a5412ea7ecb6</t>
-  </si>
-  <si>
-    <t>campaign--8f323bf8-3b9b-4bf4-97ad-3d61fc33fd82</t>
-  </si>
-  <si>
-    <t>campaign--6e5202d1-fbbe-422b-84d5-246cb35c0b2d</t>
-  </si>
-  <si>
-    <t>campaign--8ba3d669-f614-429f-9b77-a9cf527ff71d</t>
-  </si>
-  <si>
-    <t>campaign--7ce1e89d-a9af-4fb3-81ee-15ea23718846</t>
-  </si>
-  <si>
-    <t>campaign--6c24cbbb-4ce2-45a1-981a-cf0fd9c34d97</t>
-  </si>
-  <si>
-    <t>campaign--b9baf1bc-a3fa-4050-8722-e4ac1d29b0aa</t>
-  </si>
-  <si>
-    <t>campaign--eb1f4e4b-b946-449e-8752-60b5a41d8094</t>
-  </si>
-  <si>
-    <t>campaign--fa1c9409-7b35-48bb-8f3f-1de992f2a9fe</t>
-  </si>
-  <si>
-    <t>campaign--485bc4b1-d6a0-4262-b92b-de60846a3cc2</t>
-  </si>
-  <si>
-    <t>campaign--f98d27b7-b9b2-4ee5-968d-2242b9fed57d</t>
-  </si>
-  <si>
-    <t>campaign--d9246b40-5b51-4294-bcd6-dba876074271</t>
-  </si>
-  <si>
-    <t>campaign--c084e1db-0f03-44c2-8697-12757be14ecf</t>
-  </si>
-  <si>
-    <t>campaign--78366146-c147-4bca-adbc-91cf59affa19</t>
-  </si>
-  <si>
-    <t>campaign--c4b1a1bd-5808-4f82-8404-cb671321f0b8</t>
-  </si>
-  <si>
-    <t>campaign--4cb4ba5f-3257-4a64-99a7-89c1c8584ea3</t>
-  </si>
-  <si>
-    <t>campaign--bb5621a4-0317-4a72-9557-a3309369a148</t>
-  </si>
-  <si>
-    <t>campaign--c00efded-d911-444c-8743-89ddb7c2a25b</t>
-  </si>
-  <si>
-    <t>campaign--33e7df73-0ba4-4031-911d-d9a34f23381e</t>
-  </si>
-  <si>
-    <t>campaign--398bbef2-59b4-4eae-b7fb-2ddb4325a3db</t>
-  </si>
-  <si>
-    <t>campaign--5e9e3ee9-0edc-47b8-b51f-27d825c93ba6</t>
-  </si>
-  <si>
-    <t>campaign--a928c5b5-bd92-4716-bd4b-8e2e42e22ee8</t>
-  </si>
-  <si>
-    <t>campaign--13a5e084-1143-4c42-82a1-97c7cc060f9c</t>
-  </si>
-  <si>
-    <t>campaign--2f03ada1-afc9-4e6a-b822-aa65414b1b02</t>
-  </si>
-  <si>
-    <t>campaign--6d1a46e6-ac73-4930-aabd-a8f533a687cf</t>
-  </si>
-  <si>
-    <t>campaign--5f6c1d2e-8b43-49f7-9d3f-f3a0c3ae48b1</t>
-  </si>
-  <si>
-    <t>campaign--2e2bed38-682c-4d2f-ad6c-e2bb4c4cfdd0</t>
-  </si>
-  <si>
-    <t>campaign--fcb45d3f-14e8-4834-8b2c-d18b4c8f5273</t>
-  </si>
-  <si>
-    <t>campaign--c86c2f91-e10d-4e8b-b767-78378e15121e</t>
-  </si>
-  <si>
-    <t>campaign--0ba3a916-5b43-4183-b453-0927882dba85</t>
-  </si>
-  <si>
-    <t>campaign--e0cc83b8-2a5f-42f8-8537-a7a3e72ee650</t>
-  </si>
-  <si>
-    <t>campaign--4fa7d988-4c1c-4971-84cf-ca0467775997</t>
-  </si>
-  <si>
-    <t>campaign--49d099af-a6dc-4afe-8188-c064ef26fde7</t>
-  </si>
-  <si>
-    <t>campaign--007f466b-7682-4d8a-b195-22c21ff3e565</t>
-  </si>
-  <si>
-    <t>campaign--8f1d796b-636c-4cd1-86b4-37c3ece5165a</t>
-  </si>
-  <si>
-    <t>campaign--3d806c36-94c1-487f-b65e-9ff91c2a9abb</t>
-  </si>
-  <si>
-    <t>campaign--f2ebdc18-4134-4740-9f13-2c482064e83a</t>
-  </si>
-  <si>
-    <t>campaign--c4507383-caba-4152-b825-48578038d866</t>
-  </si>
-  <si>
-    <t>campaign--127d73b7-ad29-4bc6-bae2-aec0c43bad66</t>
-  </si>
-  <si>
-    <t>campaign--b67d3570-8e41-417e-8f8e-7d5ecb7e1d31</t>
-  </si>
-  <si>
-    <t>campaign--7b0b746d-42c4-4b10-aa04-8bfec1343821</t>
-  </si>
-  <si>
-    <t>campaign--d00c3e48-4826-4f1e-bfb7-118f00d84861</t>
-  </si>
-  <si>
-    <t>campaign--51b9d6b1-568b-4d68-8f9c-19a0b548272b</t>
-  </si>
-  <si>
-    <t>campaign--ce760399-e985-4e95-bb41-7d3b796dd18b</t>
-  </si>
-  <si>
-    <t>campaign--4e66eed7-56a9-48ac-8a18-99a559927eb6</t>
-  </si>
-  <si>
-    <t>campaign--152cca2d-a341-45fd-a306-6690c012f021</t>
-  </si>
-  <si>
-    <t>campaign--387e09ec-bf7a-447c-a918-bcff0ee9da8b</t>
-  </si>
-  <si>
-    <t>campaign--beeb4667-4ab9-4028-94c4-b6b19eefabeb</t>
-  </si>
-  <si>
-    <t>campaign--40524974-ff86-4741-bc58-ccfb35d10bc7</t>
-  </si>
-  <si>
-    <t>campaign--d5059819-4fb3-4b0e-9e0a-5784b854386c</t>
-  </si>
-  <si>
-    <t>campaign--0dca3871-e3fd-47d7-a07f-e9ea15919c0d</t>
-  </si>
-  <si>
-    <t>campaign--d6da9526-4dd6-4eb9-abfd-44a5e1879d41</t>
-  </si>
-  <si>
-    <t>campaign--b1e8059c-3914-414e-8a6d-0fb74549bec8</t>
-  </si>
-  <si>
-    <t>campaign--2660323c-96cd-4d12-920b-3ca598fbdb74</t>
-  </si>
-  <si>
-    <t>campaign--a51dfeb5-c6ce-44b2-9bc5-c4c6687bd2f0</t>
-  </si>
-  <si>
-    <t>campaign--f3a217be-13bd-488e-b046-33d4a55b2cf3</t>
-  </si>
-  <si>
-    <t>campaign--5424b97c-0790-47c0-bc6a-99fda22a8e9d</t>
-  </si>
-  <si>
-    <t>campaign--6733da7e-2f67-4c13-97a6-00b05a549f10</t>
-  </si>
-  <si>
-    <t>campaign--ce5cc518-cbce-4e92-b8ff-30e504c15c2c</t>
-  </si>
-  <si>
-    <t>campaign--2907649b-fd94-42fa-8784-f18f4584d71a</t>
-  </si>
-  <si>
-    <t>campaign--dddb4201-585e-47c1-95e9-425b0730fb90</t>
-  </si>
-  <si>
-    <t>campaign--cf6632c9-6e3d-4cbc-9dce-724891b573c7</t>
-  </si>
-  <si>
-    <t>campaign--e7ee89b0-2cb6-4b84-948c-7057dd523852</t>
-  </si>
-  <si>
-    <t>campaign--eddd1738-28fd-4da0-b6f4-7c44a32152b7</t>
-  </si>
-  <si>
-    <t>campaign--5fa57ffc-7b8e-49c1-82da-60712fe1a716</t>
-  </si>
-  <si>
-    <t>campaign--466f1dd3-c4d2-4076-b0d7-d52a41e7bc83</t>
-  </si>
-  <si>
-    <t>campaign--11dce568-2d19-4c59-bdfd-64ec6fced3e6</t>
-  </si>
-  <si>
-    <t>campaign--0356e86e-0974-45cf-b41d-6997de20ba10</t>
-  </si>
-  <si>
-    <t>campaign--0956db31-89c5-43f3-aaa6-f6d9b3b7ff12</t>
-  </si>
-  <si>
-    <t>campaign--5177f321-68a6-4d63-a678-c5265f63243b</t>
-  </si>
-  <si>
-    <t>campaign--7402cc4a-618b-4851-8075-cb883379e3c0</t>
-  </si>
-  <si>
-    <t>campaign--b5ce00ca-7682-4ce8-9c4c-8be0c65df490</t>
-  </si>
-  <si>
-    <t>campaign--af98cd78-ddfd-4a73-8ab2-5b920e8221ac</t>
-  </si>
-  <si>
-    <t>campaign--9f187028-927d-4536-ba2f-3f2177c0e164</t>
-  </si>
-  <si>
-    <t>campaign--66970f35-4e71-491e-932e-1fee6b188e71</t>
-  </si>
-  <si>
-    <t>campaign--d419efc6-e0ba-4f5e-83a2-46e1d38cd231</t>
-  </si>
-  <si>
-    <t>campaign--09ffe87c-9f1c-4a9e-9879-3648aa2d3535</t>
+    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
+  </si>
+  <si>
+    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
+  </si>
+  <si>
+    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
+  </si>
+  <si>
+    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
+  </si>
+  <si>
+    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
+  </si>
+  <si>
+    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
+  </si>
+  <si>
+    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
+  </si>
+  <si>
+    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
+  </si>
+  <si>
+    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
+  </si>
+  <si>
+    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
+  </si>
+  <si>
+    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
+  </si>
+  <si>
+    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
+  </si>
+  <si>
+    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
+  </si>
+  <si>
+    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
+  </si>
+  <si>
+    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
+  </si>
+  <si>
+    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
+  </si>
+  <si>
+    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
+  </si>
+  <si>
+    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
+  </si>
+  <si>
+    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
+  </si>
+  <si>
+    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
+  </si>
+  <si>
+    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
+  </si>
+  <si>
+    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
+  </si>
+  <si>
+    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
+  </si>
+  <si>
+    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
+  </si>
+  <si>
+    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
+  </si>
+  <si>
+    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
+  </si>
+  <si>
+    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
+  </si>
+  <si>
+    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
+  </si>
+  <si>
+    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
+  </si>
+  <si>
+    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
+  </si>
+  <si>
+    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
+  </si>
+  <si>
+    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
+  </si>
+  <si>
+    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
+  </si>
+  <si>
+    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
+  </si>
+  <si>
+    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
+  </si>
+  <si>
+    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
+  </si>
+  <si>
+    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
+  </si>
+  <si>
+    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
+  </si>
+  <si>
+    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
+  </si>
+  <si>
+    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
+  </si>
+  <si>
+    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
+  </si>
+  <si>
+    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
+  </si>
+  <si>
+    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
+  </si>
+  <si>
+    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
+  </si>
+  <si>
+    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
+  </si>
+  <si>
+    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
+  </si>
+  <si>
+    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
+  </si>
+  <si>
+    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
+  </si>
+  <si>
+    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
+  </si>
+  <si>
+    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
+  </si>
+  <si>
+    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
+  </si>
+  <si>
+    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
+  </si>
+  <si>
+    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
+  </si>
+  <si>
+    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
+  </si>
+  <si>
+    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
+  </si>
+  <si>
+    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
+  </si>
+  <si>
+    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
+  </si>
+  <si>
+    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
+  </si>
+  <si>
+    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
+  </si>
+  <si>
+    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
+  </si>
+  <si>
+    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
+  </si>
+  <si>
+    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
+  </si>
+  <si>
+    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
+  </si>
+  <si>
+    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
+  </si>
+  <si>
+    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
+  </si>
+  <si>
+    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
+  </si>
+  <si>
+    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
+  </si>
+  <si>
+    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
+  </si>
+  <si>
+    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
+  </si>
+  <si>
+    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
+  </si>
+  <si>
+    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
+  </si>
+  <si>
+    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
+  </si>
+  <si>
+    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
+  </si>
+  <si>
+    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
+  </si>
+  <si>
+    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
+  </si>
+  <si>
+    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
+  </si>
+  <si>
+    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
+  </si>
+  <si>
+    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
+  </si>
+  <si>
+    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
+  </si>
+  <si>
+    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
+  </si>
+  <si>
+    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
+  </si>
+  <si>
+    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
+  </si>
+  <si>
+    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
+  </si>
+  <si>
+    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
+  </si>
+  <si>
+    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
+  </si>
+  <si>
+    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
+  </si>
+  <si>
+    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
+  </si>
+  <si>
+    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
+  </si>
+  <si>
+    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
+  </si>
+  <si>
+    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
+  </si>
+  <si>
+    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
+  </si>
+  <si>
+    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
+  </si>
+  <si>
+    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
+  </si>
+  <si>
+    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
+  </si>
+  <si>
+    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
+  </si>
+  <si>
+    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
+  </si>
+  <si>
+    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
+  </si>
+  <si>
+    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
+  </si>
+  <si>
+    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
+  </si>
+  <si>
+    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
+  </si>
+  <si>
+    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
   </si>
   <si>
     <t>campaign</t>
@@ -1843,7 +1843,7 @@
     <t>Вторжение регулярной армии РФ и нанесение массированных ракетно-авиационных ударов по Киеву, Днепру, Харькову и другим украинским городам ранним утром 24 февраля 2022 года. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Систематические кибератаки на энергетические компании и муниципальные теплоснабжающие предприятия в условиях полномасштабной войны для прекращения подачи электроэнергии и тепла украинским гражданским потребителям. (Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®) (Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024). 
+    <t>Систематические кибератаки на энергетические компании и муниципальные теплоснабжающие предприятия в условиях полномасштабной войны для прекращения подачи электроэнергии и тепла украинским гражданским потребителям. (Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024) (Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024). 
 Систематическое нанесение массированных ударов крылатыми ракетами и дронами-камикадзе (Shahed) по объектам генерации (Змиевская ТЭЦ, Харьковская ТЭЦ-5, Трипольская ТЭС, ДнепроГЭС) и трансформаторным подстанциям для создания блэкаутов. (Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026)</t>
   </si>
   <si>
@@ -2003,553 +2003,553 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--889d82e4-c966-46ee-813f-71a4ed883cb3</t>
-  </si>
-  <si>
-    <t>relationship--da414b25-28e7-4ad0-8cca-2cd59cdc48e1</t>
-  </si>
-  <si>
-    <t>relationship--aad22950-d6b3-4fe0-b4b4-caad525e66f9</t>
-  </si>
-  <si>
-    <t>relationship--da141e9b-14f5-475d-99d3-c04fc29be05a</t>
-  </si>
-  <si>
-    <t>relationship--85595de6-5e82-4a7f-b38b-4b435d8cf145</t>
-  </si>
-  <si>
-    <t>relationship--7b26ad80-eb32-4bc4-862c-c1bea3fbb5b8</t>
-  </si>
-  <si>
-    <t>relationship--64c6a3db-95b7-4e80-8617-864066661402</t>
-  </si>
-  <si>
-    <t>relationship--35e874c2-2f0e-465c-84a3-1a52fb3c1b26</t>
-  </si>
-  <si>
-    <t>relationship--dcff66f2-928d-4376-b74d-88e6e8dbf2a5</t>
-  </si>
-  <si>
-    <t>relationship--d7492bb2-0caf-43b4-ae2b-8ee766277e6f</t>
-  </si>
-  <si>
-    <t>relationship--cbae46bb-6a35-426e-b26f-99c4dcfb2180</t>
-  </si>
-  <si>
-    <t>relationship--1708cf7c-b8a3-467b-bfc8-b4377ecd8c38</t>
-  </si>
-  <si>
-    <t>relationship--7574787e-7bb0-4142-9608-d3431597b447</t>
-  </si>
-  <si>
-    <t>relationship--11b3f371-48c5-4e60-aa9e-0916f44736d9</t>
-  </si>
-  <si>
-    <t>relationship--cc273750-9b46-4c99-b177-0a13451fa78b</t>
-  </si>
-  <si>
-    <t>relationship--622624c2-53db-46f8-be5e-d6e076333f46</t>
-  </si>
-  <si>
-    <t>relationship--22bea2fb-f567-4526-920e-59a0897693d6</t>
-  </si>
-  <si>
-    <t>relationship--44443958-236b-4f9d-8dd9-dd2639671b09</t>
-  </si>
-  <si>
-    <t>relationship--0eca743f-f114-4eda-8c60-ec4089510360</t>
-  </si>
-  <si>
-    <t>relationship--78491aa4-2e4c-497b-a148-f18a3699f56b</t>
-  </si>
-  <si>
-    <t>relationship--7b87aecc-4151-47c7-bdb2-52939bf7dbc3</t>
-  </si>
-  <si>
-    <t>relationship--c8b13959-0d01-4ec3-a0f5-48fc07bbf2cb</t>
-  </si>
-  <si>
-    <t>relationship--65a5ac54-0c22-4eb2-aa18-8fdad83e0379</t>
-  </si>
-  <si>
-    <t>relationship--ee484915-af85-415a-aee2-59f72dfabfee</t>
-  </si>
-  <si>
-    <t>relationship--54b740d5-dc2a-488a-9abe-15274e89c834</t>
-  </si>
-  <si>
-    <t>relationship--d4163bd3-d740-44b0-84b8-52453b734603</t>
-  </si>
-  <si>
-    <t>relationship--9f8b72df-9550-4e18-b5b9-5f6d5dbdb913</t>
-  </si>
-  <si>
-    <t>relationship--111463bd-bdd5-4238-b51c-d664db9a7527</t>
-  </si>
-  <si>
-    <t>relationship--e7d51b28-6ac8-4287-8edd-a7a2eebd5b96</t>
-  </si>
-  <si>
-    <t>relationship--c1d642c5-e1bf-4fcb-b15e-f3b758183aeb</t>
-  </si>
-  <si>
-    <t>relationship--644b2b16-6c0b-4193-9307-c7c5138365ad</t>
-  </si>
-  <si>
-    <t>relationship--5f5efdfd-5041-41ef-8ee9-25f9ab012dcf</t>
-  </si>
-  <si>
-    <t>relationship--543ae80c-998e-4a3d-87fc-2a0b9571daf1</t>
-  </si>
-  <si>
-    <t>relationship--5c23f23c-fa2c-42fc-a317-81435663b76b</t>
-  </si>
-  <si>
-    <t>relationship--90480a09-7e26-49ad-a06f-27abea71cd39</t>
-  </si>
-  <si>
-    <t>relationship--fa31a1e8-20be-4e59-acc3-f09fe1e88b70</t>
-  </si>
-  <si>
-    <t>relationship--06d0ed0b-2c51-4206-b60a-a6e4ff14aa9c</t>
-  </si>
-  <si>
-    <t>relationship--82488210-7fea-4709-b86a-ef25cc365ac6</t>
-  </si>
-  <si>
-    <t>relationship--961f7abb-d697-447f-937b-f617667fb890</t>
-  </si>
-  <si>
-    <t>relationship--afe322f3-20c6-4e19-bd5f-d934c0474718</t>
-  </si>
-  <si>
-    <t>relationship--c43b0019-ba2d-48ae-b94b-d9c00bdc7252</t>
-  </si>
-  <si>
-    <t>relationship--08a9e1b2-e85d-4cc5-bff1-39e0b459d38d</t>
-  </si>
-  <si>
-    <t>relationship--9fd32872-fa9b-4d10-a701-c9b9194b1faa</t>
-  </si>
-  <si>
-    <t>relationship--c20acf41-bf5b-459b-9d0e-13fac2907477</t>
-  </si>
-  <si>
-    <t>relationship--6a767d68-cfbb-4a18-8f10-94e866e5b8d7</t>
-  </si>
-  <si>
-    <t>relationship--a3737ab9-45f4-4cc1-b6a0-13c844b88dde</t>
-  </si>
-  <si>
-    <t>relationship--901f30d8-fc0c-4eb8-96f9-32d584a54246</t>
-  </si>
-  <si>
-    <t>relationship--b7663582-1572-4a44-b833-ad625c8cb24e</t>
-  </si>
-  <si>
-    <t>relationship--66e8ebce-a52b-4c43-9394-179226de2659</t>
-  </si>
-  <si>
-    <t>relationship--2fa363d9-3c0c-4552-90c7-8b8da0401f52</t>
-  </si>
-  <si>
-    <t>relationship--9f7e791a-cc20-4d06-9580-dd8ca3b03a4d</t>
-  </si>
-  <si>
-    <t>relationship--80b672fa-e491-44f1-9d66-d0c4886e6662</t>
-  </si>
-  <si>
-    <t>relationship--98d1d772-87b7-4001-b802-5b49faa65cee</t>
-  </si>
-  <si>
-    <t>relationship--213bdb84-51c4-45d0-89ac-99e1ee8522ee</t>
-  </si>
-  <si>
-    <t>relationship--17dea7f1-bad6-4016-b896-5ee021167a3c</t>
-  </si>
-  <si>
-    <t>relationship--7ac430ee-94d3-4633-8163-1e741c370134</t>
-  </si>
-  <si>
-    <t>relationship--422dfbc2-8291-4dc5-aefb-11bd94209cdc</t>
-  </si>
-  <si>
-    <t>relationship--11dc28fb-4450-4809-88bb-0c900fe1c2f3</t>
-  </si>
-  <si>
-    <t>relationship--dbf0b5c8-d27a-43c6-aedc-094feb1c0d90</t>
-  </si>
-  <si>
-    <t>relationship--51500d5f-2f2e-41c6-ad55-109ac321d20e</t>
-  </si>
-  <si>
-    <t>relationship--615b98b1-f463-4b83-b8a3-b570adafa3cc</t>
-  </si>
-  <si>
-    <t>relationship--f3d4e74c-fff3-4f81-b8fa-e219a78584cd</t>
-  </si>
-  <si>
-    <t>relationship--02303830-e777-4696-abd6-79af6cc46785</t>
-  </si>
-  <si>
-    <t>relationship--bd8df92b-4f7e-4fa1-a913-989c9b017938</t>
-  </si>
-  <si>
-    <t>relationship--3c03a0ec-6f48-48ea-b065-211f31f2894e</t>
-  </si>
-  <si>
-    <t>relationship--f8c0eb74-3575-4c55-a2d7-fba3ae802c40</t>
-  </si>
-  <si>
-    <t>relationship--da2da2f9-6084-45e5-a597-036208e9789e</t>
-  </si>
-  <si>
-    <t>relationship--c6ba7b3a-658d-4451-a98d-734322d8c54f</t>
-  </si>
-  <si>
-    <t>relationship--50ddb0a0-2867-44ed-91bc-b4dc901c80a3</t>
-  </si>
-  <si>
-    <t>relationship--88bccc8a-f7a2-49e1-a46f-367f8e27b642</t>
-  </si>
-  <si>
-    <t>relationship--3da1cb1c-cbae-43c0-bda4-07e3c264e71e</t>
-  </si>
-  <si>
-    <t>relationship--4f9574d4-02b8-4eca-9761-bbe5c069b344</t>
-  </si>
-  <si>
-    <t>relationship--9b16c020-b229-44f3-a8a1-c734308acc2a</t>
-  </si>
-  <si>
-    <t>relationship--4ae6a58e-d25b-48f8-ad29-e635c557e4fb</t>
-  </si>
-  <si>
-    <t>relationship--f53a0328-348d-41c6-8135-0ca1de900c44</t>
-  </si>
-  <si>
-    <t>relationship--3f994d91-2c90-41f2-92d8-263b6b544715</t>
-  </si>
-  <si>
-    <t>relationship--8df57727-064b-46cf-b734-615967f897af</t>
-  </si>
-  <si>
-    <t>relationship--0f783440-214a-4e1b-a578-17f990858926</t>
-  </si>
-  <si>
-    <t>relationship--57032a0b-d541-41be-b819-7d0d63f0b5e3</t>
-  </si>
-  <si>
-    <t>relationship--127fbaae-cb89-4739-a530-200a56c7969f</t>
-  </si>
-  <si>
-    <t>relationship--0f43555b-8d92-45d3-ba11-936e6545bc93</t>
-  </si>
-  <si>
-    <t>relationship--eeae3f06-5874-46d3-b082-b8562399910a</t>
-  </si>
-  <si>
-    <t>relationship--08d9608a-ea6a-41f0-af32-d0c899a83e7c</t>
-  </si>
-  <si>
-    <t>relationship--f1861116-7010-481e-8a86-6186461e7dbc</t>
-  </si>
-  <si>
-    <t>relationship--1821da0f-0ff6-4632-aec7-b813e5a83ca2</t>
-  </si>
-  <si>
-    <t>relationship--ae7cce33-6c06-40ca-8b00-7ba834cf1c0d</t>
-  </si>
-  <si>
-    <t>relationship--bb414712-b107-42a6-9d85-b650a2de464b</t>
-  </si>
-  <si>
-    <t>relationship--f6f0c367-67f9-48a0-a597-0ae07851f48a</t>
-  </si>
-  <si>
-    <t>relationship--d950ef63-aa43-40c9-8f83-813083d3d88f</t>
-  </si>
-  <si>
-    <t>relationship--78a7ef97-62b2-4fb4-ac12-997a6aed2ac6</t>
-  </si>
-  <si>
-    <t>relationship--8b727f87-2159-4163-939d-91e1821413e5</t>
-  </si>
-  <si>
-    <t>relationship--a04c3a8d-a32f-4a26-9115-bf067c7473c7</t>
-  </si>
-  <si>
-    <t>relationship--47631dd5-2035-4775-9342-c7a5d57463d2</t>
-  </si>
-  <si>
-    <t>relationship--22eff706-0769-49f0-9f2f-776115e3b86f</t>
-  </si>
-  <si>
-    <t>relationship--96909df7-d822-41ef-bce3-59aeb959f27f</t>
-  </si>
-  <si>
-    <t>relationship--a2be2f18-7418-4bc3-8d13-5a5cc0535a48</t>
-  </si>
-  <si>
-    <t>relationship--30fc98f5-39ab-4f73-9cf8-ecd4f13bad9c</t>
-  </si>
-  <si>
-    <t>relationship--20819672-cfc6-4d90-9978-67392464f9b5</t>
-  </si>
-  <si>
-    <t>relationship--0ea39f20-20c1-4f5a-97d8-19f243edd037</t>
-  </si>
-  <si>
-    <t>relationship--509c7f00-4bc2-49ff-93b0-830f5a811d4a</t>
-  </si>
-  <si>
-    <t>relationship--27307274-6d91-422f-892f-1920ff7f356d</t>
-  </si>
-  <si>
-    <t>relationship--ff40733b-8dae-4471-9e66-760250865fb7</t>
-  </si>
-  <si>
-    <t>relationship--493ade73-abf7-427c-9d87-81defb451d8b</t>
-  </si>
-  <si>
-    <t>relationship--e37eb846-1fc9-44d6-b0a4-05048966e228</t>
-  </si>
-  <si>
-    <t>relationship--a505add1-1a18-4ee5-b1db-fec9c4f48f9c</t>
-  </si>
-  <si>
-    <t>relationship--3b9ac042-c0a7-49ac-857f-05065c54075a</t>
-  </si>
-  <si>
-    <t>relationship--f4f67668-aa63-4766-9725-8f5b0aa8fe4e</t>
-  </si>
-  <si>
-    <t>relationship--1a0ed787-6e98-4d1c-8eaf-ad7622f746b6</t>
-  </si>
-  <si>
-    <t>relationship--51d34cd7-27af-4321-ad3b-c00925ef3bae</t>
-  </si>
-  <si>
-    <t>relationship--38934af6-e0df-4e99-8832-19dfc5aa76fb</t>
-  </si>
-  <si>
-    <t>relationship--8fe1cf5e-353d-49a0-9a18-5c9ce6519107</t>
-  </si>
-  <si>
-    <t>relationship--4b75d83e-aa45-4bdb-9e77-44ab08e9e40b</t>
-  </si>
-  <si>
-    <t>relationship--f06fd8d9-aef2-401f-a307-ca5a0e1285d2</t>
-  </si>
-  <si>
-    <t>relationship--62a5317c-5ba6-408f-9c80-5acfdbd32ee7</t>
-  </si>
-  <si>
-    <t>relationship--77903336-6ba1-40d5-91c7-6ca3ee9c4098</t>
-  </si>
-  <si>
-    <t>relationship--164df4fe-b365-4045-b692-006cc7379eaf</t>
-  </si>
-  <si>
-    <t>relationship--614cfb78-516d-4af0-a676-9f08e44f9179</t>
-  </si>
-  <si>
-    <t>relationship--49632cf4-f231-4539-bbc9-8d6680780a06</t>
-  </si>
-  <si>
-    <t>relationship--a6f31e13-5817-48e2-95f9-24e9d1cbbfc4</t>
-  </si>
-  <si>
-    <t>relationship--f8f236df-0be2-479d-9462-b5d67379bd51</t>
-  </si>
-  <si>
-    <t>relationship--408cd846-38c1-4247-9909-d37fb7b69199</t>
-  </si>
-  <si>
-    <t>relationship--b398d380-4b24-465a-a0a8-9ac8b2f5bd1b</t>
-  </si>
-  <si>
-    <t>relationship--221a7cb6-0e1b-4214-8620-8256aca937f3</t>
-  </si>
-  <si>
-    <t>relationship--b1876f95-fc2c-4f14-8cb5-afdf4ac78fd4</t>
-  </si>
-  <si>
-    <t>relationship--1a627c96-3d45-4503-b6d6-cf1bdac82c8c</t>
-  </si>
-  <si>
-    <t>relationship--abd1d624-9fb5-4369-940c-7d0015306b05</t>
-  </si>
-  <si>
-    <t>relationship--5aeacb37-7169-48d1-b03e-a8ffcf494f58</t>
-  </si>
-  <si>
-    <t>relationship--69546bbe-81ad-44d9-b7f3-7d3c24af479c</t>
-  </si>
-  <si>
-    <t>relationship--009eb8ba-56f4-4694-89af-17ea173d74cb</t>
-  </si>
-  <si>
-    <t>relationship--c0183cdf-818c-444a-9f3b-a2885749f658</t>
-  </si>
-  <si>
-    <t>relationship--07f0e483-8a65-4ad0-8068-b11e520db608</t>
-  </si>
-  <si>
-    <t>relationship--f39563eb-3ce1-408b-ad68-e1d4845500b5</t>
-  </si>
-  <si>
-    <t>relationship--fe28c216-cce3-41e9-b52d-2abf289d47ae</t>
-  </si>
-  <si>
-    <t>relationship--4065ee88-8afa-40c9-ac40-9d26f35b1f67</t>
-  </si>
-  <si>
-    <t>relationship--71f1a72d-7bbc-47d8-8e6c-8ff77ed33ea0</t>
-  </si>
-  <si>
-    <t>relationship--307b1228-84cf-49d8-853a-6af3a53c1627</t>
-  </si>
-  <si>
-    <t>relationship--d775343b-7fcc-4a1c-8e16-9a9cdb64e7a4</t>
-  </si>
-  <si>
-    <t>relationship--923a9d64-ddf0-4008-9bb2-af5d5ee0f230</t>
-  </si>
-  <si>
-    <t>relationship--82bc5611-617c-41ca-be4a-e5b3167d84ed</t>
-  </si>
-  <si>
-    <t>relationship--059aecae-97f4-4744-bcdd-a76d1a2f3f45</t>
-  </si>
-  <si>
-    <t>relationship--d7be5882-6700-4648-ba22-e980a2804072</t>
-  </si>
-  <si>
-    <t>relationship--1fe62db2-8ec1-4e0b-893d-b8c632009d9e</t>
-  </si>
-  <si>
-    <t>relationship--4826c5f8-4a5b-402c-bf84-bc13c03c3fb0</t>
-  </si>
-  <si>
-    <t>relationship--e55c1a27-ff44-4c2d-99a6-6fbd83ff60db</t>
-  </si>
-  <si>
-    <t>relationship--2912252d-746f-449f-9674-63b7caa18c56</t>
-  </si>
-  <si>
-    <t>relationship--61fe7007-0ed2-476c-a796-0d5c78694d88</t>
-  </si>
-  <si>
-    <t>relationship--289c43ba-2986-46ac-a3da-d69eef6f0a59</t>
-  </si>
-  <si>
-    <t>relationship--e2d69ef6-2ea3-4873-86f7-632c7a1fbc1c</t>
-  </si>
-  <si>
-    <t>relationship--b77d1234-dc45-4ad7-baec-4c75b7974d4e</t>
-  </si>
-  <si>
-    <t>relationship--73f6aed0-fefc-4888-8cca-cbe008ddf331</t>
-  </si>
-  <si>
-    <t>relationship--0a95e48e-b6fd-47c4-afed-08529f63fb39</t>
-  </si>
-  <si>
-    <t>relationship--9fbcddc5-9b75-451e-919a-d5e45e700a23</t>
-  </si>
-  <si>
-    <t>relationship--5d80c07d-5436-42ed-9ca4-3270c9c3d146</t>
-  </si>
-  <si>
-    <t>relationship--77cf91d2-6cb7-4ca0-9038-2b87606b5965</t>
-  </si>
-  <si>
-    <t>relationship--95635bce-78b4-4c59-b4d1-03622c8003ab</t>
-  </si>
-  <si>
-    <t>relationship--d12cff3c-fdbf-4fc7-bd6b-f1bb35b7304b</t>
-  </si>
-  <si>
-    <t>relationship--817daffb-a9b8-44e6-a395-6b7bf160e72c</t>
-  </si>
-  <si>
-    <t>relationship--fec74c64-d978-434e-bf80-197e2049f320</t>
-  </si>
-  <si>
-    <t>relationship--e93462ad-6c4e-48bd-a079-9519e3b5a04e</t>
-  </si>
-  <si>
-    <t>relationship--751f13ca-415c-4e84-a953-132107b7697e</t>
-  </si>
-  <si>
-    <t>relationship--da82a7ad-b4d7-4c94-8bea-057e671ae4a4</t>
-  </si>
-  <si>
-    <t>relationship--665cf86c-b8cf-4e87-a5e9-2cfcf18e0941</t>
-  </si>
-  <si>
-    <t>relationship--42757cb1-f4b1-4f96-9ea7-1e8e927da779</t>
-  </si>
-  <si>
-    <t>relationship--ed16aa83-affb-412b-b0e0-ff3c900821b4</t>
-  </si>
-  <si>
-    <t>relationship--abcaca4f-565d-478b-b717-29673f65534e</t>
-  </si>
-  <si>
-    <t>relationship--4254a725-81fd-452f-89f6-fc79843c701d</t>
-  </si>
-  <si>
-    <t>relationship--d05f11fd-62d3-4750-b34c-38d543b2b8c3</t>
-  </si>
-  <si>
-    <t>relationship--b68db160-d755-42d1-a36e-0971d3981d34</t>
-  </si>
-  <si>
-    <t>relationship--2735bc85-a60c-4465-a615-67902a033882</t>
-  </si>
-  <si>
-    <t>relationship--40f72abb-e0ef-4021-8aeb-0386d75fbbc5</t>
-  </si>
-  <si>
-    <t>relationship--f6de26ff-9458-4f70-9b43-8fb687b2d4d5</t>
-  </si>
-  <si>
-    <t>relationship--6dba15dc-fcbd-4e1c-963a-19a14fcaab3d</t>
-  </si>
-  <si>
-    <t>relationship--93ba7432-1e5d-4fe2-9c49-040925e42fcf</t>
-  </si>
-  <si>
-    <t>relationship--083eb465-7bc8-4e16-8155-41bbca4adf9e</t>
-  </si>
-  <si>
-    <t>relationship--bc31acf0-0893-4fc0-a6e1-b5041670f2b7</t>
-  </si>
-  <si>
-    <t>relationship--381d10a2-fd19-4e0e-9c59-0d20082fa5f1</t>
-  </si>
-  <si>
-    <t>relationship--ab67c82d-0704-4805-ad97-5b94f8e8e0dd</t>
-  </si>
-  <si>
-    <t>relationship--bc87995c-9763-461d-a407-c670d6a8772c</t>
-  </si>
-  <si>
-    <t>relationship--f039d33d-c0d7-4b3a-890c-f38e8127745a</t>
-  </si>
-  <si>
-    <t>relationship--5c06f90b-34e7-4af4-9051-814bdb4b2272</t>
-  </si>
-  <si>
-    <t>relationship--8656ea5a-2838-434f-b3e4-e46d58498762</t>
-  </si>
-  <si>
-    <t>relationship--b2de557b-fa55-4519-ac66-528e8af6a3dd</t>
-  </si>
-  <si>
-    <t>relationship--575e47df-7d05-4b63-a760-2fb8af22ca27</t>
+    <t>relationship--5614d86d-6211-45cd-ac6c-26a97c7ed3cf</t>
+  </si>
+  <si>
+    <t>relationship--c00bd06c-4bf5-4ab2-ab25-c5d571553d0c</t>
+  </si>
+  <si>
+    <t>relationship--7201fe1e-0fea-4d3b-97bf-6355ebf82318</t>
+  </si>
+  <si>
+    <t>relationship--d1870805-3ccc-4beb-b2a4-8402f288d864</t>
+  </si>
+  <si>
+    <t>relationship--a1eee09b-bd43-43e9-b586-a6b939c06a11</t>
+  </si>
+  <si>
+    <t>relationship--c274175b-6c03-49c5-a647-607cd5b0e4d2</t>
+  </si>
+  <si>
+    <t>relationship--187b5fcd-6c5c-4c42-8d07-07adbdbecd2d</t>
+  </si>
+  <si>
+    <t>relationship--1006e39a-452b-4831-be5c-fc31a3710a4c</t>
+  </si>
+  <si>
+    <t>relationship--998fc32c-1362-4fe1-badc-2c3295a58dae</t>
+  </si>
+  <si>
+    <t>relationship--b50491d9-1ef9-4e6a-a7d8-ed3bdd53bb26</t>
+  </si>
+  <si>
+    <t>relationship--816bc3db-9456-4de8-a943-e308683f2326</t>
+  </si>
+  <si>
+    <t>relationship--7e5cb007-6d19-46d2-a049-9fb76730abfc</t>
+  </si>
+  <si>
+    <t>relationship--4b7df337-6761-4f4a-8663-ffc85abd9bd7</t>
+  </si>
+  <si>
+    <t>relationship--3e1c35b2-ac79-4f76-b026-a30f8e566a41</t>
+  </si>
+  <si>
+    <t>relationship--a849cb40-97db-4468-a725-2eb757b9285f</t>
+  </si>
+  <si>
+    <t>relationship--47ff22b7-0fad-4eaa-8f49-c7ee57b2bcf5</t>
+  </si>
+  <si>
+    <t>relationship--50db3a6a-bc86-4653-92b1-cc25f4fd3b63</t>
+  </si>
+  <si>
+    <t>relationship--8312e15d-9501-45f6-b5c7-dd40ad215dc7</t>
+  </si>
+  <si>
+    <t>relationship--0cc9ae91-2019-49d4-9ae9-74cf940ab326</t>
+  </si>
+  <si>
+    <t>relationship--62cc7c54-5c61-4755-b62b-11df9f67bc7c</t>
+  </si>
+  <si>
+    <t>relationship--9520ceeb-3ab0-40cd-9976-308b5382c604</t>
+  </si>
+  <si>
+    <t>relationship--df0590aa-456d-4dcd-b3ef-9db58fcdde4d</t>
+  </si>
+  <si>
+    <t>relationship--25875951-42bf-4bd1-8846-1e2b082462c7</t>
+  </si>
+  <si>
+    <t>relationship--363d00f2-89e0-45eb-aeff-56c3eb0b7d1b</t>
+  </si>
+  <si>
+    <t>relationship--ccc50e83-1034-4626-9fad-142e49094870</t>
+  </si>
+  <si>
+    <t>relationship--0e6f9307-ac79-4d43-90f6-e73960d6ec75</t>
+  </si>
+  <si>
+    <t>relationship--24ef7132-be8a-41ec-bacf-c64882a1171d</t>
+  </si>
+  <si>
+    <t>relationship--0cf1df00-44a9-42ec-b61d-3e10fb8c67d6</t>
+  </si>
+  <si>
+    <t>relationship--03e9274c-b7a4-42d6-8f7f-78b71e30af09</t>
+  </si>
+  <si>
+    <t>relationship--5c38fc95-7bc5-4a6a-8681-48be32c65a82</t>
+  </si>
+  <si>
+    <t>relationship--066eb77b-c6df-4d8e-8599-0beb192907e4</t>
+  </si>
+  <si>
+    <t>relationship--541a4d88-df09-4c75-92ae-356afd194692</t>
+  </si>
+  <si>
+    <t>relationship--3af6830d-8cc7-4fed-b927-108a41fd4178</t>
+  </si>
+  <si>
+    <t>relationship--57631293-2a02-4489-8c56-f583e9bc5585</t>
+  </si>
+  <si>
+    <t>relationship--862f0336-33bd-4370-8af3-d29a004f0fc8</t>
+  </si>
+  <si>
+    <t>relationship--9ec2a708-84bf-4339-afb0-0162bb4748ff</t>
+  </si>
+  <si>
+    <t>relationship--4485df60-3f40-40ca-93c4-89378405dc43</t>
+  </si>
+  <si>
+    <t>relationship--722ca219-044e-4221-a0f4-444790a937ba</t>
+  </si>
+  <si>
+    <t>relationship--0819322a-18d8-4e24-b55c-206658d07525</t>
+  </si>
+  <si>
+    <t>relationship--cfa59c71-254e-4a90-903c-fcce14903069</t>
+  </si>
+  <si>
+    <t>relationship--672d610b-b36d-4dd8-b55d-8b986db8b16c</t>
+  </si>
+  <si>
+    <t>relationship--3c9fe144-c86e-42cf-b46f-9fbac0138093</t>
+  </si>
+  <si>
+    <t>relationship--0416c3e3-00bc-44e4-88b4-e2837a311840</t>
+  </si>
+  <si>
+    <t>relationship--0e328b60-be4c-4a17-a480-68f9a95774c9</t>
+  </si>
+  <si>
+    <t>relationship--05358bf0-1b8f-4d3d-9b01-37d1e4f6b814</t>
+  </si>
+  <si>
+    <t>relationship--d8ee9123-00a9-45e8-b9ed-78eaf52fd03c</t>
+  </si>
+  <si>
+    <t>relationship--c99cdf0b-238f-4f4a-bd62-e777028d0888</t>
+  </si>
+  <si>
+    <t>relationship--eb3d94ce-42c1-4f6d-9104-149587001ee8</t>
+  </si>
+  <si>
+    <t>relationship--34fa7ae0-57e6-4802-b731-2a8397e43f5c</t>
+  </si>
+  <si>
+    <t>relationship--658426eb-6159-48b7-834a-d2cba5929840</t>
+  </si>
+  <si>
+    <t>relationship--1b8afd01-f00e-4fb9-8e53-23bf378a5743</t>
+  </si>
+  <si>
+    <t>relationship--c4b84975-0d5b-41da-8dde-a1e4752f8223</t>
+  </si>
+  <si>
+    <t>relationship--3c23657a-af00-4c00-be50-0c2211096383</t>
+  </si>
+  <si>
+    <t>relationship--34f1cc09-99b9-4b55-8a11-a27b71d36a56</t>
+  </si>
+  <si>
+    <t>relationship--2d2d4647-66d2-468f-b5fa-08a23e9f3b52</t>
+  </si>
+  <si>
+    <t>relationship--32fef7ce-3ca8-42d2-9806-8f07130dc59a</t>
+  </si>
+  <si>
+    <t>relationship--45a232f8-5767-419e-9acc-94a2592789a1</t>
+  </si>
+  <si>
+    <t>relationship--8bd14d24-f013-4648-9e45-231c66bee802</t>
+  </si>
+  <si>
+    <t>relationship--e9bd60a6-0325-45da-9bda-fd854a7ce87b</t>
+  </si>
+  <si>
+    <t>relationship--724cc625-5556-40a5-ae14-3d9de64c9a19</t>
+  </si>
+  <si>
+    <t>relationship--00da6316-6f4a-4ee9-84ab-f3bf74b840dc</t>
+  </si>
+  <si>
+    <t>relationship--37a6d563-2564-4062-8967-14950a0a6ff1</t>
+  </si>
+  <si>
+    <t>relationship--5c5eb460-e73e-4c4b-8929-2f3a55616623</t>
+  </si>
+  <si>
+    <t>relationship--41bac798-9a1a-4b92-930c-227474d4cabb</t>
+  </si>
+  <si>
+    <t>relationship--5b9787dc-aaed-4206-acb6-3135336f00dc</t>
+  </si>
+  <si>
+    <t>relationship--92e54ce9-a70b-4436-be5a-e66e682935ec</t>
+  </si>
+  <si>
+    <t>relationship--689c088d-7e07-43c6-a3a3-2059035a0956</t>
+  </si>
+  <si>
+    <t>relationship--1d4bd310-a5da-42a0-896e-ea3ccf0735ef</t>
+  </si>
+  <si>
+    <t>relationship--58b1092a-2708-4e1d-b796-7570f699b314</t>
+  </si>
+  <si>
+    <t>relationship--a700b400-cfb5-4c2d-8ac6-6d3f3a976502</t>
+  </si>
+  <si>
+    <t>relationship--463138d3-daf2-4734-b553-fcc80a9f7245</t>
+  </si>
+  <si>
+    <t>relationship--12c1d59e-77ae-4c17-bd89-4f0d0855db2b</t>
+  </si>
+  <si>
+    <t>relationship--6dd4ef8d-d116-4667-98cd-25d0b4ca2eb2</t>
+  </si>
+  <si>
+    <t>relationship--28bdfc3d-faa4-4c45-8c25-506dc03861d2</t>
+  </si>
+  <si>
+    <t>relationship--2da181d8-efdd-46a5-bc48-a7e761e7700c</t>
+  </si>
+  <si>
+    <t>relationship--30caab21-d762-4082-9483-c4e4b58c8140</t>
+  </si>
+  <si>
+    <t>relationship--edd083ea-aadc-4345-844f-5d40e476e7c8</t>
+  </si>
+  <si>
+    <t>relationship--61c6a3e1-337d-4150-8e33-062db9bf48fb</t>
+  </si>
+  <si>
+    <t>relationship--69593cf2-77f5-4528-95bc-867a7cd474a6</t>
+  </si>
+  <si>
+    <t>relationship--fe839167-b221-48ff-8478-496d40f26604</t>
+  </si>
+  <si>
+    <t>relationship--33cc973e-fa84-415a-a0b3-dc6101374315</t>
+  </si>
+  <si>
+    <t>relationship--0c8a308f-fb09-4df6-9a8b-03dc281625c8</t>
+  </si>
+  <si>
+    <t>relationship--13a0fcb0-b324-4579-a852-51d59b9cfea7</t>
+  </si>
+  <si>
+    <t>relationship--03876e2e-c730-426e-9cf7-5c2d2eacfd12</t>
+  </si>
+  <si>
+    <t>relationship--ac403c59-fdb2-451d-82d5-b227f3fb004e</t>
+  </si>
+  <si>
+    <t>relationship--17501bfb-76d5-452a-a5b7-bb40a2734033</t>
+  </si>
+  <si>
+    <t>relationship--3751fcb4-a779-4bd1-8b91-b4d03da77810</t>
+  </si>
+  <si>
+    <t>relationship--db0bfcda-eb29-4562-aca0-c098711d0d07</t>
+  </si>
+  <si>
+    <t>relationship--092d1143-9f0d-4f94-b49b-b4a78e22aa1f</t>
+  </si>
+  <si>
+    <t>relationship--ff4a5303-2db3-49ae-a53f-7c2dffb9e6ee</t>
+  </si>
+  <si>
+    <t>relationship--2291dd05-1ba6-427c-8f66-f483409905d3</t>
+  </si>
+  <si>
+    <t>relationship--bdf81bef-d89b-49f8-a818-e7348ead0e7d</t>
+  </si>
+  <si>
+    <t>relationship--c0a0ed7b-7375-475c-967c-9635560013b7</t>
+  </si>
+  <si>
+    <t>relationship--35f20b51-ebde-4f96-b4f6-4612f3bceea5</t>
+  </si>
+  <si>
+    <t>relationship--b5c01c41-b1bd-403f-9c86-ee33d9233bb8</t>
+  </si>
+  <si>
+    <t>relationship--9bc2a9d1-da58-403d-98c8-6b56bfd51523</t>
+  </si>
+  <si>
+    <t>relationship--e9b6b440-e6ef-4112-91b7-a10e828f215f</t>
+  </si>
+  <si>
+    <t>relationship--d13278fb-2254-49ef-b205-01e887848910</t>
+  </si>
+  <si>
+    <t>relationship--5efc8b32-1b60-4fad-ae02-e340941487af</t>
+  </si>
+  <si>
+    <t>relationship--2511d69d-6f60-4597-8c57-c435f01cb56c</t>
+  </si>
+  <si>
+    <t>relationship--34272f39-5284-4cd8-aed4-3ac4b7afe9c0</t>
+  </si>
+  <si>
+    <t>relationship--78c44437-c23b-44e3-9b0a-dea9d31afab3</t>
+  </si>
+  <si>
+    <t>relationship--86e8bc77-6840-43e1-9b08-388dd6ce4a71</t>
+  </si>
+  <si>
+    <t>relationship--95a7d566-0538-4e17-b03f-d840ac5a6485</t>
+  </si>
+  <si>
+    <t>relationship--e08df791-6312-4452-a037-50b1c552eae6</t>
+  </si>
+  <si>
+    <t>relationship--ce048198-374c-4f04-8fc5-58aa78334838</t>
+  </si>
+  <si>
+    <t>relationship--ed1b3558-fa7e-4b78-94a6-ede294e5982b</t>
+  </si>
+  <si>
+    <t>relationship--fdb52f1a-9fce-4466-9113-080a43b19d24</t>
+  </si>
+  <si>
+    <t>relationship--a45d91e8-042e-4dde-8bf0-57d321efd381</t>
+  </si>
+  <si>
+    <t>relationship--4c063840-371e-41c6-8f16-15c3bb3b6a07</t>
+  </si>
+  <si>
+    <t>relationship--01302958-accb-41b5-bd1c-cad6bc07a1d6</t>
+  </si>
+  <si>
+    <t>relationship--1e280e04-acc2-4d3a-ad9c-8e779be2623f</t>
+  </si>
+  <si>
+    <t>relationship--68148d92-85e1-47a8-86ad-88953aad0f77</t>
+  </si>
+  <si>
+    <t>relationship--313f6ee5-9364-48f9-839d-edf4e6d25f2a</t>
+  </si>
+  <si>
+    <t>relationship--fb779776-e9f6-45e3-9cb8-c9e509c3e8a7</t>
+  </si>
+  <si>
+    <t>relationship--47e73f6e-a733-46f1-a09b-51f4a0c2574a</t>
+  </si>
+  <si>
+    <t>relationship--d48b2f17-752e-4ef0-85ca-8c5626fe5832</t>
+  </si>
+  <si>
+    <t>relationship--55b721b2-6229-4de6-9655-32647d86e186</t>
+  </si>
+  <si>
+    <t>relationship--e7753b65-5fcf-453a-9139-c1d9028cf696</t>
+  </si>
+  <si>
+    <t>relationship--5f7f0d17-361f-4a98-b1bd-0122c4d69f1d</t>
+  </si>
+  <si>
+    <t>relationship--2e1b7d0a-bc28-4539-92dd-ebfc2bb2a6fc</t>
+  </si>
+  <si>
+    <t>relationship--14628952-a9d9-4da9-a5e2-c807bebc2dbc</t>
+  </si>
+  <si>
+    <t>relationship--9708078b-3306-4693-bf99-43999bd18b3a</t>
+  </si>
+  <si>
+    <t>relationship--ac66737c-9eeb-4d82-a7ef-b0a31bba3e60</t>
+  </si>
+  <si>
+    <t>relationship--e68e8a70-ae5d-4374-9f08-1313f12c0795</t>
+  </si>
+  <si>
+    <t>relationship--f8ea8127-0143-4136-9355-f0672cc93626</t>
+  </si>
+  <si>
+    <t>relationship--9c139044-ce9e-491c-95e2-00ba93a1b5db</t>
+  </si>
+  <si>
+    <t>relationship--a74f7c11-3bc0-48bf-973f-f38cd1531a2e</t>
+  </si>
+  <si>
+    <t>relationship--7d492b91-2741-42d1-a14b-5c68ef16cdde</t>
+  </si>
+  <si>
+    <t>relationship--2e21705c-7535-43ea-971e-ae1c720f97f0</t>
+  </si>
+  <si>
+    <t>relationship--6012c812-46fa-4441-a18e-caca14be105e</t>
+  </si>
+  <si>
+    <t>relationship--7276f7e3-19cc-4f36-b52a-df9b09039d86</t>
+  </si>
+  <si>
+    <t>relationship--38b9b77e-9ac6-4123-ad64-7ee44572da1b</t>
+  </si>
+  <si>
+    <t>relationship--8ab8f626-ae23-4007-bb32-dc128a13c452</t>
+  </si>
+  <si>
+    <t>relationship--a3705dfd-d211-4b6c-b8de-a60b61232ccf</t>
+  </si>
+  <si>
+    <t>relationship--176d7e94-acc7-4510-ab33-fc50ec2eb016</t>
+  </si>
+  <si>
+    <t>relationship--72911605-8706-44a8-9133-cc55f61fbe01</t>
+  </si>
+  <si>
+    <t>relationship--3cecfb1c-8f09-451d-9727-99f8f2060f9a</t>
+  </si>
+  <si>
+    <t>relationship--889bdd3d-7042-4b09-9b8a-2c1063492550</t>
+  </si>
+  <si>
+    <t>relationship--93820292-0d07-4e8a-a732-af6f7fac18f3</t>
+  </si>
+  <si>
+    <t>relationship--d63962bf-f3fd-4159-986d-fb404f8e5c4f</t>
+  </si>
+  <si>
+    <t>relationship--8b4d20df-6e8d-48ed-ad71-b0b73b855a56</t>
+  </si>
+  <si>
+    <t>relationship--9b06ea4e-c75e-41ad-9ba0-b8050f79c4c9</t>
+  </si>
+  <si>
+    <t>relationship--304d883a-85fd-4eb0-8c79-a70babe9fa54</t>
+  </si>
+  <si>
+    <t>relationship--f2124474-a45e-4d8c-b9c3-a4485991a23e</t>
+  </si>
+  <si>
+    <t>relationship--f90a7c85-e4de-457e-b281-b8945307db07</t>
+  </si>
+  <si>
+    <t>relationship--1658c08e-93b2-490d-b21e-2dddf38e2b5c</t>
+  </si>
+  <si>
+    <t>relationship--f3fded44-1a57-418f-b6ae-29b4dbd1bc91</t>
+  </si>
+  <si>
+    <t>relationship--3f971d8b-a5a0-4f8f-b42d-a325cd802149</t>
+  </si>
+  <si>
+    <t>relationship--f45ed62a-12e3-466e-84ea-56ee39b45fe3</t>
+  </si>
+  <si>
+    <t>relationship--acab761b-d19f-4216-a982-e4e9fee04109</t>
+  </si>
+  <si>
+    <t>relationship--bd2a142c-0144-4d20-8e3d-b73ace1abff6</t>
+  </si>
+  <si>
+    <t>relationship--263060ab-6afa-4efa-8121-56ca8c19dea3</t>
+  </si>
+  <si>
+    <t>relationship--18b4ed3f-7d9c-457a-ba75-9b36acdf1b39</t>
+  </si>
+  <si>
+    <t>relationship--4bb0977b-3d05-4362-aeea-cc150865bd4b</t>
+  </si>
+  <si>
+    <t>relationship--9732d9c4-866e-4ec3-acdf-9116f0bd3293</t>
+  </si>
+  <si>
+    <t>relationship--f5e63ee5-77e5-4992-833d-257e32e5ce3e</t>
+  </si>
+  <si>
+    <t>relationship--49d946ff-1e6b-4bf2-a9f1-a9e54213b6ba</t>
+  </si>
+  <si>
+    <t>relationship--3df7af44-b568-4a7c-adf5-95885e794a2f</t>
+  </si>
+  <si>
+    <t>relationship--9e5fe4f7-cd1e-4703-bea2-829fef05d626</t>
+  </si>
+  <si>
+    <t>relationship--14bade66-db15-4761-9e73-2928a3a3891e</t>
+  </si>
+  <si>
+    <t>relationship--2acac976-88b9-4fc7-a0bd-4d03a5f3a9bf</t>
+  </si>
+  <si>
+    <t>relationship--4c3795cc-a1e9-45d1-9a1e-bbf2cde64a15</t>
+  </si>
+  <si>
+    <t>relationship--fe565642-eab5-4ff9-91e1-cea181876211</t>
+  </si>
+  <si>
+    <t>relationship--6278e5d4-ab06-4def-bece-6991bf4b857b</t>
+  </si>
+  <si>
+    <t>relationship--8ae29663-1f05-422d-ba3c-0337760daf4d</t>
+  </si>
+  <si>
+    <t>relationship--7ac36b6b-a053-4b5f-8160-03f2709d8434</t>
+  </si>
+  <si>
+    <t>relationship--33b4f3d5-4d6e-421f-a932-e2ffa44fc7a9</t>
+  </si>
+  <si>
+    <t>relationship--95d794f0-5dc8-4362-b0ff-7ed3dc1eeabd</t>
+  </si>
+  <si>
+    <t>relationship--fbf7379e-6953-413c-8932-a51888aac57e</t>
+  </si>
+  <si>
+    <t>relationship--16390e3a-f86b-4725-907f-991e84d3e0fe</t>
+  </si>
+  <si>
+    <t>relationship--c3d4eae6-f0ec-4700-91e4-270a1b5c6f38</t>
+  </si>
+  <si>
+    <t>relationship--742cbbdd-94d7-4072-9a8b-ecafc56604db</t>
+  </si>
+  <si>
+    <t>relationship--2828cfca-5ceb-4c5a-bb2f-8ffc611954fc</t>
+  </si>
+  <si>
+    <t>relationship--cb6aa417-c3bf-41e3-9e44-209705207413</t>
+  </si>
+  <si>
+    <t>relationship--9f99304a-1059-47a4-bbdf-1f76b23b8ac2</t>
+  </si>
+  <si>
+    <t>relationship--2346dccd-238f-46e8-9aba-6341e3783eda</t>
+  </si>
+  <si>
+    <t>relationship--3138c704-adf0-4cad-8d6a-ad204687d4df</t>
+  </si>
+  <si>
+    <t>relationship--0880242b-9689-482e-9459-4ebd56320f4e</t>
+  </si>
+  <si>
+    <t>relationship--9417f950-d2a7-4417-9c05-6fe57828917e</t>
+  </si>
+  <si>
+    <t>relationship--a2b54231-6b5c-40b3-a417-074b60b3b9e2</t>
+  </si>
+  <si>
+    <t>relationship--23735a53-068a-4d2a-9476-7857dd7e1b74</t>
+  </si>
+  <si>
+    <t>relationship--161fe2ca-c2dc-4d21-a9b0-95935f7d1a52</t>
   </si>
   <si>
     <t>T0030</t>
@@ -3050,253 +3050,253 @@
     <t>Спонсирование внутреннего экстремизма и радикалов</t>
   </si>
   <si>
-    <t>attack-pattern--8623a36b-99de-4dfb-ba46-b2b5e9cf0d85</t>
-  </si>
-  <si>
-    <t>attack-pattern--bf3afc82-5403-4ae9-9f69-3d9ef357c6c8</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd99f80b-0f34-4288-bc79-c0f3cf18e846</t>
-  </si>
-  <si>
-    <t>attack-pattern--dac8d747-5bf3-47af-9f54-b010ae92ccea</t>
-  </si>
-  <si>
-    <t>attack-pattern--2421e2f6-4b1f-4f1e-8faa-69e9b14cbbe8</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca41993a-f62d-477b-802f-e63f4c050380</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe23fd12-ed27-416d-a891-53fd0945c418</t>
-  </si>
-  <si>
-    <t>attack-pattern--7f745905-530b-4294-9eda-f8dafe9f0edd</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe33bd0c-bd06-451b-92ea-b2f65444329b</t>
-  </si>
-  <si>
-    <t>attack-pattern--f69b9809-b9e2-4a3e-b8d9-cf3f74af4335</t>
-  </si>
-  <si>
-    <t>attack-pattern--a26ee77d-cf1a-4687-988f-932ccc9542bf</t>
-  </si>
-  <si>
-    <t>attack-pattern--575a4091-4083-4c93-8862-74543ad2f94c</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f1e418c-f7d0-4526-9824-f880b69b0dc8</t>
-  </si>
-  <si>
-    <t>attack-pattern--8accb141-a1ff-471e-9a3a-988919bcceb6</t>
-  </si>
-  <si>
-    <t>attack-pattern--b041117e-4c21-419b-a1ad-f357fd63741f</t>
-  </si>
-  <si>
-    <t>attack-pattern--8feebaca-97cf-4478-b1d3-8e0a8ed2edc0</t>
-  </si>
-  <si>
-    <t>attack-pattern--7be66db5-2484-4f82-9c02-2c658aba5534</t>
-  </si>
-  <si>
-    <t>attack-pattern--61fccaa6-3ad9-4372-8b42-682b13577269</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd811343-f4f3-4812-ad57-477da21a7e8d</t>
-  </si>
-  <si>
-    <t>attack-pattern--60d5bdf7-06c3-4a53-b2d3-36b02a2230e3</t>
-  </si>
-  <si>
-    <t>attack-pattern--0fa8defa-fb0b-4599-9491-7d725883c3fd</t>
-  </si>
-  <si>
-    <t>attack-pattern--60a4cda8-8154-4a3f-9826-f9d39155d257</t>
-  </si>
-  <si>
-    <t>attack-pattern--72323e0d-b098-4e42-8cd1-544258dc8973</t>
-  </si>
-  <si>
-    <t>attack-pattern--0ffd53d6-5fd6-43e5-aff6-4e1d50a00743</t>
-  </si>
-  <si>
-    <t>attack-pattern--e49e8037-4bae-447d-86e6-23b275db8d96</t>
-  </si>
-  <si>
-    <t>attack-pattern--9fb6f979-a54f-46ce-9d0b-ce0c5db37e7a</t>
-  </si>
-  <si>
-    <t>attack-pattern--242eeb83-aeba-4f79-a3ae-2f62a5bc3706</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4b577cd-5a76-46f7-8c39-b96213fc4263</t>
-  </si>
-  <si>
-    <t>attack-pattern--624b5cee-3da2-4c18-906b-d1f1aca11306</t>
-  </si>
-  <si>
-    <t>attack-pattern--286b8cda-f24d-4dde-a188-c0b140491a96</t>
-  </si>
-  <si>
-    <t>attack-pattern--b516107a-c248-4465-aa68-d5e20f3bf635</t>
-  </si>
-  <si>
-    <t>attack-pattern--062669ed-dadc-446f-992c-3425ac24dd1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--ac8f6735-f593-4862-b036-039679f6825d</t>
-  </si>
-  <si>
-    <t>attack-pattern--3fff8702-55b8-4c84-a528-2b14b7b980da</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a2eea19-fa56-4b46-b746-af741b0fbe4a</t>
-  </si>
-  <si>
-    <t>attack-pattern--aeca9532-ecda-49fc-9915-fe9b53956bf8</t>
-  </si>
-  <si>
-    <t>attack-pattern--52c17a9d-8e67-4b7c-bddd-a0111496a6f5</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef93f62-3fe5-4d86-bad7-82607554a597</t>
-  </si>
-  <si>
-    <t>attack-pattern--dc37deb9-2659-4fc2-b801-127690502a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c0c59602-b27b-4b66-b864-82a05ff862db</t>
-  </si>
-  <si>
-    <t>attack-pattern--595ddc1a-2efe-4154-a6d7-880fb2fe280f</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5f6323-a749-4b89-a8ae-36633f183b54</t>
-  </si>
-  <si>
-    <t>attack-pattern--a08a6f55-9930-4233-8df3-cf86e10008ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8fc16d6-7f03-4404-9d8d-f9782a0d4b3e</t>
-  </si>
-  <si>
-    <t>attack-pattern--880b414d-a823-4193-b270-c0a7de9e6d12</t>
-  </si>
-  <si>
-    <t>attack-pattern--37844351-6c24-42d8-99ba-2eb178febd3c</t>
-  </si>
-  <si>
-    <t>attack-pattern--37759b81-258f-4d71-9703-9654ac67cab0</t>
-  </si>
-  <si>
-    <t>attack-pattern--95138ada-459f-440e-a79a-7fcf8874b584</t>
-  </si>
-  <si>
-    <t>attack-pattern--aa11cd7e-92e7-43ec-af19-193b81bdb604</t>
-  </si>
-  <si>
-    <t>attack-pattern--503486f3-22d3-4ed3-a8fb-f63db2718af0</t>
-  </si>
-  <si>
-    <t>attack-pattern--22e649d9-36b0-4f1f-88e9-e34fd12441c4</t>
-  </si>
-  <si>
-    <t>attack-pattern--2001e1d6-3887-44fe-892d-ce873833b382</t>
-  </si>
-  <si>
-    <t>attack-pattern--cf3d899a-e96c-4063-bf08-65e437c19c7f</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d97cbb0-3c4c-4fd3-9b5e-679517b777f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--14d57931-21d5-4fd1-bf37-f26ce432a5ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--71797db1-dffd-44dd-8bfa-53446c0091df</t>
-  </si>
-  <si>
-    <t>attack-pattern--019504d9-9143-4762-b36e-729108653789</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c93037a-c467-4137-81e2-c058a9d90107</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b132a9a-ecc8-4b8b-b93c-77771f5dc46c</t>
-  </si>
-  <si>
-    <t>attack-pattern--99619131-579e-49d3-aa32-d9ba015ed29a</t>
-  </si>
-  <si>
-    <t>attack-pattern--08292bee-5177-4f79-bfa6-4f0345a5a446</t>
-  </si>
-  <si>
-    <t>attack-pattern--a92eb244-48f1-4d36-91b8-9ff6404bc66d</t>
-  </si>
-  <si>
-    <t>attack-pattern--8fa70d63-cbe1-4ba7-b1a5-2573911cf454</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed09b02f-1bf8-4c07-859e-b28e828825d5</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe1389e1-23dc-4f41-b2e1-15ed665a5840</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c8faff-7670-454e-a4f0-3da445f53ac9</t>
-  </si>
-  <si>
-    <t>attack-pattern--563b0db6-14f7-4b63-8256-95de0ef5cf8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--0813df13-c30d-4a9c-badc-bf8ff641b717</t>
-  </si>
-  <si>
-    <t>attack-pattern--81623f2c-c724-43fa-bbab-429f8575f921</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae7d996b-f766-44ab-a46b-60abdd2b3ef6</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8f0d38d-8111-4ef2-87ab-d970fb6f6d04</t>
-  </si>
-  <si>
-    <t>attack-pattern--a6684ef1-fa45-4bf7-9ec1-db7ebe4dec10</t>
-  </si>
-  <si>
-    <t>attack-pattern--91bd2ac0-d39a-4a37-b4ba-3b7d9cc48480</t>
-  </si>
-  <si>
-    <t>attack-pattern--709b796b-4c14-4219-8b7d-848ccf3df33f</t>
-  </si>
-  <si>
-    <t>attack-pattern--c8e73b27-78c5-4634-93ec-287a7cd80529</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5deb62-ed66-4518-9b21-c1557815cce5</t>
-  </si>
-  <si>
-    <t>attack-pattern--229f46aa-5a77-41ce-a34b-4d978b1164ea</t>
-  </si>
-  <si>
-    <t>attack-pattern--73c181fd-e569-4225-9bfb-045b64df9b0c</t>
-  </si>
-  <si>
-    <t>attack-pattern--85208eb7-09ab-4287-a298-87298178d6c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--3a36e7b8-ad04-4cb0-8ffc-9b6502c66d77</t>
-  </si>
-  <si>
-    <t>attack-pattern--4c4ac28a-0504-4efc-b7bb-a81682cab9ef</t>
-  </si>
-  <si>
-    <t>attack-pattern--a8e7461e-9164-42e7-a275-578694585803</t>
-  </si>
-  <si>
-    <t>attack-pattern--e745fb62-c9c2-41af-affe-cac608952241</t>
+    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
+  </si>
+  <si>
+    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
+  </si>
+  <si>
+    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
+  </si>
+  <si>
+    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
+  </si>
+  <si>
+    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
+  </si>
+  <si>
+    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
+  </si>
+  <si>
+    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
+  </si>
+  <si>
+    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
+  </si>
+  <si>
+    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
+  </si>
+  <si>
+    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
+  </si>
+  <si>
+    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
+  </si>
+  <si>
+    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
+  </si>
+  <si>
+    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
+  </si>
+  <si>
+    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
+  </si>
+  <si>
+    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
+  </si>
+  <si>
+    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
+  </si>
+  <si>
+    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
+  </si>
+  <si>
+    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
+  </si>
+  <si>
+    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
+  </si>
+  <si>
+    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
+  </si>
+  <si>
+    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
+  </si>
+  <si>
+    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
+  </si>
+  <si>
+    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
+  </si>
+  <si>
+    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
+  </si>
+  <si>
+    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
+  </si>
+  <si>
+    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
+  </si>
+  <si>
+    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
+  </si>
+  <si>
+    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
+  </si>
+  <si>
+    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
+  </si>
+  <si>
+    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
+  </si>
+  <si>
+    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
+  </si>
+  <si>
+    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
+  </si>
+  <si>
+    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
+  </si>
+  <si>
+    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
+  </si>
+  <si>
+    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
+  </si>
+  <si>
+    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
+  </si>
+  <si>
+    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
+  </si>
+  <si>
+    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
+  </si>
+  <si>
+    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
+  </si>
+  <si>
+    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
+  </si>
+  <si>
+    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
+  </si>
+  <si>
+    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
+  </si>
+  <si>
+    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
+  </si>
+  <si>
+    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
+  </si>
+  <si>
+    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
+  </si>
+  <si>
+    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
+  </si>
+  <si>
+    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
+  </si>
+  <si>
+    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
+  </si>
+  <si>
+    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
+  </si>
+  <si>
+    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
+  </si>
+  <si>
+    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
+  </si>
+  <si>
+    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
+  </si>
+  <si>
+    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
+  </si>
+  <si>
+    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
+  </si>
+  <si>
+    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
+  </si>
+  <si>
+    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
+  </si>
+  <si>
+    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
+  </si>
+  <si>
+    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
   </si>
   <si>
     <t>technique</t>
@@ -3359,7 +3359,7 @@
     <t>Использование дешевой рабочей силы местного населения на шахтах и металлургических заводах в условиях тяжелейшей эксплуатации (Citation: Історія Донецької області — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Вслед за установлением контроля над митрополией последовал постепенный запрет на использование киевского извода церковнославянского языка и украинского произношения в богослужениях и книгах, что заложило фундамент для полных языковых запретов XVIII века (Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026).</t>
@@ -3527,481 +3527,481 @@
     <t>Введение обязанности предоставлять полные финансовые отчеты о доходах региона под надзор центра (Citation: Решетилівські статті — Вікіпедія 2026)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>relationship--898475e8-ebc6-40cf-9fd0-2ce5c185521c</t>
-  </si>
-  <si>
-    <t>relationship--152ba51f-eb52-4cb8-8a8c-39b5986e6f48</t>
-  </si>
-  <si>
-    <t>relationship--52e9757d-719f-45c0-9f57-a1373c929a70</t>
-  </si>
-  <si>
-    <t>relationship--b4158964-4d2d-4cfd-af14-07ad553063ca</t>
-  </si>
-  <si>
-    <t>relationship--c28addcb-3c84-4759-a937-7ef8d581a30c</t>
-  </si>
-  <si>
-    <t>relationship--600e1d1a-0904-425d-80bd-ae586e9c11c6</t>
-  </si>
-  <si>
-    <t>relationship--e8a7484f-7c4a-42c7-91f8-783be6ea95aa</t>
-  </si>
-  <si>
-    <t>relationship--4cbda5ed-2f03-4e10-8c9a-eb5979cc80aa</t>
-  </si>
-  <si>
-    <t>relationship--4f725b45-e523-44ef-b305-390164de3615</t>
-  </si>
-  <si>
-    <t>relationship--59ef994d-607d-46aa-bb29-857eb6f2b8ca</t>
-  </si>
-  <si>
-    <t>relationship--832b34e9-f5a4-47ce-b977-0f9bb63c3fcc</t>
-  </si>
-  <si>
-    <t>relationship--1ce88d63-1141-477e-9b38-931613413a6d</t>
-  </si>
-  <si>
-    <t>relationship--8f27bafb-f2d4-4470-af0f-79aca850b563</t>
-  </si>
-  <si>
-    <t>relationship--0821b1a1-15b3-414c-ab25-0c7c90c18540</t>
-  </si>
-  <si>
-    <t>relationship--96da083d-a23c-43cb-b709-92e712bce2fa</t>
-  </si>
-  <si>
-    <t>relationship--20d69c3b-be1d-4f35-a0b3-6341cdb4f3b2</t>
-  </si>
-  <si>
-    <t>relationship--64f43e2e-94d8-4e82-a9b3-394f1e06dd6d</t>
-  </si>
-  <si>
-    <t>relationship--84c4cac7-3756-409a-bf8a-5972cc3094cd</t>
-  </si>
-  <si>
-    <t>relationship--d63f16d1-1b39-4990-81b7-e03885abaf05</t>
-  </si>
-  <si>
-    <t>relationship--49c648af-fec3-4059-bf6b-9f07c4d9b1b9</t>
-  </si>
-  <si>
-    <t>relationship--e5a36c2f-adcc-4ba7-940c-5da32b713e7d</t>
-  </si>
-  <si>
-    <t>relationship--4015b538-bbcf-47d6-8495-2ecb81ef3135</t>
-  </si>
-  <si>
-    <t>relationship--78c470fa-b57b-4ec4-8462-1be58f44348f</t>
-  </si>
-  <si>
-    <t>relationship--75c2148d-7caf-44f6-9922-42576bec690f</t>
-  </si>
-  <si>
-    <t>relationship--520de64d-4c88-40d0-94ae-2857c606a373</t>
-  </si>
-  <si>
-    <t>relationship--dc6b8ca9-dfa6-4643-b9bb-3f0aff72ca24</t>
-  </si>
-  <si>
-    <t>relationship--4029f29b-f441-46ec-accd-60e98f8e60ae</t>
-  </si>
-  <si>
-    <t>relationship--74615a43-ac1f-45e5-a3d2-e3eac51c3d41</t>
-  </si>
-  <si>
-    <t>relationship--aaad3049-4e16-43d5-b00d-3f5ebd5fb04c</t>
-  </si>
-  <si>
-    <t>relationship--b7af7b9c-1e6c-428a-8387-afdab549652e</t>
-  </si>
-  <si>
-    <t>relationship--f54b229f-306f-4f88-9f8b-ac8dcd728c09</t>
-  </si>
-  <si>
-    <t>relationship--d4a1cee7-ae63-446f-9adf-e9b6e514c8d9</t>
-  </si>
-  <si>
-    <t>relationship--962d374e-49d8-4c93-8dba-c4a614dbc984</t>
-  </si>
-  <si>
-    <t>relationship--74e1ecbc-1bd7-48e9-bc0f-5d60d38a4d20</t>
-  </si>
-  <si>
-    <t>relationship--7f4db076-bf6c-43d9-bb5f-092e4ba95986</t>
-  </si>
-  <si>
-    <t>relationship--c1a4e4f5-6a73-4fed-bd14-7791771f6712</t>
-  </si>
-  <si>
-    <t>relationship--55ebdb20-8b0c-40c8-9a2f-3e1d08835cce</t>
-  </si>
-  <si>
-    <t>relationship--9d2dea45-2bd1-4b2e-8d7a-73d3a12a430e</t>
-  </si>
-  <si>
-    <t>relationship--f043b659-76a9-4b6a-b824-411010596be3</t>
-  </si>
-  <si>
-    <t>relationship--de6aebe2-a780-4a3b-a697-237b41701090</t>
-  </si>
-  <si>
-    <t>relationship--4659c792-a8f7-4e07-a1cd-82a9ea575b59</t>
-  </si>
-  <si>
-    <t>relationship--97f92d42-e04b-44fd-a24a-878f253676ca</t>
-  </si>
-  <si>
-    <t>relationship--74133ab4-4ac7-47ea-a920-924fb9a17113</t>
-  </si>
-  <si>
-    <t>relationship--2fafd992-6e0c-4a34-bcb0-bea3518108e3</t>
-  </si>
-  <si>
-    <t>relationship--a8d25bd5-9f16-44fc-88ed-156a76c85216</t>
-  </si>
-  <si>
-    <t>relationship--d8fc0f85-92c3-4b35-bba3-23fb00b34150</t>
-  </si>
-  <si>
-    <t>relationship--27c61602-1178-4ff1-99ab-6f49e5e5a21f</t>
-  </si>
-  <si>
-    <t>relationship--7363bb0c-68fb-4702-a7d7-fa42f9098c43</t>
-  </si>
-  <si>
-    <t>relationship--573b6b81-bcb9-4124-9851-57b5bd288d6d</t>
-  </si>
-  <si>
-    <t>relationship--dbf85c12-c689-4e6e-9105-2ea7a440cca2</t>
-  </si>
-  <si>
-    <t>relationship--a82659b7-c6ca-46e5-9fca-c4892d2df804</t>
-  </si>
-  <si>
-    <t>relationship--6ce11b1c-435d-4409-97c8-e39e4d4c06e7</t>
-  </si>
-  <si>
-    <t>relationship--ea06ea35-f027-45e7-9d7f-28a47a5c5c20</t>
-  </si>
-  <si>
-    <t>relationship--9d581d41-ea63-4cf1-ac6a-43efa647c556</t>
-  </si>
-  <si>
-    <t>relationship--756b275f-5c10-4751-b6ce-d58f7866edf2</t>
-  </si>
-  <si>
-    <t>relationship--2423c9bd-8308-44ab-a418-744d9ececcb1</t>
-  </si>
-  <si>
-    <t>relationship--b0eb4799-a95f-4534-97b1-ec6e43f0fc13</t>
-  </si>
-  <si>
-    <t>relationship--5d174e08-8b38-4930-a8e8-43e8dbbd654a</t>
-  </si>
-  <si>
-    <t>relationship--407b647c-a2f6-4254-9531-40e4161caa59</t>
-  </si>
-  <si>
-    <t>relationship--40a2c3a1-48a7-451e-87f4-08f7523ccdc8</t>
-  </si>
-  <si>
-    <t>relationship--c49858b7-7d2f-43b3-8ecc-8836af82b441</t>
-  </si>
-  <si>
-    <t>relationship--35cc6e24-fb14-48cc-87a6-6be33d68df85</t>
-  </si>
-  <si>
-    <t>relationship--578d5030-f47a-4d9c-9d51-f36eb2f1a6c7</t>
-  </si>
-  <si>
-    <t>relationship--94c95bcc-f95b-439b-9f18-0db1fdd0a680</t>
-  </si>
-  <si>
-    <t>relationship--5f42756f-0720-432b-a8cd-d86743a7bdb2</t>
-  </si>
-  <si>
-    <t>relationship--78e423ca-351c-409c-9fc4-68bee4c557c6</t>
-  </si>
-  <si>
-    <t>relationship--5e6374aa-e39a-41c9-b5aa-540c79e019f7</t>
-  </si>
-  <si>
-    <t>relationship--84f88caa-f439-40f6-9b9c-97398faa8f28</t>
-  </si>
-  <si>
-    <t>relationship--73e5b3c4-f741-4c88-86a8-dbe2b8969a9f</t>
-  </si>
-  <si>
-    <t>relationship--eccd5f91-d1f3-45f2-84d4-83f6eef080f9</t>
-  </si>
-  <si>
-    <t>relationship--e82060b6-9af1-406f-87d7-858c6cd3c61d</t>
-  </si>
-  <si>
-    <t>relationship--6f037053-4cfc-468a-9a7c-4554a0cd3ef3</t>
-  </si>
-  <si>
-    <t>relationship--8d84724b-aa50-4c84-850c-0abaae413772</t>
-  </si>
-  <si>
-    <t>relationship--7da2dcb7-a03b-4eba-89b2-59f4c4d65a2a</t>
-  </si>
-  <si>
-    <t>relationship--ac80003e-716a-47c1-8f05-aa12ca7ed584</t>
-  </si>
-  <si>
-    <t>relationship--a733d4c4-5666-445b-9201-30a60ecce020</t>
-  </si>
-  <si>
-    <t>relationship--c495de5d-c2e1-4c57-a959-fe45dddd0445</t>
-  </si>
-  <si>
-    <t>relationship--57725f33-3924-4850-a21e-9341c4cc014e</t>
-  </si>
-  <si>
-    <t>relationship--d4a18cd8-6d38-48ad-844d-d0f31f0f0529</t>
-  </si>
-  <si>
-    <t>relationship--51bf0925-bb22-4499-9eb1-6a614ae6ab3f</t>
-  </si>
-  <si>
-    <t>relationship--89651c38-be85-47a8-afc1-30bc1601f5a4</t>
-  </si>
-  <si>
-    <t>relationship--036d230d-877c-4deb-98fc-24ac59613ee6</t>
-  </si>
-  <si>
-    <t>relationship--c606b95d-4ec5-4ec8-aa82-1126469d12db</t>
-  </si>
-  <si>
-    <t>relationship--890ffe89-219c-4d68-9be5-03b0ba553e6a</t>
-  </si>
-  <si>
-    <t>relationship--4844f590-14d0-4fe5-9af2-2812a96ef249</t>
-  </si>
-  <si>
-    <t>relationship--11d35489-04e2-4c12-b1f2-7443031406f5</t>
-  </si>
-  <si>
-    <t>relationship--2b2eb228-6449-43a8-9d85-3e83196149d0</t>
-  </si>
-  <si>
-    <t>relationship--67a09861-6af1-4a04-a1ca-9b65f5e406a3</t>
-  </si>
-  <si>
-    <t>relationship--7251cbcf-ca88-4025-93f0-069bffc149d7</t>
-  </si>
-  <si>
-    <t>relationship--b8480c6e-3555-44e5-b672-3edbfc31241a</t>
-  </si>
-  <si>
-    <t>relationship--796757e1-c2a7-4670-b4f9-26799910eaa2</t>
-  </si>
-  <si>
-    <t>relationship--8efa44d4-d824-4868-834c-9a507d10e3d6</t>
-  </si>
-  <si>
-    <t>relationship--a4e34657-03ac-4801-b5f8-87072335310d</t>
-  </si>
-  <si>
-    <t>relationship--e30b4876-d60b-4ed0-9e9c-27d105c1ce6c</t>
-  </si>
-  <si>
-    <t>relationship--2deed8a8-8869-47a3-8d6a-607a2b055dec</t>
-  </si>
-  <si>
-    <t>relationship--9349f86e-a976-431a-9138-ae9e53e96ee0</t>
-  </si>
-  <si>
-    <t>relationship--f4ccc2ed-19f4-4cae-94c2-bbe3f207d85c</t>
-  </si>
-  <si>
-    <t>relationship--2b5787dd-0bd2-4e43-a6e6-f959f39d1acb</t>
-  </si>
-  <si>
-    <t>relationship--57065beb-9d2f-4c60-9a2c-fa961c6e48d9</t>
-  </si>
-  <si>
-    <t>relationship--06d2c06a-6f4f-4d27-82e5-8224d984525d</t>
-  </si>
-  <si>
-    <t>relationship--8ca908a6-620d-4bea-b7ec-bab44c24bea6</t>
-  </si>
-  <si>
-    <t>relationship--2f1b0d82-a607-4a8b-a071-ca9c0c86425e</t>
-  </si>
-  <si>
-    <t>relationship--d195f54a-133d-47d2-a8f1-eaaa55f1894e</t>
-  </si>
-  <si>
-    <t>relationship--67d62057-2d68-415d-9157-be8b86ee5048</t>
-  </si>
-  <si>
-    <t>relationship--f44acf97-e801-4b54-ba2f-ea3f67f3b583</t>
-  </si>
-  <si>
-    <t>relationship--279e7ba6-3c28-4584-bbee-d24a6a3e06b9</t>
-  </si>
-  <si>
-    <t>relationship--e7f1922e-2837-471e-9165-76b1a8a20ef8</t>
-  </si>
-  <si>
-    <t>relationship--91a02d9c-f828-4f69-93ce-f7a720b8fa6e</t>
-  </si>
-  <si>
-    <t>relationship--b2f38ad0-2224-4961-8a2d-1a98f60f4a64</t>
-  </si>
-  <si>
-    <t>relationship--64862ccd-dea2-469c-846f-b981ee0b105d</t>
-  </si>
-  <si>
-    <t>relationship--7823aca2-b9c8-4295-927d-b674e33be225</t>
-  </si>
-  <si>
-    <t>relationship--4ec13159-0578-406e-93c9-fecac68eb471</t>
-  </si>
-  <si>
-    <t>relationship--95544ad2-03da-47fe-b3e7-cbb77c90a687</t>
-  </si>
-  <si>
-    <t>relationship--3a664eed-abf3-468f-8ea7-0c2f56a6d797</t>
-  </si>
-  <si>
-    <t>relationship--a95870b2-df9c-4e83-8afb-288bf5a64f65</t>
-  </si>
-  <si>
-    <t>relationship--fac7f4a6-b1cf-4de8-95fd-c0572a3b49e3</t>
-  </si>
-  <si>
-    <t>relationship--634a8fb1-512a-4832-b13d-41c010932da2</t>
-  </si>
-  <si>
-    <t>relationship--504ed725-252c-49a2-8689-73512c003a43</t>
-  </si>
-  <si>
-    <t>relationship--6289257b-7a80-4ddd-99f1-cf2abd113b06</t>
-  </si>
-  <si>
-    <t>relationship--960fb835-db39-4b2c-86d0-c7568efc8c98</t>
-  </si>
-  <si>
-    <t>relationship--e846b587-1c44-4e4b-a735-f273fd1259db</t>
-  </si>
-  <si>
-    <t>relationship--86dfbe3b-c925-4dd8-951b-7e0b7023cc86</t>
-  </si>
-  <si>
-    <t>relationship--e63eb9c4-15eb-491c-866e-d30ad20f203b</t>
-  </si>
-  <si>
-    <t>relationship--a287da2c-b1f1-4f30-99a0-805cb9a711e2</t>
-  </si>
-  <si>
-    <t>relationship--b78b5df4-e2f9-4c84-8db3-49f82b02b613</t>
-  </si>
-  <si>
-    <t>relationship--d38a1a85-7935-487b-856d-dafee61523bb</t>
-  </si>
-  <si>
-    <t>relationship--efd3dc16-0b5d-45a4-b080-ee7366d1e0ab</t>
-  </si>
-  <si>
-    <t>relationship--21bc97d0-3a54-4f31-b7da-3eb6691079ce</t>
-  </si>
-  <si>
-    <t>relationship--96b7b2d3-29a8-4ad0-ac06-bb86f85c9624</t>
-  </si>
-  <si>
-    <t>relationship--6f66e358-9cc6-4991-b1c3-1bda79e978b9</t>
-  </si>
-  <si>
-    <t>relationship--7a609ccd-35e2-4ad9-9713-56aa25d8c63e</t>
-  </si>
-  <si>
-    <t>relationship--19cef2a5-a003-4cb6-8176-6f3127d1edd7</t>
-  </si>
-  <si>
-    <t>relationship--438442e6-72b6-4328-9614-bd84c18e9f37</t>
-  </si>
-  <si>
-    <t>relationship--398381aa-531c-405f-aed7-3d38dd3a237f</t>
-  </si>
-  <si>
-    <t>relationship--02eb3122-dee8-4bfc-b204-218d8b684f7a</t>
-  </si>
-  <si>
-    <t>relationship--d53bce89-a103-4d7c-8ea8-2333c6489fd6</t>
-  </si>
-  <si>
-    <t>relationship--a46628fd-fd9d-40a6-a015-c7f7be110dfb</t>
-  </si>
-  <si>
-    <t>relationship--51f3d5f4-0652-499c-80ec-45a93b0be7a5</t>
-  </si>
-  <si>
-    <t>relationship--b3f627d6-84a3-455b-bccf-7e3fa526b578</t>
-  </si>
-  <si>
-    <t>relationship--60ba7a78-9fd9-499a-a003-0cce676e699d</t>
-  </si>
-  <si>
-    <t>relationship--39739d1a-0650-4d22-8a38-7f939f45b8d8</t>
-  </si>
-  <si>
-    <t>relationship--f2d2c9d7-b46d-47e4-8fd5-742252ccd620</t>
-  </si>
-  <si>
-    <t>relationship--4153ab9f-943b-4995-943c-c14b1b339d1a</t>
-  </si>
-  <si>
-    <t>relationship--8d65f873-a4e1-4744-a9e4-ab61a7378e80</t>
-  </si>
-  <si>
-    <t>relationship--e9745134-7839-4af0-8210-bf47f45f20cc</t>
-  </si>
-  <si>
-    <t>relationship--846ac497-b1ec-4a7b-a247-8cddc509b219</t>
-  </si>
-  <si>
-    <t>relationship--9a57833c-cb56-4de0-a552-62c9f65da7a7</t>
-  </si>
-  <si>
-    <t>relationship--55c47b90-fef5-4d98-a974-2e3dba81e9f4</t>
-  </si>
-  <si>
-    <t>relationship--779b1051-442e-489d-b573-2427e75a6ec6</t>
-  </si>
-  <si>
-    <t>relationship--5134de7e-c701-4184-a01a-3d496683bf7c</t>
-  </si>
-  <si>
-    <t>relationship--c645c076-a8b7-4a94-b921-dbc3cd3e020b</t>
-  </si>
-  <si>
-    <t>relationship--d48c63a8-e715-44f4-8d8f-d6dcf924fb88</t>
-  </si>
-  <si>
-    <t>relationship--c806f5dd-16ff-48f8-8a5d-5c127f9c33af</t>
-  </si>
-  <si>
-    <t>relationship--91b5ca84-3790-43f1-94bb-8124e34bbf80</t>
-  </si>
-  <si>
-    <t>relationship--8b46fafd-0d49-4d50-afe0-86cd95871c0d</t>
-  </si>
-  <si>
-    <t>relationship--2b29244e-1ac5-4f80-828e-9aabd64d4e2d</t>
-  </si>
-  <si>
-    <t>relationship--a1ea235c-d52a-4f3d-ae88-9845dbcfc8b8</t>
-  </si>
-  <si>
-    <t>relationship--521c0b27-b0b7-4b31-a67f-f9dc575eff73</t>
-  </si>
-  <si>
-    <t>relationship--0f8eedc0-a461-476b-b8bf-57da6914a22e</t>
+    <t>relationship--54c4d918-8bc7-4364-80f9-b0caf2bf0969</t>
+  </si>
+  <si>
+    <t>relationship--73189ccc-2381-4e23-95ce-ae7a30a09f43</t>
+  </si>
+  <si>
+    <t>relationship--04b40aa1-c056-4a12-a4ca-9a5b999da66e</t>
+  </si>
+  <si>
+    <t>relationship--6fc62b9c-7886-4974-ab01-cc635d166860</t>
+  </si>
+  <si>
+    <t>relationship--17316c02-b0c3-455f-8bcd-157aba4b808d</t>
+  </si>
+  <si>
+    <t>relationship--9a4c2560-ff66-4227-a982-86d97e2ffbed</t>
+  </si>
+  <si>
+    <t>relationship--4403eef2-fe84-4921-a94f-6257d3547b6e</t>
+  </si>
+  <si>
+    <t>relationship--84d3e218-1a16-4f3d-bf83-29abb545e970</t>
+  </si>
+  <si>
+    <t>relationship--62854ef1-cc65-4a00-85d8-968cabe77970</t>
+  </si>
+  <si>
+    <t>relationship--34a8027e-bb56-4c8c-a6e5-f2eff445b635</t>
+  </si>
+  <si>
+    <t>relationship--7a5673bf-43ca-4139-ac6b-d5bb967c11e6</t>
+  </si>
+  <si>
+    <t>relationship--96d6ea01-4a3b-4a31-834e-f6a1b25d3d01</t>
+  </si>
+  <si>
+    <t>relationship--65b32450-6df6-4327-9411-bb11dd24e186</t>
+  </si>
+  <si>
+    <t>relationship--cbbeb0ed-42c2-4724-b202-23d4856aff33</t>
+  </si>
+  <si>
+    <t>relationship--f2f90e4d-5a63-40b4-adad-90332f88a7be</t>
+  </si>
+  <si>
+    <t>relationship--11b1266c-d020-420d-9c40-318b57e0bbeb</t>
+  </si>
+  <si>
+    <t>relationship--5195893a-8224-493f-bdbb-b276f796dbb8</t>
+  </si>
+  <si>
+    <t>relationship--6165994a-b952-429b-8905-431c9e06f4cf</t>
+  </si>
+  <si>
+    <t>relationship--25f80921-0d9d-4d56-8a10-0b1c86bd8490</t>
+  </si>
+  <si>
+    <t>relationship--a1ce3595-ecd4-41b1-83f7-5aa32a7a4c25</t>
+  </si>
+  <si>
+    <t>relationship--b2d2b23a-2561-4b1b-b23b-60ec84ac8559</t>
+  </si>
+  <si>
+    <t>relationship--1a5c8ccb-b7f9-4118-9977-904a79d8cd91</t>
+  </si>
+  <si>
+    <t>relationship--499220bf-45f5-42dc-9842-b2104ef2385b</t>
+  </si>
+  <si>
+    <t>relationship--975edf7f-38d6-4125-86ae-6df413e02b64</t>
+  </si>
+  <si>
+    <t>relationship--13fe682c-4d2b-498e-b0fe-5faa9627f478</t>
+  </si>
+  <si>
+    <t>relationship--f98d2762-9dda-4bb9-a018-e77fcb87b59c</t>
+  </si>
+  <si>
+    <t>relationship--cda16288-3df9-4f63-8073-a4b437c71004</t>
+  </si>
+  <si>
+    <t>relationship--1f5a1489-2483-4e84-a40e-04efed8b94b4</t>
+  </si>
+  <si>
+    <t>relationship--fb03a109-6075-4b58-afb4-6a2557f2c215</t>
+  </si>
+  <si>
+    <t>relationship--9ec9acf6-7154-4532-913c-ccdf66091156</t>
+  </si>
+  <si>
+    <t>relationship--63452325-03d3-49b1-bf54-66dfb125ec87</t>
+  </si>
+  <si>
+    <t>relationship--0e802b5c-2403-479e-ac20-06e9aa5c43ae</t>
+  </si>
+  <si>
+    <t>relationship--dfc52397-92e1-4160-a98f-34948d016360</t>
+  </si>
+  <si>
+    <t>relationship--d6cc70a9-9c36-42e2-b4a9-454d252faa7a</t>
+  </si>
+  <si>
+    <t>relationship--7c07f851-9a41-4d35-b79f-fb7069c0d04d</t>
+  </si>
+  <si>
+    <t>relationship--971fa3bc-ca45-4715-9d2c-da25aab64756</t>
+  </si>
+  <si>
+    <t>relationship--676dfa2f-887b-4a44-869a-7ef3d8e61b0a</t>
+  </si>
+  <si>
+    <t>relationship--a476ccc4-9b09-40e8-85fa-c2cb5269f2b1</t>
+  </si>
+  <si>
+    <t>relationship--e9e57c76-c09b-4fd5-b89f-46f96cca140d</t>
+  </si>
+  <si>
+    <t>relationship--cedcc327-db8f-4d4c-b1f0-f6c89260dda8</t>
+  </si>
+  <si>
+    <t>relationship--cc6b2561-a78f-4f37-aee5-e8248c3db565</t>
+  </si>
+  <si>
+    <t>relationship--685565b6-7584-4468-b179-52fe99c48584</t>
+  </si>
+  <si>
+    <t>relationship--40f1a33f-1390-4a00-b1be-cf9f1d3c976b</t>
+  </si>
+  <si>
+    <t>relationship--66b98a2b-4c8f-4386-958d-02048df51fc3</t>
+  </si>
+  <si>
+    <t>relationship--7f56817f-8b83-4c6c-b2fd-a0b7f86dec1f</t>
+  </si>
+  <si>
+    <t>relationship--1ac9ff58-8efb-419c-928c-fe3847c9188c</t>
+  </si>
+  <si>
+    <t>relationship--9c48b5cd-56e8-49a0-9b61-a580368cf0e1</t>
+  </si>
+  <si>
+    <t>relationship--9b25f341-01f3-4dfd-a588-165a86bcaace</t>
+  </si>
+  <si>
+    <t>relationship--9da377c2-38ff-439c-823b-34a5d1998571</t>
+  </si>
+  <si>
+    <t>relationship--279284af-ae24-4c2b-bc5e-17e518c8868e</t>
+  </si>
+  <si>
+    <t>relationship--a07d27b0-07d8-4981-a5a0-be24cbe07191</t>
+  </si>
+  <si>
+    <t>relationship--3e6cea56-29f5-4715-a858-a40804c68293</t>
+  </si>
+  <si>
+    <t>relationship--ffafc4ad-f136-4aae-9beb-72a49eea5020</t>
+  </si>
+  <si>
+    <t>relationship--0ff6a61c-38db-4435-9190-d7afac3f982d</t>
+  </si>
+  <si>
+    <t>relationship--1ca8158f-e8b9-4dad-a4d9-63c5e5f7b814</t>
+  </si>
+  <si>
+    <t>relationship--7039815a-5bb6-4ae6-add1-1d88c03ca42f</t>
+  </si>
+  <si>
+    <t>relationship--07c3aeaa-21f2-42bd-a3d0-ebd14c8dbf1b</t>
+  </si>
+  <si>
+    <t>relationship--38e83d08-2485-4ebe-bf67-1c981ee314ba</t>
+  </si>
+  <si>
+    <t>relationship--f9f2ba02-56ea-4444-9e3f-a47c6972d6e7</t>
+  </si>
+  <si>
+    <t>relationship--a971ee1c-e0d2-4f15-9cd2-62e3d0d32ca0</t>
+  </si>
+  <si>
+    <t>relationship--d6699f88-a5cb-40dd-ae75-19f280aeb4cb</t>
+  </si>
+  <si>
+    <t>relationship--ece83b83-27bc-4e09-a313-ad8cee5ebeb7</t>
+  </si>
+  <si>
+    <t>relationship--cb5e7817-a24b-4246-a285-3699c9a6faa1</t>
+  </si>
+  <si>
+    <t>relationship--3be951b7-a21a-4015-8629-51c108cb9c26</t>
+  </si>
+  <si>
+    <t>relationship--de9774c2-f9b4-4b84-825a-2e1b90f22f46</t>
+  </si>
+  <si>
+    <t>relationship--c94c095f-581b-4666-bc33-15a56a4f7b95</t>
+  </si>
+  <si>
+    <t>relationship--d1aa0946-d87c-45ae-b424-d9c9146f01e9</t>
+  </si>
+  <si>
+    <t>relationship--bd156b28-4368-4ef7-9442-99a4037f8990</t>
+  </si>
+  <si>
+    <t>relationship--51b252c6-f25a-4868-ba2f-5c4c5dce3575</t>
+  </si>
+  <si>
+    <t>relationship--ea59c0a9-5e60-42a9-b62c-7b1c2c235920</t>
+  </si>
+  <si>
+    <t>relationship--472e25d9-877e-4eea-8777-ff8fb1f2cf1d</t>
+  </si>
+  <si>
+    <t>relationship--15b4a1ec-a4c0-4c0d-af6b-9ce3c60dc53c</t>
+  </si>
+  <si>
+    <t>relationship--45b6dca8-89ca-4d24-89ea-a829323807cb</t>
+  </si>
+  <si>
+    <t>relationship--73e7a9e7-fd3a-4ec8-8d58-ad42c116c5e5</t>
+  </si>
+  <si>
+    <t>relationship--e25881ca-c77f-4de2-9a5a-93e603d6089d</t>
+  </si>
+  <si>
+    <t>relationship--ccbb2c32-1b08-4489-9281-a4e802aebe2c</t>
+  </si>
+  <si>
+    <t>relationship--b1254916-a50c-4122-8a8b-ddae6cb4bf3b</t>
+  </si>
+  <si>
+    <t>relationship--436a367d-751f-46ae-865b-1b08b2c94b0b</t>
+  </si>
+  <si>
+    <t>relationship--ae1830ae-193d-49fd-88b8-9ca09acab278</t>
+  </si>
+  <si>
+    <t>relationship--a00d775f-db2b-4bf4-9738-882d507f14a3</t>
+  </si>
+  <si>
+    <t>relationship--91d493cc-ed9d-410a-87da-737f90d29d5f</t>
+  </si>
+  <si>
+    <t>relationship--2a31099b-0274-4bcb-bcd8-1ab0dd82ca1a</t>
+  </si>
+  <si>
+    <t>relationship--613a2833-e940-4b58-90d7-22663e80ee19</t>
+  </si>
+  <si>
+    <t>relationship--e2b3c79f-8da6-406e-b66b-35ee86951b5c</t>
+  </si>
+  <si>
+    <t>relationship--a27107bb-ee98-440b-b975-fbe403b7d011</t>
+  </si>
+  <si>
+    <t>relationship--22684718-ebff-48c1-835a-4dbcaae467d6</t>
+  </si>
+  <si>
+    <t>relationship--6c0f5f2d-13a9-4854-b56a-31267e3e57d4</t>
+  </si>
+  <si>
+    <t>relationship--2d8f0eaa-86d6-4ec2-b131-fb0176dde252</t>
+  </si>
+  <si>
+    <t>relationship--7acaf2ec-5332-4376-b9e6-e5f7a5d4e396</t>
+  </si>
+  <si>
+    <t>relationship--51ef3804-21ae-4b4d-90ff-66961d7c3031</t>
+  </si>
+  <si>
+    <t>relationship--46f3bd13-d9a3-40ce-9833-559c430cf1de</t>
+  </si>
+  <si>
+    <t>relationship--2e7a2655-e1f7-4be0-8560-99a7ce302fda</t>
+  </si>
+  <si>
+    <t>relationship--2b1d8bec-1187-47fc-a890-9171d0af4206</t>
+  </si>
+  <si>
+    <t>relationship--0c6b277f-6616-428d-8dde-d133beab7c6b</t>
+  </si>
+  <si>
+    <t>relationship--00266455-3f2b-4b3c-8e1f-6ce6193cb8f4</t>
+  </si>
+  <si>
+    <t>relationship--7981c6df-980d-427f-b355-4ce7650a11fa</t>
+  </si>
+  <si>
+    <t>relationship--58a2fd8c-b163-4fd7-af8e-4e5f518cf565</t>
+  </si>
+  <si>
+    <t>relationship--55fad24c-1298-46ae-8628-2eec64a7d75c</t>
+  </si>
+  <si>
+    <t>relationship--1bb41d58-bb9f-4f26-b8b2-5a6600fe25d5</t>
+  </si>
+  <si>
+    <t>relationship--3e20551e-d442-43b7-9893-b825832447f8</t>
+  </si>
+  <si>
+    <t>relationship--aef61ea4-d2d3-4b7d-b3f2-eb09d9954aba</t>
+  </si>
+  <si>
+    <t>relationship--fceb239a-b0ae-48e6-bec0-0c8c7357ebd9</t>
+  </si>
+  <si>
+    <t>relationship--3380f24c-4e14-49a4-a119-a87f1b9eecd9</t>
+  </si>
+  <si>
+    <t>relationship--a22a0b8c-4032-40b7-a0ea-12e9dbf2961b</t>
+  </si>
+  <si>
+    <t>relationship--217bd9d8-a378-463f-9cc8-e7fadf8aa13d</t>
+  </si>
+  <si>
+    <t>relationship--2f9a83f4-d17c-4e2f-b852-7e1823502480</t>
+  </si>
+  <si>
+    <t>relationship--1227d382-496a-4e5d-8e55-ff384f5424d1</t>
+  </si>
+  <si>
+    <t>relationship--14448630-38e2-458b-b4e9-f8184c4c7809</t>
+  </si>
+  <si>
+    <t>relationship--893aac3e-99cc-4a45-96b3-d9cc67be9476</t>
+  </si>
+  <si>
+    <t>relationship--1a5bc425-80c9-491b-8c61-699e84666675</t>
+  </si>
+  <si>
+    <t>relationship--3129830c-d6e0-43ad-aac8-fa955eec7292</t>
+  </si>
+  <si>
+    <t>relationship--ad8190b9-1ea3-422d-9cc0-79fe25111c3b</t>
+  </si>
+  <si>
+    <t>relationship--2a74ddf8-7017-4935-821c-bcd120366aec</t>
+  </si>
+  <si>
+    <t>relationship--65ad9ce1-3c06-4312-9781-f4ab0a1b4576</t>
+  </si>
+  <si>
+    <t>relationship--0d90ba2b-7b16-4c53-9b8f-26c329a24988</t>
+  </si>
+  <si>
+    <t>relationship--a3fe44a7-14ec-4ea0-b4f4-6846c5fbc24d</t>
+  </si>
+  <si>
+    <t>relationship--5e869d43-c351-4be0-a267-f79006c39d2d</t>
+  </si>
+  <si>
+    <t>relationship--10ef8b9a-6360-401d-8baf-86e9b805780c</t>
+  </si>
+  <si>
+    <t>relationship--15dd688a-f80a-4db8-b9bc-c1cdacee5bf9</t>
+  </si>
+  <si>
+    <t>relationship--21f6c7af-2c6e-4bf7-850c-61b5194aa999</t>
+  </si>
+  <si>
+    <t>relationship--839f6e5b-5e89-44c0-a3e6-71397137e2c0</t>
+  </si>
+  <si>
+    <t>relationship--3db1a8d4-08de-47d8-b608-1855ef5fc32e</t>
+  </si>
+  <si>
+    <t>relationship--8834c869-09ab-4a5b-9269-c40d5a257df4</t>
+  </si>
+  <si>
+    <t>relationship--fdce753f-4c29-4b25-91ff-7f7d8b2afea8</t>
+  </si>
+  <si>
+    <t>relationship--a87b6855-782c-4452-bdb9-86e7e2ec6059</t>
+  </si>
+  <si>
+    <t>relationship--f81e8eb7-d4f6-4e9a-b29f-4f25d579e7da</t>
+  </si>
+  <si>
+    <t>relationship--f696fb29-1c07-45b5-b568-64f4f6fe8fec</t>
+  </si>
+  <si>
+    <t>relationship--d9fa28d8-1f00-498b-918b-26c1e7ae1c53</t>
+  </si>
+  <si>
+    <t>relationship--f045efb9-8922-4775-970d-481418f671a0</t>
+  </si>
+  <si>
+    <t>relationship--205dff75-fc00-4858-8a43-d0391dd8c888</t>
+  </si>
+  <si>
+    <t>relationship--0a3003bf-966e-423b-b592-01d663788603</t>
+  </si>
+  <si>
+    <t>relationship--90f65ece-ab59-4b9f-aa48-6f3f18d3e1eb</t>
+  </si>
+  <si>
+    <t>relationship--1d1cb160-1ad8-4e2b-a6fb-cd4745e040b4</t>
+  </si>
+  <si>
+    <t>relationship--d883cc91-90fa-4cca-a50c-7267c0aff891</t>
+  </si>
+  <si>
+    <t>relationship--5aaf25d0-bc32-4203-9c9d-d9f66bd960d1</t>
+  </si>
+  <si>
+    <t>relationship--30b46d33-7b73-4334-a1db-d91a5850d0f8</t>
+  </si>
+  <si>
+    <t>relationship--1415d9e2-3ec8-4950-a3cf-0a771978afa9</t>
+  </si>
+  <si>
+    <t>relationship--4fdb62a5-fb3e-4fb6-aa8a-b682cb4e1c20</t>
+  </si>
+  <si>
+    <t>relationship--bbe1b9bc-6806-402f-b985-2f64a72ff0e3</t>
+  </si>
+  <si>
+    <t>relationship--4262f5bf-7ff8-4bb6-84c4-e0226ad3b11d</t>
+  </si>
+  <si>
+    <t>relationship--d62debb4-770b-4b6f-8173-018af2a5b325</t>
+  </si>
+  <si>
+    <t>relationship--2c6e107e-e860-40fb-8f76-ce5682d72b02</t>
+  </si>
+  <si>
+    <t>relationship--49922116-adf1-4974-b9b4-8baef88d2dd9</t>
+  </si>
+  <si>
+    <t>relationship--d2d79914-471e-457f-ae36-41d34ccaeff6</t>
+  </si>
+  <si>
+    <t>relationship--f44aba76-9d85-4d72-a071-a2e09093df88</t>
+  </si>
+  <si>
+    <t>relationship--502e33d2-3654-4b52-a2d2-08a6a6c709f3</t>
+  </si>
+  <si>
+    <t>relationship--b0b9692d-77af-4890-986f-fc4b37d7dfa3</t>
+  </si>
+  <si>
+    <t>relationship--e5e638ab-fd72-4af1-9f8d-e2bb7d44142c</t>
+  </si>
+  <si>
+    <t>relationship--5bcf5e3f-e1a0-4b65-a5ef-c087360b918b</t>
+  </si>
+  <si>
+    <t>relationship--b8cf1b28-e865-4cd7-93f6-565527b4a923</t>
+  </si>
+  <si>
+    <t>relationship--a7a7b234-a9dd-4b62-b9ed-73f511c5adf8</t>
+  </si>
+  <si>
+    <t>relationship--63474f71-ecda-42ff-8bc1-475a951eb9d4</t>
+  </si>
+  <si>
+    <t>relationship--06e2c87e-97c1-425e-aa49-49a43aaf8c38</t>
+  </si>
+  <si>
+    <t>relationship--c5907c16-a6b2-4585-8587-743dbd102eb4</t>
+  </si>
+  <si>
+    <t>relationship--ef4b5e37-4b77-41ef-a9fd-ed32e7dd71d1</t>
+  </si>
+  <si>
+    <t>relationship--7d60876d-abd3-49cb-9646-9d3ce55e8eaa</t>
+  </si>
+  <si>
+    <t>relationship--00d76dd5-547f-4d91-a2b2-a68120947401</t>
+  </si>
+  <si>
+    <t>relationship--5d240505-32ed-4a6f-897e-bc114bded524</t>
+  </si>
+  <si>
+    <t>relationship--6867b04c-5665-48ce-a4a9-d0e025aae5b3</t>
   </si>
   <si>
     <t>reference</t>
@@ -4016,18 +4016,30 @@
     <t>2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
   </si>
   <si>
+    <t>2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024</t>
+  </si>
+  <si>
     <t>FrostyGoop Incident | MITRE ATT&amp;CK® 2024</t>
   </si>
   <si>
     <t>Іван Мазепа — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Історія Донецької області — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Історія України — Вікіпедія 2026</t>
   </si>
   <si>
     <t>Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Батуринська трагедія — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
@@ -4052,6 +4064,9 @@
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
+    <t>Карательная психиатрия в России: назад в СССР? 2020</t>
+  </si>
+  <si>
     <t>Кенгирское восстание заключённых - Википедия 2026</t>
   </si>
   <si>
@@ -4076,6 +4091,9 @@
     <t>Мазепа 2007</t>
   </si>
   <si>
+    <t>Мазепа, Иван Степанович — Википедия 2026</t>
+  </si>
+  <si>
     <t>Малоросійське генерал-губернаторство — Вікіпедія 2026</t>
   </si>
   <si>
@@ -4136,27 +4154,36 @@
     <t>Чорносотенці — Вікіпедія 2026</t>
   </si>
   <si>
-    <t>Карательная психиатрия в России: назад в СССР? 2020</t>
-  </si>
-  <si>
     <t>MITRE ATT&amp;CK®. (2023). 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
     <t>MITRE ATT&amp;CK®. (2023). 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
+    <t>MITRE ATT&amp;CK®. (2024). 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
     <t>MITRE ATT&amp;CK®. (2024). FrostyGoop Incident | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
     <t>Вікіпедія. (2026). Іван Мазепа — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Історія Донецької області — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
   </si>
   <si>
     <t>Вікіпедія. (2026). Анексія Київської митрополії Московським патріархатом — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Батуринська трагедія — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Виктор Дённингхаус. (2011). В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ ..</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
@@ -4181,6 +4208,9 @@
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
+    <t>Riddle Russia. (2020). Карательная психиатрия в России: назад в СССР?.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
   </si>
   <si>
@@ -4205,6 +4235,9 @@
     <t>Татьяна Таирова-Яковлева. (2007). Мазепа.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Мазепа, Иван Степанович — Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Малоросійське генерал-губернаторство — Вікіпедія.</t>
   </si>
   <si>
@@ -4265,27 +4298,33 @@
     <t>Википедия. (2026). Чорносотенці — Вікіпедія.</t>
   </si>
   <si>
-    <t>Riddle Russia. (2020). Карательная психиатрия в России: назад в СССР?.</t>
-  </si>
-  <si>
     <t>https://attack.mitre.org/campaigns/C0028/</t>
   </si>
   <si>
     <t>https://attack.mitre.org/campaigns/C0025/</t>
   </si>
   <si>
+    <t>https://attack.mitre.org/campaigns/C0034/</t>
+  </si>
+  <si>
     <t>https://attack.mitre.org/campaigns/C0041/</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%2594%25D0%25BE%25D0%25BD%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BE%25D0%25B1%25D0%25BB%25D0%25B0%25D1%2581%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
   </si>
   <si>
@@ -4304,6 +4343,9 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
   </si>
   <si>
+    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
   </si>
   <si>
@@ -4325,6 +4367,9 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
   </si>
   <si>
@@ -4380,9 +4425,6 @@
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
   </si>
 </sst>
 </file>
@@ -20889,7 +20931,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20908,10 +20950,10 @@
         <v>1325</v>
       </c>
       <c r="B2" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1411</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -20919,10 +20961,10 @@
         <v>1326</v>
       </c>
       <c r="B3" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1412</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -20930,10 +20972,10 @@
         <v>1327</v>
       </c>
       <c r="B4" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1413</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -20941,10 +20983,10 @@
         <v>1328</v>
       </c>
       <c r="B5" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1414</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -20952,10 +20994,10 @@
         <v>1329</v>
       </c>
       <c r="B6" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -20963,10 +21005,10 @@
         <v>1330</v>
       </c>
       <c r="B7" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1416</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -20974,7 +21016,10 @@
         <v>1331</v>
       </c>
       <c r="B8" t="s">
-        <v>1374</v>
+        <v>1379</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1427</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -20982,10 +21027,10 @@
         <v>1332</v>
       </c>
       <c r="B9" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1417</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -20993,10 +21038,10 @@
         <v>1333</v>
       </c>
       <c r="B10" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1418</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -21004,10 +21049,7 @@
         <v>1334</v>
       </c>
       <c r="B11" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1419</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -21015,10 +21057,7 @@
         <v>1335</v>
       </c>
       <c r="B12" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>1420</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -21026,10 +21065,10 @@
         <v>1336</v>
       </c>
       <c r="B13" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1421</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -21037,10 +21076,10 @@
         <v>1337</v>
       </c>
       <c r="B14" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1422</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -21048,7 +21087,10 @@
         <v>1338</v>
       </c>
       <c r="B15" t="s">
-        <v>1381</v>
+        <v>1386</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1432</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -21056,10 +21098,10 @@
         <v>1339</v>
       </c>
       <c r="B16" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1423</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -21067,10 +21109,10 @@
         <v>1340</v>
       </c>
       <c r="B17" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1424</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -21078,10 +21120,10 @@
         <v>1341</v>
       </c>
       <c r="B18" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1425</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -21089,10 +21131,7 @@
         <v>1342</v>
       </c>
       <c r="B19" t="s">
-        <v>1385</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>1426</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -21100,10 +21139,10 @@
         <v>1343</v>
       </c>
       <c r="B20" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1427</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -21111,10 +21150,10 @@
         <v>1344</v>
       </c>
       <c r="B21" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1428</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -21122,10 +21161,10 @@
         <v>1345</v>
       </c>
       <c r="B22" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1429</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -21133,7 +21172,10 @@
         <v>1346</v>
       </c>
       <c r="B23" t="s">
-        <v>1389</v>
+        <v>1394</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1439</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -21141,10 +21183,10 @@
         <v>1347</v>
       </c>
       <c r="B24" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -21152,10 +21194,10 @@
         <v>1348</v>
       </c>
       <c r="B25" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -21163,10 +21205,10 @@
         <v>1349</v>
       </c>
       <c r="B26" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -21174,10 +21216,10 @@
         <v>1350</v>
       </c>
       <c r="B27" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -21185,7 +21227,7 @@
         <v>1351</v>
       </c>
       <c r="B28" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -21193,10 +21235,10 @@
         <v>1352</v>
       </c>
       <c r="B29" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1434</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -21204,10 +21246,10 @@
         <v>1353</v>
       </c>
       <c r="B30" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1435</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -21215,10 +21257,10 @@
         <v>1354</v>
       </c>
       <c r="B31" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1436</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -21226,10 +21268,10 @@
         <v>1355</v>
       </c>
       <c r="B32" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1437</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -21237,10 +21279,10 @@
         <v>1356</v>
       </c>
       <c r="B33" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1438</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -21248,10 +21290,7 @@
         <v>1357</v>
       </c>
       <c r="B34" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>1439</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -21259,10 +21298,10 @@
         <v>1358</v>
       </c>
       <c r="B35" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1440</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -21270,10 +21309,10 @@
         <v>1359</v>
       </c>
       <c r="B36" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1441</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -21281,10 +21320,10 @@
         <v>1360</v>
       </c>
       <c r="B37" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1442</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -21292,10 +21331,10 @@
         <v>1361</v>
       </c>
       <c r="B38" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1443</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -21303,10 +21342,10 @@
         <v>1362</v>
       </c>
       <c r="B39" t="s">
-        <v>1405</v>
+        <v>1410</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1444</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -21314,10 +21353,10 @@
         <v>1363</v>
       </c>
       <c r="B40" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1445</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -21325,10 +21364,10 @@
         <v>1364</v>
       </c>
       <c r="B41" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1446</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -21336,10 +21375,10 @@
         <v>1365</v>
       </c>
       <c r="B42" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1447</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -21347,10 +21386,10 @@
         <v>1366</v>
       </c>
       <c r="B43" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1448</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -21358,10 +21397,76 @@
         <v>1367</v>
       </c>
       <c r="B44" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1449</v>
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1436</v>
       </c>
     </row>
   </sheetData>
@@ -21372,19 +21477,19 @@
     <hyperlink ref="C5" r:id="rId4"/>
     <hyperlink ref="C6" r:id="rId5"/>
     <hyperlink ref="C7" r:id="rId6"/>
-    <hyperlink ref="C9" r:id="rId7"/>
-    <hyperlink ref="C10" r:id="rId8"/>
-    <hyperlink ref="C11" r:id="rId9"/>
-    <hyperlink ref="C12" r:id="rId10"/>
-    <hyperlink ref="C13" r:id="rId11"/>
-    <hyperlink ref="C14" r:id="rId12"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C13" r:id="rId10"/>
+    <hyperlink ref="C14" r:id="rId11"/>
+    <hyperlink ref="C15" r:id="rId12"/>
     <hyperlink ref="C16" r:id="rId13"/>
     <hyperlink ref="C17" r:id="rId14"/>
     <hyperlink ref="C18" r:id="rId15"/>
-    <hyperlink ref="C19" r:id="rId16"/>
-    <hyperlink ref="C20" r:id="rId17"/>
-    <hyperlink ref="C21" r:id="rId18"/>
-    <hyperlink ref="C22" r:id="rId19"/>
+    <hyperlink ref="C20" r:id="rId16"/>
+    <hyperlink ref="C21" r:id="rId17"/>
+    <hyperlink ref="C22" r:id="rId18"/>
+    <hyperlink ref="C23" r:id="rId19"/>
     <hyperlink ref="C24" r:id="rId20"/>
     <hyperlink ref="C25" r:id="rId21"/>
     <hyperlink ref="C26" r:id="rId22"/>
@@ -21394,17 +21499,22 @@
     <hyperlink ref="C31" r:id="rId26"/>
     <hyperlink ref="C32" r:id="rId27"/>
     <hyperlink ref="C33" r:id="rId28"/>
-    <hyperlink ref="C34" r:id="rId29"/>
-    <hyperlink ref="C35" r:id="rId30"/>
-    <hyperlink ref="C36" r:id="rId31"/>
-    <hyperlink ref="C37" r:id="rId32"/>
-    <hyperlink ref="C38" r:id="rId33"/>
-    <hyperlink ref="C39" r:id="rId34"/>
-    <hyperlink ref="C40" r:id="rId35"/>
-    <hyperlink ref="C41" r:id="rId36"/>
-    <hyperlink ref="C42" r:id="rId37"/>
-    <hyperlink ref="C43" r:id="rId38"/>
-    <hyperlink ref="C44" r:id="rId39"/>
+    <hyperlink ref="C35" r:id="rId29"/>
+    <hyperlink ref="C36" r:id="rId30"/>
+    <hyperlink ref="C37" r:id="rId31"/>
+    <hyperlink ref="C38" r:id="rId32"/>
+    <hyperlink ref="C39" r:id="rId33"/>
+    <hyperlink ref="C40" r:id="rId34"/>
+    <hyperlink ref="C41" r:id="rId35"/>
+    <hyperlink ref="C42" r:id="rId36"/>
+    <hyperlink ref="C43" r:id="rId37"/>
+    <hyperlink ref="C44" r:id="rId38"/>
+    <hyperlink ref="C45" r:id="rId39"/>
+    <hyperlink ref="C46" r:id="rId40"/>
+    <hyperlink ref="C47" r:id="rId41"/>
+    <hyperlink ref="C48" r:id="rId42"/>
+    <hyperlink ref="C49" r:id="rId43"/>
+    <hyperlink ref="C50" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -98,46 +98,46 @@
     <t>S0013</t>
   </si>
   <si>
-    <t>tool--7a23a962-6a24-49c1-80ad-d7ef44f2ccac</t>
-  </si>
-  <si>
-    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
-  </si>
-  <si>
-    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
-  </si>
-  <si>
-    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
-  </si>
-  <si>
-    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
-  </si>
-  <si>
-    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
-  </si>
-  <si>
-    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
-  </si>
-  <si>
-    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
-  </si>
-  <si>
-    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
-  </si>
-  <si>
-    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
-  </si>
-  <si>
-    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
-  </si>
-  <si>
-    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
-  </si>
-  <si>
-    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
-  </si>
-  <si>
-    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
+    <t>tool--5baeca0c-852e-4e6a-a3ea-05904063aa5e</t>
+  </si>
+  <si>
+    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
+  </si>
+  <si>
+    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
+  </si>
+  <si>
+    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
+  </si>
+  <si>
+    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
+  </si>
+  <si>
+    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
+  </si>
+  <si>
+    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
+  </si>
+  <si>
+    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
+  </si>
+  <si>
+    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
+  </si>
+  <si>
+    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
+  </si>
+  <si>
+    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
+  </si>
+  <si>
+    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
+  </si>
+  <si>
+    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
+  </si>
+  <si>
+    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
   </si>
   <si>
     <t>Верховный тайный совет</t>
@@ -298,7 +298,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Перепис населення Російської імперії (1897),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Історія України — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
@@ -310,31 +310,31 @@
     <t>,(Citation: Друга Малоросійська колегія — Вікіпедія 2026),</t>
   </si>
   <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Історія України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Історія України — Вікіпедія 2026)</t>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Російсько-українська війна (з 2014),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Московсько-українська війна (1658—1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Листопадове повстання (1830—1831),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Крымская война — Википедия 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Московські статті (1665),(Citation: Русско-турецкая война (1877—1878),(Citation: Повстання бузьких козаків (1817),(Citation: Мазепа 2007),(Citation: Російсько-українська війна (з 2014),(Citation: Переяславські статті (1659),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Північна війна (1700—1721),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659)</t>
-  </si>
-  <si>
-    <t>(Citation: Руїна — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Руїна — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Рашизм: Звір з безодні 2023),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026)</t>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Крымская война — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Московсько-українська війна (1658—1659),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Листопадове повстання (1830—1831),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665),(Citation: Азовські походи (1695—1696),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -403,22 +403,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
-  </si>
-  <si>
-    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
-  </si>
-  <si>
-    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
-  </si>
-  <si>
-    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
-  </si>
-  <si>
-    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
-  </si>
-  <si>
-    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
+    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
+  </si>
+  <si>
+    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
+  </si>
+  <si>
+    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
+  </si>
+  <si>
+    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
+  </si>
+  <si>
+    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
+  </si>
+  <si>
+    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
   </si>
   <si>
     <t>group</t>
@@ -532,106 +532,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--ee1770df-945f-4564-9553-b1d84f490dcd</t>
-  </si>
-  <si>
-    <t>relationship--8bc54604-c986-43f2-a701-b12592389a95</t>
-  </si>
-  <si>
-    <t>relationship--653bfee4-8148-4228-b9ad-a0dd9f6fb024</t>
-  </si>
-  <si>
-    <t>relationship--8c5d41d1-9fc6-4849-a964-d4d4cd88d808</t>
-  </si>
-  <si>
-    <t>relationship--5be4de54-a976-41cf-9a3e-801a66dd4ab0</t>
-  </si>
-  <si>
-    <t>relationship--f005b199-111a-4b05-aefa-24a35febc482</t>
-  </si>
-  <si>
-    <t>relationship--0dbf3ce6-19bd-478e-adf9-32c6e80ed0ea</t>
-  </si>
-  <si>
-    <t>relationship--c208739a-827c-4d0e-bf28-61b916f15cfe</t>
-  </si>
-  <si>
-    <t>relationship--614fbc69-8cba-40a0-98f9-936eaac5419e</t>
-  </si>
-  <si>
-    <t>relationship--ca9d96ad-f282-4c8a-a7f1-c49268bc3a88</t>
-  </si>
-  <si>
-    <t>relationship--086b6153-43f4-47de-80df-44693f738943</t>
-  </si>
-  <si>
-    <t>relationship--8a4808c1-777c-40fc-aa35-f6cd68dc33c2</t>
-  </si>
-  <si>
-    <t>relationship--37a411b5-a9ad-4aa3-b275-64db44664d5d</t>
-  </si>
-  <si>
-    <t>relationship--aee80eb9-ab23-4760-8add-e0216bd30a05</t>
-  </si>
-  <si>
-    <t>relationship--ca3971ca-3608-4f4b-ba38-3b8e016ebf03</t>
-  </si>
-  <si>
-    <t>relationship--80974889-50af-4c79-93b8-102362fc0530</t>
-  </si>
-  <si>
-    <t>relationship--e6ca03f6-6ec1-4870-bcb9-a3c507268afb</t>
-  </si>
-  <si>
-    <t>relationship--2a6b0d1a-4fc7-40de-9362-c8eb8abcb9fa</t>
-  </si>
-  <si>
-    <t>relationship--df0ae14a-9167-4c70-bba9-d917ecd1bcbe</t>
-  </si>
-  <si>
-    <t>relationship--38cbf6e2-05be-4c93-9361-7c3355dec29f</t>
-  </si>
-  <si>
-    <t>relationship--eb3986b1-fecd-4d37-92dd-0c8250ef0740</t>
-  </si>
-  <si>
-    <t>relationship--388cb58a-f6b1-432c-aa19-57cc86f8713f</t>
-  </si>
-  <si>
-    <t>relationship--c6850c22-f194-48a1-b786-c5cf857b99cd</t>
-  </si>
-  <si>
-    <t>relationship--917fb287-22e5-452a-9dc2-8c5c8aca7d1b</t>
-  </si>
-  <si>
-    <t>relationship--34cf12dd-b962-4ebe-830a-d8f1c7ff5c4f</t>
-  </si>
-  <si>
-    <t>relationship--94711d8b-0578-438a-9d73-eafd0c1bc983</t>
-  </si>
-  <si>
-    <t>relationship--8045380f-5282-4b2f-ab8f-cb92ffd304a3</t>
-  </si>
-  <si>
-    <t>relationship--3536b790-3098-4639-9c74-ac882b5ab83e</t>
-  </si>
-  <si>
-    <t>relationship--c09a449b-0b73-4e67-abc0-922897a14e61</t>
-  </si>
-  <si>
-    <t>relationship--079404c8-fadc-4028-b464-f31ba21f9514</t>
-  </si>
-  <si>
-    <t>relationship--51aabffe-86e6-4eaa-bf10-1d5525e930ad</t>
-  </si>
-  <si>
-    <t>relationship--49567418-6145-460a-ab69-bcb7861395ac</t>
-  </si>
-  <si>
-    <t>relationship--69dc0331-617e-4089-ac23-257dbeee91a6</t>
-  </si>
-  <si>
-    <t>relationship--57e6a8bb-5b08-4144-8f3d-8b095b08d609</t>
+    <t>relationship--bb009c88-365d-4fab-bf01-19c7661e62af</t>
+  </si>
+  <si>
+    <t>relationship--77b46dc8-4a63-44dd-9bd7-031969ec253c</t>
+  </si>
+  <si>
+    <t>relationship--5bde57b1-9715-42f1-b049-e06f015a1772</t>
+  </si>
+  <si>
+    <t>relationship--a14a9035-fa57-4d41-89f7-891ac9fcf81f</t>
+  </si>
+  <si>
+    <t>relationship--1c1b685c-3181-4352-b249-432542879ed6</t>
+  </si>
+  <si>
+    <t>relationship--475161f8-6686-424b-9917-db6889a0fcf3</t>
+  </si>
+  <si>
+    <t>relationship--13ac5123-1a57-4b3a-8d5a-662c89bf41a2</t>
+  </si>
+  <si>
+    <t>relationship--f5209d1a-7895-4020-acae-5dc4e5d8bfc0</t>
+  </si>
+  <si>
+    <t>relationship--5ee5526e-96eb-41af-b8b8-c90b91e64049</t>
+  </si>
+  <si>
+    <t>relationship--3be37c13-b9bc-47bb-8653-fa401dabd4e7</t>
+  </si>
+  <si>
+    <t>relationship--b0c2c062-c89e-4085-8716-bad67e98026e</t>
+  </si>
+  <si>
+    <t>relationship--31fd82da-dfa8-42b5-95dd-f168e6627746</t>
+  </si>
+  <si>
+    <t>relationship--2c5e4520-1275-4ab3-a9a8-2e2b1e964c13</t>
+  </si>
+  <si>
+    <t>relationship--b55647cc-a783-4225-b64b-618bc0c73e2b</t>
+  </si>
+  <si>
+    <t>relationship--6014c6c0-0579-4b5e-a854-2e87b36442cf</t>
+  </si>
+  <si>
+    <t>relationship--9c8d906b-4588-4163-b779-c3b8321985df</t>
+  </si>
+  <si>
+    <t>relationship--1419cb9b-276d-4b72-a3f1-6788f5712c97</t>
+  </si>
+  <si>
+    <t>relationship--a0a599d6-96f3-46a9-8021-f95ca90c5c60</t>
+  </si>
+  <si>
+    <t>relationship--422caa87-ac34-4167-80a3-e3f294b52304</t>
+  </si>
+  <si>
+    <t>relationship--d95d1848-9eb8-41a1-9eb4-0dab6d9b048c</t>
+  </si>
+  <si>
+    <t>relationship--c8ddd7ea-ed8e-4c46-8d00-0188061a5430</t>
+  </si>
+  <si>
+    <t>relationship--b4237490-0e8a-46d4-95a6-1cdaa172bcc8</t>
+  </si>
+  <si>
+    <t>relationship--6d106e24-cb8f-42ae-8ea2-c24c3ac66a5e</t>
+  </si>
+  <si>
+    <t>relationship--d3e614da-a65e-49a8-b28c-1bda5c4ff9ad</t>
+  </si>
+  <si>
+    <t>relationship--673fe51c-7945-423e-9767-3b824d79a43f</t>
+  </si>
+  <si>
+    <t>relationship--b4b464b3-2e82-48ba-b3e5-8680a6803204</t>
+  </si>
+  <si>
+    <t>relationship--ec2419f7-91b8-4498-b50c-0deec7e9eed4</t>
+  </si>
+  <si>
+    <t>relationship--62fc2c5e-3c4f-4760-ba3a-320af5a52635</t>
+  </si>
+  <si>
+    <t>relationship--5c3c5267-b7aa-47e8-a640-d413fe3d0e2b</t>
+  </si>
+  <si>
+    <t>relationship--559bac5f-e601-4430-a4d1-3e40065ec036</t>
+  </si>
+  <si>
+    <t>relationship--aaed89ae-ca29-4a00-9e21-1cc9143a649e</t>
+  </si>
+  <si>
+    <t>relationship--acd4d015-7a92-4a60-8741-9e316340e075</t>
+  </si>
+  <si>
+    <t>relationship--3d963d7d-a454-4e0a-9940-35584a671824</t>
+  </si>
+  <si>
+    <t>relationship--e1c4bbc4-90c4-48de-8589-c0a639fef400</t>
   </si>
   <si>
     <t>C0009</t>
@@ -1240,307 +1240,307 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
-  </si>
-  <si>
-    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
-  </si>
-  <si>
-    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
-  </si>
-  <si>
-    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
-  </si>
-  <si>
-    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
-  </si>
-  <si>
-    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
-  </si>
-  <si>
-    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
-  </si>
-  <si>
-    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
-  </si>
-  <si>
-    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
-  </si>
-  <si>
-    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
-  </si>
-  <si>
-    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
-  </si>
-  <si>
-    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
-  </si>
-  <si>
-    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
-  </si>
-  <si>
-    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
-  </si>
-  <si>
-    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
-  </si>
-  <si>
-    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
-  </si>
-  <si>
-    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
-  </si>
-  <si>
-    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
-  </si>
-  <si>
-    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
-  </si>
-  <si>
-    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
-  </si>
-  <si>
-    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
-  </si>
-  <si>
-    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
-  </si>
-  <si>
-    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
-  </si>
-  <si>
-    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
-  </si>
-  <si>
-    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
-  </si>
-  <si>
-    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
-  </si>
-  <si>
-    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
-  </si>
-  <si>
-    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
-  </si>
-  <si>
-    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
-  </si>
-  <si>
-    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
-  </si>
-  <si>
-    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
-  </si>
-  <si>
-    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
-  </si>
-  <si>
-    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
-  </si>
-  <si>
-    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
-  </si>
-  <si>
-    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
-  </si>
-  <si>
-    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
-  </si>
-  <si>
-    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
-  </si>
-  <si>
-    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
-  </si>
-  <si>
-    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
-  </si>
-  <si>
-    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
-  </si>
-  <si>
-    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
-  </si>
-  <si>
-    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
-  </si>
-  <si>
-    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
-  </si>
-  <si>
-    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
-  </si>
-  <si>
-    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
-  </si>
-  <si>
-    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
-  </si>
-  <si>
-    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
-  </si>
-  <si>
-    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
-  </si>
-  <si>
-    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
-  </si>
-  <si>
-    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
-  </si>
-  <si>
-    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
-  </si>
-  <si>
-    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
-  </si>
-  <si>
-    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
-  </si>
-  <si>
-    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
-  </si>
-  <si>
-    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
-  </si>
-  <si>
-    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
-  </si>
-  <si>
-    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
-  </si>
-  <si>
-    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
-  </si>
-  <si>
-    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
-  </si>
-  <si>
-    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
-  </si>
-  <si>
-    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
-  </si>
-  <si>
-    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
-  </si>
-  <si>
-    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
-  </si>
-  <si>
-    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
-  </si>
-  <si>
-    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
-  </si>
-  <si>
-    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
-  </si>
-  <si>
-    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
-  </si>
-  <si>
-    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
-  </si>
-  <si>
-    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
-  </si>
-  <si>
-    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
-  </si>
-  <si>
-    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
-  </si>
-  <si>
-    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
-  </si>
-  <si>
-    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
-  </si>
-  <si>
-    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
-  </si>
-  <si>
-    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
-  </si>
-  <si>
-    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
-  </si>
-  <si>
-    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
-  </si>
-  <si>
-    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
-  </si>
-  <si>
-    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
-  </si>
-  <si>
-    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
-  </si>
-  <si>
-    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
-  </si>
-  <si>
-    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
-  </si>
-  <si>
-    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
-  </si>
-  <si>
-    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
-  </si>
-  <si>
-    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
-  </si>
-  <si>
-    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
-  </si>
-  <si>
-    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
-  </si>
-  <si>
-    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
-  </si>
-  <si>
-    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
-  </si>
-  <si>
-    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
-  </si>
-  <si>
-    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
-  </si>
-  <si>
-    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
-  </si>
-  <si>
-    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
-  </si>
-  <si>
-    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
-  </si>
-  <si>
-    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
-  </si>
-  <si>
-    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
-  </si>
-  <si>
-    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
-  </si>
-  <si>
-    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
-  </si>
-  <si>
-    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
-  </si>
-  <si>
-    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
-  </si>
-  <si>
-    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
+    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
+  </si>
+  <si>
+    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
+  </si>
+  <si>
+    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
+  </si>
+  <si>
+    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
+  </si>
+  <si>
+    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
+  </si>
+  <si>
+    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
+  </si>
+  <si>
+    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
+  </si>
+  <si>
+    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
+  </si>
+  <si>
+    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
+  </si>
+  <si>
+    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
+  </si>
+  <si>
+    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
+  </si>
+  <si>
+    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
+  </si>
+  <si>
+    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
+  </si>
+  <si>
+    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
+  </si>
+  <si>
+    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
+  </si>
+  <si>
+    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
+  </si>
+  <si>
+    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
+  </si>
+  <si>
+    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
+  </si>
+  <si>
+    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
+  </si>
+  <si>
+    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
+  </si>
+  <si>
+    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
+  </si>
+  <si>
+    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
+  </si>
+  <si>
+    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
+  </si>
+  <si>
+    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
+  </si>
+  <si>
+    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
+  </si>
+  <si>
+    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
+  </si>
+  <si>
+    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
+  </si>
+  <si>
+    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
+  </si>
+  <si>
+    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
+  </si>
+  <si>
+    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
+  </si>
+  <si>
+    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
+  </si>
+  <si>
+    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
+  </si>
+  <si>
+    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
+  </si>
+  <si>
+    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
+  </si>
+  <si>
+    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
+  </si>
+  <si>
+    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
+  </si>
+  <si>
+    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
+  </si>
+  <si>
+    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
+  </si>
+  <si>
+    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
+  </si>
+  <si>
+    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
+  </si>
+  <si>
+    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
+  </si>
+  <si>
+    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
+  </si>
+  <si>
+    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
+  </si>
+  <si>
+    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
+  </si>
+  <si>
+    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
+  </si>
+  <si>
+    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
+  </si>
+  <si>
+    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
+  </si>
+  <si>
+    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
+  </si>
+  <si>
+    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
+  </si>
+  <si>
+    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
+  </si>
+  <si>
+    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
+  </si>
+  <si>
+    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
+  </si>
+  <si>
+    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
+  </si>
+  <si>
+    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
+  </si>
+  <si>
+    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
+  </si>
+  <si>
+    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
+  </si>
+  <si>
+    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
+  </si>
+  <si>
+    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
+  </si>
+  <si>
+    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
+  </si>
+  <si>
+    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
+  </si>
+  <si>
+    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
+  </si>
+  <si>
+    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
+  </si>
+  <si>
+    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
+  </si>
+  <si>
+    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
+  </si>
+  <si>
+    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
+  </si>
+  <si>
+    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
+  </si>
+  <si>
+    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
+  </si>
+  <si>
+    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
+  </si>
+  <si>
+    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
+  </si>
+  <si>
+    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
+  </si>
+  <si>
+    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
+  </si>
+  <si>
+    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
+  </si>
+  <si>
+    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
+  </si>
+  <si>
+    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
+  </si>
+  <si>
+    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
+  </si>
+  <si>
+    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
+  </si>
+  <si>
+    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
+  </si>
+  <si>
+    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
+  </si>
+  <si>
+    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
+  </si>
+  <si>
+    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
+  </si>
+  <si>
+    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
+  </si>
+  <si>
+    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
+  </si>
+  <si>
+    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
+  </si>
+  <si>
+    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
+  </si>
+  <si>
+    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
+  </si>
+  <si>
+    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
+  </si>
+  <si>
+    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
+  </si>
+  <si>
+    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
+  </si>
+  <si>
+    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
+  </si>
+  <si>
+    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
+  </si>
+  <si>
+    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
+  </si>
+  <si>
+    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
+  </si>
+  <si>
+    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
+  </si>
+  <si>
+    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
+  </si>
+  <si>
+    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
+  </si>
+  <si>
+    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
+  </si>
+  <si>
+    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
+  </si>
+  <si>
+    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
+  </si>
+  <si>
+    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
+  </si>
+  <si>
+    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
+  </si>
+  <si>
+    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
   </si>
   <si>
     <t>campaign</t>
@@ -2003,553 +2003,553 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--5614d86d-6211-45cd-ac6c-26a97c7ed3cf</t>
-  </si>
-  <si>
-    <t>relationship--c00bd06c-4bf5-4ab2-ab25-c5d571553d0c</t>
-  </si>
-  <si>
-    <t>relationship--7201fe1e-0fea-4d3b-97bf-6355ebf82318</t>
-  </si>
-  <si>
-    <t>relationship--d1870805-3ccc-4beb-b2a4-8402f288d864</t>
-  </si>
-  <si>
-    <t>relationship--a1eee09b-bd43-43e9-b586-a6b939c06a11</t>
-  </si>
-  <si>
-    <t>relationship--c274175b-6c03-49c5-a647-607cd5b0e4d2</t>
-  </si>
-  <si>
-    <t>relationship--187b5fcd-6c5c-4c42-8d07-07adbdbecd2d</t>
-  </si>
-  <si>
-    <t>relationship--1006e39a-452b-4831-be5c-fc31a3710a4c</t>
-  </si>
-  <si>
-    <t>relationship--998fc32c-1362-4fe1-badc-2c3295a58dae</t>
-  </si>
-  <si>
-    <t>relationship--b50491d9-1ef9-4e6a-a7d8-ed3bdd53bb26</t>
-  </si>
-  <si>
-    <t>relationship--816bc3db-9456-4de8-a943-e308683f2326</t>
-  </si>
-  <si>
-    <t>relationship--7e5cb007-6d19-46d2-a049-9fb76730abfc</t>
-  </si>
-  <si>
-    <t>relationship--4b7df337-6761-4f4a-8663-ffc85abd9bd7</t>
-  </si>
-  <si>
-    <t>relationship--3e1c35b2-ac79-4f76-b026-a30f8e566a41</t>
-  </si>
-  <si>
-    <t>relationship--a849cb40-97db-4468-a725-2eb757b9285f</t>
-  </si>
-  <si>
-    <t>relationship--47ff22b7-0fad-4eaa-8f49-c7ee57b2bcf5</t>
-  </si>
-  <si>
-    <t>relationship--50db3a6a-bc86-4653-92b1-cc25f4fd3b63</t>
-  </si>
-  <si>
-    <t>relationship--8312e15d-9501-45f6-b5c7-dd40ad215dc7</t>
-  </si>
-  <si>
-    <t>relationship--0cc9ae91-2019-49d4-9ae9-74cf940ab326</t>
-  </si>
-  <si>
-    <t>relationship--62cc7c54-5c61-4755-b62b-11df9f67bc7c</t>
-  </si>
-  <si>
-    <t>relationship--9520ceeb-3ab0-40cd-9976-308b5382c604</t>
-  </si>
-  <si>
-    <t>relationship--df0590aa-456d-4dcd-b3ef-9db58fcdde4d</t>
-  </si>
-  <si>
-    <t>relationship--25875951-42bf-4bd1-8846-1e2b082462c7</t>
-  </si>
-  <si>
-    <t>relationship--363d00f2-89e0-45eb-aeff-56c3eb0b7d1b</t>
-  </si>
-  <si>
-    <t>relationship--ccc50e83-1034-4626-9fad-142e49094870</t>
-  </si>
-  <si>
-    <t>relationship--0e6f9307-ac79-4d43-90f6-e73960d6ec75</t>
-  </si>
-  <si>
-    <t>relationship--24ef7132-be8a-41ec-bacf-c64882a1171d</t>
-  </si>
-  <si>
-    <t>relationship--0cf1df00-44a9-42ec-b61d-3e10fb8c67d6</t>
-  </si>
-  <si>
-    <t>relationship--03e9274c-b7a4-42d6-8f7f-78b71e30af09</t>
-  </si>
-  <si>
-    <t>relationship--5c38fc95-7bc5-4a6a-8681-48be32c65a82</t>
-  </si>
-  <si>
-    <t>relationship--066eb77b-c6df-4d8e-8599-0beb192907e4</t>
-  </si>
-  <si>
-    <t>relationship--541a4d88-df09-4c75-92ae-356afd194692</t>
-  </si>
-  <si>
-    <t>relationship--3af6830d-8cc7-4fed-b927-108a41fd4178</t>
-  </si>
-  <si>
-    <t>relationship--57631293-2a02-4489-8c56-f583e9bc5585</t>
-  </si>
-  <si>
-    <t>relationship--862f0336-33bd-4370-8af3-d29a004f0fc8</t>
-  </si>
-  <si>
-    <t>relationship--9ec2a708-84bf-4339-afb0-0162bb4748ff</t>
-  </si>
-  <si>
-    <t>relationship--4485df60-3f40-40ca-93c4-89378405dc43</t>
-  </si>
-  <si>
-    <t>relationship--722ca219-044e-4221-a0f4-444790a937ba</t>
-  </si>
-  <si>
-    <t>relationship--0819322a-18d8-4e24-b55c-206658d07525</t>
-  </si>
-  <si>
-    <t>relationship--cfa59c71-254e-4a90-903c-fcce14903069</t>
-  </si>
-  <si>
-    <t>relationship--672d610b-b36d-4dd8-b55d-8b986db8b16c</t>
-  </si>
-  <si>
-    <t>relationship--3c9fe144-c86e-42cf-b46f-9fbac0138093</t>
-  </si>
-  <si>
-    <t>relationship--0416c3e3-00bc-44e4-88b4-e2837a311840</t>
-  </si>
-  <si>
-    <t>relationship--0e328b60-be4c-4a17-a480-68f9a95774c9</t>
-  </si>
-  <si>
-    <t>relationship--05358bf0-1b8f-4d3d-9b01-37d1e4f6b814</t>
-  </si>
-  <si>
-    <t>relationship--d8ee9123-00a9-45e8-b9ed-78eaf52fd03c</t>
-  </si>
-  <si>
-    <t>relationship--c99cdf0b-238f-4f4a-bd62-e777028d0888</t>
-  </si>
-  <si>
-    <t>relationship--eb3d94ce-42c1-4f6d-9104-149587001ee8</t>
-  </si>
-  <si>
-    <t>relationship--34fa7ae0-57e6-4802-b731-2a8397e43f5c</t>
-  </si>
-  <si>
-    <t>relationship--658426eb-6159-48b7-834a-d2cba5929840</t>
-  </si>
-  <si>
-    <t>relationship--1b8afd01-f00e-4fb9-8e53-23bf378a5743</t>
-  </si>
-  <si>
-    <t>relationship--c4b84975-0d5b-41da-8dde-a1e4752f8223</t>
-  </si>
-  <si>
-    <t>relationship--3c23657a-af00-4c00-be50-0c2211096383</t>
-  </si>
-  <si>
-    <t>relationship--34f1cc09-99b9-4b55-8a11-a27b71d36a56</t>
-  </si>
-  <si>
-    <t>relationship--2d2d4647-66d2-468f-b5fa-08a23e9f3b52</t>
-  </si>
-  <si>
-    <t>relationship--32fef7ce-3ca8-42d2-9806-8f07130dc59a</t>
-  </si>
-  <si>
-    <t>relationship--45a232f8-5767-419e-9acc-94a2592789a1</t>
-  </si>
-  <si>
-    <t>relationship--8bd14d24-f013-4648-9e45-231c66bee802</t>
-  </si>
-  <si>
-    <t>relationship--e9bd60a6-0325-45da-9bda-fd854a7ce87b</t>
-  </si>
-  <si>
-    <t>relationship--724cc625-5556-40a5-ae14-3d9de64c9a19</t>
-  </si>
-  <si>
-    <t>relationship--00da6316-6f4a-4ee9-84ab-f3bf74b840dc</t>
-  </si>
-  <si>
-    <t>relationship--37a6d563-2564-4062-8967-14950a0a6ff1</t>
-  </si>
-  <si>
-    <t>relationship--5c5eb460-e73e-4c4b-8929-2f3a55616623</t>
-  </si>
-  <si>
-    <t>relationship--41bac798-9a1a-4b92-930c-227474d4cabb</t>
-  </si>
-  <si>
-    <t>relationship--5b9787dc-aaed-4206-acb6-3135336f00dc</t>
-  </si>
-  <si>
-    <t>relationship--92e54ce9-a70b-4436-be5a-e66e682935ec</t>
-  </si>
-  <si>
-    <t>relationship--689c088d-7e07-43c6-a3a3-2059035a0956</t>
-  </si>
-  <si>
-    <t>relationship--1d4bd310-a5da-42a0-896e-ea3ccf0735ef</t>
-  </si>
-  <si>
-    <t>relationship--58b1092a-2708-4e1d-b796-7570f699b314</t>
-  </si>
-  <si>
-    <t>relationship--a700b400-cfb5-4c2d-8ac6-6d3f3a976502</t>
-  </si>
-  <si>
-    <t>relationship--463138d3-daf2-4734-b553-fcc80a9f7245</t>
-  </si>
-  <si>
-    <t>relationship--12c1d59e-77ae-4c17-bd89-4f0d0855db2b</t>
-  </si>
-  <si>
-    <t>relationship--6dd4ef8d-d116-4667-98cd-25d0b4ca2eb2</t>
-  </si>
-  <si>
-    <t>relationship--28bdfc3d-faa4-4c45-8c25-506dc03861d2</t>
-  </si>
-  <si>
-    <t>relationship--2da181d8-efdd-46a5-bc48-a7e761e7700c</t>
-  </si>
-  <si>
-    <t>relationship--30caab21-d762-4082-9483-c4e4b58c8140</t>
-  </si>
-  <si>
-    <t>relationship--edd083ea-aadc-4345-844f-5d40e476e7c8</t>
-  </si>
-  <si>
-    <t>relationship--61c6a3e1-337d-4150-8e33-062db9bf48fb</t>
-  </si>
-  <si>
-    <t>relationship--69593cf2-77f5-4528-95bc-867a7cd474a6</t>
-  </si>
-  <si>
-    <t>relationship--fe839167-b221-48ff-8478-496d40f26604</t>
-  </si>
-  <si>
-    <t>relationship--33cc973e-fa84-415a-a0b3-dc6101374315</t>
-  </si>
-  <si>
-    <t>relationship--0c8a308f-fb09-4df6-9a8b-03dc281625c8</t>
-  </si>
-  <si>
-    <t>relationship--13a0fcb0-b324-4579-a852-51d59b9cfea7</t>
-  </si>
-  <si>
-    <t>relationship--03876e2e-c730-426e-9cf7-5c2d2eacfd12</t>
-  </si>
-  <si>
-    <t>relationship--ac403c59-fdb2-451d-82d5-b227f3fb004e</t>
-  </si>
-  <si>
-    <t>relationship--17501bfb-76d5-452a-a5b7-bb40a2734033</t>
-  </si>
-  <si>
-    <t>relationship--3751fcb4-a779-4bd1-8b91-b4d03da77810</t>
-  </si>
-  <si>
-    <t>relationship--db0bfcda-eb29-4562-aca0-c098711d0d07</t>
-  </si>
-  <si>
-    <t>relationship--092d1143-9f0d-4f94-b49b-b4a78e22aa1f</t>
-  </si>
-  <si>
-    <t>relationship--ff4a5303-2db3-49ae-a53f-7c2dffb9e6ee</t>
-  </si>
-  <si>
-    <t>relationship--2291dd05-1ba6-427c-8f66-f483409905d3</t>
-  </si>
-  <si>
-    <t>relationship--bdf81bef-d89b-49f8-a818-e7348ead0e7d</t>
-  </si>
-  <si>
-    <t>relationship--c0a0ed7b-7375-475c-967c-9635560013b7</t>
-  </si>
-  <si>
-    <t>relationship--35f20b51-ebde-4f96-b4f6-4612f3bceea5</t>
-  </si>
-  <si>
-    <t>relationship--b5c01c41-b1bd-403f-9c86-ee33d9233bb8</t>
-  </si>
-  <si>
-    <t>relationship--9bc2a9d1-da58-403d-98c8-6b56bfd51523</t>
-  </si>
-  <si>
-    <t>relationship--e9b6b440-e6ef-4112-91b7-a10e828f215f</t>
-  </si>
-  <si>
-    <t>relationship--d13278fb-2254-49ef-b205-01e887848910</t>
-  </si>
-  <si>
-    <t>relationship--5efc8b32-1b60-4fad-ae02-e340941487af</t>
-  </si>
-  <si>
-    <t>relationship--2511d69d-6f60-4597-8c57-c435f01cb56c</t>
-  </si>
-  <si>
-    <t>relationship--34272f39-5284-4cd8-aed4-3ac4b7afe9c0</t>
-  </si>
-  <si>
-    <t>relationship--78c44437-c23b-44e3-9b0a-dea9d31afab3</t>
-  </si>
-  <si>
-    <t>relationship--86e8bc77-6840-43e1-9b08-388dd6ce4a71</t>
-  </si>
-  <si>
-    <t>relationship--95a7d566-0538-4e17-b03f-d840ac5a6485</t>
-  </si>
-  <si>
-    <t>relationship--e08df791-6312-4452-a037-50b1c552eae6</t>
-  </si>
-  <si>
-    <t>relationship--ce048198-374c-4f04-8fc5-58aa78334838</t>
-  </si>
-  <si>
-    <t>relationship--ed1b3558-fa7e-4b78-94a6-ede294e5982b</t>
-  </si>
-  <si>
-    <t>relationship--fdb52f1a-9fce-4466-9113-080a43b19d24</t>
-  </si>
-  <si>
-    <t>relationship--a45d91e8-042e-4dde-8bf0-57d321efd381</t>
-  </si>
-  <si>
-    <t>relationship--4c063840-371e-41c6-8f16-15c3bb3b6a07</t>
-  </si>
-  <si>
-    <t>relationship--01302958-accb-41b5-bd1c-cad6bc07a1d6</t>
-  </si>
-  <si>
-    <t>relationship--1e280e04-acc2-4d3a-ad9c-8e779be2623f</t>
-  </si>
-  <si>
-    <t>relationship--68148d92-85e1-47a8-86ad-88953aad0f77</t>
-  </si>
-  <si>
-    <t>relationship--313f6ee5-9364-48f9-839d-edf4e6d25f2a</t>
-  </si>
-  <si>
-    <t>relationship--fb779776-e9f6-45e3-9cb8-c9e509c3e8a7</t>
-  </si>
-  <si>
-    <t>relationship--47e73f6e-a733-46f1-a09b-51f4a0c2574a</t>
-  </si>
-  <si>
-    <t>relationship--d48b2f17-752e-4ef0-85ca-8c5626fe5832</t>
-  </si>
-  <si>
-    <t>relationship--55b721b2-6229-4de6-9655-32647d86e186</t>
-  </si>
-  <si>
-    <t>relationship--e7753b65-5fcf-453a-9139-c1d9028cf696</t>
-  </si>
-  <si>
-    <t>relationship--5f7f0d17-361f-4a98-b1bd-0122c4d69f1d</t>
-  </si>
-  <si>
-    <t>relationship--2e1b7d0a-bc28-4539-92dd-ebfc2bb2a6fc</t>
-  </si>
-  <si>
-    <t>relationship--14628952-a9d9-4da9-a5e2-c807bebc2dbc</t>
-  </si>
-  <si>
-    <t>relationship--9708078b-3306-4693-bf99-43999bd18b3a</t>
-  </si>
-  <si>
-    <t>relationship--ac66737c-9eeb-4d82-a7ef-b0a31bba3e60</t>
-  </si>
-  <si>
-    <t>relationship--e68e8a70-ae5d-4374-9f08-1313f12c0795</t>
-  </si>
-  <si>
-    <t>relationship--f8ea8127-0143-4136-9355-f0672cc93626</t>
-  </si>
-  <si>
-    <t>relationship--9c139044-ce9e-491c-95e2-00ba93a1b5db</t>
-  </si>
-  <si>
-    <t>relationship--a74f7c11-3bc0-48bf-973f-f38cd1531a2e</t>
-  </si>
-  <si>
-    <t>relationship--7d492b91-2741-42d1-a14b-5c68ef16cdde</t>
-  </si>
-  <si>
-    <t>relationship--2e21705c-7535-43ea-971e-ae1c720f97f0</t>
-  </si>
-  <si>
-    <t>relationship--6012c812-46fa-4441-a18e-caca14be105e</t>
-  </si>
-  <si>
-    <t>relationship--7276f7e3-19cc-4f36-b52a-df9b09039d86</t>
-  </si>
-  <si>
-    <t>relationship--38b9b77e-9ac6-4123-ad64-7ee44572da1b</t>
-  </si>
-  <si>
-    <t>relationship--8ab8f626-ae23-4007-bb32-dc128a13c452</t>
-  </si>
-  <si>
-    <t>relationship--a3705dfd-d211-4b6c-b8de-a60b61232ccf</t>
-  </si>
-  <si>
-    <t>relationship--176d7e94-acc7-4510-ab33-fc50ec2eb016</t>
-  </si>
-  <si>
-    <t>relationship--72911605-8706-44a8-9133-cc55f61fbe01</t>
-  </si>
-  <si>
-    <t>relationship--3cecfb1c-8f09-451d-9727-99f8f2060f9a</t>
-  </si>
-  <si>
-    <t>relationship--889bdd3d-7042-4b09-9b8a-2c1063492550</t>
-  </si>
-  <si>
-    <t>relationship--93820292-0d07-4e8a-a732-af6f7fac18f3</t>
-  </si>
-  <si>
-    <t>relationship--d63962bf-f3fd-4159-986d-fb404f8e5c4f</t>
-  </si>
-  <si>
-    <t>relationship--8b4d20df-6e8d-48ed-ad71-b0b73b855a56</t>
-  </si>
-  <si>
-    <t>relationship--9b06ea4e-c75e-41ad-9ba0-b8050f79c4c9</t>
-  </si>
-  <si>
-    <t>relationship--304d883a-85fd-4eb0-8c79-a70babe9fa54</t>
-  </si>
-  <si>
-    <t>relationship--f2124474-a45e-4d8c-b9c3-a4485991a23e</t>
-  </si>
-  <si>
-    <t>relationship--f90a7c85-e4de-457e-b281-b8945307db07</t>
-  </si>
-  <si>
-    <t>relationship--1658c08e-93b2-490d-b21e-2dddf38e2b5c</t>
-  </si>
-  <si>
-    <t>relationship--f3fded44-1a57-418f-b6ae-29b4dbd1bc91</t>
-  </si>
-  <si>
-    <t>relationship--3f971d8b-a5a0-4f8f-b42d-a325cd802149</t>
-  </si>
-  <si>
-    <t>relationship--f45ed62a-12e3-466e-84ea-56ee39b45fe3</t>
-  </si>
-  <si>
-    <t>relationship--acab761b-d19f-4216-a982-e4e9fee04109</t>
-  </si>
-  <si>
-    <t>relationship--bd2a142c-0144-4d20-8e3d-b73ace1abff6</t>
-  </si>
-  <si>
-    <t>relationship--263060ab-6afa-4efa-8121-56ca8c19dea3</t>
-  </si>
-  <si>
-    <t>relationship--18b4ed3f-7d9c-457a-ba75-9b36acdf1b39</t>
-  </si>
-  <si>
-    <t>relationship--4bb0977b-3d05-4362-aeea-cc150865bd4b</t>
-  </si>
-  <si>
-    <t>relationship--9732d9c4-866e-4ec3-acdf-9116f0bd3293</t>
-  </si>
-  <si>
-    <t>relationship--f5e63ee5-77e5-4992-833d-257e32e5ce3e</t>
-  </si>
-  <si>
-    <t>relationship--49d946ff-1e6b-4bf2-a9f1-a9e54213b6ba</t>
-  </si>
-  <si>
-    <t>relationship--3df7af44-b568-4a7c-adf5-95885e794a2f</t>
-  </si>
-  <si>
-    <t>relationship--9e5fe4f7-cd1e-4703-bea2-829fef05d626</t>
-  </si>
-  <si>
-    <t>relationship--14bade66-db15-4761-9e73-2928a3a3891e</t>
-  </si>
-  <si>
-    <t>relationship--2acac976-88b9-4fc7-a0bd-4d03a5f3a9bf</t>
-  </si>
-  <si>
-    <t>relationship--4c3795cc-a1e9-45d1-9a1e-bbf2cde64a15</t>
-  </si>
-  <si>
-    <t>relationship--fe565642-eab5-4ff9-91e1-cea181876211</t>
-  </si>
-  <si>
-    <t>relationship--6278e5d4-ab06-4def-bece-6991bf4b857b</t>
-  </si>
-  <si>
-    <t>relationship--8ae29663-1f05-422d-ba3c-0337760daf4d</t>
-  </si>
-  <si>
-    <t>relationship--7ac36b6b-a053-4b5f-8160-03f2709d8434</t>
-  </si>
-  <si>
-    <t>relationship--33b4f3d5-4d6e-421f-a932-e2ffa44fc7a9</t>
-  </si>
-  <si>
-    <t>relationship--95d794f0-5dc8-4362-b0ff-7ed3dc1eeabd</t>
-  </si>
-  <si>
-    <t>relationship--fbf7379e-6953-413c-8932-a51888aac57e</t>
-  </si>
-  <si>
-    <t>relationship--16390e3a-f86b-4725-907f-991e84d3e0fe</t>
-  </si>
-  <si>
-    <t>relationship--c3d4eae6-f0ec-4700-91e4-270a1b5c6f38</t>
-  </si>
-  <si>
-    <t>relationship--742cbbdd-94d7-4072-9a8b-ecafc56604db</t>
-  </si>
-  <si>
-    <t>relationship--2828cfca-5ceb-4c5a-bb2f-8ffc611954fc</t>
-  </si>
-  <si>
-    <t>relationship--cb6aa417-c3bf-41e3-9e44-209705207413</t>
-  </si>
-  <si>
-    <t>relationship--9f99304a-1059-47a4-bbdf-1f76b23b8ac2</t>
-  </si>
-  <si>
-    <t>relationship--2346dccd-238f-46e8-9aba-6341e3783eda</t>
-  </si>
-  <si>
-    <t>relationship--3138c704-adf0-4cad-8d6a-ad204687d4df</t>
-  </si>
-  <si>
-    <t>relationship--0880242b-9689-482e-9459-4ebd56320f4e</t>
-  </si>
-  <si>
-    <t>relationship--9417f950-d2a7-4417-9c05-6fe57828917e</t>
-  </si>
-  <si>
-    <t>relationship--a2b54231-6b5c-40b3-a417-074b60b3b9e2</t>
-  </si>
-  <si>
-    <t>relationship--23735a53-068a-4d2a-9476-7857dd7e1b74</t>
-  </si>
-  <si>
-    <t>relationship--161fe2ca-c2dc-4d21-a9b0-95935f7d1a52</t>
+    <t>relationship--16144da2-91f9-49e6-917d-a71bbff07b37</t>
+  </si>
+  <si>
+    <t>relationship--9697c005-6797-4bf7-a837-4f028c927ee6</t>
+  </si>
+  <si>
+    <t>relationship--6e404788-5d9d-414b-a956-d54684562ead</t>
+  </si>
+  <si>
+    <t>relationship--2c434e02-6e26-4156-ae31-6b299dae7863</t>
+  </si>
+  <si>
+    <t>relationship--37a22f39-51a3-4b42-8cbf-4682cb984c5f</t>
+  </si>
+  <si>
+    <t>relationship--de3e18c5-8e55-4213-b7a5-016f634f52d6</t>
+  </si>
+  <si>
+    <t>relationship--b294a298-4572-45ba-83cd-6febe20eb9c8</t>
+  </si>
+  <si>
+    <t>relationship--2a87fd2a-b184-456a-9ff3-5287906fb03f</t>
+  </si>
+  <si>
+    <t>relationship--2984ab74-0098-40b3-910a-a4468d5b1140</t>
+  </si>
+  <si>
+    <t>relationship--f455f2ef-5c5e-4c45-ad3f-b7e6496eb027</t>
+  </si>
+  <si>
+    <t>relationship--4bc8e783-3567-4fb8-867d-b2b0591c3676</t>
+  </si>
+  <si>
+    <t>relationship--ae99f88c-b34e-48a8-b884-8751b57831c3</t>
+  </si>
+  <si>
+    <t>relationship--913af001-f7cb-4207-8322-14ef2f4f006b</t>
+  </si>
+  <si>
+    <t>relationship--fcb25d74-cfa2-45a2-af99-29eb0ad4b064</t>
+  </si>
+  <si>
+    <t>relationship--ba3d5ece-0df2-4f39-a0e6-2ab151c4f803</t>
+  </si>
+  <si>
+    <t>relationship--98d13a8f-5671-46ab-98bf-dcee471a7416</t>
+  </si>
+  <si>
+    <t>relationship--6dd55282-c047-46db-b47d-ffef75634f32</t>
+  </si>
+  <si>
+    <t>relationship--6576dbf2-9887-46d4-b7c0-077b0aa6d520</t>
+  </si>
+  <si>
+    <t>relationship--82e78eaa-a5b5-4328-a73f-d51422047701</t>
+  </si>
+  <si>
+    <t>relationship--c407b553-608e-42df-8f20-99867374029b</t>
+  </si>
+  <si>
+    <t>relationship--58cbd296-f428-4f07-9627-ef721bca5e24</t>
+  </si>
+  <si>
+    <t>relationship--4e4c1786-5c5a-49fc-bd5f-4f98209e04a8</t>
+  </si>
+  <si>
+    <t>relationship--3fd82cd0-8553-4535-9d88-2432d8d6c588</t>
+  </si>
+  <si>
+    <t>relationship--1dbbc37e-23d4-44c4-acdc-e3cac17cc385</t>
+  </si>
+  <si>
+    <t>relationship--fbde6f1d-be2f-4e5f-92a5-c9e21f6b00e6</t>
+  </si>
+  <si>
+    <t>relationship--44b541d4-16cd-4697-91ed-8959150b93ea</t>
+  </si>
+  <si>
+    <t>relationship--bc00c803-905b-483d-a214-b756ab179b45</t>
+  </si>
+  <si>
+    <t>relationship--930512ae-f088-4597-bae8-dcc756d386d6</t>
+  </si>
+  <si>
+    <t>relationship--1e3bdd39-f6fd-459b-953c-ddafac2af3ee</t>
+  </si>
+  <si>
+    <t>relationship--6cda8772-c59c-40f6-951e-7203c973239e</t>
+  </si>
+  <si>
+    <t>relationship--26435369-1682-4a9f-a340-a6ff3307ec65</t>
+  </si>
+  <si>
+    <t>relationship--46ba6b14-29ac-4278-b078-f34ba26b1be5</t>
+  </si>
+  <si>
+    <t>relationship--b0380dea-279d-4897-9888-5307871a3acb</t>
+  </si>
+  <si>
+    <t>relationship--ade84795-f059-4866-a09e-37e6ac5adf40</t>
+  </si>
+  <si>
+    <t>relationship--62bee3ce-caad-42e9-b7bd-9c2262a342cc</t>
+  </si>
+  <si>
+    <t>relationship--d7952f2c-eaf9-43a6-a7b0-b46555772b73</t>
+  </si>
+  <si>
+    <t>relationship--3d23f2db-b299-4698-8767-c4d5bc249f9c</t>
+  </si>
+  <si>
+    <t>relationship--51baad2a-4458-43c3-a534-392226563e3e</t>
+  </si>
+  <si>
+    <t>relationship--f125e8d8-5e5f-4821-9e91-21780cd1efd6</t>
+  </si>
+  <si>
+    <t>relationship--c9d89fd2-934d-49d0-bcc6-892b5bc54c05</t>
+  </si>
+  <si>
+    <t>relationship--ce4f2eda-e514-4c3d-8877-f503c4fcee9d</t>
+  </si>
+  <si>
+    <t>relationship--6c0df7e5-7d02-4aeb-961c-dc80d2bb33b6</t>
+  </si>
+  <si>
+    <t>relationship--7dc82937-c2c7-4121-b82f-1b15049d4567</t>
+  </si>
+  <si>
+    <t>relationship--1438c8ef-dd0f-46a1-a329-7a84094089a7</t>
+  </si>
+  <si>
+    <t>relationship--10b591e9-7eed-4d3f-9cb3-261d8bdf56f5</t>
+  </si>
+  <si>
+    <t>relationship--6320ca25-0dec-426b-a89f-1901840d4a9b</t>
+  </si>
+  <si>
+    <t>relationship--cc37dc30-86e3-4e5b-826c-87bc71b2f98b</t>
+  </si>
+  <si>
+    <t>relationship--434be38d-f7c2-4833-98af-4f52da9cc033</t>
+  </si>
+  <si>
+    <t>relationship--58c8f148-2f0b-40dd-9946-4e4b08b5a9e1</t>
+  </si>
+  <si>
+    <t>relationship--6e559c18-f8de-46cc-8a2c-903c7173ba23</t>
+  </si>
+  <si>
+    <t>relationship--7bccdde2-9194-47a0-a92f-44b4e77a8a1b</t>
+  </si>
+  <si>
+    <t>relationship--8cae63fe-5d4f-407d-bbdd-3ffbdacaa5f7</t>
+  </si>
+  <si>
+    <t>relationship--e15f196e-7079-436f-80ff-106dfbfcb050</t>
+  </si>
+  <si>
+    <t>relationship--5818dc97-498b-4db4-821f-eabf92cc0147</t>
+  </si>
+  <si>
+    <t>relationship--a31d3284-f6df-4832-8e81-ca077371c7a0</t>
+  </si>
+  <si>
+    <t>relationship--07d341f1-5e24-4da9-96ed-ceaeec948632</t>
+  </si>
+  <si>
+    <t>relationship--36acbe6c-f5be-48c5-8910-6f4d6a84c5b2</t>
+  </si>
+  <si>
+    <t>relationship--b079861e-56d8-44f5-9e8c-a969b05fd089</t>
+  </si>
+  <si>
+    <t>relationship--878b41f7-4aa2-4254-bda7-45809fbcf30e</t>
+  </si>
+  <si>
+    <t>relationship--05cc6a6d-7c0c-4ec8-babb-4f489f107014</t>
+  </si>
+  <si>
+    <t>relationship--8e01371e-9a5c-4f4e-b109-a7f005b94faa</t>
+  </si>
+  <si>
+    <t>relationship--5081685d-0e81-4e84-b914-876e5723e0b1</t>
+  </si>
+  <si>
+    <t>relationship--9a11a133-cf32-4216-bd62-e8d351e98517</t>
+  </si>
+  <si>
+    <t>relationship--b33a6108-0645-4a98-8bdc-2cfe83bfbd05</t>
+  </si>
+  <si>
+    <t>relationship--bf3b16c7-2687-4e50-b058-2b9980d05443</t>
+  </si>
+  <si>
+    <t>relationship--c67ab420-a3b8-4617-b942-fa34e0df8c81</t>
+  </si>
+  <si>
+    <t>relationship--c8bc29c2-0d05-4b84-b82e-576a60d9ca1b</t>
+  </si>
+  <si>
+    <t>relationship--818b14a7-3bf9-4917-974c-7283e66d21fc</t>
+  </si>
+  <si>
+    <t>relationship--d99f39d0-fb23-460a-a041-4d9557b9b445</t>
+  </si>
+  <si>
+    <t>relationship--f3c6f5e7-4e68-4633-b7d9-e2b35b32bd0d</t>
+  </si>
+  <si>
+    <t>relationship--d28c162f-cc0d-45ef-926b-5ecc38320d78</t>
+  </si>
+  <si>
+    <t>relationship--bf09b1a3-7528-424a-ad44-13d32054a3aa</t>
+  </si>
+  <si>
+    <t>relationship--2f3cdf54-d10f-43ea-8e57-ec386e7a5a04</t>
+  </si>
+  <si>
+    <t>relationship--736363d3-ad9d-49b8-8469-50f98e2ffcc6</t>
+  </si>
+  <si>
+    <t>relationship--7d80956f-0e1d-4804-83c2-3fb5e44342e0</t>
+  </si>
+  <si>
+    <t>relationship--8ed5c2d1-de73-46aa-a16a-aaed5f37518e</t>
+  </si>
+  <si>
+    <t>relationship--332abc6c-519c-49ea-8fdf-4c2ad58c5d30</t>
+  </si>
+  <si>
+    <t>relationship--65ee3d9c-ae09-4e8d-987d-6cc1d219e01f</t>
+  </si>
+  <si>
+    <t>relationship--1bee2722-fd00-4414-b078-719bb1bc13fc</t>
+  </si>
+  <si>
+    <t>relationship--e13a70ac-3b25-4075-bb54-0d44ba465878</t>
+  </si>
+  <si>
+    <t>relationship--29a3ce2b-6be4-44fb-8fae-beef5f0296a1</t>
+  </si>
+  <si>
+    <t>relationship--9c61218c-a3e3-4688-8723-8a681f5d4799</t>
+  </si>
+  <si>
+    <t>relationship--9b31e25d-8cbe-455c-954b-206d112c4a0a</t>
+  </si>
+  <si>
+    <t>relationship--da89423c-a636-491c-b7a6-20300d79e176</t>
+  </si>
+  <si>
+    <t>relationship--65d9dcda-82e0-4983-98d9-09100bf11f69</t>
+  </si>
+  <si>
+    <t>relationship--a66e5426-deea-479c-9b33-48831ef1f74f</t>
+  </si>
+  <si>
+    <t>relationship--8a7f492f-6d0f-48ef-8475-cf6d9343beae</t>
+  </si>
+  <si>
+    <t>relationship--d7cba973-52a5-4ffa-8792-fad9de0f4ff5</t>
+  </si>
+  <si>
+    <t>relationship--66c41619-1a71-4cdf-959c-b20e132a9feb</t>
+  </si>
+  <si>
+    <t>relationship--1c5a2877-55d2-47f0-852c-41cffd9ea9cd</t>
+  </si>
+  <si>
+    <t>relationship--338d5a11-cbad-444b-b042-b4aaae1152ef</t>
+  </si>
+  <si>
+    <t>relationship--15a7a091-9597-443c-9546-c8c0b6f7015e</t>
+  </si>
+  <si>
+    <t>relationship--b397365a-1c8a-4bf6-9323-b3fa37ec8120</t>
+  </si>
+  <si>
+    <t>relationship--0944d14f-213e-42c6-9227-990789faa016</t>
+  </si>
+  <si>
+    <t>relationship--93c54f83-b658-4267-9ebd-1d808cf45f79</t>
+  </si>
+  <si>
+    <t>relationship--83510ac8-d535-4650-8d81-ebdbe8b636d3</t>
+  </si>
+  <si>
+    <t>relationship--834f449c-b379-41ab-8593-fdc8a6f7da85</t>
+  </si>
+  <si>
+    <t>relationship--25bfdfd7-c584-4eee-badb-e362294f2728</t>
+  </si>
+  <si>
+    <t>relationship--6540b8e2-98fe-49f7-8a99-50d9dd1b8a11</t>
+  </si>
+  <si>
+    <t>relationship--ea9fe07e-1615-4dcf-a3bd-33abcf4ffd14</t>
+  </si>
+  <si>
+    <t>relationship--95761fd2-eff3-4bbd-a79a-d47e24029c7f</t>
+  </si>
+  <si>
+    <t>relationship--9ac65c10-b5e4-4ae1-ac04-e2577a4aff40</t>
+  </si>
+  <si>
+    <t>relationship--b8c173ac-8a9e-4765-bb1c-39b1ee53caac</t>
+  </si>
+  <si>
+    <t>relationship--117354e0-cd7d-484e-8756-87c5bb5fcd00</t>
+  </si>
+  <si>
+    <t>relationship--d435d200-8dbb-4172-80cb-ec869208eca5</t>
+  </si>
+  <si>
+    <t>relationship--eff1e690-9246-4cf9-b550-79f17cb29b68</t>
+  </si>
+  <si>
+    <t>relationship--9bae57d2-f5dc-42a0-836b-0f349e4cdc25</t>
+  </si>
+  <si>
+    <t>relationship--0156d507-7b40-45ec-8289-0f4fa5ba6163</t>
+  </si>
+  <si>
+    <t>relationship--33ab6ec3-19cf-4b49-8724-2b4af682af04</t>
+  </si>
+  <si>
+    <t>relationship--e1842498-5a34-4609-8db6-b2f82df3b197</t>
+  </si>
+  <si>
+    <t>relationship--719527aa-6dc8-4a61-a342-91d03a5c2d21</t>
+  </si>
+  <si>
+    <t>relationship--ba2437e9-e819-46a7-bab0-0878dbf9846d</t>
+  </si>
+  <si>
+    <t>relationship--818f6226-9afb-4912-b6a3-b69725ad0e2a</t>
+  </si>
+  <si>
+    <t>relationship--3a49096f-d797-4844-a514-37aadfb14943</t>
+  </si>
+  <si>
+    <t>relationship--a210a033-712a-4265-af86-ce866ebe8502</t>
+  </si>
+  <si>
+    <t>relationship--0e65dd55-8151-4a51-9adb-ad2b722c7b11</t>
+  </si>
+  <si>
+    <t>relationship--36958ad9-6617-44a9-ad62-03aa55bac03a</t>
+  </si>
+  <si>
+    <t>relationship--ace3997d-4e21-4b81-b6d6-147e08c0b0c2</t>
+  </si>
+  <si>
+    <t>relationship--65dfe9e2-f92b-41f5-a8d7-4d0cb775fd3c</t>
+  </si>
+  <si>
+    <t>relationship--57e70d24-0604-4783-99d1-8efa72bc229d</t>
+  </si>
+  <si>
+    <t>relationship--040c9390-eb5e-49cb-b5bf-d96b81a19376</t>
+  </si>
+  <si>
+    <t>relationship--d1bd4886-86ef-4466-a263-446fe6e1866f</t>
+  </si>
+  <si>
+    <t>relationship--f0b97568-130b-464d-8b32-c4d044aab10d</t>
+  </si>
+  <si>
+    <t>relationship--3dc31397-38e8-4bc1-bd09-06e562e88e3e</t>
+  </si>
+  <si>
+    <t>relationship--938ee97f-1383-42f4-a3fb-f79e9c820e3e</t>
+  </si>
+  <si>
+    <t>relationship--76049fb7-5bc2-4c9e-ba0e-297af2a4ef6b</t>
+  </si>
+  <si>
+    <t>relationship--ff825748-c271-4e23-981a-ace5d89e2f0d</t>
+  </si>
+  <si>
+    <t>relationship--c82e0390-57e7-451d-a05b-56a4cc08989b</t>
+  </si>
+  <si>
+    <t>relationship--777a2696-e49b-4777-9f59-3361cf2d959b</t>
+  </si>
+  <si>
+    <t>relationship--8bdae4af-4576-4585-9cc5-e67149a7a200</t>
+  </si>
+  <si>
+    <t>relationship--399137a2-b686-429b-a19e-996acc7a7bdb</t>
+  </si>
+  <si>
+    <t>relationship--78f7ba38-124d-49f4-aed3-9d01c6378d20</t>
+  </si>
+  <si>
+    <t>relationship--8e2c490b-78d0-4915-85f2-227774d6bb35</t>
+  </si>
+  <si>
+    <t>relationship--7d6fed15-cb67-4aeb-ba7e-4a5ac7f66e2e</t>
+  </si>
+  <si>
+    <t>relationship--93000c5d-435d-4b59-9bd9-6d18f4e88428</t>
+  </si>
+  <si>
+    <t>relationship--78cbaae0-d659-4816-9359-5700b0606cdf</t>
+  </si>
+  <si>
+    <t>relationship--ab8e5783-d185-4c0f-a17a-74ad9e6a2395</t>
+  </si>
+  <si>
+    <t>relationship--b2df047b-98d1-45d7-b379-53985bddf1c4</t>
+  </si>
+  <si>
+    <t>relationship--093ff580-0911-4ef5-aaae-92411c9b6597</t>
+  </si>
+  <si>
+    <t>relationship--16ee1bba-6e3c-440b-ba1f-56293093ae00</t>
+  </si>
+  <si>
+    <t>relationship--b884c378-1ffb-4f35-9e95-278a0657ecb7</t>
+  </si>
+  <si>
+    <t>relationship--f45365a5-32b0-417c-95f2-19c2f90abf3f</t>
+  </si>
+  <si>
+    <t>relationship--fbc3460b-ad11-409e-8859-f19a4ebe8d2e</t>
+  </si>
+  <si>
+    <t>relationship--d0393c1a-f522-4c8a-b58c-a9946069de19</t>
+  </si>
+  <si>
+    <t>relationship--155f9979-73ec-4eba-8808-38de97758784</t>
+  </si>
+  <si>
+    <t>relationship--f85f0758-4c57-4e59-a2b0-dd5977a28769</t>
+  </si>
+  <si>
+    <t>relationship--cc9b386b-845a-4409-a53c-e88fe3165ca7</t>
+  </si>
+  <si>
+    <t>relationship--c02574e7-28f8-4149-9e60-de548f2b2739</t>
+  </si>
+  <si>
+    <t>relationship--c70d52db-bc94-4b2e-af45-20f3874bfedd</t>
+  </si>
+  <si>
+    <t>relationship--e4d5e664-a09e-41aa-8901-163d02b7287b</t>
+  </si>
+  <si>
+    <t>relationship--3b3277ba-6e98-4c8e-8b72-d65d2c00ae61</t>
+  </si>
+  <si>
+    <t>relationship--190fb4f5-b465-4775-9528-46d207d120b2</t>
+  </si>
+  <si>
+    <t>relationship--12db5486-053c-48ed-bb49-48b1e4b11391</t>
+  </si>
+  <si>
+    <t>relationship--fc4c3558-5f44-4a25-898a-91cd7a53e0c4</t>
+  </si>
+  <si>
+    <t>relationship--32fbbc5a-d409-4e61-9a20-e1c8ef9a9f42</t>
+  </si>
+  <si>
+    <t>relationship--443f6959-879a-43a2-ae33-c42f99cf5108</t>
+  </si>
+  <si>
+    <t>relationship--63d649b8-b431-413e-b07d-eca5e0019b2a</t>
+  </si>
+  <si>
+    <t>relationship--8302cd38-5016-42ed-accb-70cdb1d2996e</t>
+  </si>
+  <si>
+    <t>relationship--461e13fb-702e-42e7-91b5-f27c6db3ea70</t>
+  </si>
+  <si>
+    <t>relationship--b85d0c7b-f276-4a67-a101-da016bce172a</t>
+  </si>
+  <si>
+    <t>relationship--b0d665a3-7b3c-4aa3-9687-a3a5368ac34e</t>
+  </si>
+  <si>
+    <t>relationship--3101592e-1242-464d-adcb-9c68c43f6ac1</t>
+  </si>
+  <si>
+    <t>relationship--6e72e46e-9f47-43db-9851-59d899089853</t>
+  </si>
+  <si>
+    <t>relationship--d872ba7d-f1bd-4e7d-83cb-4237e5a6ccae</t>
+  </si>
+  <si>
+    <t>relationship--205a45c2-7248-43c9-8fbc-b25eb7af9d3e</t>
+  </si>
+  <si>
+    <t>relationship--4b2a8dc7-2b7b-42ab-90c2-c202d6c481e9</t>
+  </si>
+  <si>
+    <t>relationship--bc9a8aa8-b287-4ec4-bb2d-5f64eadcc530</t>
+  </si>
+  <si>
+    <t>relationship--fa65970c-ac67-4d39-aaf4-cd3c7bbbadcd</t>
+  </si>
+  <si>
+    <t>relationship--b781b174-17d4-41fa-879e-962fa3c6472e</t>
+  </si>
+  <si>
+    <t>relationship--ec58069d-2af0-4181-bac9-4dddda88c28c</t>
+  </si>
+  <si>
+    <t>relationship--f8ae12cf-66ec-4c01-a250-46bb97f99c7d</t>
+  </si>
+  <si>
+    <t>relationship--6e8f3632-6158-4971-bf6c-f6b75abaa66d</t>
+  </si>
+  <si>
+    <t>relationship--3d819923-9d97-4a8b-a67c-30fde21645b9</t>
+  </si>
+  <si>
+    <t>relationship--f3e7964d-4204-43d9-95ba-a61a39073b86</t>
+  </si>
+  <si>
+    <t>relationship--a9a82add-18b6-4428-b7d4-a07995c91849</t>
+  </si>
+  <si>
+    <t>relationship--8df00cdb-e745-4f6f-b241-b40ee4cad23c</t>
+  </si>
+  <si>
+    <t>relationship--4f13473b-9a37-4531-b782-850ced97e89d</t>
+  </si>
+  <si>
+    <t>relationship--8b6fa31a-3839-49f7-9e18-677cc43b927d</t>
+  </si>
+  <si>
+    <t>relationship--2fb417b5-205b-4b9f-98fc-c9db2c7172b3</t>
+  </si>
+  <si>
+    <t>relationship--24a70091-a353-470d-81e3-cf75b2979c7c</t>
+  </si>
+  <si>
+    <t>relationship--63722a18-6f07-4a93-8e38-135c8fbcbb56</t>
+  </si>
+  <si>
+    <t>relationship--d43afa20-2d6c-47c9-abbb-fba45f539dc7</t>
+  </si>
+  <si>
+    <t>relationship--e513611f-dbb7-41ad-8e96-eeab94495952</t>
   </si>
   <si>
     <t>T0030</t>
@@ -3050,253 +3050,253 @@
     <t>Спонсирование внутреннего экстремизма и радикалов</t>
   </si>
   <si>
-    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
-  </si>
-  <si>
-    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
-  </si>
-  <si>
-    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
-  </si>
-  <si>
-    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
-  </si>
-  <si>
-    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
-  </si>
-  <si>
-    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
-  </si>
-  <si>
-    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
-  </si>
-  <si>
-    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
-  </si>
-  <si>
-    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
-  </si>
-  <si>
-    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
-  </si>
-  <si>
-    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
-  </si>
-  <si>
-    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
-  </si>
-  <si>
-    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
-  </si>
-  <si>
-    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
-  </si>
-  <si>
-    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
-  </si>
-  <si>
-    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
-  </si>
-  <si>
-    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
-  </si>
-  <si>
-    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
-  </si>
-  <si>
-    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
-  </si>
-  <si>
-    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
-  </si>
-  <si>
-    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
-  </si>
-  <si>
-    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
-  </si>
-  <si>
-    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
-  </si>
-  <si>
-    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
-  </si>
-  <si>
-    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
-  </si>
-  <si>
-    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
-  </si>
-  <si>
-    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
-  </si>
-  <si>
-    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
-  </si>
-  <si>
-    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
-  </si>
-  <si>
-    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
-  </si>
-  <si>
-    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
-  </si>
-  <si>
-    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
-  </si>
-  <si>
-    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
-  </si>
-  <si>
-    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
-  </si>
-  <si>
-    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
-  </si>
-  <si>
-    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
-  </si>
-  <si>
-    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
-  </si>
-  <si>
-    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
-  </si>
-  <si>
-    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
-  </si>
-  <si>
-    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
-  </si>
-  <si>
-    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
-  </si>
-  <si>
-    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
-  </si>
-  <si>
-    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
-  </si>
-  <si>
-    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
-  </si>
-  <si>
-    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
-  </si>
-  <si>
-    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
-  </si>
-  <si>
-    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
-  </si>
-  <si>
-    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
-  </si>
-  <si>
-    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
-  </si>
-  <si>
-    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
-  </si>
-  <si>
-    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
-  </si>
-  <si>
-    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
-  </si>
-  <si>
-    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
-  </si>
-  <si>
-    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
-  </si>
-  <si>
-    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
-  </si>
-  <si>
-    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
-  </si>
-  <si>
-    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
+    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
+  </si>
+  <si>
+    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
+  </si>
+  <si>
+    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
+  </si>
+  <si>
+    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
+  </si>
+  <si>
+    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
+  </si>
+  <si>
+    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
+  </si>
+  <si>
+    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
+  </si>
+  <si>
+    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
+  </si>
+  <si>
+    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
+  </si>
+  <si>
+    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
+  </si>
+  <si>
+    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
+  </si>
+  <si>
+    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
+  </si>
+  <si>
+    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
+  </si>
+  <si>
+    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
+  </si>
+  <si>
+    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
+  </si>
+  <si>
+    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
+  </si>
+  <si>
+    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
+  </si>
+  <si>
+    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
+  </si>
+  <si>
+    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
+  </si>
+  <si>
+    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
+  </si>
+  <si>
+    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
+  </si>
+  <si>
+    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
+  </si>
+  <si>
+    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
+  </si>
+  <si>
+    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
+  </si>
+  <si>
+    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
+  </si>
+  <si>
+    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
+  </si>
+  <si>
+    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
+  </si>
+  <si>
+    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
+  </si>
+  <si>
+    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
+  </si>
+  <si>
+    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
+  </si>
+  <si>
+    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
+  </si>
+  <si>
+    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
+  </si>
+  <si>
+    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
+  </si>
+  <si>
+    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
+  </si>
+  <si>
+    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
+  </si>
+  <si>
+    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
+  </si>
+  <si>
+    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
+  </si>
+  <si>
+    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
+  </si>
+  <si>
+    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
+  </si>
+  <si>
+    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
+  </si>
+  <si>
+    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
+  </si>
+  <si>
+    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
+  </si>
+  <si>
+    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
+  </si>
+  <si>
+    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
+  </si>
+  <si>
+    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
+  </si>
+  <si>
+    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
+  </si>
+  <si>
+    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
+  </si>
+  <si>
+    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
+  </si>
+  <si>
+    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
+  </si>
+  <si>
+    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
+  </si>
+  <si>
+    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
+  </si>
+  <si>
+    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
+  </si>
+  <si>
+    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
+  </si>
+  <si>
+    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
+  </si>
+  <si>
+    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
   </si>
   <si>
     <t>technique</t>
@@ -3527,481 +3527,481 @@
     <t>Введение обязанности предоставлять полные финансовые отчеты о доходах региона под надзор центра (Citation: Решетилівські статті — Вікіпедія 2026)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>relationship--54c4d918-8bc7-4364-80f9-b0caf2bf0969</t>
-  </si>
-  <si>
-    <t>relationship--73189ccc-2381-4e23-95ce-ae7a30a09f43</t>
-  </si>
-  <si>
-    <t>relationship--04b40aa1-c056-4a12-a4ca-9a5b999da66e</t>
-  </si>
-  <si>
-    <t>relationship--6fc62b9c-7886-4974-ab01-cc635d166860</t>
-  </si>
-  <si>
-    <t>relationship--17316c02-b0c3-455f-8bcd-157aba4b808d</t>
-  </si>
-  <si>
-    <t>relationship--9a4c2560-ff66-4227-a982-86d97e2ffbed</t>
-  </si>
-  <si>
-    <t>relationship--4403eef2-fe84-4921-a94f-6257d3547b6e</t>
-  </si>
-  <si>
-    <t>relationship--84d3e218-1a16-4f3d-bf83-29abb545e970</t>
-  </si>
-  <si>
-    <t>relationship--62854ef1-cc65-4a00-85d8-968cabe77970</t>
-  </si>
-  <si>
-    <t>relationship--34a8027e-bb56-4c8c-a6e5-f2eff445b635</t>
-  </si>
-  <si>
-    <t>relationship--7a5673bf-43ca-4139-ac6b-d5bb967c11e6</t>
-  </si>
-  <si>
-    <t>relationship--96d6ea01-4a3b-4a31-834e-f6a1b25d3d01</t>
-  </si>
-  <si>
-    <t>relationship--65b32450-6df6-4327-9411-bb11dd24e186</t>
-  </si>
-  <si>
-    <t>relationship--cbbeb0ed-42c2-4724-b202-23d4856aff33</t>
-  </si>
-  <si>
-    <t>relationship--f2f90e4d-5a63-40b4-adad-90332f88a7be</t>
-  </si>
-  <si>
-    <t>relationship--11b1266c-d020-420d-9c40-318b57e0bbeb</t>
-  </si>
-  <si>
-    <t>relationship--5195893a-8224-493f-bdbb-b276f796dbb8</t>
-  </si>
-  <si>
-    <t>relationship--6165994a-b952-429b-8905-431c9e06f4cf</t>
-  </si>
-  <si>
-    <t>relationship--25f80921-0d9d-4d56-8a10-0b1c86bd8490</t>
-  </si>
-  <si>
-    <t>relationship--a1ce3595-ecd4-41b1-83f7-5aa32a7a4c25</t>
-  </si>
-  <si>
-    <t>relationship--b2d2b23a-2561-4b1b-b23b-60ec84ac8559</t>
-  </si>
-  <si>
-    <t>relationship--1a5c8ccb-b7f9-4118-9977-904a79d8cd91</t>
-  </si>
-  <si>
-    <t>relationship--499220bf-45f5-42dc-9842-b2104ef2385b</t>
-  </si>
-  <si>
-    <t>relationship--975edf7f-38d6-4125-86ae-6df413e02b64</t>
-  </si>
-  <si>
-    <t>relationship--13fe682c-4d2b-498e-b0fe-5faa9627f478</t>
-  </si>
-  <si>
-    <t>relationship--f98d2762-9dda-4bb9-a018-e77fcb87b59c</t>
-  </si>
-  <si>
-    <t>relationship--cda16288-3df9-4f63-8073-a4b437c71004</t>
-  </si>
-  <si>
-    <t>relationship--1f5a1489-2483-4e84-a40e-04efed8b94b4</t>
-  </si>
-  <si>
-    <t>relationship--fb03a109-6075-4b58-afb4-6a2557f2c215</t>
-  </si>
-  <si>
-    <t>relationship--9ec9acf6-7154-4532-913c-ccdf66091156</t>
-  </si>
-  <si>
-    <t>relationship--63452325-03d3-49b1-bf54-66dfb125ec87</t>
-  </si>
-  <si>
-    <t>relationship--0e802b5c-2403-479e-ac20-06e9aa5c43ae</t>
-  </si>
-  <si>
-    <t>relationship--dfc52397-92e1-4160-a98f-34948d016360</t>
-  </si>
-  <si>
-    <t>relationship--d6cc70a9-9c36-42e2-b4a9-454d252faa7a</t>
-  </si>
-  <si>
-    <t>relationship--7c07f851-9a41-4d35-b79f-fb7069c0d04d</t>
-  </si>
-  <si>
-    <t>relationship--971fa3bc-ca45-4715-9d2c-da25aab64756</t>
-  </si>
-  <si>
-    <t>relationship--676dfa2f-887b-4a44-869a-7ef3d8e61b0a</t>
-  </si>
-  <si>
-    <t>relationship--a476ccc4-9b09-40e8-85fa-c2cb5269f2b1</t>
-  </si>
-  <si>
-    <t>relationship--e9e57c76-c09b-4fd5-b89f-46f96cca140d</t>
-  </si>
-  <si>
-    <t>relationship--cedcc327-db8f-4d4c-b1f0-f6c89260dda8</t>
-  </si>
-  <si>
-    <t>relationship--cc6b2561-a78f-4f37-aee5-e8248c3db565</t>
-  </si>
-  <si>
-    <t>relationship--685565b6-7584-4468-b179-52fe99c48584</t>
-  </si>
-  <si>
-    <t>relationship--40f1a33f-1390-4a00-b1be-cf9f1d3c976b</t>
-  </si>
-  <si>
-    <t>relationship--66b98a2b-4c8f-4386-958d-02048df51fc3</t>
-  </si>
-  <si>
-    <t>relationship--7f56817f-8b83-4c6c-b2fd-a0b7f86dec1f</t>
-  </si>
-  <si>
-    <t>relationship--1ac9ff58-8efb-419c-928c-fe3847c9188c</t>
-  </si>
-  <si>
-    <t>relationship--9c48b5cd-56e8-49a0-9b61-a580368cf0e1</t>
-  </si>
-  <si>
-    <t>relationship--9b25f341-01f3-4dfd-a588-165a86bcaace</t>
-  </si>
-  <si>
-    <t>relationship--9da377c2-38ff-439c-823b-34a5d1998571</t>
-  </si>
-  <si>
-    <t>relationship--279284af-ae24-4c2b-bc5e-17e518c8868e</t>
-  </si>
-  <si>
-    <t>relationship--a07d27b0-07d8-4981-a5a0-be24cbe07191</t>
-  </si>
-  <si>
-    <t>relationship--3e6cea56-29f5-4715-a858-a40804c68293</t>
-  </si>
-  <si>
-    <t>relationship--ffafc4ad-f136-4aae-9beb-72a49eea5020</t>
-  </si>
-  <si>
-    <t>relationship--0ff6a61c-38db-4435-9190-d7afac3f982d</t>
-  </si>
-  <si>
-    <t>relationship--1ca8158f-e8b9-4dad-a4d9-63c5e5f7b814</t>
-  </si>
-  <si>
-    <t>relationship--7039815a-5bb6-4ae6-add1-1d88c03ca42f</t>
-  </si>
-  <si>
-    <t>relationship--07c3aeaa-21f2-42bd-a3d0-ebd14c8dbf1b</t>
-  </si>
-  <si>
-    <t>relationship--38e83d08-2485-4ebe-bf67-1c981ee314ba</t>
-  </si>
-  <si>
-    <t>relationship--f9f2ba02-56ea-4444-9e3f-a47c6972d6e7</t>
-  </si>
-  <si>
-    <t>relationship--a971ee1c-e0d2-4f15-9cd2-62e3d0d32ca0</t>
-  </si>
-  <si>
-    <t>relationship--d6699f88-a5cb-40dd-ae75-19f280aeb4cb</t>
-  </si>
-  <si>
-    <t>relationship--ece83b83-27bc-4e09-a313-ad8cee5ebeb7</t>
-  </si>
-  <si>
-    <t>relationship--cb5e7817-a24b-4246-a285-3699c9a6faa1</t>
-  </si>
-  <si>
-    <t>relationship--3be951b7-a21a-4015-8629-51c108cb9c26</t>
-  </si>
-  <si>
-    <t>relationship--de9774c2-f9b4-4b84-825a-2e1b90f22f46</t>
-  </si>
-  <si>
-    <t>relationship--c94c095f-581b-4666-bc33-15a56a4f7b95</t>
-  </si>
-  <si>
-    <t>relationship--d1aa0946-d87c-45ae-b424-d9c9146f01e9</t>
-  </si>
-  <si>
-    <t>relationship--bd156b28-4368-4ef7-9442-99a4037f8990</t>
-  </si>
-  <si>
-    <t>relationship--51b252c6-f25a-4868-ba2f-5c4c5dce3575</t>
-  </si>
-  <si>
-    <t>relationship--ea59c0a9-5e60-42a9-b62c-7b1c2c235920</t>
-  </si>
-  <si>
-    <t>relationship--472e25d9-877e-4eea-8777-ff8fb1f2cf1d</t>
-  </si>
-  <si>
-    <t>relationship--15b4a1ec-a4c0-4c0d-af6b-9ce3c60dc53c</t>
-  </si>
-  <si>
-    <t>relationship--45b6dca8-89ca-4d24-89ea-a829323807cb</t>
-  </si>
-  <si>
-    <t>relationship--73e7a9e7-fd3a-4ec8-8d58-ad42c116c5e5</t>
-  </si>
-  <si>
-    <t>relationship--e25881ca-c77f-4de2-9a5a-93e603d6089d</t>
-  </si>
-  <si>
-    <t>relationship--ccbb2c32-1b08-4489-9281-a4e802aebe2c</t>
-  </si>
-  <si>
-    <t>relationship--b1254916-a50c-4122-8a8b-ddae6cb4bf3b</t>
-  </si>
-  <si>
-    <t>relationship--436a367d-751f-46ae-865b-1b08b2c94b0b</t>
-  </si>
-  <si>
-    <t>relationship--ae1830ae-193d-49fd-88b8-9ca09acab278</t>
-  </si>
-  <si>
-    <t>relationship--a00d775f-db2b-4bf4-9738-882d507f14a3</t>
-  </si>
-  <si>
-    <t>relationship--91d493cc-ed9d-410a-87da-737f90d29d5f</t>
-  </si>
-  <si>
-    <t>relationship--2a31099b-0274-4bcb-bcd8-1ab0dd82ca1a</t>
-  </si>
-  <si>
-    <t>relationship--613a2833-e940-4b58-90d7-22663e80ee19</t>
-  </si>
-  <si>
-    <t>relationship--e2b3c79f-8da6-406e-b66b-35ee86951b5c</t>
-  </si>
-  <si>
-    <t>relationship--a27107bb-ee98-440b-b975-fbe403b7d011</t>
-  </si>
-  <si>
-    <t>relationship--22684718-ebff-48c1-835a-4dbcaae467d6</t>
-  </si>
-  <si>
-    <t>relationship--6c0f5f2d-13a9-4854-b56a-31267e3e57d4</t>
-  </si>
-  <si>
-    <t>relationship--2d8f0eaa-86d6-4ec2-b131-fb0176dde252</t>
-  </si>
-  <si>
-    <t>relationship--7acaf2ec-5332-4376-b9e6-e5f7a5d4e396</t>
-  </si>
-  <si>
-    <t>relationship--51ef3804-21ae-4b4d-90ff-66961d7c3031</t>
-  </si>
-  <si>
-    <t>relationship--46f3bd13-d9a3-40ce-9833-559c430cf1de</t>
-  </si>
-  <si>
-    <t>relationship--2e7a2655-e1f7-4be0-8560-99a7ce302fda</t>
-  </si>
-  <si>
-    <t>relationship--2b1d8bec-1187-47fc-a890-9171d0af4206</t>
-  </si>
-  <si>
-    <t>relationship--0c6b277f-6616-428d-8dde-d133beab7c6b</t>
-  </si>
-  <si>
-    <t>relationship--00266455-3f2b-4b3c-8e1f-6ce6193cb8f4</t>
-  </si>
-  <si>
-    <t>relationship--7981c6df-980d-427f-b355-4ce7650a11fa</t>
-  </si>
-  <si>
-    <t>relationship--58a2fd8c-b163-4fd7-af8e-4e5f518cf565</t>
-  </si>
-  <si>
-    <t>relationship--55fad24c-1298-46ae-8628-2eec64a7d75c</t>
-  </si>
-  <si>
-    <t>relationship--1bb41d58-bb9f-4f26-b8b2-5a6600fe25d5</t>
-  </si>
-  <si>
-    <t>relationship--3e20551e-d442-43b7-9893-b825832447f8</t>
-  </si>
-  <si>
-    <t>relationship--aef61ea4-d2d3-4b7d-b3f2-eb09d9954aba</t>
-  </si>
-  <si>
-    <t>relationship--fceb239a-b0ae-48e6-bec0-0c8c7357ebd9</t>
-  </si>
-  <si>
-    <t>relationship--3380f24c-4e14-49a4-a119-a87f1b9eecd9</t>
-  </si>
-  <si>
-    <t>relationship--a22a0b8c-4032-40b7-a0ea-12e9dbf2961b</t>
-  </si>
-  <si>
-    <t>relationship--217bd9d8-a378-463f-9cc8-e7fadf8aa13d</t>
-  </si>
-  <si>
-    <t>relationship--2f9a83f4-d17c-4e2f-b852-7e1823502480</t>
-  </si>
-  <si>
-    <t>relationship--1227d382-496a-4e5d-8e55-ff384f5424d1</t>
-  </si>
-  <si>
-    <t>relationship--14448630-38e2-458b-b4e9-f8184c4c7809</t>
-  </si>
-  <si>
-    <t>relationship--893aac3e-99cc-4a45-96b3-d9cc67be9476</t>
-  </si>
-  <si>
-    <t>relationship--1a5bc425-80c9-491b-8c61-699e84666675</t>
-  </si>
-  <si>
-    <t>relationship--3129830c-d6e0-43ad-aac8-fa955eec7292</t>
-  </si>
-  <si>
-    <t>relationship--ad8190b9-1ea3-422d-9cc0-79fe25111c3b</t>
-  </si>
-  <si>
-    <t>relationship--2a74ddf8-7017-4935-821c-bcd120366aec</t>
-  </si>
-  <si>
-    <t>relationship--65ad9ce1-3c06-4312-9781-f4ab0a1b4576</t>
-  </si>
-  <si>
-    <t>relationship--0d90ba2b-7b16-4c53-9b8f-26c329a24988</t>
-  </si>
-  <si>
-    <t>relationship--a3fe44a7-14ec-4ea0-b4f4-6846c5fbc24d</t>
-  </si>
-  <si>
-    <t>relationship--5e869d43-c351-4be0-a267-f79006c39d2d</t>
-  </si>
-  <si>
-    <t>relationship--10ef8b9a-6360-401d-8baf-86e9b805780c</t>
-  </si>
-  <si>
-    <t>relationship--15dd688a-f80a-4db8-b9bc-c1cdacee5bf9</t>
-  </si>
-  <si>
-    <t>relationship--21f6c7af-2c6e-4bf7-850c-61b5194aa999</t>
-  </si>
-  <si>
-    <t>relationship--839f6e5b-5e89-44c0-a3e6-71397137e2c0</t>
-  </si>
-  <si>
-    <t>relationship--3db1a8d4-08de-47d8-b608-1855ef5fc32e</t>
-  </si>
-  <si>
-    <t>relationship--8834c869-09ab-4a5b-9269-c40d5a257df4</t>
-  </si>
-  <si>
-    <t>relationship--fdce753f-4c29-4b25-91ff-7f7d8b2afea8</t>
-  </si>
-  <si>
-    <t>relationship--a87b6855-782c-4452-bdb9-86e7e2ec6059</t>
-  </si>
-  <si>
-    <t>relationship--f81e8eb7-d4f6-4e9a-b29f-4f25d579e7da</t>
-  </si>
-  <si>
-    <t>relationship--f696fb29-1c07-45b5-b568-64f4f6fe8fec</t>
-  </si>
-  <si>
-    <t>relationship--d9fa28d8-1f00-498b-918b-26c1e7ae1c53</t>
-  </si>
-  <si>
-    <t>relationship--f045efb9-8922-4775-970d-481418f671a0</t>
-  </si>
-  <si>
-    <t>relationship--205dff75-fc00-4858-8a43-d0391dd8c888</t>
-  </si>
-  <si>
-    <t>relationship--0a3003bf-966e-423b-b592-01d663788603</t>
-  </si>
-  <si>
-    <t>relationship--90f65ece-ab59-4b9f-aa48-6f3f18d3e1eb</t>
-  </si>
-  <si>
-    <t>relationship--1d1cb160-1ad8-4e2b-a6fb-cd4745e040b4</t>
-  </si>
-  <si>
-    <t>relationship--d883cc91-90fa-4cca-a50c-7267c0aff891</t>
-  </si>
-  <si>
-    <t>relationship--5aaf25d0-bc32-4203-9c9d-d9f66bd960d1</t>
-  </si>
-  <si>
-    <t>relationship--30b46d33-7b73-4334-a1db-d91a5850d0f8</t>
-  </si>
-  <si>
-    <t>relationship--1415d9e2-3ec8-4950-a3cf-0a771978afa9</t>
-  </si>
-  <si>
-    <t>relationship--4fdb62a5-fb3e-4fb6-aa8a-b682cb4e1c20</t>
-  </si>
-  <si>
-    <t>relationship--bbe1b9bc-6806-402f-b985-2f64a72ff0e3</t>
-  </si>
-  <si>
-    <t>relationship--4262f5bf-7ff8-4bb6-84c4-e0226ad3b11d</t>
-  </si>
-  <si>
-    <t>relationship--d62debb4-770b-4b6f-8173-018af2a5b325</t>
-  </si>
-  <si>
-    <t>relationship--2c6e107e-e860-40fb-8f76-ce5682d72b02</t>
-  </si>
-  <si>
-    <t>relationship--49922116-adf1-4974-b9b4-8baef88d2dd9</t>
-  </si>
-  <si>
-    <t>relationship--d2d79914-471e-457f-ae36-41d34ccaeff6</t>
-  </si>
-  <si>
-    <t>relationship--f44aba76-9d85-4d72-a071-a2e09093df88</t>
-  </si>
-  <si>
-    <t>relationship--502e33d2-3654-4b52-a2d2-08a6a6c709f3</t>
-  </si>
-  <si>
-    <t>relationship--b0b9692d-77af-4890-986f-fc4b37d7dfa3</t>
-  </si>
-  <si>
-    <t>relationship--e5e638ab-fd72-4af1-9f8d-e2bb7d44142c</t>
-  </si>
-  <si>
-    <t>relationship--5bcf5e3f-e1a0-4b65-a5ef-c087360b918b</t>
-  </si>
-  <si>
-    <t>relationship--b8cf1b28-e865-4cd7-93f6-565527b4a923</t>
-  </si>
-  <si>
-    <t>relationship--a7a7b234-a9dd-4b62-b9ed-73f511c5adf8</t>
-  </si>
-  <si>
-    <t>relationship--63474f71-ecda-42ff-8bc1-475a951eb9d4</t>
-  </si>
-  <si>
-    <t>relationship--06e2c87e-97c1-425e-aa49-49a43aaf8c38</t>
-  </si>
-  <si>
-    <t>relationship--c5907c16-a6b2-4585-8587-743dbd102eb4</t>
-  </si>
-  <si>
-    <t>relationship--ef4b5e37-4b77-41ef-a9fd-ed32e7dd71d1</t>
-  </si>
-  <si>
-    <t>relationship--7d60876d-abd3-49cb-9646-9d3ce55e8eaa</t>
-  </si>
-  <si>
-    <t>relationship--00d76dd5-547f-4d91-a2b2-a68120947401</t>
-  </si>
-  <si>
-    <t>relationship--5d240505-32ed-4a6f-897e-bc114bded524</t>
-  </si>
-  <si>
-    <t>relationship--6867b04c-5665-48ce-a4a9-d0e025aae5b3</t>
+    <t>relationship--0fc9df02-2663-4be2-ae57-b47e321d5c5b</t>
+  </si>
+  <si>
+    <t>relationship--e5b4df88-6b23-491f-b483-8551a0ea2bf0</t>
+  </si>
+  <si>
+    <t>relationship--0644e98b-0ba5-405e-890c-fb8c222e1439</t>
+  </si>
+  <si>
+    <t>relationship--8ac25ca3-96cf-4c52-a237-b9062e106f74</t>
+  </si>
+  <si>
+    <t>relationship--3e8a36d8-88aa-468c-9c2c-dc6a2763f906</t>
+  </si>
+  <si>
+    <t>relationship--da148c65-5f4a-4a95-87a3-c6b87f8379ea</t>
+  </si>
+  <si>
+    <t>relationship--f701788a-e221-4dd1-9128-95b9a0d023c8</t>
+  </si>
+  <si>
+    <t>relationship--bf4a83fc-a160-498d-b894-772828c88b1c</t>
+  </si>
+  <si>
+    <t>relationship--57bd8188-1eec-4025-b4f3-e7efaef6549b</t>
+  </si>
+  <si>
+    <t>relationship--a936931c-9625-4d84-9987-ca3f67d5fe58</t>
+  </si>
+  <si>
+    <t>relationship--7e8e6538-c636-4e58-9203-c7b1520d6c27</t>
+  </si>
+  <si>
+    <t>relationship--969684f6-68ed-4fd1-bc86-632f849b1bbd</t>
+  </si>
+  <si>
+    <t>relationship--29b789a0-4a47-4569-b028-52c5f6f00ed7</t>
+  </si>
+  <si>
+    <t>relationship--7bb60df4-1c22-4b9b-b8d2-805d486ae9fa</t>
+  </si>
+  <si>
+    <t>relationship--0e2144a3-1971-40e2-9381-96702aa05be4</t>
+  </si>
+  <si>
+    <t>relationship--0e3a834c-4d76-4a14-8f0b-9b01782f7a2a</t>
+  </si>
+  <si>
+    <t>relationship--465f4881-318d-4da2-b4f0-5d289443f6fa</t>
+  </si>
+  <si>
+    <t>relationship--e1b6ebd1-cbe7-4c53-afd3-37030a935932</t>
+  </si>
+  <si>
+    <t>relationship--6cdb2e97-2d6d-4c25-bc19-5a4b3544d232</t>
+  </si>
+  <si>
+    <t>relationship--a4a38ef0-3b9c-45c0-9306-aff86b2387ae</t>
+  </si>
+  <si>
+    <t>relationship--657542f6-b8c1-4a4e-8893-4fe28a4cdee8</t>
+  </si>
+  <si>
+    <t>relationship--6e36c6de-fbf1-4a16-89da-71294bd0dc93</t>
+  </si>
+  <si>
+    <t>relationship--4370f48f-01cd-46ca-97ea-64afdd48aea4</t>
+  </si>
+  <si>
+    <t>relationship--633ed359-9c30-4a9f-a839-395bb299df98</t>
+  </si>
+  <si>
+    <t>relationship--6202b96d-be8b-4dba-b845-af6c1b249723</t>
+  </si>
+  <si>
+    <t>relationship--2b2a351f-b83e-479f-94f1-253242777b55</t>
+  </si>
+  <si>
+    <t>relationship--95c2a5c2-fd4e-4783-8d91-8da9d5d3fbe2</t>
+  </si>
+  <si>
+    <t>relationship--afcffc6b-70fb-4c03-81ca-fef5944088a2</t>
+  </si>
+  <si>
+    <t>relationship--9504d767-5432-4d80-8013-53c83f7c22f1</t>
+  </si>
+  <si>
+    <t>relationship--611edf19-465c-4f5d-85bb-aeefd6e995e2</t>
+  </si>
+  <si>
+    <t>relationship--dff55fe5-c06c-40d4-a686-5a431b3e98d8</t>
+  </si>
+  <si>
+    <t>relationship--d68069d1-821b-4e7a-ad14-ed1c1939ed38</t>
+  </si>
+  <si>
+    <t>relationship--83a81dbd-94b4-4eab-bcb0-44e580bc0fbd</t>
+  </si>
+  <si>
+    <t>relationship--e6ca9bad-b837-485a-8561-fe0c0f67a174</t>
+  </si>
+  <si>
+    <t>relationship--5bd244d1-5516-474b-b6c6-8f6e1751959e</t>
+  </si>
+  <si>
+    <t>relationship--f05c64f4-6a88-49ed-b077-8de036f40556</t>
+  </si>
+  <si>
+    <t>relationship--e0673107-5991-4109-8db8-520134cc2146</t>
+  </si>
+  <si>
+    <t>relationship--97d08a69-727a-4f0e-83b1-063f58e68ba4</t>
+  </si>
+  <si>
+    <t>relationship--6e962e55-cd15-45d1-9203-8e33bd78ab60</t>
+  </si>
+  <si>
+    <t>relationship--405625f8-e751-4bd7-85fa-258ad6f2b68a</t>
+  </si>
+  <si>
+    <t>relationship--9ed83b23-a904-429c-92a6-ce90942689de</t>
+  </si>
+  <si>
+    <t>relationship--bae03c3e-e80f-45db-87ed-892807e2178e</t>
+  </si>
+  <si>
+    <t>relationship--080ed8e8-2c28-4e8b-b6a7-45145ea0128a</t>
+  </si>
+  <si>
+    <t>relationship--8bcd799f-e5b8-4633-b7bd-b2e5f721fea6</t>
+  </si>
+  <si>
+    <t>relationship--8483e736-649f-492e-a9f5-7f4222459993</t>
+  </si>
+  <si>
+    <t>relationship--0bf70881-3dcb-4784-be1a-6291c9c92fc1</t>
+  </si>
+  <si>
+    <t>relationship--53b4c112-a429-43b5-a40a-134a823673af</t>
+  </si>
+  <si>
+    <t>relationship--29686751-4d79-46cf-8a7b-e9837d808aae</t>
+  </si>
+  <si>
+    <t>relationship--aadc9e12-57f1-4c6e-b5c4-a3ef30807211</t>
+  </si>
+  <si>
+    <t>relationship--07d2ef94-6812-42bb-ab5a-43d6355050ca</t>
+  </si>
+  <si>
+    <t>relationship--70e8cecb-6d07-45c3-9b13-019a92a70701</t>
+  </si>
+  <si>
+    <t>relationship--f8216de2-1ed0-4fbe-ad57-d72c52ecccdc</t>
+  </si>
+  <si>
+    <t>relationship--be802805-0e80-4510-88e2-36bd8e2bef66</t>
+  </si>
+  <si>
+    <t>relationship--584c2186-1549-43f8-bf0c-431e2b6b5010</t>
+  </si>
+  <si>
+    <t>relationship--90e4c5e3-7c6d-4e55-8725-d48eca01a678</t>
+  </si>
+  <si>
+    <t>relationship--e9a6f035-155a-4704-9b4f-14b4b61dd8f8</t>
+  </si>
+  <si>
+    <t>relationship--3db8866a-062d-4995-a079-92aa94987cd6</t>
+  </si>
+  <si>
+    <t>relationship--78de6c1b-d105-463b-bd2e-cc387e513a04</t>
+  </si>
+  <si>
+    <t>relationship--85f50e8e-4090-4472-a182-467c3f609cb2</t>
+  </si>
+  <si>
+    <t>relationship--8e9eda91-5e66-416f-bb44-b303c726c86a</t>
+  </si>
+  <si>
+    <t>relationship--8d0c0c6c-a6b7-4773-a0ac-0c6dad8866a1</t>
+  </si>
+  <si>
+    <t>relationship--e72dfa93-e5ae-4efe-a8ff-f7bdacfae145</t>
+  </si>
+  <si>
+    <t>relationship--d5616a46-fabb-4875-861f-d986a816162a</t>
+  </si>
+  <si>
+    <t>relationship--417e33c5-7b63-440a-9e43-94fae2304c40</t>
+  </si>
+  <si>
+    <t>relationship--2b27b61a-ed32-4cb0-b945-db8901d861b9</t>
+  </si>
+  <si>
+    <t>relationship--03bff8b0-2774-4899-a2ae-991c5caccc2f</t>
+  </si>
+  <si>
+    <t>relationship--7032ef5f-c42b-4239-91fc-996ab9c33b83</t>
+  </si>
+  <si>
+    <t>relationship--ced5e698-bb1b-4f5b-a57f-e80fdcb1def1</t>
+  </si>
+  <si>
+    <t>relationship--12b4d92f-9c0a-4b57-b5da-5644f0640104</t>
+  </si>
+  <si>
+    <t>relationship--e33d4ef5-b340-497d-9db7-f723f793d14b</t>
+  </si>
+  <si>
+    <t>relationship--6a71645c-e668-4c35-af1a-068c183f8c81</t>
+  </si>
+  <si>
+    <t>relationship--8dc5252a-2a4a-40b6-9579-2ac103aa6e5e</t>
+  </si>
+  <si>
+    <t>relationship--066972ee-074b-4c3c-992c-eb0950164778</t>
+  </si>
+  <si>
+    <t>relationship--da41731f-9712-4e17-8d67-493d30b959e3</t>
+  </si>
+  <si>
+    <t>relationship--a64f0e5e-e1eb-49c7-8f9f-809fd64cd5ad</t>
+  </si>
+  <si>
+    <t>relationship--19d74513-f877-42bb-a3dd-9cb8e098f7c8</t>
+  </si>
+  <si>
+    <t>relationship--b9cb0d82-e343-4008-89d5-12ac6796966b</t>
+  </si>
+  <si>
+    <t>relationship--8301a987-0a3b-48c4-8ebe-9775eac9700e</t>
+  </si>
+  <si>
+    <t>relationship--6082181d-42e4-4a00-88b9-fb7f05f08650</t>
+  </si>
+  <si>
+    <t>relationship--3ff626c6-8623-4924-9ad8-0cc56833003c</t>
+  </si>
+  <si>
+    <t>relationship--9a131f74-b423-4e60-9bc4-6cce5360b8bc</t>
+  </si>
+  <si>
+    <t>relationship--0e02357c-c07e-47b2-805b-c05265688163</t>
+  </si>
+  <si>
+    <t>relationship--3a8c4403-d83b-4eae-9655-968bea432709</t>
+  </si>
+  <si>
+    <t>relationship--750fef77-11a1-474a-a028-65e894b53482</t>
+  </si>
+  <si>
+    <t>relationship--fff3aef4-c045-41d2-9c1a-1c4960a5b465</t>
+  </si>
+  <si>
+    <t>relationship--7148e04c-a774-454c-8c96-5142c0ee1331</t>
+  </si>
+  <si>
+    <t>relationship--94123636-25d9-4c52-bc8e-fa2b6af78f7d</t>
+  </si>
+  <si>
+    <t>relationship--c96aa7f2-2ff5-45e4-8ce0-993e46b0f7ce</t>
+  </si>
+  <si>
+    <t>relationship--c88dccf7-073f-4b73-95b8-f6c141c2ea88</t>
+  </si>
+  <si>
+    <t>relationship--aa18ba5c-4772-4de6-8df6-97103c857633</t>
+  </si>
+  <si>
+    <t>relationship--ae0d4f48-7ca8-4e86-beb4-2fc5e34613d7</t>
+  </si>
+  <si>
+    <t>relationship--3d65f0d0-9ca6-4c8a-a0f2-a2f32cf3117d</t>
+  </si>
+  <si>
+    <t>relationship--7045ddce-4798-4f62-bbb9-657acf7e895e</t>
+  </si>
+  <si>
+    <t>relationship--3096006d-9acf-4b9c-a667-01cdc7d7c99f</t>
+  </si>
+  <si>
+    <t>relationship--168aae8a-1325-4d12-8e76-912245ef0e79</t>
+  </si>
+  <si>
+    <t>relationship--f0fb29ec-513b-4c24-922f-81bfb4d4e2a2</t>
+  </si>
+  <si>
+    <t>relationship--e2b323f7-fe5f-4725-ba72-f0dd7ba91c5a</t>
+  </si>
+  <si>
+    <t>relationship--2a6b3098-d2b8-4363-8a6b-29f869aaf8c5</t>
+  </si>
+  <si>
+    <t>relationship--9c4bfad0-d523-4ec7-8e70-8cb64f4a9043</t>
+  </si>
+  <si>
+    <t>relationship--59f9d0e9-3202-4c50-8172-f73fe9eb7131</t>
+  </si>
+  <si>
+    <t>relationship--60f81fbf-1bd9-4c2f-b5df-7f6ed6f17c3d</t>
+  </si>
+  <si>
+    <t>relationship--225cefd8-2903-4317-af4f-35fa55e94032</t>
+  </si>
+  <si>
+    <t>relationship--416d1d17-f865-4b1a-8f81-b82260aced75</t>
+  </si>
+  <si>
+    <t>relationship--b67bd861-444f-4f04-a6e1-9b0d1c3c67c4</t>
+  </si>
+  <si>
+    <t>relationship--2a77ae94-5326-4980-ae79-c7e881ae7de5</t>
+  </si>
+  <si>
+    <t>relationship--649413cf-6855-42d3-b7d2-f0a5abf6676f</t>
+  </si>
+  <si>
+    <t>relationship--18106a1c-5855-4d6b-92b8-56905db21203</t>
+  </si>
+  <si>
+    <t>relationship--d2ca5391-f68f-441c-ad33-1dc1f2402e3c</t>
+  </si>
+  <si>
+    <t>relationship--4d34b1a4-fc22-4817-b194-5b0b3dfb0814</t>
+  </si>
+  <si>
+    <t>relationship--9ee851e9-b992-4e8f-9c2b-432ec620e219</t>
+  </si>
+  <si>
+    <t>relationship--b1baa091-4cd0-4638-a837-6a07ad23bcb8</t>
+  </si>
+  <si>
+    <t>relationship--00dfae9d-7870-47fd-98b0-206114ba58d9</t>
+  </si>
+  <si>
+    <t>relationship--f939a8be-2236-4d77-86b5-287b54c7c32a</t>
+  </si>
+  <si>
+    <t>relationship--d676c970-f90d-4397-bf58-c5a03f8bfc59</t>
+  </si>
+  <si>
+    <t>relationship--efc80a10-3b08-4ba7-b038-178817d44f66</t>
+  </si>
+  <si>
+    <t>relationship--6c9b61bd-0b24-4114-84f1-86c2046aa9c6</t>
+  </si>
+  <si>
+    <t>relationship--86626dfd-325d-4c7d-9bf4-e8257116723e</t>
+  </si>
+  <si>
+    <t>relationship--0bd740fe-817a-43ab-80c1-dd570939c124</t>
+  </si>
+  <si>
+    <t>relationship--9107543d-cc94-4c75-8b4d-8e3f49490734</t>
+  </si>
+  <si>
+    <t>relationship--41f7475a-c31b-496c-8375-52b0d70258a0</t>
+  </si>
+  <si>
+    <t>relationship--c5d53690-5de6-4764-93e2-09e1b9744076</t>
+  </si>
+  <si>
+    <t>relationship--8ce2c861-8d58-4ffd-8c50-78c112daa96d</t>
+  </si>
+  <si>
+    <t>relationship--173660ca-1b8b-40c5-89a0-02813361a6fc</t>
+  </si>
+  <si>
+    <t>relationship--d959e6e3-e593-41c2-8f4c-4f95d0a732ce</t>
+  </si>
+  <si>
+    <t>relationship--9a518d2e-0857-40f8-a7f3-b2e1cdc14621</t>
+  </si>
+  <si>
+    <t>relationship--88165274-fe0a-467c-add8-8b7f67b17b80</t>
+  </si>
+  <si>
+    <t>relationship--ba38f840-9a97-4864-b29b-79af50e2d0f0</t>
+  </si>
+  <si>
+    <t>relationship--deca8f6f-dedd-43ec-8a6d-734952d9bd73</t>
+  </si>
+  <si>
+    <t>relationship--bdb96b60-ec68-4ee8-8d96-8d2a78fb7dc0</t>
+  </si>
+  <si>
+    <t>relationship--390041a9-89ff-43f9-aff4-d45d6a485a55</t>
+  </si>
+  <si>
+    <t>relationship--c9af633c-6d9d-4870-b227-32d5ec24cd56</t>
+  </si>
+  <si>
+    <t>relationship--75a13b48-8e93-4fb6-9773-f77a50243288</t>
+  </si>
+  <si>
+    <t>relationship--15f5af70-262e-41e0-8aba-fa599d341328</t>
+  </si>
+  <si>
+    <t>relationship--711996e9-34ae-4810-8d7a-21a44ffa7fe9</t>
+  </si>
+  <si>
+    <t>relationship--9a3c95c6-23e4-4c0f-8844-52d958f1dbe8</t>
+  </si>
+  <si>
+    <t>relationship--d5500959-3922-4bb2-9c2e-72df957cc5e1</t>
+  </si>
+  <si>
+    <t>relationship--7f6a069d-a281-4ca3-9c5d-7f40d7d57610</t>
+  </si>
+  <si>
+    <t>relationship--a10ca265-b361-4b4c-9de0-d1c1309a80a5</t>
+  </si>
+  <si>
+    <t>relationship--73a49bef-fe4c-459e-8fd8-836fcf3e0641</t>
+  </si>
+  <si>
+    <t>relationship--0cd4c6e2-7736-4613-b2a5-6c711975a0ae</t>
+  </si>
+  <si>
+    <t>relationship--bf56a23c-8789-41b1-af63-46b900047f5a</t>
+  </si>
+  <si>
+    <t>relationship--f3e20272-250d-4f8c-b9e6-f2d9ab1ee9d0</t>
+  </si>
+  <si>
+    <t>relationship--1afbd67d-8510-433b-a617-2720cfd43de3</t>
+  </si>
+  <si>
+    <t>relationship--950ce7a6-f20d-4429-8270-cbe702f9b8a4</t>
+  </si>
+  <si>
+    <t>relationship--d70c1641-5355-48a5-8a08-f6c589f1b7bf</t>
+  </si>
+  <si>
+    <t>relationship--f2315b08-5655-4313-8ae3-121331d6895b</t>
+  </si>
+  <si>
+    <t>relationship--8eae276b-a879-4b89-b777-a1cbc639ca44</t>
+  </si>
+  <si>
+    <t>relationship--c06b6614-aedc-4ee6-8a39-9953db7fe4c7</t>
+  </si>
+  <si>
+    <t>relationship--0a7daa8c-a8f9-4b8e-be70-9bea46ea2bd9</t>
+  </si>
+  <si>
+    <t>relationship--104478ca-397a-4f1a-88a9-cc288cc01269</t>
+  </si>
+  <si>
+    <t>relationship--b82e7c93-0bc3-4694-b8d3-f1865eacc556</t>
+  </si>
+  <si>
+    <t>relationship--5e334d35-427c-4965-8fa3-d390a2aec408</t>
+  </si>
+  <si>
+    <t>relationship--9bc4b721-8658-49f6-b490-726dbec2b451</t>
+  </si>
+  <si>
+    <t>relationship--4da5a977-b962-49e5-ab52-2e0e5f7e890a</t>
+  </si>
+  <si>
+    <t>relationship--b8c316e5-c364-4d3c-8de5-7aa98d597d2c</t>
+  </si>
+  <si>
+    <t>relationship--2e1b44f7-f38a-4868-910a-85e88baa212b</t>
+  </si>
+  <si>
+    <t>relationship--b535b75e-dae6-4781-9a69-21c2e2065f3b</t>
+  </si>
+  <si>
+    <t>relationship--7da26f74-c81f-49d8-b7e7-28e0a9ad2d2b</t>
+  </si>
+  <si>
+    <t>relationship--2cc2e74c-b0bf-4057-b099-ac8686c66a45</t>
   </si>
   <si>
     <t>reference</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -298,7 +298,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Перепис населення Російської імперії (1897),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Історія України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
@@ -310,31 +310,31 @@
     <t>,(Citation: Друга Малоросійська колегія — Вікіпедія 2026),</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Російсько-українська війна (з 2014),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Крымская война — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Русско-турецкая война (1768—1774),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Московсько-українська війна (1658—1659),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Повстання бузьких козаків (1817),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Листопадове повстання (1830—1831),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Московсько-українська війна (1658—1659),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Руїна — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Рашизм: Звір з безодні 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Московські статті (1665),(Citation: Азовські походи (1695—1696),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русско-турецкая война (1877—1878),(Citation: Польское восстание (1863—1864),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Русско-турецкая война (1768—1774),(Citation: Московські статті (1665),(Citation: Переяславські статті (1659),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Листопадове повстання (1830—1831),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Крымская война — Википедия 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Московсько-українська війна (1658—1659),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Запорозька Січ — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Руїна — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Рашизм: Звір з безодні 2023),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Азовські походи (1695—1696),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Малоросійський приказ — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>source ID</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-software.xlsx
@@ -98,46 +98,46 @@
     <t>S0013</t>
   </si>
   <si>
-    <t>tool--5baeca0c-852e-4e6a-a3ea-05904063aa5e</t>
-  </si>
-  <si>
-    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
-  </si>
-  <si>
-    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
-  </si>
-  <si>
-    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
-  </si>
-  <si>
-    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
-  </si>
-  <si>
-    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
-  </si>
-  <si>
-    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
-  </si>
-  <si>
-    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
-  </si>
-  <si>
-    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
-  </si>
-  <si>
-    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
-  </si>
-  <si>
-    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
-  </si>
-  <si>
-    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
-  </si>
-  <si>
-    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
-  </si>
-  <si>
-    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
+    <t>tool--47f86c6e-ebb2-4f00-8483-c5d35824ca66</t>
+  </si>
+  <si>
+    <t>tool--ceb165df-32e3-4d83-bdb6-db5ae496484d</t>
+  </si>
+  <si>
+    <t>tool--c245c447-66cb-48db-b15b-df8d8e0dd436</t>
+  </si>
+  <si>
+    <t>tool--1483b76f-f40e-4689-a9d1-55b8eac05837</t>
+  </si>
+  <si>
+    <t>tool--065f9ef9-fbc6-40da-9537-1f0ba3d48637</t>
+  </si>
+  <si>
+    <t>tool--bc2f8deb-bfa4-4bfe-a514-08eaffbdace0</t>
+  </si>
+  <si>
+    <t>tool--6cb97aa5-9ef0-4ccb-9e82-bbfc1ac6f9dc</t>
+  </si>
+  <si>
+    <t>tool--efbad242-63d3-40cf-9c6a-9ffe1578cc1e</t>
+  </si>
+  <si>
+    <t>tool--2ac13435-bb23-4791-b014-496ba930d1d1</t>
+  </si>
+  <si>
+    <t>tool--2d431e42-ef16-4d1a-9e90-7e5e0ffb410d</t>
+  </si>
+  <si>
+    <t>tool--6a1a7dc9-5d85-444a-b140-04e777c873f0</t>
+  </si>
+  <si>
+    <t>tool--0f891574-2d64-4b40-959a-6822e47af301</t>
+  </si>
+  <si>
+    <t>tool--2632cb38-aa7a-411c-a58d-f5ecef972484</t>
+  </si>
+  <si>
+    <t>tool--f00b45db-5e26-4a45-a418-6af97faa4a4d</t>
   </si>
   <si>
     <t>Верховный тайный совет</t>
@@ -298,7 +298,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Перепис населення Російської імперії (1897),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Історія України — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Історія Донецької області — Вікіпедія 2026)</t>
+    <t>(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Рашизм: Звір з безодні 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Перепис населення Російської імперії (1897),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Російсько-українська війна (з 2014),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія Донецької області — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Всесоюзний референдум про збереження СРСР — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Історія України — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
@@ -310,31 +310,31 @@
     <t>,(Citation: Друга Малоросійська колегія — Вікіпедія 2026),</t>
   </si>
   <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007)</t>
-  </si>
-  <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Киевский синопсис — Википедия 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Російсько-українська війна (з 2014),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русско-турецкая война (1877—1878),(Citation: Польское восстание (1863—1864),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Історія України — Вікіпедія 2026),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Русско-турецкая война (1768—1774),(Citation: Московські статті (1665),(Citation: Переяславські статті (1659),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Листопадове повстання (1830—1831),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Російсько-турецька війна (1806—1812),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Крымская война — Википедия 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Московсько-українська війна (1658—1659),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Запорозька Січ — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Руїна — Вікіпедія 2026),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Історія України — Вікіпедія 2026),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Рашизм: Звір з безодні 2023),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Московські статті (1665),(Citation: Північна війна (1700—1721),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Азовські походи (1695—1696),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Малоросійський приказ — Вікіпедія 2026)</t>
+    <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Смуга осілості — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Крымская война — Википедия 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Русско-турецкая война (1768—1774),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Російсько-турецька війна (1806—1812),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Переяславські статті (1659),(Citation: Русско-турецкая война (1877—1878),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Московські статті (1665),(Citation: Листопадове повстання (1830—1831),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Польское восстание (1863—1864),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Переяславські статті (1659),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Народний рух України — Вікіпедія 2026),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Азовські походи (1695—1696),(Citation: Північна війна (1700—1721),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Московські статті (1665),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -403,22 +403,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
-  </si>
-  <si>
-    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
-  </si>
-  <si>
-    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
-  </si>
-  <si>
-    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
-  </si>
-  <si>
-    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
-  </si>
-  <si>
-    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
+    <t>intrusion-set--00d5aa42-725d-45ea-8815-ccc615a4d517</t>
+  </si>
+  <si>
+    <t>intrusion-set--3fb8da0b-6311-48dc-9b3e-0a6816345b77</t>
+  </si>
+  <si>
+    <t>intrusion-set--1f6d7249-6192-46e5-b1c5-793a60706469</t>
+  </si>
+  <si>
+    <t>intrusion-set--002e0782-6856-438e-bc83-3c5ebbcba18d</t>
+  </si>
+  <si>
+    <t>intrusion-set--f2a7d9cd-c26b-4ff1-a215-41d91c2ede51</t>
+  </si>
+  <si>
+    <t>intrusion-set--13896fcc-2d95-4d93-bb1e-073c354eab10</t>
   </si>
   <si>
     <t>group</t>
@@ -532,106 +532,106 @@
     <t>Провоцирование большевиками восстания рабочих завода «Арсенал» в самом Киеве для оттягивания резервов украинских властей прямо во время наступления красных войск. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>relationship--bb009c88-365d-4fab-bf01-19c7661e62af</t>
-  </si>
-  <si>
-    <t>relationship--77b46dc8-4a63-44dd-9bd7-031969ec253c</t>
-  </si>
-  <si>
-    <t>relationship--5bde57b1-9715-42f1-b049-e06f015a1772</t>
-  </si>
-  <si>
-    <t>relationship--a14a9035-fa57-4d41-89f7-891ac9fcf81f</t>
-  </si>
-  <si>
-    <t>relationship--1c1b685c-3181-4352-b249-432542879ed6</t>
-  </si>
-  <si>
-    <t>relationship--475161f8-6686-424b-9917-db6889a0fcf3</t>
-  </si>
-  <si>
-    <t>relationship--13ac5123-1a57-4b3a-8d5a-662c89bf41a2</t>
-  </si>
-  <si>
-    <t>relationship--f5209d1a-7895-4020-acae-5dc4e5d8bfc0</t>
-  </si>
-  <si>
-    <t>relationship--5ee5526e-96eb-41af-b8b8-c90b91e64049</t>
-  </si>
-  <si>
-    <t>relationship--3be37c13-b9bc-47bb-8653-fa401dabd4e7</t>
-  </si>
-  <si>
-    <t>relationship--b0c2c062-c89e-4085-8716-bad67e98026e</t>
-  </si>
-  <si>
-    <t>relationship--31fd82da-dfa8-42b5-95dd-f168e6627746</t>
-  </si>
-  <si>
-    <t>relationship--2c5e4520-1275-4ab3-a9a8-2e2b1e964c13</t>
-  </si>
-  <si>
-    <t>relationship--b55647cc-a783-4225-b64b-618bc0c73e2b</t>
-  </si>
-  <si>
-    <t>relationship--6014c6c0-0579-4b5e-a854-2e87b36442cf</t>
-  </si>
-  <si>
-    <t>relationship--9c8d906b-4588-4163-b779-c3b8321985df</t>
-  </si>
-  <si>
-    <t>relationship--1419cb9b-276d-4b72-a3f1-6788f5712c97</t>
-  </si>
-  <si>
-    <t>relationship--a0a599d6-96f3-46a9-8021-f95ca90c5c60</t>
-  </si>
-  <si>
-    <t>relationship--422caa87-ac34-4167-80a3-e3f294b52304</t>
-  </si>
-  <si>
-    <t>relationship--d95d1848-9eb8-41a1-9eb4-0dab6d9b048c</t>
-  </si>
-  <si>
-    <t>relationship--c8ddd7ea-ed8e-4c46-8d00-0188061a5430</t>
-  </si>
-  <si>
-    <t>relationship--b4237490-0e8a-46d4-95a6-1cdaa172bcc8</t>
-  </si>
-  <si>
-    <t>relationship--6d106e24-cb8f-42ae-8ea2-c24c3ac66a5e</t>
-  </si>
-  <si>
-    <t>relationship--d3e614da-a65e-49a8-b28c-1bda5c4ff9ad</t>
-  </si>
-  <si>
-    <t>relationship--673fe51c-7945-423e-9767-3b824d79a43f</t>
-  </si>
-  <si>
-    <t>relationship--b4b464b3-2e82-48ba-b3e5-8680a6803204</t>
-  </si>
-  <si>
-    <t>relationship--ec2419f7-91b8-4498-b50c-0deec7e9eed4</t>
-  </si>
-  <si>
-    <t>relationship--62fc2c5e-3c4f-4760-ba3a-320af5a52635</t>
-  </si>
-  <si>
-    <t>relationship--5c3c5267-b7aa-47e8-a640-d413fe3d0e2b</t>
-  </si>
-  <si>
-    <t>relationship--559bac5f-e601-4430-a4d1-3e40065ec036</t>
-  </si>
-  <si>
-    <t>relationship--aaed89ae-ca29-4a00-9e21-1cc9143a649e</t>
-  </si>
-  <si>
-    <t>relationship--acd4d015-7a92-4a60-8741-9e316340e075</t>
-  </si>
-  <si>
-    <t>relationship--3d963d7d-a454-4e0a-9940-35584a671824</t>
-  </si>
-  <si>
-    <t>relationship--e1c4bbc4-90c4-48de-8589-c0a639fef400</t>
+    <t>relationship--da050063-c065-4f64-b603-131c66564b27</t>
+  </si>
+  <si>
+    <t>relationship--7b77da04-ab8c-4853-ba78-ea68f918045f</t>
+  </si>
+  <si>
+    <t>relationship--d968e9cf-bac9-4fb8-bbac-8c2d02c54083</t>
+  </si>
+  <si>
+    <t>relationship--8a7e5e2f-2743-4768-bbc1-d3e89f312afa</t>
+  </si>
+  <si>
+    <t>relationship--daaa48ef-0c36-4443-b4a5-48114ee2269f</t>
+  </si>
+  <si>
+    <t>relationship--769748a7-f54a-4f41-9094-ad4f900591bf</t>
+  </si>
+  <si>
+    <t>relationship--ec87abc6-9641-4378-bc37-f1922bfa6e68</t>
+  </si>
+  <si>
+    <t>relationship--f123e402-c95a-4a58-a035-6769d33fba66</t>
+  </si>
+  <si>
+    <t>relationship--caa25457-ebc1-40b0-a2b4-774edffb669b</t>
+  </si>
+  <si>
+    <t>relationship--3e901e91-7d1a-4367-96d1-10be8c0b2df9</t>
+  </si>
+  <si>
+    <t>relationship--77cbf7e0-4ec3-4601-bfa7-e8e423f7ab0b</t>
+  </si>
+  <si>
+    <t>relationship--2c0a3765-6c13-410f-88d3-4fc78b67c0b4</t>
+  </si>
+  <si>
+    <t>relationship--bec6de6d-8e8d-4b94-a2c9-505039cde2e9</t>
+  </si>
+  <si>
+    <t>relationship--3a1ab7c1-8c43-48bd-94e3-915f6bde530f</t>
+  </si>
+  <si>
+    <t>relationship--68f9fe2a-e37e-44a7-a84f-197229636901</t>
+  </si>
+  <si>
+    <t>relationship--39580415-eb7f-4b71-b66a-b4e8f0df0f55</t>
+  </si>
+  <si>
+    <t>relationship--f49caced-62b5-4b68-b4dd-9fe6a7292e55</t>
+  </si>
+  <si>
+    <t>relationship--58b2abb6-02a7-45b3-8b5f-ec850122407a</t>
+  </si>
+  <si>
+    <t>relationship--d9035eff-e382-4c9d-aabc-937a7a051226</t>
+  </si>
+  <si>
+    <t>relationship--20d559c7-dba2-42fc-99f4-a6edaa1a32d4</t>
+  </si>
+  <si>
+    <t>relationship--6e948f4a-29cd-40a3-8f09-e0e70a92ec4e</t>
+  </si>
+  <si>
+    <t>relationship--0dfe276a-ab5f-4f02-8e44-434fa746e9ae</t>
+  </si>
+  <si>
+    <t>relationship--3f2d01b8-8530-4c17-8d6e-7d42d400a7e2</t>
+  </si>
+  <si>
+    <t>relationship--d9aec82b-c059-4c8a-bdf5-a7db19f9021c</t>
+  </si>
+  <si>
+    <t>relationship--8c5450b9-b74f-4d36-adf4-ac1da91a3111</t>
+  </si>
+  <si>
+    <t>relationship--532c2ae2-b015-410f-8ec4-63524e3e6c9f</t>
+  </si>
+  <si>
+    <t>relationship--dd7f3637-6aab-4fa1-95ad-c7004e880c76</t>
+  </si>
+  <si>
+    <t>relationship--b73f3df6-f349-49a0-85da-c9bb9849bfb0</t>
+  </si>
+  <si>
+    <t>relationship--8a035471-857e-40ba-953b-0aaa72176ee8</t>
+  </si>
+  <si>
+    <t>relationship--2328e2b4-4bc6-4432-afaf-43eaa9f10b9c</t>
+  </si>
+  <si>
+    <t>relationship--9c72f6da-453c-404e-87df-1a6c2b00e71c</t>
+  </si>
+  <si>
+    <t>relationship--8c006b00-a342-47c9-8e1b-2c6e44da94b5</t>
+  </si>
+  <si>
+    <t>relationship--dbd05fa7-67b6-402c-8c1c-1cd01026667b</t>
+  </si>
+  <si>
+    <t>relationship--82dfe3d2-cf42-4e0b-9d66-e20ec755ae3f</t>
   </si>
   <si>
     <t>C0009</t>
@@ -1240,307 +1240,307 @@
     <t>Юридическое поглощение через создание СССР (1922–1924)</t>
   </si>
   <si>
-    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
-  </si>
-  <si>
-    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
-  </si>
-  <si>
-    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
-  </si>
-  <si>
-    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
-  </si>
-  <si>
-    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
-  </si>
-  <si>
-    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
-  </si>
-  <si>
-    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
-  </si>
-  <si>
-    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
-  </si>
-  <si>
-    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
-  </si>
-  <si>
-    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
-  </si>
-  <si>
-    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
-  </si>
-  <si>
-    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
-  </si>
-  <si>
-    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
-  </si>
-  <si>
-    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
-  </si>
-  <si>
-    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
-  </si>
-  <si>
-    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
-  </si>
-  <si>
-    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
-  </si>
-  <si>
-    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
-  </si>
-  <si>
-    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
-  </si>
-  <si>
-    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
-  </si>
-  <si>
-    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
-  </si>
-  <si>
-    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
-  </si>
-  <si>
-    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
-  </si>
-  <si>
-    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
-  </si>
-  <si>
-    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
-  </si>
-  <si>
-    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
-  </si>
-  <si>
-    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
-  </si>
-  <si>
-    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
-  </si>
-  <si>
-    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
-  </si>
-  <si>
-    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
-  </si>
-  <si>
-    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
-  </si>
-  <si>
-    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
-  </si>
-  <si>
-    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
-  </si>
-  <si>
-    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
-  </si>
-  <si>
-    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
-  </si>
-  <si>
-    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
-  </si>
-  <si>
-    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
-  </si>
-  <si>
-    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
-  </si>
-  <si>
-    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
-  </si>
-  <si>
-    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
-  </si>
-  <si>
-    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
-  </si>
-  <si>
-    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
-  </si>
-  <si>
-    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
-  </si>
-  <si>
-    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
-  </si>
-  <si>
-    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
-  </si>
-  <si>
-    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
-  </si>
-  <si>
-    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
-  </si>
-  <si>
-    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
-  </si>
-  <si>
-    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
-  </si>
-  <si>
-    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
-  </si>
-  <si>
-    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
-  </si>
-  <si>
-    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
-  </si>
-  <si>
-    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
-  </si>
-  <si>
-    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
-  </si>
-  <si>
-    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
-  </si>
-  <si>
-    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
-  </si>
-  <si>
-    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
-  </si>
-  <si>
-    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
-  </si>
-  <si>
-    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
-  </si>
-  <si>
-    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
-  </si>
-  <si>
-    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
-  </si>
-  <si>
-    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
-  </si>
-  <si>
-    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
-  </si>
-  <si>
-    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
-  </si>
-  <si>
-    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
-  </si>
-  <si>
-    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
-  </si>
-  <si>
-    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
-  </si>
-  <si>
-    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
-  </si>
-  <si>
-    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
-  </si>
-  <si>
-    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
-  </si>
-  <si>
-    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
-  </si>
-  <si>
-    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
-  </si>
-  <si>
-    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
-  </si>
-  <si>
-    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
-  </si>
-  <si>
-    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
-  </si>
-  <si>
-    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
-  </si>
-  <si>
-    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
-  </si>
-  <si>
-    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
-  </si>
-  <si>
-    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
-  </si>
-  <si>
-    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
-  </si>
-  <si>
-    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
-  </si>
-  <si>
-    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
-  </si>
-  <si>
-    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
-  </si>
-  <si>
-    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
-  </si>
-  <si>
-    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
-  </si>
-  <si>
-    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
-  </si>
-  <si>
-    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
-  </si>
-  <si>
-    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
-  </si>
-  <si>
-    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
-  </si>
-  <si>
-    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
-  </si>
-  <si>
-    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
-  </si>
-  <si>
-    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
-  </si>
-  <si>
-    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
-  </si>
-  <si>
-    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
-  </si>
-  <si>
-    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
-  </si>
-  <si>
-    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
-  </si>
-  <si>
-    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
-  </si>
-  <si>
-    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
-  </si>
-  <si>
-    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
-  </si>
-  <si>
-    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
-  </si>
-  <si>
-    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
+    <t>campaign--beb3c204-bc97-4d59-9de6-ecdb0c1a8fa6</t>
+  </si>
+  <si>
+    <t>campaign--36718563-750c-4243-ac67-2afb9313199c</t>
+  </si>
+  <si>
+    <t>campaign--c0a083ff-f66b-4fe1-bbc2-eaf9c87ecafa</t>
+  </si>
+  <si>
+    <t>campaign--36b6cac5-68cd-44e9-948e-cdadfaeb03c0</t>
+  </si>
+  <si>
+    <t>campaign--931e85ed-d20f-4aab-ad0e-c481f9b6f9a4</t>
+  </si>
+  <si>
+    <t>campaign--aa92e9bb-c0c0-404b-b04e-cf449ba5e39d</t>
+  </si>
+  <si>
+    <t>campaign--618bc33c-2bd3-40a0-aecc-7d7b87050c1b</t>
+  </si>
+  <si>
+    <t>campaign--f62ceaad-15da-4759-8904-81880a93f161</t>
+  </si>
+  <si>
+    <t>campaign--81490a22-d3ad-4dac-a642-e2eba0016b14</t>
+  </si>
+  <si>
+    <t>campaign--4a9d685a-9b20-4f1d-8915-4ada209c8cca</t>
+  </si>
+  <si>
+    <t>campaign--528c16c6-f91f-414a-8371-eab2292b3449</t>
+  </si>
+  <si>
+    <t>campaign--7b330b89-cb3c-4f20-a141-0e7d3be39898</t>
+  </si>
+  <si>
+    <t>campaign--eddeafb4-a875-4655-84a6-c63e89eeefd0</t>
+  </si>
+  <si>
+    <t>campaign--be2b48b0-daea-4dc8-b2be-24ebe5913dc5</t>
+  </si>
+  <si>
+    <t>campaign--7b32e63c-318e-4976-9a47-235504a9ebe1</t>
+  </si>
+  <si>
+    <t>campaign--6f93731b-4153-48bc-902d-f4e0ea897aa8</t>
+  </si>
+  <si>
+    <t>campaign--5d1e342a-8efe-4664-8157-4cc7ed55477a</t>
+  </si>
+  <si>
+    <t>campaign--dd4a2a03-d604-48f7-88b6-5a4fce5d3965</t>
+  </si>
+  <si>
+    <t>campaign--fc8f8fea-2e44-4409-a72b-e75ab314ec8a</t>
+  </si>
+  <si>
+    <t>campaign--f0c6054b-c01a-4747-b587-9903218358b2</t>
+  </si>
+  <si>
+    <t>campaign--2c6e0dec-e346-4ed4-b88f-5711faad6118</t>
+  </si>
+  <si>
+    <t>campaign--17e5ae14-9fa2-4925-bb28-0cdfc14fc1d7</t>
+  </si>
+  <si>
+    <t>campaign--5b639678-3921-474c-8c9e-4015ec9f949c</t>
+  </si>
+  <si>
+    <t>campaign--d1030d85-2e68-49b2-928c-2a14317de1bd</t>
+  </si>
+  <si>
+    <t>campaign--06927989-0878-4b74-9a28-35325dfa70f2</t>
+  </si>
+  <si>
+    <t>campaign--ea29169a-53a3-40d2-bd80-07873f4c7316</t>
+  </si>
+  <si>
+    <t>campaign--561a04bb-a336-4395-b343-c56073b71789</t>
+  </si>
+  <si>
+    <t>campaign--9707df54-95c3-4aa7-b931-57ee1a5c16f6</t>
+  </si>
+  <si>
+    <t>campaign--3dfcbbbc-e0ba-4b67-8bc2-810834ae08b3</t>
+  </si>
+  <si>
+    <t>campaign--f60fcbc2-4c94-4ef8-95b5-44d6aa0b3b8d</t>
+  </si>
+  <si>
+    <t>campaign--12b79d1c-2782-49d5-9a19-c40468968332</t>
+  </si>
+  <si>
+    <t>campaign--72bd14c6-9a8d-429e-8a8f-46ab0d667364</t>
+  </si>
+  <si>
+    <t>campaign--5fa83a2b-9405-4ea4-b37e-cd9d0ce57755</t>
+  </si>
+  <si>
+    <t>campaign--cc574bdf-4d55-47c1-b2fa-6bdb93755eea</t>
+  </si>
+  <si>
+    <t>campaign--27a779bf-b31d-4bbb-ace6-71f927cbde26</t>
+  </si>
+  <si>
+    <t>campaign--61a87e18-b207-448e-ba3a-c2a8d198974b</t>
+  </si>
+  <si>
+    <t>campaign--84ae7b7b-64d5-4093-a6a9-6dfacd6c66bf</t>
+  </si>
+  <si>
+    <t>campaign--67012817-6f85-428b-a010-93c08f2b76da</t>
+  </si>
+  <si>
+    <t>campaign--5dd1d621-c811-42cf-82c2-3406994dfde6</t>
+  </si>
+  <si>
+    <t>campaign--ace5b016-3d27-4b37-b2d2-d556647b00f1</t>
+  </si>
+  <si>
+    <t>campaign--4f18507b-2f69-46a9-85d5-40f17338779f</t>
+  </si>
+  <si>
+    <t>campaign--59f53554-bb3e-47d5-b876-5384f7e36329</t>
+  </si>
+  <si>
+    <t>campaign--5bcf32f4-e373-4f37-9efc-e49505e85e22</t>
+  </si>
+  <si>
+    <t>campaign--0aa91ac6-7a07-4d24-a072-994296a51cfa</t>
+  </si>
+  <si>
+    <t>campaign--9a502692-8621-4955-85ad-e7f7eb03cca2</t>
+  </si>
+  <si>
+    <t>campaign--a2171902-2718-49d1-b854-c8226a719312</t>
+  </si>
+  <si>
+    <t>campaign--592aa280-7cce-445b-b6e9-9abb88c52a90</t>
+  </si>
+  <si>
+    <t>campaign--19a08a71-50bd-429a-be2a-499c11fa5ccc</t>
+  </si>
+  <si>
+    <t>campaign--371756b0-4caf-470c-963c-a9cbaa8ee88b</t>
+  </si>
+  <si>
+    <t>campaign--4b25ef2f-6bb6-4d1d-a732-11a375521f54</t>
+  </si>
+  <si>
+    <t>campaign--a84dbd97-d0f4-4692-a0ab-e9d979d8a010</t>
+  </si>
+  <si>
+    <t>campaign--b767d548-72af-449a-adf8-63595a15dd6e</t>
+  </si>
+  <si>
+    <t>campaign--77beb7ac-80f5-4895-a7ea-b1dd56dacba4</t>
+  </si>
+  <si>
+    <t>campaign--06dfe566-0f1e-46bb-a5dc-ec4aff46135b</t>
+  </si>
+  <si>
+    <t>campaign--0975d9fe-1c4b-49ef-98ef-23d2b4210e88</t>
+  </si>
+  <si>
+    <t>campaign--b63c414e-aa3e-40c9-bb67-1f2d9ee5f71f</t>
+  </si>
+  <si>
+    <t>campaign--5478ddf2-476b-4d6c-a3aa-7096f3d5aca8</t>
+  </si>
+  <si>
+    <t>campaign--3574027e-078d-4e16-8484-b1dbe338ce61</t>
+  </si>
+  <si>
+    <t>campaign--1ddc10f7-4e18-404e-8910-5d8680bf7a82</t>
+  </si>
+  <si>
+    <t>campaign--39aac990-a61c-41dc-b9c5-b18f149b5cf8</t>
+  </si>
+  <si>
+    <t>campaign--3568c587-8fdb-4536-8de4-ebd3429b4cbd</t>
+  </si>
+  <si>
+    <t>campaign--e4ce65e2-37dd-4c97-98b8-c68fd507b4cc</t>
+  </si>
+  <si>
+    <t>campaign--0f94ee1d-db92-4fa1-9026-3308a6277f00</t>
+  </si>
+  <si>
+    <t>campaign--59491b04-3f44-42a9-bc41-7d0f175853c0</t>
+  </si>
+  <si>
+    <t>campaign--e509ef5e-b2d6-4520-8195-26f2931f56ff</t>
+  </si>
+  <si>
+    <t>campaign--dcf07b78-3dce-40f2-8c30-1e73ee27fb0a</t>
+  </si>
+  <si>
+    <t>campaign--e325f77e-16fc-4649-8dd9-ef74d4b8663c</t>
+  </si>
+  <si>
+    <t>campaign--fd91a053-f9b7-4cc1-879c-caa2f8a041f7</t>
+  </si>
+  <si>
+    <t>campaign--f4dffb8c-e664-4427-b25f-8a0f193c7649</t>
+  </si>
+  <si>
+    <t>campaign--e2f24cd2-ae30-4dcc-8c0e-6cbb3a0464a8</t>
+  </si>
+  <si>
+    <t>campaign--a48ef2d9-78c7-4412-830d-dfe17d102cc6</t>
+  </si>
+  <si>
+    <t>campaign--3396a968-9eeb-49ec-8dcd-18ff2d01b35b</t>
+  </si>
+  <si>
+    <t>campaign--02b7be7b-141b-4c27-a0c3-3a43f03219c9</t>
+  </si>
+  <si>
+    <t>campaign--b0acd87c-70ac-4d2d-a36b-2dec78583175</t>
+  </si>
+  <si>
+    <t>campaign--c0720a94-3178-4c69-8054-087ed0662c46</t>
+  </si>
+  <si>
+    <t>campaign--63c55fc1-e70c-4fdd-902a-14d4ca487812</t>
+  </si>
+  <si>
+    <t>campaign--40149032-0db8-4fbd-b5d4-a067b866c148</t>
+  </si>
+  <si>
+    <t>campaign--bfd071be-b1d5-44da-8f9d-e43041680ae7</t>
+  </si>
+  <si>
+    <t>campaign--bd6a4377-7f19-4732-a9f2-a3e0af5594a2</t>
+  </si>
+  <si>
+    <t>campaign--f1f67736-a37e-460d-8b05-49e59aad8ec3</t>
+  </si>
+  <si>
+    <t>campaign--696708cb-0055-44d8-99cb-f7fd2f15f721</t>
+  </si>
+  <si>
+    <t>campaign--2737ed0c-704b-422c-b4bd-d03d60ae1708</t>
+  </si>
+  <si>
+    <t>campaign--5a853b42-811c-495c-8cc3-4e44a8a1725c</t>
+  </si>
+  <si>
+    <t>campaign--87706f0a-efab-41dd-b40e-09d912b278fb</t>
+  </si>
+  <si>
+    <t>campaign--ee040f1e-7348-49a8-994b-429ea4f44ee9</t>
+  </si>
+  <si>
+    <t>campaign--627bf55a-42e0-4287-8113-35f4341ecab6</t>
+  </si>
+  <si>
+    <t>campaign--de98247a-897f-403e-9754-dae2fce2e39b</t>
+  </si>
+  <si>
+    <t>campaign--09020393-e2d9-4947-8e9e-0628160d3e3f</t>
+  </si>
+  <si>
+    <t>campaign--f5d8d5a7-70b7-4fc5-8971-e0eb43a47434</t>
+  </si>
+  <si>
+    <t>campaign--b6a88759-5300-4aaa-b49d-bf2236862685</t>
+  </si>
+  <si>
+    <t>campaign--b0168a30-f171-4142-9634-414781200ed4</t>
+  </si>
+  <si>
+    <t>campaign--c5d71421-e843-4a24-8444-46ebb0ad5b3e</t>
+  </si>
+  <si>
+    <t>campaign--97256eb3-cff9-433b-a6f2-48a15cbd9b9a</t>
+  </si>
+  <si>
+    <t>campaign--0d91cd39-b6e8-4cfe-adb1-cfc73904b0ab</t>
+  </si>
+  <si>
+    <t>campaign--44e766de-62fa-4407-8edc-b12167d3326c</t>
+  </si>
+  <si>
+    <t>campaign--bb6eedd8-fddb-409d-9b1f-c3a68aa615d5</t>
+  </si>
+  <si>
+    <t>campaign--674f47b9-9ec6-4c86-b3b7-63e25a43288e</t>
+  </si>
+  <si>
+    <t>campaign--fb281d58-2cc6-4a74-94c9-102105e35802</t>
+  </si>
+  <si>
+    <t>campaign--a4877dac-0e19-420c-87e8-e72f8806a3a5</t>
+  </si>
+  <si>
+    <t>campaign--1322fb40-8292-41fa-82bb-ea1743b9ce37</t>
+  </si>
+  <si>
+    <t>campaign--dcad1425-9259-44ad-a22e-bb1ba03156cb</t>
   </si>
   <si>
     <t>campaign</t>
@@ -2003,553 +2003,553 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--16144da2-91f9-49e6-917d-a71bbff07b37</t>
-  </si>
-  <si>
-    <t>relationship--9697c005-6797-4bf7-a837-4f028c927ee6</t>
-  </si>
-  <si>
-    <t>relationship--6e404788-5d9d-414b-a956-d54684562ead</t>
-  </si>
-  <si>
-    <t>relationship--2c434e02-6e26-4156-ae31-6b299dae7863</t>
-  </si>
-  <si>
-    <t>relationship--37a22f39-51a3-4b42-8cbf-4682cb984c5f</t>
-  </si>
-  <si>
-    <t>relationship--de3e18c5-8e55-4213-b7a5-016f634f52d6</t>
-  </si>
-  <si>
-    <t>relationship--b294a298-4572-45ba-83cd-6febe20eb9c8</t>
-  </si>
-  <si>
-    <t>relationship--2a87fd2a-b184-456a-9ff3-5287906fb03f</t>
-  </si>
-  <si>
-    <t>relationship--2984ab74-0098-40b3-910a-a4468d5b1140</t>
-  </si>
-  <si>
-    <t>relationship--f455f2ef-5c5e-4c45-ad3f-b7e6496eb027</t>
-  </si>
-  <si>
-    <t>relationship--4bc8e783-3567-4fb8-867d-b2b0591c3676</t>
-  </si>
-  <si>
-    <t>relationship--ae99f88c-b34e-48a8-b884-8751b57831c3</t>
-  </si>
-  <si>
-    <t>relationship--913af001-f7cb-4207-8322-14ef2f4f006b</t>
-  </si>
-  <si>
-    <t>relationship--fcb25d74-cfa2-45a2-af99-29eb0ad4b064</t>
-  </si>
-  <si>
-    <t>relationship--ba3d5ece-0df2-4f39-a0e6-2ab151c4f803</t>
-  </si>
-  <si>
-    <t>relationship--98d13a8f-5671-46ab-98bf-dcee471a7416</t>
-  </si>
-  <si>
-    <t>relationship--6dd55282-c047-46db-b47d-ffef75634f32</t>
-  </si>
-  <si>
-    <t>relationship--6576dbf2-9887-46d4-b7c0-077b0aa6d520</t>
-  </si>
-  <si>
-    <t>relationship--82e78eaa-a5b5-4328-a73f-d51422047701</t>
-  </si>
-  <si>
-    <t>relationship--c407b553-608e-42df-8f20-99867374029b</t>
-  </si>
-  <si>
-    <t>relationship--58cbd296-f428-4f07-9627-ef721bca5e24</t>
-  </si>
-  <si>
-    <t>relationship--4e4c1786-5c5a-49fc-bd5f-4f98209e04a8</t>
-  </si>
-  <si>
-    <t>relationship--3fd82cd0-8553-4535-9d88-2432d8d6c588</t>
-  </si>
-  <si>
-    <t>relationship--1dbbc37e-23d4-44c4-acdc-e3cac17cc385</t>
-  </si>
-  <si>
-    <t>relationship--fbde6f1d-be2f-4e5f-92a5-c9e21f6b00e6</t>
-  </si>
-  <si>
-    <t>relationship--44b541d4-16cd-4697-91ed-8959150b93ea</t>
-  </si>
-  <si>
-    <t>relationship--bc00c803-905b-483d-a214-b756ab179b45</t>
-  </si>
-  <si>
-    <t>relationship--930512ae-f088-4597-bae8-dcc756d386d6</t>
-  </si>
-  <si>
-    <t>relationship--1e3bdd39-f6fd-459b-953c-ddafac2af3ee</t>
-  </si>
-  <si>
-    <t>relationship--6cda8772-c59c-40f6-951e-7203c973239e</t>
-  </si>
-  <si>
-    <t>relationship--26435369-1682-4a9f-a340-a6ff3307ec65</t>
-  </si>
-  <si>
-    <t>relationship--46ba6b14-29ac-4278-b078-f34ba26b1be5</t>
-  </si>
-  <si>
-    <t>relationship--b0380dea-279d-4897-9888-5307871a3acb</t>
-  </si>
-  <si>
-    <t>relationship--ade84795-f059-4866-a09e-37e6ac5adf40</t>
-  </si>
-  <si>
-    <t>relationship--62bee3ce-caad-42e9-b7bd-9c2262a342cc</t>
-  </si>
-  <si>
-    <t>relationship--d7952f2c-eaf9-43a6-a7b0-b46555772b73</t>
-  </si>
-  <si>
-    <t>relationship--3d23f2db-b299-4698-8767-c4d5bc249f9c</t>
-  </si>
-  <si>
-    <t>relationship--51baad2a-4458-43c3-a534-392226563e3e</t>
-  </si>
-  <si>
-    <t>relationship--f125e8d8-5e5f-4821-9e91-21780cd1efd6</t>
-  </si>
-  <si>
-    <t>relationship--c9d89fd2-934d-49d0-bcc6-892b5bc54c05</t>
-  </si>
-  <si>
-    <t>relationship--ce4f2eda-e514-4c3d-8877-f503c4fcee9d</t>
-  </si>
-  <si>
-    <t>relationship--6c0df7e5-7d02-4aeb-961c-dc80d2bb33b6</t>
-  </si>
-  <si>
-    <t>relationship--7dc82937-c2c7-4121-b82f-1b15049d4567</t>
-  </si>
-  <si>
-    <t>relationship--1438c8ef-dd0f-46a1-a329-7a84094089a7</t>
-  </si>
-  <si>
-    <t>relationship--10b591e9-7eed-4d3f-9cb3-261d8bdf56f5</t>
-  </si>
-  <si>
-    <t>relationship--6320ca25-0dec-426b-a89f-1901840d4a9b</t>
-  </si>
-  <si>
-    <t>relationship--cc37dc30-86e3-4e5b-826c-87bc71b2f98b</t>
-  </si>
-  <si>
-    <t>relationship--434be38d-f7c2-4833-98af-4f52da9cc033</t>
-  </si>
-  <si>
-    <t>relationship--58c8f148-2f0b-40dd-9946-4e4b08b5a9e1</t>
-  </si>
-  <si>
-    <t>relationship--6e559c18-f8de-46cc-8a2c-903c7173ba23</t>
-  </si>
-  <si>
-    <t>relationship--7bccdde2-9194-47a0-a92f-44b4e77a8a1b</t>
-  </si>
-  <si>
-    <t>relationship--8cae63fe-5d4f-407d-bbdd-3ffbdacaa5f7</t>
-  </si>
-  <si>
-    <t>relationship--e15f196e-7079-436f-80ff-106dfbfcb050</t>
-  </si>
-  <si>
-    <t>relationship--5818dc97-498b-4db4-821f-eabf92cc0147</t>
-  </si>
-  <si>
-    <t>relationship--a31d3284-f6df-4832-8e81-ca077371c7a0</t>
-  </si>
-  <si>
-    <t>relationship--07d341f1-5e24-4da9-96ed-ceaeec948632</t>
-  </si>
-  <si>
-    <t>relationship--36acbe6c-f5be-48c5-8910-6f4d6a84c5b2</t>
-  </si>
-  <si>
-    <t>relationship--b079861e-56d8-44f5-9e8c-a969b05fd089</t>
-  </si>
-  <si>
-    <t>relationship--878b41f7-4aa2-4254-bda7-45809fbcf30e</t>
-  </si>
-  <si>
-    <t>relationship--05cc6a6d-7c0c-4ec8-babb-4f489f107014</t>
-  </si>
-  <si>
-    <t>relationship--8e01371e-9a5c-4f4e-b109-a7f005b94faa</t>
-  </si>
-  <si>
-    <t>relationship--5081685d-0e81-4e84-b914-876e5723e0b1</t>
-  </si>
-  <si>
-    <t>relationship--9a11a133-cf32-4216-bd62-e8d351e98517</t>
-  </si>
-  <si>
-    <t>relationship--b33a6108-0645-4a98-8bdc-2cfe83bfbd05</t>
-  </si>
-  <si>
-    <t>relationship--bf3b16c7-2687-4e50-b058-2b9980d05443</t>
-  </si>
-  <si>
-    <t>relationship--c67ab420-a3b8-4617-b942-fa34e0df8c81</t>
-  </si>
-  <si>
-    <t>relationship--c8bc29c2-0d05-4b84-b82e-576a60d9ca1b</t>
-  </si>
-  <si>
-    <t>relationship--818b14a7-3bf9-4917-974c-7283e66d21fc</t>
-  </si>
-  <si>
-    <t>relationship--d99f39d0-fb23-460a-a041-4d9557b9b445</t>
-  </si>
-  <si>
-    <t>relationship--f3c6f5e7-4e68-4633-b7d9-e2b35b32bd0d</t>
-  </si>
-  <si>
-    <t>relationship--d28c162f-cc0d-45ef-926b-5ecc38320d78</t>
-  </si>
-  <si>
-    <t>relationship--bf09b1a3-7528-424a-ad44-13d32054a3aa</t>
-  </si>
-  <si>
-    <t>relationship--2f3cdf54-d10f-43ea-8e57-ec386e7a5a04</t>
-  </si>
-  <si>
-    <t>relationship--736363d3-ad9d-49b8-8469-50f98e2ffcc6</t>
-  </si>
-  <si>
-    <t>relationship--7d80956f-0e1d-4804-83c2-3fb5e44342e0</t>
-  </si>
-  <si>
-    <t>relationship--8ed5c2d1-de73-46aa-a16a-aaed5f37518e</t>
-  </si>
-  <si>
-    <t>relationship--332abc6c-519c-49ea-8fdf-4c2ad58c5d30</t>
-  </si>
-  <si>
-    <t>relationship--65ee3d9c-ae09-4e8d-987d-6cc1d219e01f</t>
-  </si>
-  <si>
-    <t>relationship--1bee2722-fd00-4414-b078-719bb1bc13fc</t>
-  </si>
-  <si>
-    <t>relationship--e13a70ac-3b25-4075-bb54-0d44ba465878</t>
-  </si>
-  <si>
-    <t>relationship--29a3ce2b-6be4-44fb-8fae-beef5f0296a1</t>
-  </si>
-  <si>
-    <t>relationship--9c61218c-a3e3-4688-8723-8a681f5d4799</t>
-  </si>
-  <si>
-    <t>relationship--9b31e25d-8cbe-455c-954b-206d112c4a0a</t>
-  </si>
-  <si>
-    <t>relationship--da89423c-a636-491c-b7a6-20300d79e176</t>
-  </si>
-  <si>
-    <t>relationship--65d9dcda-82e0-4983-98d9-09100bf11f69</t>
-  </si>
-  <si>
-    <t>relationship--a66e5426-deea-479c-9b33-48831ef1f74f</t>
-  </si>
-  <si>
-    <t>relationship--8a7f492f-6d0f-48ef-8475-cf6d9343beae</t>
-  </si>
-  <si>
-    <t>relationship--d7cba973-52a5-4ffa-8792-fad9de0f4ff5</t>
-  </si>
-  <si>
-    <t>relationship--66c41619-1a71-4cdf-959c-b20e132a9feb</t>
-  </si>
-  <si>
-    <t>relationship--1c5a2877-55d2-47f0-852c-41cffd9ea9cd</t>
-  </si>
-  <si>
-    <t>relationship--338d5a11-cbad-444b-b042-b4aaae1152ef</t>
-  </si>
-  <si>
-    <t>relationship--15a7a091-9597-443c-9546-c8c0b6f7015e</t>
-  </si>
-  <si>
-    <t>relationship--b397365a-1c8a-4bf6-9323-b3fa37ec8120</t>
-  </si>
-  <si>
-    <t>relationship--0944d14f-213e-42c6-9227-990789faa016</t>
-  </si>
-  <si>
-    <t>relationship--93c54f83-b658-4267-9ebd-1d808cf45f79</t>
-  </si>
-  <si>
-    <t>relationship--83510ac8-d535-4650-8d81-ebdbe8b636d3</t>
-  </si>
-  <si>
-    <t>relationship--834f449c-b379-41ab-8593-fdc8a6f7da85</t>
-  </si>
-  <si>
-    <t>relationship--25bfdfd7-c584-4eee-badb-e362294f2728</t>
-  </si>
-  <si>
-    <t>relationship--6540b8e2-98fe-49f7-8a99-50d9dd1b8a11</t>
-  </si>
-  <si>
-    <t>relationship--ea9fe07e-1615-4dcf-a3bd-33abcf4ffd14</t>
-  </si>
-  <si>
-    <t>relationship--95761fd2-eff3-4bbd-a79a-d47e24029c7f</t>
-  </si>
-  <si>
-    <t>relationship--9ac65c10-b5e4-4ae1-ac04-e2577a4aff40</t>
-  </si>
-  <si>
-    <t>relationship--b8c173ac-8a9e-4765-bb1c-39b1ee53caac</t>
-  </si>
-  <si>
-    <t>relationship--117354e0-cd7d-484e-8756-87c5bb5fcd00</t>
-  </si>
-  <si>
-    <t>relationship--d435d200-8dbb-4172-80cb-ec869208eca5</t>
-  </si>
-  <si>
-    <t>relationship--eff1e690-9246-4cf9-b550-79f17cb29b68</t>
-  </si>
-  <si>
-    <t>relationship--9bae57d2-f5dc-42a0-836b-0f349e4cdc25</t>
-  </si>
-  <si>
-    <t>relationship--0156d507-7b40-45ec-8289-0f4fa5ba6163</t>
-  </si>
-  <si>
-    <t>relationship--33ab6ec3-19cf-4b49-8724-2b4af682af04</t>
-  </si>
-  <si>
-    <t>relationship--e1842498-5a34-4609-8db6-b2f82df3b197</t>
-  </si>
-  <si>
-    <t>relationship--719527aa-6dc8-4a61-a342-91d03a5c2d21</t>
-  </si>
-  <si>
-    <t>relationship--ba2437e9-e819-46a7-bab0-0878dbf9846d</t>
-  </si>
-  <si>
-    <t>relationship--818f6226-9afb-4912-b6a3-b69725ad0e2a</t>
-  </si>
-  <si>
-    <t>relationship--3a49096f-d797-4844-a514-37aadfb14943</t>
-  </si>
-  <si>
-    <t>relationship--a210a033-712a-4265-af86-ce866ebe8502</t>
-  </si>
-  <si>
-    <t>relationship--0e65dd55-8151-4a51-9adb-ad2b722c7b11</t>
-  </si>
-  <si>
-    <t>relationship--36958ad9-6617-44a9-ad62-03aa55bac03a</t>
-  </si>
-  <si>
-    <t>relationship--ace3997d-4e21-4b81-b6d6-147e08c0b0c2</t>
-  </si>
-  <si>
-    <t>relationship--65dfe9e2-f92b-41f5-a8d7-4d0cb775fd3c</t>
-  </si>
-  <si>
-    <t>relationship--57e70d24-0604-4783-99d1-8efa72bc229d</t>
-  </si>
-  <si>
-    <t>relationship--040c9390-eb5e-49cb-b5bf-d96b81a19376</t>
-  </si>
-  <si>
-    <t>relationship--d1bd4886-86ef-4466-a263-446fe6e1866f</t>
-  </si>
-  <si>
-    <t>relationship--f0b97568-130b-464d-8b32-c4d044aab10d</t>
-  </si>
-  <si>
-    <t>relationship--3dc31397-38e8-4bc1-bd09-06e562e88e3e</t>
-  </si>
-  <si>
-    <t>relationship--938ee97f-1383-42f4-a3fb-f79e9c820e3e</t>
-  </si>
-  <si>
-    <t>relationship--76049fb7-5bc2-4c9e-ba0e-297af2a4ef6b</t>
-  </si>
-  <si>
-    <t>relationship--ff825748-c271-4e23-981a-ace5d89e2f0d</t>
-  </si>
-  <si>
-    <t>relationship--c82e0390-57e7-451d-a05b-56a4cc08989b</t>
-  </si>
-  <si>
-    <t>relationship--777a2696-e49b-4777-9f59-3361cf2d959b</t>
-  </si>
-  <si>
-    <t>relationship--8bdae4af-4576-4585-9cc5-e67149a7a200</t>
-  </si>
-  <si>
-    <t>relationship--399137a2-b686-429b-a19e-996acc7a7bdb</t>
-  </si>
-  <si>
-    <t>relationship--78f7ba38-124d-49f4-aed3-9d01c6378d20</t>
-  </si>
-  <si>
-    <t>relationship--8e2c490b-78d0-4915-85f2-227774d6bb35</t>
-  </si>
-  <si>
-    <t>relationship--7d6fed15-cb67-4aeb-ba7e-4a5ac7f66e2e</t>
-  </si>
-  <si>
-    <t>relationship--93000c5d-435d-4b59-9bd9-6d18f4e88428</t>
-  </si>
-  <si>
-    <t>relationship--78cbaae0-d659-4816-9359-5700b0606cdf</t>
-  </si>
-  <si>
-    <t>relationship--ab8e5783-d185-4c0f-a17a-74ad9e6a2395</t>
-  </si>
-  <si>
-    <t>relationship--b2df047b-98d1-45d7-b379-53985bddf1c4</t>
-  </si>
-  <si>
-    <t>relationship--093ff580-0911-4ef5-aaae-92411c9b6597</t>
-  </si>
-  <si>
-    <t>relationship--16ee1bba-6e3c-440b-ba1f-56293093ae00</t>
-  </si>
-  <si>
-    <t>relationship--b884c378-1ffb-4f35-9e95-278a0657ecb7</t>
-  </si>
-  <si>
-    <t>relationship--f45365a5-32b0-417c-95f2-19c2f90abf3f</t>
-  </si>
-  <si>
-    <t>relationship--fbc3460b-ad11-409e-8859-f19a4ebe8d2e</t>
-  </si>
-  <si>
-    <t>relationship--d0393c1a-f522-4c8a-b58c-a9946069de19</t>
-  </si>
-  <si>
-    <t>relationship--155f9979-73ec-4eba-8808-38de97758784</t>
-  </si>
-  <si>
-    <t>relationship--f85f0758-4c57-4e59-a2b0-dd5977a28769</t>
-  </si>
-  <si>
-    <t>relationship--cc9b386b-845a-4409-a53c-e88fe3165ca7</t>
-  </si>
-  <si>
-    <t>relationship--c02574e7-28f8-4149-9e60-de548f2b2739</t>
-  </si>
-  <si>
-    <t>relationship--c70d52db-bc94-4b2e-af45-20f3874bfedd</t>
-  </si>
-  <si>
-    <t>relationship--e4d5e664-a09e-41aa-8901-163d02b7287b</t>
-  </si>
-  <si>
-    <t>relationship--3b3277ba-6e98-4c8e-8b72-d65d2c00ae61</t>
-  </si>
-  <si>
-    <t>relationship--190fb4f5-b465-4775-9528-46d207d120b2</t>
-  </si>
-  <si>
-    <t>relationship--12db5486-053c-48ed-bb49-48b1e4b11391</t>
-  </si>
-  <si>
-    <t>relationship--fc4c3558-5f44-4a25-898a-91cd7a53e0c4</t>
-  </si>
-  <si>
-    <t>relationship--32fbbc5a-d409-4e61-9a20-e1c8ef9a9f42</t>
-  </si>
-  <si>
-    <t>relationship--443f6959-879a-43a2-ae33-c42f99cf5108</t>
-  </si>
-  <si>
-    <t>relationship--63d649b8-b431-413e-b07d-eca5e0019b2a</t>
-  </si>
-  <si>
-    <t>relationship--8302cd38-5016-42ed-accb-70cdb1d2996e</t>
-  </si>
-  <si>
-    <t>relationship--461e13fb-702e-42e7-91b5-f27c6db3ea70</t>
-  </si>
-  <si>
-    <t>relationship--b85d0c7b-f276-4a67-a101-da016bce172a</t>
-  </si>
-  <si>
-    <t>relationship--b0d665a3-7b3c-4aa3-9687-a3a5368ac34e</t>
-  </si>
-  <si>
-    <t>relationship--3101592e-1242-464d-adcb-9c68c43f6ac1</t>
-  </si>
-  <si>
-    <t>relationship--6e72e46e-9f47-43db-9851-59d899089853</t>
-  </si>
-  <si>
-    <t>relationship--d872ba7d-f1bd-4e7d-83cb-4237e5a6ccae</t>
-  </si>
-  <si>
-    <t>relationship--205a45c2-7248-43c9-8fbc-b25eb7af9d3e</t>
-  </si>
-  <si>
-    <t>relationship--4b2a8dc7-2b7b-42ab-90c2-c202d6c481e9</t>
-  </si>
-  <si>
-    <t>relationship--bc9a8aa8-b287-4ec4-bb2d-5f64eadcc530</t>
-  </si>
-  <si>
-    <t>relationship--fa65970c-ac67-4d39-aaf4-cd3c7bbbadcd</t>
-  </si>
-  <si>
-    <t>relationship--b781b174-17d4-41fa-879e-962fa3c6472e</t>
-  </si>
-  <si>
-    <t>relationship--ec58069d-2af0-4181-bac9-4dddda88c28c</t>
-  </si>
-  <si>
-    <t>relationship--f8ae12cf-66ec-4c01-a250-46bb97f99c7d</t>
-  </si>
-  <si>
-    <t>relationship--6e8f3632-6158-4971-bf6c-f6b75abaa66d</t>
-  </si>
-  <si>
-    <t>relationship--3d819923-9d97-4a8b-a67c-30fde21645b9</t>
-  </si>
-  <si>
-    <t>relationship--f3e7964d-4204-43d9-95ba-a61a39073b86</t>
-  </si>
-  <si>
-    <t>relationship--a9a82add-18b6-4428-b7d4-a07995c91849</t>
-  </si>
-  <si>
-    <t>relationship--8df00cdb-e745-4f6f-b241-b40ee4cad23c</t>
-  </si>
-  <si>
-    <t>relationship--4f13473b-9a37-4531-b782-850ced97e89d</t>
-  </si>
-  <si>
-    <t>relationship--8b6fa31a-3839-49f7-9e18-677cc43b927d</t>
-  </si>
-  <si>
-    <t>relationship--2fb417b5-205b-4b9f-98fc-c9db2c7172b3</t>
-  </si>
-  <si>
-    <t>relationship--24a70091-a353-470d-81e3-cf75b2979c7c</t>
-  </si>
-  <si>
-    <t>relationship--63722a18-6f07-4a93-8e38-135c8fbcbb56</t>
-  </si>
-  <si>
-    <t>relationship--d43afa20-2d6c-47c9-abbb-fba45f539dc7</t>
-  </si>
-  <si>
-    <t>relationship--e513611f-dbb7-41ad-8e96-eeab94495952</t>
+    <t>relationship--9fb1dadb-6d3f-40e5-9828-73388e0638c5</t>
+  </si>
+  <si>
+    <t>relationship--faadc597-9690-4e02-a5ba-d30fa2c1a6ff</t>
+  </si>
+  <si>
+    <t>relationship--72fd4507-3c2b-4d2d-936d-115eb2db082e</t>
+  </si>
+  <si>
+    <t>relationship--14e5019a-ff6b-4d16-843d-f230c8b31449</t>
+  </si>
+  <si>
+    <t>relationship--07b1fe99-cf2a-4dfa-895b-1706b47ac0a8</t>
+  </si>
+  <si>
+    <t>relationship--d959c266-b1b0-4028-a8f5-588c9ac8d808</t>
+  </si>
+  <si>
+    <t>relationship--ddd78385-2e5b-4bc4-87c9-296835aba967</t>
+  </si>
+  <si>
+    <t>relationship--c6c2ecfa-e336-40b9-8a61-c559493ba53a</t>
+  </si>
+  <si>
+    <t>relationship--c1f2c61c-e583-4a90-bc1e-48c37ac7da80</t>
+  </si>
+  <si>
+    <t>relationship--a5bdba47-602d-4c72-add1-e2b9d356a805</t>
+  </si>
+  <si>
+    <t>relationship--0d4ad55d-27c9-4b5f-94b4-9f1cd82ded45</t>
+  </si>
+  <si>
+    <t>relationship--d7d13c19-848b-4855-a16b-990dfd4f1937</t>
+  </si>
+  <si>
+    <t>relationship--1d09545a-5099-447a-bf44-bbd866ca616c</t>
+  </si>
+  <si>
+    <t>relationship--1d79dbe3-a334-4517-88c2-d23da8df8638</t>
+  </si>
+  <si>
+    <t>relationship--a1bca3ae-9153-4286-bc34-699d4f20263d</t>
+  </si>
+  <si>
+    <t>relationship--d2759f49-0558-4cfc-9e2e-b70723a49996</t>
+  </si>
+  <si>
+    <t>relationship--77575e2e-6811-4cb4-9f81-5f599ef84f1c</t>
+  </si>
+  <si>
+    <t>relationship--76fa5b1e-ed9e-4086-a62f-bab667b127e8</t>
+  </si>
+  <si>
+    <t>relationship--9150447e-d6af-4287-b6b5-25ef90d0af2f</t>
+  </si>
+  <si>
+    <t>relationship--c6ec71c6-3d86-44d4-9d8d-d78b780fd5f6</t>
+  </si>
+  <si>
+    <t>relationship--9a03d005-9028-480c-ab2b-0df5fdfb0854</t>
+  </si>
+  <si>
+    <t>relationship--a3f9d96a-79a6-4d08-88de-f7f3e0494318</t>
+  </si>
+  <si>
+    <t>relationship--d5f1256b-e1a5-47d7-9825-17316c748a8a</t>
+  </si>
+  <si>
+    <t>relationship--c6dea6b1-feee-445b-bb03-35e0d8624150</t>
+  </si>
+  <si>
+    <t>relationship--9c8be662-685e-422b-8108-44f148dfaaff</t>
+  </si>
+  <si>
+    <t>relationship--e6b9443b-b2e7-42a4-b3c2-578e0cc061e8</t>
+  </si>
+  <si>
+    <t>relationship--bf022f1e-0e47-405a-8aab-9d70097d29ac</t>
+  </si>
+  <si>
+    <t>relationship--7702c830-5d58-4a9d-a1fb-07080c1fbc70</t>
+  </si>
+  <si>
+    <t>relationship--741d6d94-565a-4e73-b84b-30b951e84b9b</t>
+  </si>
+  <si>
+    <t>relationship--c7d2ac6d-d1aa-406f-87f9-d25f3aca9d54</t>
+  </si>
+  <si>
+    <t>relationship--88066d09-6cab-4c27-aaf4-714d7e357d7d</t>
+  </si>
+  <si>
+    <t>relationship--aaff9a45-eb22-419c-af24-6a60e392177b</t>
+  </si>
+  <si>
+    <t>relationship--cf6222ed-8e03-4ff2-be24-4bcdf38811d6</t>
+  </si>
+  <si>
+    <t>relationship--3650c411-4a6d-4fa6-bdc9-037fb6df7aa9</t>
+  </si>
+  <si>
+    <t>relationship--35a1ea74-eb63-499c-93e8-daf6bae1e192</t>
+  </si>
+  <si>
+    <t>relationship--a2c9cd1e-711b-4a2c-84f4-3ceae2afbc2b</t>
+  </si>
+  <si>
+    <t>relationship--340c9070-b776-42cc-a324-99b3409376e8</t>
+  </si>
+  <si>
+    <t>relationship--91da6122-40ff-4c06-a298-53a9b6dee773</t>
+  </si>
+  <si>
+    <t>relationship--d2530cd3-a018-4ab3-b89d-8976f20519d2</t>
+  </si>
+  <si>
+    <t>relationship--e84d1b2e-8258-49f2-98e4-2c0e785f8c57</t>
+  </si>
+  <si>
+    <t>relationship--c6c9a988-3680-4158-a714-1e9a24679356</t>
+  </si>
+  <si>
+    <t>relationship--5f7f4377-1e63-4127-bd77-30d1861c64ed</t>
+  </si>
+  <si>
+    <t>relationship--d0ac3428-6e0b-4691-945e-5f99e34af693</t>
+  </si>
+  <si>
+    <t>relationship--26594c8f-2a5c-4f8b-8353-1da9705fae3a</t>
+  </si>
+  <si>
+    <t>relationship--34a0151e-d7cb-4e0e-882e-b82ab87be9d9</t>
+  </si>
+  <si>
+    <t>relationship--41446641-4bde-4905-a1a3-d60c781673d7</t>
+  </si>
+  <si>
+    <t>relationship--e059c3d4-b998-477f-a02c-b99161060103</t>
+  </si>
+  <si>
+    <t>relationship--6e1474bc-6f09-48ee-a450-c3326d5040b4</t>
+  </si>
+  <si>
+    <t>relationship--b0f60820-9214-416f-a0ea-c7612fc8781a</t>
+  </si>
+  <si>
+    <t>relationship--e19c72c6-2939-4141-8960-26d74f226e49</t>
+  </si>
+  <si>
+    <t>relationship--8819d183-102a-4e3d-ae51-28d6a089cad6</t>
+  </si>
+  <si>
+    <t>relationship--04608265-f9e7-4075-8fa8-bb91cb94eb38</t>
+  </si>
+  <si>
+    <t>relationship--35148382-8ec7-42f8-8525-9f9604c75346</t>
+  </si>
+  <si>
+    <t>relationship--ba17a4a0-3889-4ca1-a103-2495b5a5fb1e</t>
+  </si>
+  <si>
+    <t>relationship--21485f15-215c-4125-91f6-3c442a9ae40d</t>
+  </si>
+  <si>
+    <t>relationship--db01fe14-080e-4fd7-b0fd-cd75c58e206c</t>
+  </si>
+  <si>
+    <t>relationship--eec52f79-e724-4c09-9db9-dcca3161c6fe</t>
+  </si>
+  <si>
+    <t>relationship--632fa03d-06cd-4ffe-ad01-0c672bd98660</t>
+  </si>
+  <si>
+    <t>relationship--09ad1b11-635e-49f6-8cd7-b4de49b53698</t>
+  </si>
+  <si>
+    <t>relationship--d8a3c857-d0bb-4d39-a8fd-a55df4fb6f08</t>
+  </si>
+  <si>
+    <t>relationship--f34acf31-e727-4bf1-b655-cbbd2faef950</t>
+  </si>
+  <si>
+    <t>relationship--e5f194bb-39f2-4186-82b0-210962e5e799</t>
+  </si>
+  <si>
+    <t>relationship--ff90a4e4-17cf-44a1-bd7f-1a76e7edcf86</t>
+  </si>
+  <si>
+    <t>relationship--f7a8f5a2-318a-44fa-b6d2-536c814b4f5b</t>
+  </si>
+  <si>
+    <t>relationship--55dc7c77-cc95-4a32-a1b4-6a865cb6f5d8</t>
+  </si>
+  <si>
+    <t>relationship--c6939d44-b491-45dc-8fa7-45ea8e05af9a</t>
+  </si>
+  <si>
+    <t>relationship--4025e60f-0e56-49b8-9907-0055c8f3419f</t>
+  </si>
+  <si>
+    <t>relationship--9be091bc-db4a-47ad-96a4-9e4710810823</t>
+  </si>
+  <si>
+    <t>relationship--b47053d1-e25b-4635-ae65-cc69b4229945</t>
+  </si>
+  <si>
+    <t>relationship--41e40288-caf3-40b0-a859-df5430a609c2</t>
+  </si>
+  <si>
+    <t>relationship--e244100a-909b-45af-99f6-04308fb91caa</t>
+  </si>
+  <si>
+    <t>relationship--a06e1699-b65d-4e31-8b76-7b1dbf1dabdc</t>
+  </si>
+  <si>
+    <t>relationship--a70f0f15-7d61-4e63-b31c-ab51f344588f</t>
+  </si>
+  <si>
+    <t>relationship--96df3b0e-fb37-47b2-9edf-82d2e274c965</t>
+  </si>
+  <si>
+    <t>relationship--4f07ca2c-3292-4bac-a169-ea3e60408256</t>
+  </si>
+  <si>
+    <t>relationship--38ac0aef-c565-4e73-a23e-8696f1040842</t>
+  </si>
+  <si>
+    <t>relationship--049bf566-251d-4c99-af14-48b3ee0ebe41</t>
+  </si>
+  <si>
+    <t>relationship--98ce83a2-f7c3-435a-9adb-f2d2dee7eb22</t>
+  </si>
+  <si>
+    <t>relationship--a1695f95-b193-4696-ae76-65301c5b3d27</t>
+  </si>
+  <si>
+    <t>relationship--7d6c88ef-01a9-462f-95fd-f1dc1d3df7e1</t>
+  </si>
+  <si>
+    <t>relationship--9cdc9871-8cc2-4457-9e4c-72a43fd878ba</t>
+  </si>
+  <si>
+    <t>relationship--35424d8e-8166-46ea-a958-1fec4d058695</t>
+  </si>
+  <si>
+    <t>relationship--97002d57-dd28-4666-8ef1-4b61dc5e54b4</t>
+  </si>
+  <si>
+    <t>relationship--fefe23e4-ea26-46f1-a365-c1a019f37d95</t>
+  </si>
+  <si>
+    <t>relationship--c8004c66-79e1-4dd2-a19d-44a3fe247aea</t>
+  </si>
+  <si>
+    <t>relationship--4915ec10-40da-49e7-9b0f-1add01f70bdf</t>
+  </si>
+  <si>
+    <t>relationship--1ce06a85-eaf8-498f-b20a-ecf3de66c2cb</t>
+  </si>
+  <si>
+    <t>relationship--452d1e7d-adff-4c97-8329-6fbba68fda8e</t>
+  </si>
+  <si>
+    <t>relationship--91146e4f-fac8-45d8-b415-e2876986f3b3</t>
+  </si>
+  <si>
+    <t>relationship--293e00a2-cd1f-4bf2-b557-f50c23fa2685</t>
+  </si>
+  <si>
+    <t>relationship--4a3f366a-cafb-46ce-9732-dfaad5dc1080</t>
+  </si>
+  <si>
+    <t>relationship--1b00a3a5-ddb9-450f-b32d-9fa28a1ba009</t>
+  </si>
+  <si>
+    <t>relationship--403c2394-0447-41aa-807f-02ab159f61e1</t>
+  </si>
+  <si>
+    <t>relationship--42a54b0e-32d0-446f-9fe6-bf079ba926e6</t>
+  </si>
+  <si>
+    <t>relationship--2448a68a-67d6-4494-9f1e-7da4ed9ef6d5</t>
+  </si>
+  <si>
+    <t>relationship--f2530ee9-11cb-4f72-a0e0-84693e6c07d1</t>
+  </si>
+  <si>
+    <t>relationship--6ebfd71f-80ca-4024-a33e-d411f93ba1b6</t>
+  </si>
+  <si>
+    <t>relationship--7356fd91-b6e6-4b7b-ab3d-cc2da25f2a3b</t>
+  </si>
+  <si>
+    <t>relationship--a0a4b16a-1fa2-47d0-ad24-562a63babe3b</t>
+  </si>
+  <si>
+    <t>relationship--9d590f0d-46e1-4cf8-a6a3-974b7a9fc32f</t>
+  </si>
+  <si>
+    <t>relationship--70660c56-d98d-4dab-9887-8a125e1fd558</t>
+  </si>
+  <si>
+    <t>relationship--3080fecb-4449-427e-b825-562b1f5429c4</t>
+  </si>
+  <si>
+    <t>relationship--ff7e7411-7631-436d-85d1-7d07c93e2e2f</t>
+  </si>
+  <si>
+    <t>relationship--8421111a-1bdd-496a-b9c9-a3d9eb196e5c</t>
+  </si>
+  <si>
+    <t>relationship--2cac0497-8b82-44d9-8cae-bb2b20c53828</t>
+  </si>
+  <si>
+    <t>relationship--5baf6c1f-8702-42f6-91ef-e7f9239b0d3c</t>
+  </si>
+  <si>
+    <t>relationship--fd6499be-35d9-403b-ad6d-55ff783b487d</t>
+  </si>
+  <si>
+    <t>relationship--ecaf9231-d8c9-4f83-84fb-2f4dcffef950</t>
+  </si>
+  <si>
+    <t>relationship--ff47682d-e1c3-4d0f-9617-2db64d5336fe</t>
+  </si>
+  <si>
+    <t>relationship--ff18bf3f-c203-4923-97be-647c6141e68d</t>
+  </si>
+  <si>
+    <t>relationship--112a1ef7-9aed-4cb1-9671-8e46450a4e10</t>
+  </si>
+  <si>
+    <t>relationship--2b6a4902-65af-4973-8a68-d99bda767670</t>
+  </si>
+  <si>
+    <t>relationship--33895acb-8526-4c63-9529-a24f57c7c984</t>
+  </si>
+  <si>
+    <t>relationship--2ef067f2-77a6-405d-8d27-b2b32780d80e</t>
+  </si>
+  <si>
+    <t>relationship--fa88292b-99c1-4074-8a12-d4964d7d65c7</t>
+  </si>
+  <si>
+    <t>relationship--3a3faa8b-465b-4954-ada2-7d65907f0157</t>
+  </si>
+  <si>
+    <t>relationship--9ad1973f-73c0-4f6c-9df5-03418c10a146</t>
+  </si>
+  <si>
+    <t>relationship--81aa0cdd-b1c5-480a-a8f6-ec07645cca95</t>
+  </si>
+  <si>
+    <t>relationship--c65136e6-32f9-4434-ba30-65679f00fc27</t>
+  </si>
+  <si>
+    <t>relationship--9c13b868-1879-4e01-a998-cc937879d3b0</t>
+  </si>
+  <si>
+    <t>relationship--4d73be4d-233e-422f-b20d-8ee7e0901aff</t>
+  </si>
+  <si>
+    <t>relationship--c8e02b88-534a-41a7-aeb0-682d58a4ec42</t>
+  </si>
+  <si>
+    <t>relationship--ceee9957-dcf0-4fad-86ba-3a5fc064f2d8</t>
+  </si>
+  <si>
+    <t>relationship--25925782-3eda-4d7a-a5ca-4038cce94ddc</t>
+  </si>
+  <si>
+    <t>relationship--bf380855-3541-4e77-85a2-beb798452793</t>
+  </si>
+  <si>
+    <t>relationship--bdee1210-8da5-42de-9f93-dd8ddc0dac63</t>
+  </si>
+  <si>
+    <t>relationship--efa244d7-20b8-4846-9556-ee08d55b2997</t>
+  </si>
+  <si>
+    <t>relationship--a5de4eea-da1f-4185-8d88-f065a22018e2</t>
+  </si>
+  <si>
+    <t>relationship--c8b2bfe4-d4bb-450c-a211-39c476dd0960</t>
+  </si>
+  <si>
+    <t>relationship--c1a17585-0bfd-4643-a957-a7e53c1e8710</t>
+  </si>
+  <si>
+    <t>relationship--73a37c72-9eb2-496b-9290-5ef2a44a8e8b</t>
+  </si>
+  <si>
+    <t>relationship--2848a711-a9aa-4fd1-a298-90b8618ad5ef</t>
+  </si>
+  <si>
+    <t>relationship--208134a5-8f6b-48c2-9631-bf2bb5e2f2b5</t>
+  </si>
+  <si>
+    <t>relationship--a7c80b03-bfdc-4680-bcf3-8df4963526ec</t>
+  </si>
+  <si>
+    <t>relationship--48797067-a677-4757-95f7-694978fb3ad0</t>
+  </si>
+  <si>
+    <t>relationship--b7032820-cc1f-411a-9669-4e033cb6c4bf</t>
+  </si>
+  <si>
+    <t>relationship--de6ac0b8-7290-49c8-a9f8-254ae4bfef2b</t>
+  </si>
+  <si>
+    <t>relationship--7b4285f3-5912-41c8-9155-6b9a1b841284</t>
+  </si>
+  <si>
+    <t>relationship--8d0cfd35-f4ff-4fb4-980e-20eb758d419b</t>
+  </si>
+  <si>
+    <t>relationship--6b17b7f1-9d6a-401a-87be-793855e793c7</t>
+  </si>
+  <si>
+    <t>relationship--0246d310-2efa-420b-a3cc-d612374fc588</t>
+  </si>
+  <si>
+    <t>relationship--944a2456-8e29-4ec5-8410-de866f447038</t>
+  </si>
+  <si>
+    <t>relationship--8a37370b-0106-4b2b-9b9e-ba64341ae42f</t>
+  </si>
+  <si>
+    <t>relationship--b89c972a-724a-4910-91cd-2c62b807d8e0</t>
+  </si>
+  <si>
+    <t>relationship--9935ac01-8b31-4f42-b729-5baf24ade44e</t>
+  </si>
+  <si>
+    <t>relationship--6086eac4-0f55-40d6-937c-d1bbbe652594</t>
+  </si>
+  <si>
+    <t>relationship--0c3af4a9-1da2-42fc-9a83-fee6a88d0896</t>
+  </si>
+  <si>
+    <t>relationship--fbec3e9a-9a8c-4b13-8dff-266db118db49</t>
+  </si>
+  <si>
+    <t>relationship--56fa56bc-79c0-406c-80c3-f2c7b0db929c</t>
+  </si>
+  <si>
+    <t>relationship--b1a47e0d-a395-4c14-96b4-08aff6329358</t>
+  </si>
+  <si>
+    <t>relationship--dc9c99f8-0b05-49b3-be6d-3d12ac743657</t>
+  </si>
+  <si>
+    <t>relationship--37195b48-a88f-4565-823c-fae4c1e37bec</t>
+  </si>
+  <si>
+    <t>relationship--0c9fa89f-5a20-4f2b-8fcf-e23197d6c524</t>
+  </si>
+  <si>
+    <t>relationship--a20788de-d039-4100-9b35-371cf615dfc8</t>
+  </si>
+  <si>
+    <t>relationship--d167789c-26a8-4b0a-a8f4-09984513c2d2</t>
+  </si>
+  <si>
+    <t>relationship--690bea0d-d155-4ef5-bd33-ba648e71f4a0</t>
+  </si>
+  <si>
+    <t>relationship--1b68bf01-b795-40fd-9d77-649764dc2945</t>
+  </si>
+  <si>
+    <t>relationship--7d3b7623-8648-400d-a0e4-aaf5e3e53dcf</t>
+  </si>
+  <si>
+    <t>relationship--40215d2f-18b6-41c9-95b2-31b3e5970c19</t>
+  </si>
+  <si>
+    <t>relationship--8c21bd6d-214b-4ed6-bfe2-04d78b11e191</t>
+  </si>
+  <si>
+    <t>relationship--49563f40-ffd6-41dc-bb16-74fba6e3ea07</t>
+  </si>
+  <si>
+    <t>relationship--d930801b-253c-4b70-9f42-ee2032047b33</t>
+  </si>
+  <si>
+    <t>relationship--5eaf5c87-ec9a-4b27-b182-5f950c02981d</t>
+  </si>
+  <si>
+    <t>relationship--42b4181c-692e-401a-a4c6-bfc6efe48d5b</t>
+  </si>
+  <si>
+    <t>relationship--99d520c9-1182-4b76-9201-fc543c885216</t>
+  </si>
+  <si>
+    <t>relationship--7044da1c-80ac-48a7-a764-7df52f7ecb7e</t>
+  </si>
+  <si>
+    <t>relationship--3c558bdf-09f9-4ef8-bd2d-9bb126ec3eff</t>
+  </si>
+  <si>
+    <t>relationship--66bde137-c075-40b9-ab52-b5cf9b3e8daf</t>
+  </si>
+  <si>
+    <t>relationship--7c23580d-69a5-4956-b5d6-cef981a93327</t>
+  </si>
+  <si>
+    <t>relationship--55760606-a78c-443c-b4e1-2fd35e1cde08</t>
+  </si>
+  <si>
+    <t>relationship--57734d21-89fc-4c80-89ab-e7211fcd5744</t>
+  </si>
+  <si>
+    <t>relationship--4fb15e85-ef3d-45ed-8097-602f89e7f66a</t>
+  </si>
+  <si>
+    <t>relationship--0b180d62-3450-4a18-a566-2b95d5570e9b</t>
+  </si>
+  <si>
+    <t>relationship--08e2b7fc-70f5-4b8b-9c5f-6f3f6ca45f95</t>
+  </si>
+  <si>
+    <t>relationship--29e15874-779e-457c-a3b0-57f3d22aa4c5</t>
+  </si>
+  <si>
+    <t>relationship--8d5fc67e-19cf-443d-a625-90faafa8b071</t>
+  </si>
+  <si>
+    <t>relationship--86273ea8-f37b-405b-a645-7483ef63632b</t>
+  </si>
+  <si>
+    <t>relationship--1e3b664b-31cd-4d9f-82ea-a61374a63058</t>
+  </si>
+  <si>
+    <t>relationship--b66acb93-03aa-4297-a817-296072208092</t>
+  </si>
+  <si>
+    <t>relationship--ac5e90cf-bc78-41d1-8ca3-537b815bc474</t>
+  </si>
+  <si>
+    <t>relationship--9639eada-10de-47b2-a413-3ee0c7801f8f</t>
+  </si>
+  <si>
+    <t>relationship--74bb8abe-dd1b-435f-8c64-e019caa81eb5</t>
+  </si>
+  <si>
+    <t>relationship--64c443e1-c8d4-4535-bccd-3a09aa043086</t>
   </si>
   <si>
     <t>T0030</t>
@@ -3050,253 +3050,253 @@
     <t>Спонсирование внутреннего экстремизма и радикалов</t>
   </si>
   <si>
-    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
-  </si>
-  <si>
-    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
-  </si>
-  <si>
-    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
-  </si>
-  <si>
-    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
-  </si>
-  <si>
-    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
-  </si>
-  <si>
-    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
-  </si>
-  <si>
-    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
-  </si>
-  <si>
-    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
-  </si>
-  <si>
-    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
-  </si>
-  <si>
-    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
-  </si>
-  <si>
-    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
-  </si>
-  <si>
-    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
-  </si>
-  <si>
-    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
-  </si>
-  <si>
-    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
-  </si>
-  <si>
-    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
-  </si>
-  <si>
-    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
-  </si>
-  <si>
-    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
-  </si>
-  <si>
-    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
-  </si>
-  <si>
-    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
-  </si>
-  <si>
-    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
-  </si>
-  <si>
-    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
-  </si>
-  <si>
-    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
-  </si>
-  <si>
-    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
-  </si>
-  <si>
-    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
-  </si>
-  <si>
-    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
-  </si>
-  <si>
-    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
-  </si>
-  <si>
-    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
-  </si>
-  <si>
-    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
-  </si>
-  <si>
-    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
-  </si>
-  <si>
-    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
-  </si>
-  <si>
-    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
-  </si>
-  <si>
-    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
-  </si>
-  <si>
-    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
-  </si>
-  <si>
-    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
-  </si>
-  <si>
-    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
-  </si>
-  <si>
-    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
-  </si>
-  <si>
-    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
-  </si>
-  <si>
-    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
-  </si>
-  <si>
-    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
-  </si>
-  <si>
-    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
-  </si>
-  <si>
-    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
-  </si>
-  <si>
-    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
-  </si>
-  <si>
-    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
-  </si>
-  <si>
-    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
-  </si>
-  <si>
-    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
-  </si>
-  <si>
-    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
-  </si>
-  <si>
-    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
-  </si>
-  <si>
-    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
-  </si>
-  <si>
-    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
-  </si>
-  <si>
-    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
-  </si>
-  <si>
-    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
-  </si>
-  <si>
-    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
-  </si>
-  <si>
-    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
-  </si>
-  <si>
-    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
-  </si>
-  <si>
-    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
-  </si>
-  <si>
-    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
-  </si>
-  <si>
-    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
-  </si>
-  <si>
-    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
-  </si>
-  <si>
-    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
-  </si>
-  <si>
-    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
-  </si>
-  <si>
-    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
-  </si>
-  <si>
-    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
-  </si>
-  <si>
-    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
+    <t>attack-pattern--71fb05ba-3eab-4f5c-ba49-a67390e5fc13</t>
+  </si>
+  <si>
+    <t>attack-pattern--49394ec7-2785-4aca-9975-684937954136</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea37d3cc-2d42-45db-bad0-d7012841e93d</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d1eb227-fa81-4405-a0da-241f20f31dea</t>
+  </si>
+  <si>
+    <t>attack-pattern--f578e2ce-75c5-4a8c-8d47-63ce9a9138c0</t>
+  </si>
+  <si>
+    <t>attack-pattern--b99f4011-58e6-451b-81a1-1ce712a80a70</t>
+  </si>
+  <si>
+    <t>attack-pattern--d974ffeb-b434-47fa-9665-cff3eb08afd7</t>
+  </si>
+  <si>
+    <t>attack-pattern--eb4e21e3-74e1-4c36-9847-f819d0da7468</t>
+  </si>
+  <si>
+    <t>attack-pattern--9482f472-eefe-4b92-b476-a9b5f3b343ff</t>
+  </si>
+  <si>
+    <t>attack-pattern--7a0e5d1e-3983-4db9-b8e7-22aa583a2858</t>
+  </si>
+  <si>
+    <t>attack-pattern--0bb3bb16-2da8-4789-ba21-e514db2101f5</t>
+  </si>
+  <si>
+    <t>attack-pattern--1bd02aba-634a-4588-9786-fc30696e70b5</t>
+  </si>
+  <si>
+    <t>attack-pattern--e84b6176-a783-444d-8a2a-e5f1fd0d764c</t>
+  </si>
+  <si>
+    <t>attack-pattern--35b2816a-2fa1-429f-a041-5f6ffc581e69</t>
+  </si>
+  <si>
+    <t>attack-pattern--7f0aa4ca-fe15-4b83-bab8-922d4698446f</t>
+  </si>
+  <si>
+    <t>attack-pattern--fb59974b-817d-48bb-81f3-4dd9873bd6b4</t>
+  </si>
+  <si>
+    <t>attack-pattern--f9a845df-3e98-4ac7-9ef9-489dfd667aaf</t>
+  </si>
+  <si>
+    <t>attack-pattern--5a006ee6-b55d-4072-b4d2-92a59016f7f6</t>
+  </si>
+  <si>
+    <t>attack-pattern--1179ba8e-8da5-4aa9-8165-120b23ad1fec</t>
+  </si>
+  <si>
+    <t>attack-pattern--9bb95249-6747-41c3-b711-7f5094e85ae7</t>
+  </si>
+  <si>
+    <t>attack-pattern--af62ced2-68d3-492b-98ce-c999c9827400</t>
+  </si>
+  <si>
+    <t>attack-pattern--4183c4e4-db10-432a-bca9-e1b23e3da61f</t>
+  </si>
+  <si>
+    <t>attack-pattern--44563dbb-1be9-46bc-9a66-af5e19b2106d</t>
+  </si>
+  <si>
+    <t>attack-pattern--107c88d2-2c1e-4f39-b5cc-0d909875c061</t>
+  </si>
+  <si>
+    <t>attack-pattern--8532007d-d463-45cc-958a-fe79d1d83608</t>
+  </si>
+  <si>
+    <t>attack-pattern--5b69d1b6-c6dd-4f6d-8909-ee09462cfad8</t>
+  </si>
+  <si>
+    <t>attack-pattern--24b1fa21-90c3-464f-833f-ac108ecc78d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1db6118-0a31-4730-bde2-8fac46c3e137</t>
+  </si>
+  <si>
+    <t>attack-pattern--c393033f-0d84-45b8-bf52-eb210a212208</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e90492-d231-402a-a465-3f5bc479a1e8</t>
+  </si>
+  <si>
+    <t>attack-pattern--d735ca35-037b-4a3a-b196-89833a86103d</t>
+  </si>
+  <si>
+    <t>attack-pattern--7aee84dc-e060-4d3c-ac28-c6defb82a28b</t>
+  </si>
+  <si>
+    <t>attack-pattern--52bef255-ae4c-4e58-b916-db73b8409467</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed62c8ca-77f7-4c09-acb3-2258db6f7d60</t>
+  </si>
+  <si>
+    <t>attack-pattern--22b543df-dfb1-49fc-8d95-c374e058f540</t>
+  </si>
+  <si>
+    <t>attack-pattern--04898e9d-6eef-499f-8d56-bfd1c2af2c6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--97651d27-015f-4e58-b447-bc29c4569898</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f064151-346c-4c9a-9376-b7b632f1e384</t>
+  </si>
+  <si>
+    <t>attack-pattern--f4d219bd-ff07-431e-9ace-0021dc1336d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--1bc0c743-4448-42f5-97f0-d4e107fab546</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef81761d-ca4c-4cf6-be70-349d2288f494</t>
+  </si>
+  <si>
+    <t>attack-pattern--336d16d8-fe0b-4c75-a34c-54fab8d76a2f</t>
+  </si>
+  <si>
+    <t>attack-pattern--944cf29d-d469-4233-aac4-379f43393faf</t>
+  </si>
+  <si>
+    <t>attack-pattern--137882c2-807a-40d3-b4b1-f6a204a18347</t>
+  </si>
+  <si>
+    <t>attack-pattern--b661aaca-a287-468b-88df-878b68349563</t>
+  </si>
+  <si>
+    <t>attack-pattern--80dfaadf-e59e-45e8-8ea6-1d438ac88184</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab499b3c-40d3-4e5a-8de3-3ff1466362c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f49883b-8f7f-45db-b962-d3017cc85771</t>
+  </si>
+  <si>
+    <t>attack-pattern--ccac8b90-d32e-4daa-b524-8c0134ff7d4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--3f65d725-4c10-41c5-b822-f324cb8e9b5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--1346bbf5-d81b-4d05-b377-bdc659611dce</t>
+  </si>
+  <si>
+    <t>attack-pattern--de25c05a-bf38-438b-927f-bc4dcb46653c</t>
+  </si>
+  <si>
+    <t>attack-pattern--6acaa0d2-b311-43d0-bf45-42f11350a821</t>
+  </si>
+  <si>
+    <t>attack-pattern--023c87b7-782d-4f6e-82f6-84485c8409be</t>
+  </si>
+  <si>
+    <t>attack-pattern--257839c4-791b-4968-b2dc-23e6c882655c</t>
+  </si>
+  <si>
+    <t>attack-pattern--68303848-d811-444e-9c48-90bacb503e96</t>
+  </si>
+  <si>
+    <t>attack-pattern--3045e408-7cdd-45fa-b0e0-ac789bda69d1</t>
+  </si>
+  <si>
+    <t>attack-pattern--e9a7afa4-472f-45a0-9982-44652e7f5062</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef572bf1-2a59-4459-856a-70d90d0d0395</t>
+  </si>
+  <si>
+    <t>attack-pattern--c56b38dd-5f25-422e-9698-d5bba69b683f</t>
+  </si>
+  <si>
+    <t>attack-pattern--4f945941-64c6-443a-988b-7dd2bdbb0748</t>
+  </si>
+  <si>
+    <t>attack-pattern--261c27b8-7ad3-447b-bbc3-160ef90be57d</t>
+  </si>
+  <si>
+    <t>attack-pattern--a16626c3-d9fc-4781-a7d4-10c13bd9336f</t>
+  </si>
+  <si>
+    <t>attack-pattern--b8de1150-a710-4046-ace7-5c0877fa0bff</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b194f79-84f8-4b29-9ce9-cfa85642e44f</t>
+  </si>
+  <si>
+    <t>attack-pattern--7319913c-e3a4-4b03-a99c-3680896d81b7</t>
+  </si>
+  <si>
+    <t>attack-pattern--18bfffe3-6edf-438e-a946-488affc66f7a</t>
+  </si>
+  <si>
+    <t>attack-pattern--1fb1fa4c-bf4e-4fa8-a32f-a4896e48fef5</t>
+  </si>
+  <si>
+    <t>attack-pattern--aa1b9222-fcb9-447f-b977-fdfb30faa681</t>
+  </si>
+  <si>
+    <t>attack-pattern--3a5d809f-d5a5-49b8-8a87-adb7babcf139</t>
+  </si>
+  <si>
+    <t>attack-pattern--834b21dc-f1f6-4fc5-b05a-e75753a12b5e</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d525dd4-9996-48c0-8b48-87019adce8e1</t>
+  </si>
+  <si>
+    <t>attack-pattern--1439ce66-b7a2-4db6-a8f7-d2ded55aa3b4</t>
+  </si>
+  <si>
+    <t>attack-pattern--cd9deeb5-27a6-44c7-a11f-f5381bd4054a</t>
+  </si>
+  <si>
+    <t>attack-pattern--993fbcf3-8292-45af-817f-edd7d88c57ea</t>
+  </si>
+  <si>
+    <t>attack-pattern--923f47cf-b68d-460e-9fe0-110a95077f6a</t>
+  </si>
+  <si>
+    <t>attack-pattern--68d98ee4-53c5-4745-9d7f-483114cc6999</t>
+  </si>
+  <si>
+    <t>attack-pattern--2c6e3672-d316-4467-8f4b-c5d2837957f0</t>
+  </si>
+  <si>
+    <t>attack-pattern--c0c319d3-3928-4843-9aeb-c57677814069</t>
+  </si>
+  <si>
+    <t>attack-pattern--29ec00bf-fdfe-4900-bf0b-83e650136a16</t>
+  </si>
+  <si>
+    <t>attack-pattern--030bbee9-626f-4024-aa7f-05ef7fbb844f</t>
+  </si>
+  <si>
+    <t>attack-pattern--088dd75c-3d48-434e-95d2-19d0e3147c5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--c1d667b7-eee5-402c-a154-9dbbb2a23436</t>
   </si>
   <si>
     <t>technique</t>
@@ -3527,481 +3527,481 @@
     <t>Введение обязанности предоставлять полные финансовые отчеты о доходах региона под надзор центра (Citation: Решетилівські статті — Вікіпедія 2026)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>relationship--0fc9df02-2663-4be2-ae57-b47e321d5c5b</t>
-  </si>
-  <si>
-    <t>relationship--e5b4df88-6b23-491f-b483-8551a0ea2bf0</t>
-  </si>
-  <si>
-    <t>relationship--0644e98b-0ba5-405e-890c-fb8c222e1439</t>
-  </si>
-  <si>
-    <t>relationship--8ac25ca3-96cf-4c52-a237-b9062e106f74</t>
-  </si>
-  <si>
-    <t>relationship--3e8a36d8-88aa-468c-9c2c-dc6a2763f906</t>
-  </si>
-  <si>
-    <t>relationship--da148c65-5f4a-4a95-87a3-c6b87f8379ea</t>
-  </si>
-  <si>
-    <t>relationship--f701788a-e221-4dd1-9128-95b9a0d023c8</t>
-  </si>
-  <si>
-    <t>relationship--bf4a83fc-a160-498d-b894-772828c88b1c</t>
-  </si>
-  <si>
-    <t>relationship--57bd8188-1eec-4025-b4f3-e7efaef6549b</t>
-  </si>
-  <si>
-    <t>relationship--a936931c-9625-4d84-9987-ca3f67d5fe58</t>
-  </si>
-  <si>
-    <t>relationship--7e8e6538-c636-4e58-9203-c7b1520d6c27</t>
-  </si>
-  <si>
-    <t>relationship--969684f6-68ed-4fd1-bc86-632f849b1bbd</t>
-  </si>
-  <si>
-    <t>relationship--29b789a0-4a47-4569-b028-52c5f6f00ed7</t>
-  </si>
-  <si>
-    <t>relationship--7bb60df4-1c22-4b9b-b8d2-805d486ae9fa</t>
-  </si>
-  <si>
-    <t>relationship--0e2144a3-1971-40e2-9381-96702aa05be4</t>
-  </si>
-  <si>
-    <t>relationship--0e3a834c-4d76-4a14-8f0b-9b01782f7a2a</t>
-  </si>
-  <si>
-    <t>relationship--465f4881-318d-4da2-b4f0-5d289443f6fa</t>
-  </si>
-  <si>
-    <t>relationship--e1b6ebd1-cbe7-4c53-afd3-37030a935932</t>
-  </si>
-  <si>
-    <t>relationship--6cdb2e97-2d6d-4c25-bc19-5a4b3544d232</t>
-  </si>
-  <si>
-    <t>relationship--a4a38ef0-3b9c-45c0-9306-aff86b2387ae</t>
-  </si>
-  <si>
-    <t>relationship--657542f6-b8c1-4a4e-8893-4fe28a4cdee8</t>
-  </si>
-  <si>
-    <t>relationship--6e36c6de-fbf1-4a16-89da-71294bd0dc93</t>
-  </si>
-  <si>
-    <t>relationship--4370f48f-01cd-46ca-97ea-64afdd48aea4</t>
-  </si>
-  <si>
-    <t>relationship--633ed359-9c30-4a9f-a839-395bb299df98</t>
-  </si>
-  <si>
-    <t>relationship--6202b96d-be8b-4dba-b845-af6c1b249723</t>
-  </si>
-  <si>
-    <t>relationship--2b2a351f-b83e-479f-94f1-253242777b55</t>
-  </si>
-  <si>
-    <t>relationship--95c2a5c2-fd4e-4783-8d91-8da9d5d3fbe2</t>
-  </si>
-  <si>
-    <t>relationship--afcffc6b-70fb-4c03-81ca-fef5944088a2</t>
-  </si>
-  <si>
-    <t>relationship--9504d767-5432-4d80-8013-53c83f7c22f1</t>
-  </si>
-  <si>
-    <t>relationship--611edf19-465c-4f5d-85bb-aeefd6e995e2</t>
-  </si>
-  <si>
-    <t>relationship--dff55fe5-c06c-40d4-a686-5a431b3e98d8</t>
-  </si>
-  <si>
-    <t>relationship--d68069d1-821b-4e7a-ad14-ed1c1939ed38</t>
-  </si>
-  <si>
-    <t>relationship--83a81dbd-94b4-4eab-bcb0-44e580bc0fbd</t>
-  </si>
-  <si>
-    <t>relationship--e6ca9bad-b837-485a-8561-fe0c0f67a174</t>
-  </si>
-  <si>
-    <t>relationship--5bd244d1-5516-474b-b6c6-8f6e1751959e</t>
-  </si>
-  <si>
-    <t>relationship--f05c64f4-6a88-49ed-b077-8de036f40556</t>
-  </si>
-  <si>
-    <t>relationship--e0673107-5991-4109-8db8-520134cc2146</t>
-  </si>
-  <si>
-    <t>relationship--97d08a69-727a-4f0e-83b1-063f58e68ba4</t>
-  </si>
-  <si>
-    <t>relationship--6e962e55-cd15-45d1-9203-8e33bd78ab60</t>
-  </si>
-  <si>
-    <t>relationship--405625f8-e751-4bd7-85fa-258ad6f2b68a</t>
-  </si>
-  <si>
-    <t>relationship--9ed83b23-a904-429c-92a6-ce90942689de</t>
-  </si>
-  <si>
-    <t>relationship--bae03c3e-e80f-45db-87ed-892807e2178e</t>
-  </si>
-  <si>
-    <t>relationship--080ed8e8-2c28-4e8b-b6a7-45145ea0128a</t>
-  </si>
-  <si>
-    <t>relationship--8bcd799f-e5b8-4633-b7bd-b2e5f721fea6</t>
-  </si>
-  <si>
-    <t>relationship--8483e736-649f-492e-a9f5-7f4222459993</t>
-  </si>
-  <si>
-    <t>relationship--0bf70881-3dcb-4784-be1a-6291c9c92fc1</t>
-  </si>
-  <si>
-    <t>relationship--53b4c112-a429-43b5-a40a-134a823673af</t>
-  </si>
-  <si>
-    <t>relationship--29686751-4d79-46cf-8a7b-e9837d808aae</t>
-  </si>
-  <si>
-    <t>relationship--aadc9e12-57f1-4c6e-b5c4-a3ef30807211</t>
-  </si>
-  <si>
-    <t>relationship--07d2ef94-6812-42bb-ab5a-43d6355050ca</t>
-  </si>
-  <si>
-    <t>relationship--70e8cecb-6d07-45c3-9b13-019a92a70701</t>
-  </si>
-  <si>
-    <t>relationship--f8216de2-1ed0-4fbe-ad57-d72c52ecccdc</t>
-  </si>
-  <si>
-    <t>relationship--be802805-0e80-4510-88e2-36bd8e2bef66</t>
-  </si>
-  <si>
-    <t>relationship--584c2186-1549-43f8-bf0c-431e2b6b5010</t>
-  </si>
-  <si>
-    <t>relationship--90e4c5e3-7c6d-4e55-8725-d48eca01a678</t>
-  </si>
-  <si>
-    <t>relationship--e9a6f035-155a-4704-9b4f-14b4b61dd8f8</t>
-  </si>
-  <si>
-    <t>relationship--3db8866a-062d-4995-a079-92aa94987cd6</t>
-  </si>
-  <si>
-    <t>relationship--78de6c1b-d105-463b-bd2e-cc387e513a04</t>
-  </si>
-  <si>
-    <t>relationship--85f50e8e-4090-4472-a182-467c3f609cb2</t>
-  </si>
-  <si>
-    <t>relationship--8e9eda91-5e66-416f-bb44-b303c726c86a</t>
-  </si>
-  <si>
-    <t>relationship--8d0c0c6c-a6b7-4773-a0ac-0c6dad8866a1</t>
-  </si>
-  <si>
-    <t>relationship--e72dfa93-e5ae-4efe-a8ff-f7bdacfae145</t>
-  </si>
-  <si>
-    <t>relationship--d5616a46-fabb-4875-861f-d986a816162a</t>
-  </si>
-  <si>
-    <t>relationship--417e33c5-7b63-440a-9e43-94fae2304c40</t>
-  </si>
-  <si>
-    <t>relationship--2b27b61a-ed32-4cb0-b945-db8901d861b9</t>
-  </si>
-  <si>
-    <t>relationship--03bff8b0-2774-4899-a2ae-991c5caccc2f</t>
-  </si>
-  <si>
-    <t>relationship--7032ef5f-c42b-4239-91fc-996ab9c33b83</t>
-  </si>
-  <si>
-    <t>relationship--ced5e698-bb1b-4f5b-a57f-e80fdcb1def1</t>
-  </si>
-  <si>
-    <t>relationship--12b4d92f-9c0a-4b57-b5da-5644f0640104</t>
-  </si>
-  <si>
-    <t>relationship--e33d4ef5-b340-497d-9db7-f723f793d14b</t>
-  </si>
-  <si>
-    <t>relationship--6a71645c-e668-4c35-af1a-068c183f8c81</t>
-  </si>
-  <si>
-    <t>relationship--8dc5252a-2a4a-40b6-9579-2ac103aa6e5e</t>
-  </si>
-  <si>
-    <t>relationship--066972ee-074b-4c3c-992c-eb0950164778</t>
-  </si>
-  <si>
-    <t>relationship--da41731f-9712-4e17-8d67-493d30b959e3</t>
-  </si>
-  <si>
-    <t>relationship--a64f0e5e-e1eb-49c7-8f9f-809fd64cd5ad</t>
-  </si>
-  <si>
-    <t>relationship--19d74513-f877-42bb-a3dd-9cb8e098f7c8</t>
-  </si>
-  <si>
-    <t>relationship--b9cb0d82-e343-4008-89d5-12ac6796966b</t>
-  </si>
-  <si>
-    <t>relationship--8301a987-0a3b-48c4-8ebe-9775eac9700e</t>
-  </si>
-  <si>
-    <t>relationship--6082181d-42e4-4a00-88b9-fb7f05f08650</t>
-  </si>
-  <si>
-    <t>relationship--3ff626c6-8623-4924-9ad8-0cc56833003c</t>
-  </si>
-  <si>
-    <t>relationship--9a131f74-b423-4e60-9bc4-6cce5360b8bc</t>
-  </si>
-  <si>
-    <t>relationship--0e02357c-c07e-47b2-805b-c05265688163</t>
-  </si>
-  <si>
-    <t>relationship--3a8c4403-d83b-4eae-9655-968bea432709</t>
-  </si>
-  <si>
-    <t>relationship--750fef77-11a1-474a-a028-65e894b53482</t>
-  </si>
-  <si>
-    <t>relationship--fff3aef4-c045-41d2-9c1a-1c4960a5b465</t>
-  </si>
-  <si>
-    <t>relationship--7148e04c-a774-454c-8c96-5142c0ee1331</t>
-  </si>
-  <si>
-    <t>relationship--94123636-25d9-4c52-bc8e-fa2b6af78f7d</t>
-  </si>
-  <si>
-    <t>relationship--c96aa7f2-2ff5-45e4-8ce0-993e46b0f7ce</t>
-  </si>
-  <si>
-    <t>relationship--c88dccf7-073f-4b73-95b8-f6c141c2ea88</t>
-  </si>
-  <si>
-    <t>relationship--aa18ba5c-4772-4de6-8df6-97103c857633</t>
-  </si>
-  <si>
-    <t>relationship--ae0d4f48-7ca8-4e86-beb4-2fc5e34613d7</t>
-  </si>
-  <si>
-    <t>relationship--3d65f0d0-9ca6-4c8a-a0f2-a2f32cf3117d</t>
-  </si>
-  <si>
-    <t>relationship--7045ddce-4798-4f62-bbb9-657acf7e895e</t>
-  </si>
-  <si>
-    <t>relationship--3096006d-9acf-4b9c-a667-01cdc7d7c99f</t>
-  </si>
-  <si>
-    <t>relationship--168aae8a-1325-4d12-8e76-912245ef0e79</t>
-  </si>
-  <si>
-    <t>relationship--f0fb29ec-513b-4c24-922f-81bfb4d4e2a2</t>
-  </si>
-  <si>
-    <t>relationship--e2b323f7-fe5f-4725-ba72-f0dd7ba91c5a</t>
-  </si>
-  <si>
-    <t>relationship--2a6b3098-d2b8-4363-8a6b-29f869aaf8c5</t>
-  </si>
-  <si>
-    <t>relationship--9c4bfad0-d523-4ec7-8e70-8cb64f4a9043</t>
-  </si>
-  <si>
-    <t>relationship--59f9d0e9-3202-4c50-8172-f73fe9eb7131</t>
-  </si>
-  <si>
-    <t>relationship--60f81fbf-1bd9-4c2f-b5df-7f6ed6f17c3d</t>
-  </si>
-  <si>
-    <t>relationship--225cefd8-2903-4317-af4f-35fa55e94032</t>
-  </si>
-  <si>
-    <t>relationship--416d1d17-f865-4b1a-8f81-b82260aced75</t>
-  </si>
-  <si>
-    <t>relationship--b67bd861-444f-4f04-a6e1-9b0d1c3c67c4</t>
-  </si>
-  <si>
-    <t>relationship--2a77ae94-5326-4980-ae79-c7e881ae7de5</t>
-  </si>
-  <si>
-    <t>relationship--649413cf-6855-42d3-b7d2-f0a5abf6676f</t>
-  </si>
-  <si>
-    <t>relationship--18106a1c-5855-4d6b-92b8-56905db21203</t>
-  </si>
-  <si>
-    <t>relationship--d2ca5391-f68f-441c-ad33-1dc1f2402e3c</t>
-  </si>
-  <si>
-    <t>relationship--4d34b1a4-fc22-4817-b194-5b0b3dfb0814</t>
-  </si>
-  <si>
-    <t>relationship--9ee851e9-b992-4e8f-9c2b-432ec620e219</t>
-  </si>
-  <si>
-    <t>relationship--b1baa091-4cd0-4638-a837-6a07ad23bcb8</t>
-  </si>
-  <si>
-    <t>relationship--00dfae9d-7870-47fd-98b0-206114ba58d9</t>
-  </si>
-  <si>
-    <t>relationship--f939a8be-2236-4d77-86b5-287b54c7c32a</t>
-  </si>
-  <si>
-    <t>relationship--d676c970-f90d-4397-bf58-c5a03f8bfc59</t>
-  </si>
-  <si>
-    <t>relationship--efc80a10-3b08-4ba7-b038-178817d44f66</t>
-  </si>
-  <si>
-    <t>relationship--6c9b61bd-0b24-4114-84f1-86c2046aa9c6</t>
-  </si>
-  <si>
-    <t>relationship--86626dfd-325d-4c7d-9bf4-e8257116723e</t>
-  </si>
-  <si>
-    <t>relationship--0bd740fe-817a-43ab-80c1-dd570939c124</t>
-  </si>
-  <si>
-    <t>relationship--9107543d-cc94-4c75-8b4d-8e3f49490734</t>
-  </si>
-  <si>
-    <t>relationship--41f7475a-c31b-496c-8375-52b0d70258a0</t>
-  </si>
-  <si>
-    <t>relationship--c5d53690-5de6-4764-93e2-09e1b9744076</t>
-  </si>
-  <si>
-    <t>relationship--8ce2c861-8d58-4ffd-8c50-78c112daa96d</t>
-  </si>
-  <si>
-    <t>relationship--173660ca-1b8b-40c5-89a0-02813361a6fc</t>
-  </si>
-  <si>
-    <t>relationship--d959e6e3-e593-41c2-8f4c-4f95d0a732ce</t>
-  </si>
-  <si>
-    <t>relationship--9a518d2e-0857-40f8-a7f3-b2e1cdc14621</t>
-  </si>
-  <si>
-    <t>relationship--88165274-fe0a-467c-add8-8b7f67b17b80</t>
-  </si>
-  <si>
-    <t>relationship--ba38f840-9a97-4864-b29b-79af50e2d0f0</t>
-  </si>
-  <si>
-    <t>relationship--deca8f6f-dedd-43ec-8a6d-734952d9bd73</t>
-  </si>
-  <si>
-    <t>relationship--bdb96b60-ec68-4ee8-8d96-8d2a78fb7dc0</t>
-  </si>
-  <si>
-    <t>relationship--390041a9-89ff-43f9-aff4-d45d6a485a55</t>
-  </si>
-  <si>
-    <t>relationship--c9af633c-6d9d-4870-b227-32d5ec24cd56</t>
-  </si>
-  <si>
-    <t>relationship--75a13b48-8e93-4fb6-9773-f77a50243288</t>
-  </si>
-  <si>
-    <t>relationship--15f5af70-262e-41e0-8aba-fa599d341328</t>
-  </si>
-  <si>
-    <t>relationship--711996e9-34ae-4810-8d7a-21a44ffa7fe9</t>
-  </si>
-  <si>
-    <t>relationship--9a3c95c6-23e4-4c0f-8844-52d958f1dbe8</t>
-  </si>
-  <si>
-    <t>relationship--d5500959-3922-4bb2-9c2e-72df957cc5e1</t>
-  </si>
-  <si>
-    <t>relationship--7f6a069d-a281-4ca3-9c5d-7f40d7d57610</t>
-  </si>
-  <si>
-    <t>relationship--a10ca265-b361-4b4c-9de0-d1c1309a80a5</t>
-  </si>
-  <si>
-    <t>relationship--73a49bef-fe4c-459e-8fd8-836fcf3e0641</t>
-  </si>
-  <si>
-    <t>relationship--0cd4c6e2-7736-4613-b2a5-6c711975a0ae</t>
-  </si>
-  <si>
-    <t>relationship--bf56a23c-8789-41b1-af63-46b900047f5a</t>
-  </si>
-  <si>
-    <t>relationship--f3e20272-250d-4f8c-b9e6-f2d9ab1ee9d0</t>
-  </si>
-  <si>
-    <t>relationship--1afbd67d-8510-433b-a617-2720cfd43de3</t>
-  </si>
-  <si>
-    <t>relationship--950ce7a6-f20d-4429-8270-cbe702f9b8a4</t>
-  </si>
-  <si>
-    <t>relationship--d70c1641-5355-48a5-8a08-f6c589f1b7bf</t>
-  </si>
-  <si>
-    <t>relationship--f2315b08-5655-4313-8ae3-121331d6895b</t>
-  </si>
-  <si>
-    <t>relationship--8eae276b-a879-4b89-b777-a1cbc639ca44</t>
-  </si>
-  <si>
-    <t>relationship--c06b6614-aedc-4ee6-8a39-9953db7fe4c7</t>
-  </si>
-  <si>
-    <t>relationship--0a7daa8c-a8f9-4b8e-be70-9bea46ea2bd9</t>
-  </si>
-  <si>
-    <t>relationship--104478ca-397a-4f1a-88a9-cc288cc01269</t>
-  </si>
-  <si>
-    <t>relationship--b82e7c93-0bc3-4694-b8d3-f1865eacc556</t>
-  </si>
-  <si>
-    <t>relationship--5e334d35-427c-4965-8fa3-d390a2aec408</t>
-  </si>
-  <si>
-    <t>relationship--9bc4b721-8658-49f6-b490-726dbec2b451</t>
-  </si>
-  <si>
-    <t>relationship--4da5a977-b962-49e5-ab52-2e0e5f7e890a</t>
-  </si>
-  <si>
-    <t>relationship--b8c316e5-c364-4d3c-8de5-7aa98d597d2c</t>
-  </si>
-  <si>
-    <t>relationship--2e1b44f7-f38a-4868-910a-85e88baa212b</t>
-  </si>
-  <si>
-    <t>relationship--b535b75e-dae6-4781-9a69-21c2e2065f3b</t>
-  </si>
-  <si>
-    <t>relationship--7da26f74-c81f-49d8-b7e7-28e0a9ad2d2b</t>
-  </si>
-  <si>
-    <t>relationship--2cc2e74c-b0bf-4057-b099-ac8686c66a45</t>
+    <t>relationship--f57639bf-201d-4950-a5cd-fe88131263d2</t>
+  </si>
+  <si>
+    <t>relationship--1aef3932-9976-42c8-980e-1d9efff3d421</t>
+  </si>
+  <si>
+    <t>relationship--1e4b2641-38f4-4e96-abdb-d938ae6c6238</t>
+  </si>
+  <si>
+    <t>relationship--e287ae25-2e74-46aa-9b98-26c6a19bf65c</t>
+  </si>
+  <si>
+    <t>relationship--d2a67c7f-869e-478d-9871-59136624729a</t>
+  </si>
+  <si>
+    <t>relationship--6acb8cbb-4f84-4909-9b4e-2c8202d04abe</t>
+  </si>
+  <si>
+    <t>relationship--66666a90-5cb2-4740-aafe-9a5299fbe3f9</t>
+  </si>
+  <si>
+    <t>relationship--66ca0d56-9c4d-41db-900c-9dfcff7fe057</t>
+  </si>
+  <si>
+    <t>relationship--4bfd2c7b-9c17-466b-9bbc-bdc63032c3e5</t>
+  </si>
+  <si>
+    <t>relationship--d07b4055-b125-4228-992e-6e802c7a93e5</t>
+  </si>
+  <si>
+    <t>relationship--560be8a7-57ae-4dd3-bba0-c198ef86b643</t>
+  </si>
+  <si>
+    <t>relationship--fd809d03-b56d-4cb1-ab27-0df8bdb16010</t>
+  </si>
+  <si>
+    <t>relationship--db6ed9ba-d766-4ba6-ab10-829dba38cc29</t>
+  </si>
+  <si>
+    <t>relationship--9898f608-301d-4ee1-9af7-76120f8f33a1</t>
+  </si>
+  <si>
+    <t>relationship--ba8b2cb4-a978-4bfc-90ff-0f052f754ffa</t>
+  </si>
+  <si>
+    <t>relationship--87a11c30-2455-4c22-b451-f0891145a71e</t>
+  </si>
+  <si>
+    <t>relationship--aded852e-212a-467f-b078-ea92938e146a</t>
+  </si>
+  <si>
+    <t>relationship--3c2dfcb9-c806-406e-b98e-8c858d3c84ce</t>
+  </si>
+  <si>
+    <t>relationship--3ead08d2-96ee-4dba-a512-7c74ce81420b</t>
+  </si>
+  <si>
+    <t>relationship--fbff1298-e133-43b5-8048-44a12db54c6b</t>
+  </si>
+  <si>
+    <t>relationship--95320403-f9e3-4539-9622-7123db51532a</t>
+  </si>
+  <si>
+    <t>relationship--1c07b56c-b0f8-4d44-adf0-61fab799bb51</t>
+  </si>
+  <si>
+    <t>relationship--371bf0de-ef2b-4d23-9f3a-fa4e4bd70675</t>
+  </si>
+  <si>
+    <t>relationship--4e7f0703-4a4a-4100-ace3-c5e0f236041c</t>
+  </si>
+  <si>
+    <t>relationship--832eaa6e-6def-41bc-af18-64e083bb5bb9</t>
+  </si>
+  <si>
+    <t>relationship--227fe652-ed44-4899-a63d-6f4f0340ccc8</t>
+  </si>
+  <si>
+    <t>relationship--4dbc7d46-2c40-4cf8-b932-0ef494b70824</t>
+  </si>
+  <si>
+    <t>relationship--6bf0493a-2765-4878-8bc9-7da8aaa08690</t>
+  </si>
+  <si>
+    <t>relationship--5a545a86-385a-452f-b672-07daffb240a6</t>
+  </si>
+  <si>
+    <t>relationship--58454603-5adb-4d47-8073-b0fd3ff41b48</t>
+  </si>
+  <si>
+    <t>relationship--6114c657-8545-4b80-b759-ec9eb97496b5</t>
+  </si>
+  <si>
+    <t>relationship--cb3c049e-0fc6-407d-bcd1-5c181f383e6a</t>
+  </si>
+  <si>
+    <t>relationship--c92e04c5-1ab3-4d20-8240-2dfcfe12818d</t>
+  </si>
+  <si>
+    <t>relationship--d31acd52-174a-4a02-b0da-3ae9e90e726f</t>
+  </si>
+  <si>
+    <t>relationship--8c2f592b-0f60-438c-ae97-e0a43726e484</t>
+  </si>
+  <si>
+    <t>relationship--bcefa2a4-d79c-476a-9079-c86e034cf032</t>
+  </si>
+  <si>
+    <t>relationship--350248bf-2314-4746-ace1-022505408aa3</t>
+  </si>
+  <si>
+    <t>relationship--89ee6808-4eb6-4311-8f59-81b5849af53d</t>
+  </si>
+  <si>
+    <t>relationship--9d6bd921-7587-4be6-986e-3eba7dec6aeb</t>
+  </si>
+  <si>
+    <t>relationship--2faffb4d-f7bf-46fa-a07e-d77f0ea7a683</t>
+  </si>
+  <si>
+    <t>relationship--ea9a6b8b-2bf5-4ec6-b6ce-bc9d1c084186</t>
+  </si>
+  <si>
+    <t>relationship--4bf236fc-b663-4ee3-b41c-dee2b4de2579</t>
+  </si>
+  <si>
+    <t>relationship--b47641a3-817f-41bc-a3b7-ddf0b8b09215</t>
+  </si>
+  <si>
+    <t>relationship--f45ac9f8-f7e0-4858-bb3a-6765e3d37fc7</t>
+  </si>
+  <si>
+    <t>relationship--888de46e-4ebe-4057-adca-05da7851d732</t>
+  </si>
+  <si>
+    <t>relationship--098053f3-ecc7-4a8e-b48a-076c3a6c4248</t>
+  </si>
+  <si>
+    <t>relationship--11a6a9a8-2bf7-406f-af05-38bf00996763</t>
+  </si>
+  <si>
+    <t>relationship--eb103c6c-e029-410d-b091-baccb8e3baed</t>
+  </si>
+  <si>
+    <t>relationship--1bda8ee5-4aed-411d-92cb-0d686c7bf109</t>
+  </si>
+  <si>
+    <t>relationship--f6c605eb-71f9-4e45-a469-1c13eea0057c</t>
+  </si>
+  <si>
+    <t>relationship--34778cd5-5f2e-4850-8ca5-277697ec6f26</t>
+  </si>
+  <si>
+    <t>relationship--8479afda-003f-45ee-88a5-42cb2601f60d</t>
+  </si>
+  <si>
+    <t>relationship--0b860690-4b4b-4de0-b97f-0f03e5bae7b1</t>
+  </si>
+  <si>
+    <t>relationship--8d99c363-5696-4ec1-93d2-76a1efc2be24</t>
+  </si>
+  <si>
+    <t>relationship--97a46902-0296-4c08-8573-7a1a141108c4</t>
+  </si>
+  <si>
+    <t>relationship--2e336a93-79a2-48d4-9cb2-80cc70b0a788</t>
+  </si>
+  <si>
+    <t>relationship--91608beb-1733-48fb-aaae-5245f2c2ab5f</t>
+  </si>
+  <si>
+    <t>relationship--28c14042-3560-4fa2-ae10-93ff029006c1</t>
+  </si>
+  <si>
+    <t>relationship--6d2bfe6f-2e24-4a26-a4ec-7d97ba3e3ee1</t>
+  </si>
+  <si>
+    <t>relationship--606777db-3c58-4fc6-87fc-84295bbd7c08</t>
+  </si>
+  <si>
+    <t>relationship--71021127-3d72-4d1d-8eda-4cd4758cb2ef</t>
+  </si>
+  <si>
+    <t>relationship--39024a63-5cf2-404a-8955-e00e9fd0cc74</t>
+  </si>
+  <si>
+    <t>relationship--4786afb9-7ece-4b67-9b03-5f06d6a87640</t>
+  </si>
+  <si>
+    <t>relationship--d8704b08-6efe-48d2-9fe1-b11e6e9b239f</t>
+  </si>
+  <si>
+    <t>relationship--a5590456-58a3-4763-8656-c6c698745e04</t>
+  </si>
+  <si>
+    <t>relationship--c276cc79-9a85-4b84-a7f6-cb2d4d8ddce2</t>
+  </si>
+  <si>
+    <t>relationship--0e91cd31-618f-4d5f-9783-6456a1bf170b</t>
+  </si>
+  <si>
+    <t>relationship--d10aca3c-9c26-482f-abc8-ab07765940b3</t>
+  </si>
+  <si>
+    <t>relationship--f6182e0f-3db8-4362-85ee-6f5cc00b0073</t>
+  </si>
+  <si>
+    <t>relationship--a749cb84-86d9-404c-903a-78bf514e0165</t>
+  </si>
+  <si>
+    <t>relationship--621f3b93-d229-4d3d-9e6c-98224c3a8ca4</t>
+  </si>
+  <si>
+    <t>relationship--6a2b063b-ac17-40ef-a680-2be97a56779b</t>
+  </si>
+  <si>
+    <t>relationship--c12e5a55-f163-4252-8415-90c4173c4357</t>
+  </si>
+  <si>
+    <t>relationship--f1caf9f5-5188-4fe6-973b-f611211d04c9</t>
+  </si>
+  <si>
+    <t>relationship--11031d92-5798-45c9-8451-acf7e7338360</t>
+  </si>
+  <si>
+    <t>relationship--1aa34e58-85eb-48cd-8374-01cc00b65152</t>
+  </si>
+  <si>
+    <t>relationship--9a451426-b708-4bd0-b4f7-c66ef3274f01</t>
+  </si>
+  <si>
+    <t>relationship--4fa88cf6-6bc2-4738-a61a-02f7e74410d5</t>
+  </si>
+  <si>
+    <t>relationship--476ee537-2472-458d-881c-64b3f4f9255d</t>
+  </si>
+  <si>
+    <t>relationship--070a0e74-189d-4a2b-a541-7deb1b750704</t>
+  </si>
+  <si>
+    <t>relationship--6ec59964-2d4f-47a8-a276-945647c64424</t>
+  </si>
+  <si>
+    <t>relationship--b817bccc-ef96-4808-b3e9-fca648d47d91</t>
+  </si>
+  <si>
+    <t>relationship--5afb96a6-107e-4f01-9ea4-0714279d56ea</t>
+  </si>
+  <si>
+    <t>relationship--af335d81-3aa2-42f2-8fd6-7f1a104bf891</t>
+  </si>
+  <si>
+    <t>relationship--cda4575c-0391-4246-8c83-dcade4e0c409</t>
+  </si>
+  <si>
+    <t>relationship--a30d0a72-891d-452e-87b8-656803733bf9</t>
+  </si>
+  <si>
+    <t>relationship--f3c93591-35f1-42e0-b9a6-9069194543df</t>
+  </si>
+  <si>
+    <t>relationship--05fbff25-57d7-40fd-9873-2d11967342f9</t>
+  </si>
+  <si>
+    <t>relationship--4dc049b7-3fff-462d-bfa0-9d54c502b9c7</t>
+  </si>
+  <si>
+    <t>relationship--bef86b86-c298-4799-b9fe-ddef9bd0ac3f</t>
+  </si>
+  <si>
+    <t>relationship--2dccb134-959a-441e-9567-ca71764282da</t>
+  </si>
+  <si>
+    <t>relationship--fc6886a0-507b-4f42-9116-9babce24c66c</t>
+  </si>
+  <si>
+    <t>relationship--cb4841e5-fcbf-4238-97ab-ac1491674c04</t>
+  </si>
+  <si>
+    <t>relationship--fa1031d5-eb45-4a63-939d-c75bbb0c0e41</t>
+  </si>
+  <si>
+    <t>relationship--4b7736ca-d14a-4f63-b42d-38ac979d394f</t>
+  </si>
+  <si>
+    <t>relationship--0cc787a2-e033-46f6-b624-51f5e2f0490b</t>
+  </si>
+  <si>
+    <t>relationship--6f5fe5a3-3a8e-47e0-99b6-a8d515a90518</t>
+  </si>
+  <si>
+    <t>relationship--55fb6563-517e-40fa-9886-67d2f81c628c</t>
+  </si>
+  <si>
+    <t>relationship--474ecfda-ac24-4ecc-8354-046d96c042d0</t>
+  </si>
+  <si>
+    <t>relationship--edef7abf-cd62-4d73-ac53-91defb58eab5</t>
+  </si>
+  <si>
+    <t>relationship--93de474b-1c3b-4541-9f3e-b92dce277007</t>
+  </si>
+  <si>
+    <t>relationship--79a4fe06-b6e4-46f4-a39a-0e9f0eca392d</t>
+  </si>
+  <si>
+    <t>relationship--f3ed7ecf-0230-44e4-85bd-3034a52c0ff1</t>
+  </si>
+  <si>
+    <t>relationship--644c5915-567b-49d8-9972-fe404438e5fb</t>
+  </si>
+  <si>
+    <t>relationship--3f899c83-638c-4849-932d-b26081165ff5</t>
+  </si>
+  <si>
+    <t>relationship--3bb0fad7-3142-46fc-b8c7-2ec840c329f9</t>
+  </si>
+  <si>
+    <t>relationship--871b5ea1-0a83-41a1-8063-9fa059ad485b</t>
+  </si>
+  <si>
+    <t>relationship--78583edd-dabe-4257-afa5-6277798a3cd3</t>
+  </si>
+  <si>
+    <t>relationship--9be2642e-ce3d-4789-9abd-eb74d7bd03f7</t>
+  </si>
+  <si>
+    <t>relationship--94712f84-0253-436e-b21d-289210e1defb</t>
+  </si>
+  <si>
+    <t>relationship--c73dedd6-8bae-492c-a165-31fb9afd51d8</t>
+  </si>
+  <si>
+    <t>relationship--f2b648a4-0b24-46eb-84eb-25e7d0ee66f0</t>
+  </si>
+  <si>
+    <t>relationship--dd1bdb48-a2e6-4fb8-8df1-1681eec3f2a8</t>
+  </si>
+  <si>
+    <t>relationship--e56f09db-7b44-4ba2-89a6-5cccf25898cd</t>
+  </si>
+  <si>
+    <t>relationship--7f39f7d4-cb35-4494-8690-597ca5e703e3</t>
+  </si>
+  <si>
+    <t>relationship--48560cde-91cf-43a4-bea6-9eb20f8414e1</t>
+  </si>
+  <si>
+    <t>relationship--e0d04d2e-7d69-4faa-b211-a0e0c94f2162</t>
+  </si>
+  <si>
+    <t>relationship--7db6debd-6a95-4272-8894-61c4b24f6059</t>
+  </si>
+  <si>
+    <t>relationship--a1925a59-fd14-4698-9847-6bf720ac2140</t>
+  </si>
+  <si>
+    <t>relationship--ce446af8-353b-40f8-b5af-63f9c61bbe60</t>
+  </si>
+  <si>
+    <t>relationship--6643128f-179c-4803-8c05-acd5ce1d7113</t>
+  </si>
+  <si>
+    <t>relationship--29b6a613-4df6-479a-ac3f-0c4d90d4231b</t>
+  </si>
+  <si>
+    <t>relationship--a6a374a1-49e1-4fa7-b837-9d2c855646d6</t>
+  </si>
+  <si>
+    <t>relationship--6a04fb16-d247-4703-b70b-933427dc6b47</t>
+  </si>
+  <si>
+    <t>relationship--e10761b8-38e0-40c2-b491-48a76b7646f1</t>
+  </si>
+  <si>
+    <t>relationship--b53f022a-ff91-4a2f-87c0-1a0f50a03000</t>
+  </si>
+  <si>
+    <t>relationship--4d654486-4763-4c37-936f-52e5f24ff8b6</t>
+  </si>
+  <si>
+    <t>relationship--cf099842-4240-4d4e-a249-ba214c3823b9</t>
+  </si>
+  <si>
+    <t>relationship--7be0184f-af80-4e3e-aec0-8bb363d21a54</t>
+  </si>
+  <si>
+    <t>relationship--876b6e5e-60fe-4d5c-bae7-31eff45f261c</t>
+  </si>
+  <si>
+    <t>relationship--1717dd61-13b5-4346-839d-d6bdd20f4e29</t>
+  </si>
+  <si>
+    <t>relationship--6d6d6c18-9ff1-4a46-8662-d9beaaca9d63</t>
+  </si>
+  <si>
+    <t>relationship--ea862a9a-c106-424d-a9a7-ef7629cc9199</t>
+  </si>
+  <si>
+    <t>relationship--f29daea4-3b0d-48fc-86a6-8c53545c246a</t>
+  </si>
+  <si>
+    <t>relationship--035b8dc2-d73b-4409-bfa1-cf3d701630be</t>
+  </si>
+  <si>
+    <t>relationship--459b3155-fbc5-4213-90bc-35d637128985</t>
+  </si>
+  <si>
+    <t>relationship--904dead1-b87a-49a5-be62-70b0b0fec3fc</t>
+  </si>
+  <si>
+    <t>relationship--2328cd3f-30f3-43db-a812-fd5a9013a5f5</t>
+  </si>
+  <si>
+    <t>relationship--76cffb3c-73f3-4a6b-b472-dcd422cf8591</t>
+  </si>
+  <si>
+    <t>relationship--08955afe-f5b2-415b-b89d-cfedbc995ed3</t>
+  </si>
+  <si>
+    <t>relationship--9ea0825a-9469-43a8-b230-20f6b8b06d4a</t>
+  </si>
+  <si>
+    <t>relationship--4b496da7-3950-4445-9e90-1528dedef982</t>
+  </si>
+  <si>
+    <t>relationship--fcc56dd6-5d05-4ee0-80d3-6ea7c0bf08f9</t>
+  </si>
+  <si>
+    <t>relationship--06b14ac1-7b3b-4dc1-b994-4f9f9b34ecd9</t>
+  </si>
+  <si>
+    <t>relationship--9668dac7-82df-4bc6-8926-5447ff4e8d4e</t>
+  </si>
+  <si>
+    <t>relationship--f027dd94-b25c-4645-ba72-7ebb97256db4</t>
+  </si>
+  <si>
+    <t>relationship--6f13c2bf-ae08-488e-b7e2-d5ed14019131</t>
+  </si>
+  <si>
+    <t>relationship--5dc08eb4-7b37-4029-9a23-cdbc6e8c12d2</t>
+  </si>
+  <si>
+    <t>relationship--f4c4c0f7-c3a0-4706-b1d1-01b1ade0399c</t>
+  </si>
+  <si>
+    <t>relationship--28f1db21-1311-46c1-b61c-18e27b2dd2ad</t>
+  </si>
+  <si>
+    <t>relationship--85879eb1-2ad3-4e34-b4c8-2b92b8c16004</t>
+  </si>
+  <si>
+    <t>relationship--a6a460d5-d66c-4645-9faf-50ff3a1ae761</t>
+  </si>
+  <si>
+    <t>relationship--ea5777fb-7134-40ad-8225-e40b20f6b3fe</t>
+  </si>
+  <si>
+    <t>relationship--e24b8e58-bef9-4025-9699-9f0f21096e9b</t>
+  </si>
+  <si>
+    <t>relationship--aebd94e5-71c8-41d7-9f5c-502f466308fd</t>
+  </si>
+  <si>
+    <t>relationship--9c2d4a8d-05cd-4bf7-ac8d-b035158fcaa8</t>
+  </si>
+  <si>
+    <t>relationship--ad659c12-7af0-4cd5-b6cf-9146f1b135a9</t>
+  </si>
+  <si>
+    <t>relationship--756baf2a-6726-4d50-a686-eef3b149952f</t>
+  </si>
+  <si>
+    <t>relationship--3011cf6e-fbd4-4eec-b6e3-03d0d51d3733</t>
   </si>
   <si>
     <t>reference</t>
@@ -4310,121 +4310,121 @@
     <t>https://attack.mitre.org/campaigns/C0041/</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%2594%25D0%25BE%25D0%25BD%25D0%25B5%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BE%25D0%25B1%25D0%25BB%25D0%25B0%25D1%2581%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D0%B2%D0%B0%D0%BD_%D0%9C%D0%B0%D0%B7%D0%B5%D0%BF%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D1%81%D1%82%D0%BE%D1%80%D1%96%D1%8F_%D0%94%D0%BE%D0%BD%D0%B5%D1%86%D1%8C%D0%BA%D0%BE%D1%97_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%86%D1%81%D1%82%D0%BE%D1%80%D1%96%D1%8F_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%90%D0%BD%D0%B5%D0%BA%D1%81%D1%96%D1%8F_%D0%9A%D0%B8%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%BC%D0%B8%D1%82%D1%80%D0%BE%D0%BF%D0%BE%D0%BB%D1%96%D1%97_%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%B8%D0%BC_%D0%BF%D0%B0%D1%82%D1%80%D1%96%D0%B0%D1%80%D1%85%D0%B0%D1%82%D0%BE%D0%BC</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%91%D0%B0%D1%82%D1%83%D1%80%D0%B8%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D1%82%D1%80%D0%B0%D0%B3%D0%B5%D0%B4%D1%96%D1%8F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%92%D1%81%D0%B5%D1%81%D0%BE%D1%8E%D0%B7%D0%BD%D0%B8%D0%B9_%D1%80%D0%B5%D1%84%D0%B5%D1%80%D0%B5%D0%BD%D0%B4%D1%83%D0%BC_%D0%BF%D1%80%D0%BE_%D0%B7%D0%B1%D0%B5%D1%80%D0%B5%D0%B6%D0%B5%D0%BD%D0%BD%D1%8F_%D0%A1%D0%A0%D0%A1%D0%A0</t>
   </si>
   <si>
     <t>https://www.obozrevatel.com/novosti-obschestvo/dvojnoe-prestuplenie-sssr-kak-sovetyi-skryivali-chernobyilskuyu-katastrofu.htm</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B4%25D0%25B5%25D0%25B7%25D1%2596%25D0%25BD%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2594%25D1%2580%25D1%2583%25D0%25B3%25D0%25B0_%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25B3%25D1%2596%25D1%258F</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25B4%25D1%2583%25D0%25BD%25D0%25B0%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%B4%D0%B5%D0%B7%D1%96%D0%BD%D1%84%D0%BE%D1%80%D0%BC%D0%B0%D1%86%D1%96%D1%8F_%D0%BF%D1%96%D0%B4_%D1%87%D0%B0%D1%81_%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%B2%D1%96%D0%B9%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%94%D1%80%D1%83%D0%B3%D0%B0_%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%BA%D0%BE%D0%BB%D0%B5%D0%B3%D1%96%D1%8F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%97%D0%B0%D0%B4%D1%83%D0%BD%D0%B0%D0%B9%D1%81%D1%8C%D0%BA%D0%B0_%D0%A1%D1%96%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%97%D0%B0%D0%BF%D0%BE%D1%80%D0%BE%D0%B7%D1%8C%D0%BA%D0%B0_%D0%A1%D1%96%D1%87</t>
   </si>
   <si>
     <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B5%D0%BD%D0%B3%D0%B8%D1%80%D1%81%D0%BA%D0%BE%D0%B5_%D0%B2%D0%BE%D1%81%D1%81%D1%82%D0%B0%D0%BD%D0%B8%D0%B5_%D0%B7%D0%B0%D0%BA%D0%BB%D1%8E%D1%87%D1%91%D0%BD%D0%BD%D1%8B%D1%85</t>
   </si>
   <si>
     <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B8%D0%B5%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%81%D0%B8%D0%BD%D0%BE%D0%BF%D1%81%D0%B8%D1%81</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2580%25D0%25B8%25D0%25BB%25D0%25BE-%25D0%259C%25D0%25B5%25D1%2584%25D0%25BE%25D0%25B4%25D1%2596%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D1%2582%25D0%25BE%25D0%25B2%25D0%25B0%25D1%2580%25D0%25B8%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D0%25BD%25D0%25BE%25D1%2582%25D0%25BE%25D0%25BF%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D1%2580%25D1%258B%25D0%25BC%25D1%2581%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2583%25D0%25B1%25D0%25B5%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25B4%25D0%25BE%25D0%25B3%25D0%25BE%25D0%25B2%25D1%2596%25D1%2580</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2580%25D0%25B8%25D0%25BA%25D0%25B0%25D0%25B7</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259D%25D0%25B0%25D1%2580%25D0%25BE%25D0%25B4%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B4%25D1%2596%25D0%25BB%25D0%25B8_%25D0%25A0%25D0%25B5%25D1%2587%25D1%2596_%25D0%259F%25D0%25BE%25D1%2581%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B8%25D1%2582%25D0%25BE%25D1%2597</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25B5%25D1%2588%25D0%25B5%25D1%2582%25D0%25B8%25D0%25BB%25D1%2596%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25B8%25D0%25B5_%25D1%2583%25D0%25B4%25D0%25B0%25D1%2580%25D1%258B_%25D0%25BF%25D0%25BE_%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D0%25B8%25D0%25BD%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D1%258D%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B3%25D0%25BE%25D1%2581%25D0%25B8%25D1%2581%25D1%2582%25D0%25B5%25D0%25BC%25D0%25B5</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%B8%D1%80%D0%B8%D0%BB%D0%BE-%D0%9C%D0%B5%D1%84%D0%BE%D0%B4%D1%96%D1%97%D0%B2%D1%81%D1%8C%D0%BA%D0%B5_%D1%82%D0%BE%D0%B2%D0%B0%D1%80%D0%B8%D1%81%D1%82%D0%B2%D0%BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9A%D0%BE%D0%BD%D0%BE%D1%82%D0%BE%D0%BF%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D1%80%D1%8B%D0%BC%D1%81%D0%BA%D0%B0%D1%8F_%D0%B2%D0%BE%D0%B9%D0%BD%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%83%D0%B1%D0%B5%D0%BD%D1%81%D1%8C%D0%BA%D0%B8%D0%B9_%D0%B4%D0%BE%D0%B3%D0%BE%D0%B2%D1%96%D1%80</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9B%D1%96%D0%BA%D0%B2%D1%96%D0%B4%D0%B0%D1%86%D1%96%D1%8F_%D0%B0%D0%B2%D1%82%D0%BE%D0%BD%D0%BE%D0%BC%D1%96%D1%97_%D0%93%D0%B5%D1%82%D1%8C%D0%BC%D0%B0%D0%BD%D1%89%D0%B8%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B0%D0%B7%D0%B5%D0%BF%D0%B0%2C_%D0%98%D0%B2%D0%B0%D0%BD_%D0%A1%D1%82%D0%B5%D0%BF%D0%B0%D0%BD%D0%BE%D0%B2%D0%B8%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B5_%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D0%BB-%D0%B3%D1%83%D0%B1%D0%B5%D1%80%D0%BD%D0%B0%D1%82%D0%BE%D1%80%D1%81%D1%82%D0%B2%D0%BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%B0%D0%BB%D0%BE%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%B8%D0%B9_%D0%BF%D1%80%D0%B8%D0%BA%D0%B0%D0%B7</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9D%D0%B0%D1%80%D0%BE%D0%B4%D0%BD%D0%B8%D0%B9_%D1%80%D1%83%D1%85_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%BE%D0%B4%D1%96%D0%BB%D0%B8_%D0%A0%D0%B5%D1%87%D1%96_%D0%9F%D0%BE%D1%81%D0%BF%D0%BE%D0%BB%D0%B8%D1%82%D0%BE%D1%97</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D0%B5%D1%88%D0%B5%D1%82%D0%B8%D0%BB%D1%96%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A0%D0%BE%D1%81%D1%81%D0%B8%D0%B9%D1%81%D0%BA%D0%B8%D0%B5_%D1%83%D0%B4%D0%B0%D1%80%D1%8B_%D0%BF%D0%BE_%D1%83%D0%BA%D1%80%D0%B0%D0%B8%D0%BD%D1%81%D0%BA%D0%BE%D0%B9_%D1%8D%D0%BD%D0%B5%D1%80%D0%B3%D0%BE%D1%81%D0%B8%D1%81%D1%82%D0%B5%D0%BC%D0%B5</t>
   </si>
   <si>
     <t>https://web.archive.org/web/20160304195659/http%3A//www.memo.ru/2010/09/27/rch.pdf</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D0%25B8%25D1%2584%25D1%2596%25D0%25BA%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%81%D0%B8%D1%84%D1%96%D0%BA%D0%B0%D1%86%D1%96%D1%8F_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%97%D0%BD%D0%B0</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2596%25D1%2588%25D0%25B8%25D1%2582%25D0%25B5%25D0%25BB%25D1%258C%25D0%25BD%25D1%2596_%25D0%25BF%25D1%2583%25D0%25BD%25D0%25BA%25D1%2582%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25B5%25D1%2580%25D0%25BF%25D0%25BD%25D0%25B5%25D0%25B2%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2583%25D1%2582%25D1%2587</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BA%25D0%25B0%25D1%2581%25D1%2583%25D0%25B2%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2581%25D1%2582%25D1%2580%25D0%25BE%25D1%258E_%25D0%25B2_%25D0%25A1%25D0%25BB%25D0%25BE%25D0%25B1%25D1%2596%25D0%25B4%25D1%2581%25D1%258C%25D0%25BA%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BC%25D1%2583%25D0%25B3%25D0%25B0_%25D0%25BE%25D1%2581%25D1%2596%25D0%25BB%25D0%25BE%25D1%2581%25D1%2582%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D1%2582%25D0%25BE%25D0%25BB%25D0%25B8%25D0%25BF%25D1%2596%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2580%25D0%25B5%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25B4%25D0%25B0%25D1%2580%25D0%25B8_%25D0%25BF%25D0%25BE_%25D0%25BE%25D0%25B1%2527%25D1%2594%25D0%25BA%25D1%2582%25D0%25B0%25D1%2585_%25D0%25BA%25D1%2580%25D0%25B8%25D1%2582%25D0%25B8%25D1%2587%25D0%25BD%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BD%25D1%2584%25D1%2580%25D0%25B0%25D1%2581%25D1%2582%25D1%2580%25D1%2583%25D0%25BA%25D1%2582%25D1%2583%25D1%2580%25D0%25B8_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D0%25B2_%25D0%259F%25D0%25B5%25D1%2580%25D1%2588%25D1%2596%25D0%25B9_%25D1%2581%25D0%25B2%25D1%2596%25D1%2582%25D0%25BE%25D0%25B2%25D1%2596%25D0%25B9_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D1%2596</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D1%2583_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0%25D1%2585_%25D0%259D%25D0%25B0%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25BE%25D0%25BD%25D0%25B0</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%96%D1%88%D0%B8%D1%82%D0%B5%D0%BB%D1%8C%D0%BD%D1%96_%D0%BF%D1%83%D0%BD%D0%BA%D1%82%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%B5%D1%80%D0%BF%D0%BD%D0%B5%D0%B2%D0%B8%D0%B9_%D0%BF%D1%83%D1%82%D1%87</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%BA%D0%B0%D1%81%D1%83%D0%B2%D0%B0%D0%BD%D0%BD%D1%8F_%D0%BA%D0%BE%D0%B7%D0%B0%D1%86%D1%8C%D0%BA%D0%BE%D0%B3%D0%BE_%D1%83%D1%81%D1%82%D1%80%D0%BE%D1%8E_%D0%B2_%D0%A1%D0%BB%D0%BE%D0%B1%D1%96%D0%B4%D1%81%D1%8C%D0%BA%D1%96%D0%B9_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D0%BC%D1%83%D0%B3%D0%B0_%D0%BE%D1%81%D1%96%D0%BB%D0%BE%D1%81%D1%82%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A1%D1%82%D0%BE%D0%BB%D0%B8%D0%BF%D1%96%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B5%D1%84%D0%BE%D1%80%D0%BC%D0%B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%B4%D0%B0%D1%80%D0%B8_%D0%BF%D0%BE_%D0%BE%D0%B1%27%D1%94%D0%BA%D1%82%D0%B0%D1%85_%D0%BA%D1%80%D0%B8%D1%82%D0%B8%D1%87%D0%BD%D0%BE%D1%97_%D1%96%D0%BD%D1%84%D1%80%D0%B0%D1%81%D1%82%D1%80%D1%83%D0%BA%D1%82%D1%83%D1%80%D0%B8_%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B8_%D0%BF%D1%96%D0%B4_%D1%87%D0%B0%D1%81_%D1%80%D0%BE%D1%81%D1%96%D0%B9%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%BE%D1%97_%D0%B2%D1%96%D0%B9%D0%BD%D0%B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B0_%D0%B2_%D0%9F%D0%B5%D1%80%D1%88%D1%96%D0%B9_%D1%81%D0%B2%D1%96%D1%82%D0%BE%D0%B2%D1%96%D0%B9_%D0%B2%D1%96%D0%B9%D0%BD%D1%96</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%A3%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D0%B0_%D1%83_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0%D1%85_%D0%9D%D0%B0%D0%BF%D0%BE%D0%BB%D0%B5%D0%BE%D0%BD%D0%B0</t>
   </si>
   <si>
     <t>https://beda.media/ru/articles/war-in-chechnya-chronicle-part1-ru</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
+    <t>https://uk.wikipedia.org/wiki/%D0%A7%D0%BE%D1%80%D0%BD%D0%BE%D1%81%D0%BE%D1%82%D0%B5%D0%BD%D1%86%D1%96</t>
   </si>
 </sst>
 </file>
